--- a/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
+++ b/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc.sharepoint.com/sites/CharlascortasSSOsemanalesCuyotenango/Shared Documents/General/04. Registros 2026/09. Nivel De Seguridad/NUEVO NIVEL DE SEGURIDAD - 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{B31B9B4D-0810-47E6-ACB2-FA5D1859CF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF264E71-1441-4FD6-91A2-4A0C24F5D32F}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{B31B9B4D-0810-47E6-ACB2-FA5D1859CF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27FE309F-596F-46A3-BEDE-089DF08A5ABE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="1" r:id="rId1"/>
@@ -1598,6 +1598,21 @@
     <xf numFmtId="10" fontId="36" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
@@ -1616,21 +1631,6 @@
     <xf numFmtId="0" fontId="25" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1639,15 +1639,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1661,6 +1652,15 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3789,7 +3789,7 @@
                   <c:v>0.88027777777777783</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.43205333333333323</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -4524,48 +4524,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="85" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="91"/>
-      <c r="AB1" s="91"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
       <c r="AR1" s="42"/>
-      <c r="AS1" s="92" t="s">
+      <c r="AS1" s="86" t="s">
         <v>221</v>
       </c>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="92"/>
-      <c r="BA1" s="92"/>
+      <c r="AT1" s="86"/>
+      <c r="AU1" s="86"/>
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="86"/>
+      <c r="AY1" s="86"/>
+      <c r="AZ1" s="86"/>
+      <c r="BA1" s="86"/>
       <c r="BB1" s="42"/>
       <c r="BC1" s="42"/>
     </row>
@@ -4573,11 +4573,11 @@
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="87" t="s">
         <v>222</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="F2" s="5" t="s">
         <v>148</v>
       </c>
@@ -4586,20 +4586,20 @@
       </c>
       <c r="AR2" s="42"/>
       <c r="AS2" s="44"/>
-      <c r="AT2" s="94" t="s">
+      <c r="AT2" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="AU2" s="94"/>
-      <c r="AV2" s="94"/>
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="88"/>
       <c r="AW2" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="AX2" s="95" t="s">
+      <c r="AX2" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="AY2" s="95"/>
-      <c r="AZ2" s="95"/>
-      <c r="BA2" s="95"/>
+      <c r="AY2" s="89"/>
+      <c r="AZ2" s="89"/>
+      <c r="BA2" s="89"/>
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
@@ -4639,66 +4639,66 @@
       <c r="A4" s="51"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88" t="s">
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88" t="s">
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88" t="s">
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88" t="s">
+      <c r="P4" s="93"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88" t="s">
+      <c r="S4" s="93"/>
+      <c r="T4" s="93"/>
+      <c r="U4" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="V4" s="88"/>
-      <c r="W4" s="89" t="s">
+      <c r="V4" s="93"/>
+      <c r="W4" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="88" t="s">
+      <c r="X4" s="94"/>
+      <c r="Y4" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
-      <c r="AB4" s="88"/>
-      <c r="AC4" s="88"/>
-      <c r="AD4" s="89" t="s">
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
+      <c r="AB4" s="93"/>
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="90" t="s">
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="95" t="s">
         <v>170</v>
       </c>
-      <c r="AQ4" s="90"/>
+      <c r="AQ4" s="95"/>
       <c r="AR4" s="42"/>
       <c r="AS4" s="52" t="str">
         <f>'Captura Junio'!B6</f>
@@ -7474,16 +7474,16 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="AR19" s="42"/>
-      <c r="AS19" s="85" t="s">
+      <c r="AS19" s="90" t="s">
         <v>223</v>
       </c>
-      <c r="AT19" s="85"/>
-      <c r="AU19" s="85"/>
-      <c r="AV19" s="85"/>
-      <c r="AW19" s="85"/>
-      <c r="AX19" s="85"/>
-      <c r="AY19" s="85"/>
-      <c r="AZ19" s="85"/>
+      <c r="AT19" s="90"/>
+      <c r="AU19" s="90"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="90"/>
+      <c r="AY19" s="90"/>
+      <c r="AZ19" s="90"/>
       <c r="BA19" s="71">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.83357372900851168</v>
@@ -7650,9 +7650,9 @@
       <c r="BB20" s="42"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
       <c r="F22" s="51"/>
@@ -7679,11 +7679,11 @@
       <c r="AV22" s="75"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="73"/>
       <c r="E23" s="73"/>
       <c r="F23" s="73"/>
@@ -7741,11 +7741,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
@@ -7759,6 +7754,11 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="greaterThanOrEqual">
@@ -7840,48 +7840,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="85" t="s">
         <v>224</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="91"/>
-      <c r="AB1" s="91"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
       <c r="AR1" s="42"/>
-      <c r="AS1" s="92" t="s">
+      <c r="AS1" s="86" t="s">
         <v>225</v>
       </c>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="92"/>
-      <c r="BA1" s="92"/>
+      <c r="AT1" s="86"/>
+      <c r="AU1" s="86"/>
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="86"/>
+      <c r="AY1" s="86"/>
+      <c r="AZ1" s="86"/>
+      <c r="BA1" s="86"/>
       <c r="BB1" s="42"/>
       <c r="BC1" s="42"/>
     </row>
@@ -7889,11 +7889,11 @@
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="87" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="F2" s="5" t="s">
         <v>148</v>
       </c>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="AR2" s="42"/>
       <c r="AS2" s="44"/>
-      <c r="AT2" s="94" t="s">
+      <c r="AT2" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="AU2" s="94"/>
-      <c r="AV2" s="94"/>
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="88"/>
       <c r="AW2" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="AX2" s="95" t="s">
+      <c r="AX2" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="AY2" s="95"/>
-      <c r="AZ2" s="95"/>
-      <c r="BA2" s="95"/>
+      <c r="AY2" s="89"/>
+      <c r="AZ2" s="89"/>
+      <c r="BA2" s="89"/>
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
@@ -7955,66 +7955,66 @@
       <c r="A4" s="51"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88" t="s">
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88" t="s">
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88" t="s">
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88" t="s">
+      <c r="P4" s="93"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88" t="s">
+      <c r="S4" s="93"/>
+      <c r="T4" s="93"/>
+      <c r="U4" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="V4" s="88"/>
-      <c r="W4" s="89" t="s">
+      <c r="V4" s="93"/>
+      <c r="W4" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="88" t="s">
+      <c r="X4" s="94"/>
+      <c r="Y4" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
-      <c r="AB4" s="88"/>
-      <c r="AC4" s="88"/>
-      <c r="AD4" s="89" t="s">
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
+      <c r="AB4" s="93"/>
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="90" t="s">
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="95" t="s">
         <v>170</v>
       </c>
-      <c r="AQ4" s="90"/>
+      <c r="AQ4" s="95"/>
       <c r="AR4" s="42"/>
       <c r="AS4" s="52" t="str">
         <f>'Captura Julio'!B6</f>
@@ -10790,16 +10790,16 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="AR19" s="42"/>
-      <c r="AS19" s="85" t="s">
+      <c r="AS19" s="90" t="s">
         <v>227</v>
       </c>
-      <c r="AT19" s="85"/>
-      <c r="AU19" s="85"/>
-      <c r="AV19" s="85"/>
-      <c r="AW19" s="85"/>
-      <c r="AX19" s="85"/>
-      <c r="AY19" s="85"/>
-      <c r="AZ19" s="85"/>
+      <c r="AT19" s="90"/>
+      <c r="AU19" s="90"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="90"/>
+      <c r="AY19" s="90"/>
+      <c r="AZ19" s="90"/>
       <c r="BA19" s="71">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.88027777777777783</v>
@@ -10966,9 +10966,9 @@
       <c r="BB20" s="42"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
       <c r="F22" s="51"/>
@@ -10995,11 +10995,11 @@
       <c r="AV22" s="75"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="73"/>
       <c r="E23" s="73"/>
       <c r="F23" s="73"/>
@@ -11057,11 +11057,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
@@ -11075,6 +11070,11 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="56" priority="5" operator="greaterThanOrEqual">
@@ -11154,48 +11154,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="85" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="91"/>
-      <c r="AB1" s="91"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
       <c r="AR1" s="42"/>
-      <c r="AS1" s="92" t="s">
+      <c r="AS1" s="86" t="s">
         <v>229</v>
       </c>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="92"/>
-      <c r="BA1" s="92"/>
+      <c r="AT1" s="86"/>
+      <c r="AU1" s="86"/>
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="86"/>
+      <c r="AY1" s="86"/>
+      <c r="AZ1" s="86"/>
+      <c r="BA1" s="86"/>
       <c r="BB1" s="42"/>
       <c r="BC1" s="42"/>
     </row>
@@ -11203,11 +11203,11 @@
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="87" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="F2" s="5" t="s">
         <v>148</v>
       </c>
@@ -11216,20 +11216,20 @@
       </c>
       <c r="AR2" s="42"/>
       <c r="AS2" s="44"/>
-      <c r="AT2" s="94" t="s">
+      <c r="AT2" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="AU2" s="94"/>
-      <c r="AV2" s="94"/>
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="88"/>
       <c r="AW2" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="AX2" s="95" t="s">
+      <c r="AX2" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="AY2" s="95"/>
-      <c r="AZ2" s="95"/>
-      <c r="BA2" s="95"/>
+      <c r="AY2" s="89"/>
+      <c r="AZ2" s="89"/>
+      <c r="BA2" s="89"/>
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
@@ -11269,66 +11269,66 @@
       <c r="A4" s="51"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88" t="s">
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88" t="s">
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88" t="s">
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88" t="s">
+      <c r="P4" s="93"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88" t="s">
+      <c r="S4" s="93"/>
+      <c r="T4" s="93"/>
+      <c r="U4" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="V4" s="88"/>
-      <c r="W4" s="89" t="s">
+      <c r="V4" s="93"/>
+      <c r="W4" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="88" t="s">
+      <c r="X4" s="94"/>
+      <c r="Y4" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
-      <c r="AB4" s="88"/>
-      <c r="AC4" s="88"/>
-      <c r="AD4" s="89" t="s">
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
+      <c r="AB4" s="93"/>
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="90" t="s">
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="95" t="s">
         <v>170</v>
       </c>
-      <c r="AQ4" s="90"/>
+      <c r="AQ4" s="95"/>
       <c r="AR4" s="42"/>
       <c r="AS4" s="52" t="str">
         <f>'Captura Agosto'!B6</f>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="AW4" s="53">
         <f>'Captura Agosto'!G6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX4" s="53">
         <f>'Captura Agosto'!X6</f>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="BA4" s="55">
         <f>'Captura Agosto'!AQ6</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BB4" s="42"/>
       <c r="BC4" s="42"/>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="AW5" s="60">
         <f>'Captura Agosto'!G7</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX5" s="60">
         <f>'Captura Agosto'!X7</f>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="BA5" s="62">
         <f>'Captura Agosto'!AQ7</f>
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="BB5" s="42"/>
       <c r="BC5" s="42"/>
@@ -11551,18 +11551,18 @@
         <v>Fredy Fuentes</v>
       </c>
       <c r="D6" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="65">
         <v>0</v>
       </c>
       <c r="F6" s="11">
         <f t="shared" ref="F6:F20" si="0">AVERAGE(D6,E6)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="66">
         <f>F6*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H6" s="67">
         <v>38</v>
@@ -11679,11 +11679,11 @@
       </c>
       <c r="AP6" s="11">
         <f t="shared" ref="AP6:AP20" si="3">G6+K6+N6+Q6+T6+V6+X6</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AQ6" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP6-IF(S6="NO",Parametros!$E$17,0))+AC6)-AN6-IF(AO6="SI",Parametros!$E$33,0))</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AR6" s="42"/>
       <c r="AS6" s="52" t="str">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="AW6" s="53">
         <f>'Captura Agosto'!G8</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX6" s="53">
         <f>'Captura Agosto'!X8</f>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="BA6" s="55">
         <f>'Captura Agosto'!AQ8</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BB6" s="42"/>
       <c r="BC6" s="42"/>
@@ -11737,18 +11737,18 @@
         <v>Carlos Chavez</v>
       </c>
       <c r="D7" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="65">
         <v>0</v>
       </c>
       <c r="F7" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="66">
         <f>F7*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H7" s="67"/>
       <c r="I7" s="67"/>
@@ -11861,11 +11861,11 @@
       </c>
       <c r="AP7" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="AQ7" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP7-IF(S7="NO",Parametros!$E$17,0))+AC7)-AN7-IF(AO7="SI",Parametros!$E$33,0))</f>
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="AR7" s="42"/>
       <c r="AS7" s="59" t="str">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="AT7" s="60">
         <f>'Captura Agosto'!K9+'Captura Agosto'!N9+'Captura Agosto'!Q9</f>
-        <v>0</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="AU7" s="60">
         <f>'Captura Agosto'!T9</f>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="AW7" s="60">
         <f>'Captura Agosto'!G9</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX7" s="60">
         <f>'Captura Agosto'!X9</f>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="BA7" s="62">
         <f>'Captura Agosto'!AQ9</f>
-        <v>0.25</v>
+        <v>0.42520000000000002</v>
       </c>
       <c r="BB7" s="42"/>
       <c r="BC7" s="42"/>
@@ -11919,18 +11919,18 @@
         <v>Alejandro Martinez</v>
       </c>
       <c r="D8" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="65">
         <v>0</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G8" s="66">
         <f>F8*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H8" s="67">
         <v>38</v>
@@ -12047,11 +12047,11 @@
       </c>
       <c r="AP8" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AQ8" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP8-IF(S8="NO",Parametros!$E$17,0))+AC8)-AN8-IF(AO8="SI",Parametros!$E$33,0))</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AR8" s="42"/>
       <c r="AS8" s="52" t="str">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="AW8" s="53">
         <f>'Captura Agosto'!G10</f>
-        <v>0</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="AX8" s="53">
         <f>'Captura Agosto'!X10</f>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="BA8" s="55">
         <f>'Captura Agosto'!AQ10</f>
-        <v>0.33</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="BB8" s="42"/>
       <c r="BC8" s="42"/>
@@ -12105,18 +12105,18 @@
         <v>Jimmy Velasquez</v>
       </c>
       <c r="D9" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="65">
         <v>0</v>
       </c>
       <c r="F9" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G9" s="66">
         <f>F9*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H9" s="67"/>
       <c r="I9" s="67"/>
@@ -12128,14 +12128,14 @@
         <v>0</v>
       </c>
       <c r="L9" s="65">
-        <v>0</v>
+        <v>0.94</v>
       </c>
       <c r="M9" s="68" t="s">
         <v>200</v>
       </c>
       <c r="N9" s="66">
         <f>IF(M9="NO",0,L9*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="O9" s="65">
         <v>0</v>
@@ -12229,11 +12229,11 @@
       </c>
       <c r="AP9" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.42520000000000002</v>
       </c>
       <c r="AQ9" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP9-IF(S9="NO",Parametros!$E$17,0))+AC9)-AN9-IF(AO9="SI",Parametros!$E$33,0))</f>
-        <v>0.25</v>
+        <v>0.42520000000000002</v>
       </c>
       <c r="AR9" s="42"/>
       <c r="AS9" s="59" t="str">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="AW9" s="60">
         <f>'Captura Agosto'!G11</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX9" s="60">
         <f>'Captura Agosto'!X11</f>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="BA9" s="62">
         <f>'Captura Agosto'!AQ11</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BB9" s="42"/>
       <c r="BC9" s="42"/>
@@ -12287,18 +12287,18 @@
         <v>Jessica Loarca</v>
       </c>
       <c r="D10" s="65">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E10" s="65">
         <v>0</v>
       </c>
       <c r="F10" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G10" s="66">
         <f>F10*Parametros!$E$6</f>
-        <v>0</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="H10" s="67">
         <v>38</v>
@@ -12415,11 +12415,11 @@
       </c>
       <c r="AP10" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="AQ10" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP10-IF(S10="NO",Parametros!$E$17,0))+AC10)-AN10-IF(AO10="SI",Parametros!$E$33,0))</f>
-        <v>0.33</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="AR10" s="42"/>
       <c r="AS10" s="52" t="str">
@@ -12440,7 +12440,7 @@
       </c>
       <c r="AW10" s="53">
         <f>'Captura Agosto'!G12</f>
-        <v>0</v>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="AX10" s="53">
         <f>'Captura Agosto'!X12</f>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="BA10" s="55">
         <f>'Captura Agosto'!AQ12</f>
-        <v>0.33</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="BB10" s="42"/>
       <c r="BC10" s="42"/>
@@ -12473,18 +12473,18 @@
         <v>Edson Bonifacio</v>
       </c>
       <c r="D11" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="65">
         <v>0</v>
       </c>
       <c r="F11" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G11" s="66">
         <f>F11*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H11" s="67">
         <v>38</v>
@@ -12601,11 +12601,11 @@
       </c>
       <c r="AP11" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AQ11" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP11-IF(S11="NO",Parametros!$E$17,0))+AC11)-AN11-IF(AO11="SI",Parametros!$E$33,0))</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AR11" s="42"/>
       <c r="AS11" s="59" t="str">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="AW11" s="60">
         <f>'Captura Agosto'!G13</f>
-        <v>0</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="AX11" s="60">
         <f>'Captura Agosto'!X13</f>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="BA11" s="62">
         <f>'Captura Agosto'!AQ13</f>
-        <v>0.3972</v>
+        <v>0.49419999999999997</v>
       </c>
       <c r="BB11" s="42"/>
       <c r="BC11" s="42"/>
@@ -12659,18 +12659,18 @@
         <v>Adrian Santisteban</v>
       </c>
       <c r="D12" s="65">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E12" s="65">
         <v>0</v>
       </c>
       <c r="F12" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="G12" s="66">
         <f>F12*Parametros!$E$6</f>
-        <v>0</v>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="H12" s="67">
         <v>38</v>
@@ -12787,11 +12787,11 @@
       </c>
       <c r="AP12" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="AQ12" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP12-IF(S12="NO",Parametros!$E$17,0))+AC12)-AN12-IF(AO12="SI",Parametros!$E$33,0))</f>
-        <v>0.33</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="AR12" s="42"/>
       <c r="AS12" s="52" t="str">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="AW12" s="53">
         <f>'Captura Agosto'!G14</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX12" s="53">
         <f>'Captura Agosto'!X14</f>
@@ -12828,7 +12828,7 @@
       </c>
       <c r="BA12" s="55">
         <f>'Captura Agosto'!AQ14</f>
-        <v>0.40039999999999998</v>
+        <v>0.50039999999999996</v>
       </c>
       <c r="BB12" s="42"/>
       <c r="BC12" s="42"/>
@@ -12845,18 +12845,18 @@
         <v>Amilcar Ralda</v>
       </c>
       <c r="D13" s="65">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E13" s="65">
         <v>0</v>
       </c>
       <c r="F13" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="G13" s="66">
         <f>F13*Parametros!$E$6</f>
-        <v>0</v>
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="H13" s="67">
         <v>38</v>
@@ -12973,11 +12973,11 @@
       </c>
       <c r="AP13" s="11">
         <f t="shared" si="3"/>
-        <v>0.3972</v>
+        <v>0.49419999999999997</v>
       </c>
       <c r="AQ13" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP13-IF(S13="NO",Parametros!$E$17,0))+AC13)-AN13-IF(AO13="SI",Parametros!$E$33,0))</f>
-        <v>0.3972</v>
+        <v>0.49419999999999997</v>
       </c>
       <c r="AR13" s="42"/>
       <c r="AS13" s="59" t="str">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="AW13" s="60">
         <f>'Captura Agosto'!G15</f>
-        <v>0</v>
+        <v>5.2000000000000005E-2</v>
       </c>
       <c r="AX13" s="60">
         <f>'Captura Agosto'!X15</f>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="BA13" s="62">
         <f>'Captura Agosto'!AQ15</f>
-        <v>0.33</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="BB13" s="42"/>
       <c r="BC13" s="42"/>
@@ -13031,18 +13031,18 @@
         <v>Amilcar Ralda</v>
       </c>
       <c r="D14" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="65">
         <v>0</v>
       </c>
       <c r="F14" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G14" s="66">
         <f>F14*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H14" s="67">
         <v>38</v>
@@ -13159,11 +13159,11 @@
       </c>
       <c r="AP14" s="11">
         <f t="shared" si="3"/>
-        <v>0.40039999999999998</v>
+        <v>0.50039999999999996</v>
       </c>
       <c r="AQ14" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP14-IF(S14="NO",Parametros!$E$17,0))+AC14)-AN14-IF(AO14="SI",Parametros!$E$33,0))</f>
-        <v>0.40039999999999998</v>
+        <v>0.50039999999999996</v>
       </c>
       <c r="AR14" s="42"/>
       <c r="AS14" s="52" t="str">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AW14" s="53">
         <f>'Captura Agosto'!G16</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX14" s="53">
         <f>'Captura Agosto'!X16</f>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="BA14" s="55">
         <f>'Captura Agosto'!AQ16</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BB14" s="42"/>
       <c r="BC14" s="42"/>
@@ -13217,18 +13217,18 @@
         <v>Mario Ramos</v>
       </c>
       <c r="D15" s="65">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="E15" s="65">
         <v>0</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="G15" s="66">
         <f>F15*Parametros!$E$6</f>
-        <v>0</v>
+        <v>5.2000000000000005E-2</v>
       </c>
       <c r="H15" s="67">
         <v>38</v>
@@ -13345,11 +13345,11 @@
       </c>
       <c r="AP15" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="AQ15" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP15-IF(S15="NO",Parametros!$E$17,0))+AC15)-AN15-IF(AO15="SI",Parametros!$E$33,0))</f>
-        <v>0.33</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="AR15" s="42"/>
       <c r="AS15" s="59" t="str">
@@ -13370,7 +13370,7 @@
       </c>
       <c r="AW15" s="60">
         <f>'Captura Agosto'!G17</f>
-        <v>0</v>
+        <v>9.2000000000000012E-2</v>
       </c>
       <c r="AX15" s="60">
         <f>'Captura Agosto'!X17</f>
@@ -13386,7 +13386,7 @@
       </c>
       <c r="BA15" s="62">
         <f>'Captura Agosto'!AQ17</f>
-        <v>0.33</v>
+        <v>0.42200000000000004</v>
       </c>
       <c r="BB15" s="42"/>
       <c r="BC15" s="42"/>
@@ -13403,18 +13403,18 @@
         <v>Mario Ramos</v>
       </c>
       <c r="D16" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="65">
         <v>0</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G16" s="66">
         <f>F16*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H16" s="67">
         <v>38</v>
@@ -13531,11 +13531,11 @@
       </c>
       <c r="AP16" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AQ16" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP16-IF(S16="NO",Parametros!$E$17,0))+AC16)-AN16-IF(AO16="SI",Parametros!$E$33,0))</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AR16" s="42"/>
       <c r="AS16" s="52" t="str">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="AW16" s="53">
         <f>'Captura Agosto'!G18</f>
-        <v>0</v>
+        <v>8.7000000000000008E-2</v>
       </c>
       <c r="AX16" s="53">
         <f>'Captura Agosto'!X18</f>
@@ -13572,7 +13572,7 @@
       </c>
       <c r="BA16" s="55">
         <f>'Captura Agosto'!AQ18</f>
-        <v>0.33</v>
+        <v>0.41700000000000004</v>
       </c>
       <c r="BB16" s="42"/>
       <c r="BC16" s="42"/>
@@ -13589,18 +13589,18 @@
         <v>Roy Luarca</v>
       </c>
       <c r="D17" s="65">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="E17" s="65">
         <v>0</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="G17" s="66">
         <f>F17*Parametros!$E$6</f>
-        <v>0</v>
+        <v>9.2000000000000012E-2</v>
       </c>
       <c r="H17" s="67">
         <v>38</v>
@@ -13717,11 +13717,11 @@
       </c>
       <c r="AP17" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.42200000000000004</v>
       </c>
       <c r="AQ17" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP17-IF(S17="NO",Parametros!$E$17,0))+AC17)-AN17-IF(AO17="SI",Parametros!$E$33,0))</f>
-        <v>0.33</v>
+        <v>0.42200000000000004</v>
       </c>
       <c r="AR17" s="42"/>
       <c r="AS17" s="59" t="str">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AW17" s="60">
         <f>'Captura Agosto'!G19</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX17" s="60">
         <f>'Captura Agosto'!X19</f>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="BA17" s="62">
         <f>'Captura Agosto'!AQ19</f>
-        <v>0.41000000000000003</v>
+        <v>0.51</v>
       </c>
       <c r="BB17" s="42"/>
       <c r="BC17" s="42"/>
@@ -13775,18 +13775,18 @@
         <v>Eliu Tello</v>
       </c>
       <c r="D18" s="65">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="E18" s="65">
         <v>0</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="G18" s="66">
         <f>F18*Parametros!$E$6</f>
-        <v>0</v>
+        <v>8.7000000000000008E-2</v>
       </c>
       <c r="H18" s="67">
         <v>38</v>
@@ -13903,11 +13903,11 @@
       </c>
       <c r="AP18" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.41700000000000004</v>
       </c>
       <c r="AQ18" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP18-IF(S18="NO",Parametros!$E$17,0))+AC18)-AN18-IF(AO18="SI",Parametros!$E$33,0))</f>
-        <v>0.33</v>
+        <v>0.41700000000000004</v>
       </c>
       <c r="AR18" s="42"/>
       <c r="AS18" s="52" t="str">
@@ -13928,7 +13928,7 @@
       </c>
       <c r="AW18" s="53">
         <f>'Captura Agosto'!G20</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX18" s="53">
         <f>'Captura Agosto'!X20</f>
@@ -13944,7 +13944,7 @@
       </c>
       <c r="BA18" s="55">
         <f>'Captura Agosto'!AQ20</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BB18" s="42"/>
       <c r="BC18" s="42"/>
@@ -13961,18 +13961,18 @@
         <v>Miguel Godinez</v>
       </c>
       <c r="D19" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="65">
         <v>0</v>
       </c>
       <c r="F19" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="66">
         <f>F19*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H19" s="67">
         <v>38</v>
@@ -14089,26 +14089,26 @@
       </c>
       <c r="AP19" s="11">
         <f t="shared" si="3"/>
-        <v>0.41000000000000003</v>
+        <v>0.51</v>
       </c>
       <c r="AQ19" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP19-IF(S19="NO",Parametros!$E$17,0))+AC19)-AN19-IF(AO19="SI",Parametros!$E$33,0))</f>
-        <v>0.41000000000000003</v>
+        <v>0.51</v>
       </c>
       <c r="AR19" s="42"/>
-      <c r="AS19" s="85" t="s">
+      <c r="AS19" s="90" t="s">
         <v>231</v>
       </c>
-      <c r="AT19" s="85"/>
-      <c r="AU19" s="85"/>
-      <c r="AV19" s="85"/>
-      <c r="AW19" s="85"/>
-      <c r="AX19" s="85"/>
-      <c r="AY19" s="85"/>
-      <c r="AZ19" s="85"/>
+      <c r="AT19" s="90"/>
+      <c r="AU19" s="90"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="90"/>
+      <c r="AY19" s="90"/>
+      <c r="AZ19" s="90"/>
       <c r="BA19" s="71">
         <f>AVERAGE(BA4:BA18)</f>
-        <v>0.33384000000000003</v>
+        <v>0.43205333333333323</v>
       </c>
       <c r="BB19" s="42"/>
       <c r="BC19" s="42"/>
@@ -14125,18 +14125,18 @@
         <v>Adrian Santisteban</v>
       </c>
       <c r="D20" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="65">
         <v>0</v>
       </c>
       <c r="F20" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G20" s="66">
         <f>F20*Parametros!$E$6</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H20" s="67">
         <v>38</v>
@@ -14253,11 +14253,11 @@
       </c>
       <c r="AP20" s="11">
         <f t="shared" si="3"/>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AQ20" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP20-IF(S20="NO",Parametros!$E$17,0))+AC20)-AN20-IF(AO20="SI",Parametros!$E$33,0))</f>
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AR20" s="42"/>
       <c r="AS20" s="42"/>
@@ -14272,9 +14272,9 @@
       <c r="BB20" s="42"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
       <c r="F22" s="51"/>
@@ -14301,11 +14301,11 @@
       <c r="AV22" s="72"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="73"/>
       <c r="E23" s="73"/>
       <c r="F23" s="73"/>
@@ -14347,7 +14347,7 @@
       <c r="AP23" s="73"/>
       <c r="AQ23" s="74">
         <f>AVERAGE(AQ6:AQ20)</f>
-        <v>0.33384000000000003</v>
+        <v>0.43205333333333323</v>
       </c>
       <c r="AR23" s="42"/>
       <c r="AS23" s="42"/>
@@ -14363,11 +14363,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
@@ -14381,6 +14376,11 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="47" priority="5" operator="greaterThanOrEqual">
@@ -14426,7 +14426,7 @@
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="decimal" showErrorMessage="1" errorTitle="Valor invalido" error="Ingrese un porcentaje entre 0% y 100%" sqref="D6:E20 L6:L20 O6:O20 R6:R20 U6:U20" xr:uid="{00000000-0002-0000-0B00-000002000000}">
+    <dataValidation type="decimal" showErrorMessage="1" errorTitle="Valor invalido" error="Ingrese un porcentaje entre 0% y 100%" sqref="U6:U20 L6:L20 O6:O20 R6:R20 D6:E20" xr:uid="{00000000-0002-0000-0B00-000002000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -14460,48 +14460,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="85" t="s">
         <v>232</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="91"/>
-      <c r="AB1" s="91"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
       <c r="AR1" s="42"/>
-      <c r="AS1" s="92" t="s">
+      <c r="AS1" s="86" t="s">
         <v>233</v>
       </c>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="92"/>
-      <c r="BA1" s="92"/>
+      <c r="AT1" s="86"/>
+      <c r="AU1" s="86"/>
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="86"/>
+      <c r="AY1" s="86"/>
+      <c r="AZ1" s="86"/>
+      <c r="BA1" s="86"/>
       <c r="BB1" s="42"/>
       <c r="BC1" s="42"/>
     </row>
@@ -14509,11 +14509,11 @@
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="F2" s="5" t="s">
         <v>148</v>
       </c>
@@ -14522,20 +14522,20 @@
       </c>
       <c r="AR2" s="42"/>
       <c r="AS2" s="44"/>
-      <c r="AT2" s="94" t="s">
+      <c r="AT2" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="AU2" s="94"/>
-      <c r="AV2" s="94"/>
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="88"/>
       <c r="AW2" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="AX2" s="95" t="s">
+      <c r="AX2" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="AY2" s="95"/>
-      <c r="AZ2" s="95"/>
-      <c r="BA2" s="95"/>
+      <c r="AY2" s="89"/>
+      <c r="AZ2" s="89"/>
+      <c r="BA2" s="89"/>
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
@@ -14575,66 +14575,66 @@
       <c r="A4" s="51"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88" t="s">
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88" t="s">
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88" t="s">
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88" t="s">
+      <c r="P4" s="93"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88" t="s">
+      <c r="S4" s="93"/>
+      <c r="T4" s="93"/>
+      <c r="U4" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="V4" s="88"/>
-      <c r="W4" s="89" t="s">
+      <c r="V4" s="93"/>
+      <c r="W4" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="88" t="s">
+      <c r="X4" s="94"/>
+      <c r="Y4" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
-      <c r="AB4" s="88"/>
-      <c r="AC4" s="88"/>
-      <c r="AD4" s="89" t="s">
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
+      <c r="AB4" s="93"/>
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="90" t="s">
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="95" t="s">
         <v>170</v>
       </c>
-      <c r="AQ4" s="90"/>
+      <c r="AQ4" s="95"/>
       <c r="AR4" s="42"/>
       <c r="AS4" s="52" t="str">
         <f>'Captura Septiembre'!B6</f>
@@ -17410,16 +17410,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="42"/>
-      <c r="AS19" s="85" t="s">
+      <c r="AS19" s="90" t="s">
         <v>235</v>
       </c>
-      <c r="AT19" s="85"/>
-      <c r="AU19" s="85"/>
-      <c r="AV19" s="85"/>
-      <c r="AW19" s="85"/>
-      <c r="AX19" s="85"/>
-      <c r="AY19" s="85"/>
-      <c r="AZ19" s="85"/>
+      <c r="AT19" s="90"/>
+      <c r="AU19" s="90"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="90"/>
+      <c r="AY19" s="90"/>
+      <c r="AZ19" s="90"/>
       <c r="BA19" s="71">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -17586,9 +17586,9 @@
       <c r="BB20" s="42"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
       <c r="F22" s="51"/>
@@ -17615,11 +17615,11 @@
       <c r="AV22" s="72"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="73"/>
       <c r="E23" s="73"/>
       <c r="F23" s="73"/>
@@ -17677,11 +17677,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
@@ -17695,6 +17690,11 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="38" priority="5" operator="greaterThanOrEqual">
@@ -17774,48 +17774,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="85" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="91"/>
-      <c r="AB1" s="91"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
       <c r="AR1" s="42"/>
-      <c r="AS1" s="92" t="s">
+      <c r="AS1" s="86" t="s">
         <v>237</v>
       </c>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="92"/>
-      <c r="BA1" s="92"/>
+      <c r="AT1" s="86"/>
+      <c r="AU1" s="86"/>
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="86"/>
+      <c r="AY1" s="86"/>
+      <c r="AZ1" s="86"/>
+      <c r="BA1" s="86"/>
       <c r="BB1" s="42"/>
       <c r="BC1" s="42"/>
     </row>
@@ -17823,11 +17823,11 @@
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="87" t="s">
         <v>238</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="F2" s="5" t="s">
         <v>148</v>
       </c>
@@ -17836,20 +17836,20 @@
       </c>
       <c r="AR2" s="42"/>
       <c r="AS2" s="44"/>
-      <c r="AT2" s="94" t="s">
+      <c r="AT2" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="AU2" s="94"/>
-      <c r="AV2" s="94"/>
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="88"/>
       <c r="AW2" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="AX2" s="95" t="s">
+      <c r="AX2" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="AY2" s="95"/>
-      <c r="AZ2" s="95"/>
-      <c r="BA2" s="95"/>
+      <c r="AY2" s="89"/>
+      <c r="AZ2" s="89"/>
+      <c r="BA2" s="89"/>
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
@@ -17889,66 +17889,66 @@
       <c r="A4" s="51"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88" t="s">
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88" t="s">
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88" t="s">
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88" t="s">
+      <c r="P4" s="93"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88" t="s">
+      <c r="S4" s="93"/>
+      <c r="T4" s="93"/>
+      <c r="U4" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="V4" s="88"/>
-      <c r="W4" s="89" t="s">
+      <c r="V4" s="93"/>
+      <c r="W4" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="88" t="s">
+      <c r="X4" s="94"/>
+      <c r="Y4" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
-      <c r="AB4" s="88"/>
-      <c r="AC4" s="88"/>
-      <c r="AD4" s="89" t="s">
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
+      <c r="AB4" s="93"/>
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="90" t="s">
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="95" t="s">
         <v>170</v>
       </c>
-      <c r="AQ4" s="90"/>
+      <c r="AQ4" s="95"/>
       <c r="AR4" s="42"/>
       <c r="AS4" s="52" t="str">
         <f>'Captura Octubre'!B6</f>
@@ -20724,16 +20724,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="42"/>
-      <c r="AS19" s="85" t="s">
+      <c r="AS19" s="90" t="s">
         <v>239</v>
       </c>
-      <c r="AT19" s="85"/>
-      <c r="AU19" s="85"/>
-      <c r="AV19" s="85"/>
-      <c r="AW19" s="85"/>
-      <c r="AX19" s="85"/>
-      <c r="AY19" s="85"/>
-      <c r="AZ19" s="85"/>
+      <c r="AT19" s="90"/>
+      <c r="AU19" s="90"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="90"/>
+      <c r="AY19" s="90"/>
+      <c r="AZ19" s="90"/>
       <c r="BA19" s="71">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -20900,9 +20900,9 @@
       <c r="BB20" s="42"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
       <c r="F22" s="51"/>
@@ -20929,11 +20929,11 @@
       <c r="AV22" s="72"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="73"/>
       <c r="E23" s="73"/>
       <c r="F23" s="73"/>
@@ -20991,11 +20991,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
@@ -21009,6 +21004,11 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="29" priority="5" operator="greaterThanOrEqual">
@@ -21088,48 +21088,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="85" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="91"/>
-      <c r="AB1" s="91"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
       <c r="AR1" s="42"/>
-      <c r="AS1" s="92" t="s">
+      <c r="AS1" s="86" t="s">
         <v>241</v>
       </c>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="92"/>
-      <c r="BA1" s="92"/>
+      <c r="AT1" s="86"/>
+      <c r="AU1" s="86"/>
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="86"/>
+      <c r="AY1" s="86"/>
+      <c r="AZ1" s="86"/>
+      <c r="BA1" s="86"/>
       <c r="BB1" s="42"/>
       <c r="BC1" s="42"/>
     </row>
@@ -21137,11 +21137,11 @@
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="87" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="F2" s="5" t="s">
         <v>148</v>
       </c>
@@ -21150,20 +21150,20 @@
       </c>
       <c r="AR2" s="42"/>
       <c r="AS2" s="44"/>
-      <c r="AT2" s="94" t="s">
+      <c r="AT2" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="AU2" s="94"/>
-      <c r="AV2" s="94"/>
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="88"/>
       <c r="AW2" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="AX2" s="95" t="s">
+      <c r="AX2" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="AY2" s="95"/>
-      <c r="AZ2" s="95"/>
-      <c r="BA2" s="95"/>
+      <c r="AY2" s="89"/>
+      <c r="AZ2" s="89"/>
+      <c r="BA2" s="89"/>
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
@@ -21203,66 +21203,66 @@
       <c r="A4" s="51"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88" t="s">
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88" t="s">
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88" t="s">
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88" t="s">
+      <c r="P4" s="93"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88" t="s">
+      <c r="S4" s="93"/>
+      <c r="T4" s="93"/>
+      <c r="U4" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="V4" s="88"/>
-      <c r="W4" s="89" t="s">
+      <c r="V4" s="93"/>
+      <c r="W4" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="88" t="s">
+      <c r="X4" s="94"/>
+      <c r="Y4" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
-      <c r="AB4" s="88"/>
-      <c r="AC4" s="88"/>
-      <c r="AD4" s="89" t="s">
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
+      <c r="AB4" s="93"/>
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="90" t="s">
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="95" t="s">
         <v>170</v>
       </c>
-      <c r="AQ4" s="90"/>
+      <c r="AQ4" s="95"/>
       <c r="AR4" s="42"/>
       <c r="AS4" s="52" t="str">
         <f>'Captura Noviembre'!B6</f>
@@ -24038,16 +24038,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="42"/>
-      <c r="AS19" s="85" t="s">
+      <c r="AS19" s="90" t="s">
         <v>243</v>
       </c>
-      <c r="AT19" s="85"/>
-      <c r="AU19" s="85"/>
-      <c r="AV19" s="85"/>
-      <c r="AW19" s="85"/>
-      <c r="AX19" s="85"/>
-      <c r="AY19" s="85"/>
-      <c r="AZ19" s="85"/>
+      <c r="AT19" s="90"/>
+      <c r="AU19" s="90"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="90"/>
+      <c r="AY19" s="90"/>
+      <c r="AZ19" s="90"/>
       <c r="BA19" s="71">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -24214,9 +24214,9 @@
       <c r="BB20" s="42"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
       <c r="F22" s="51"/>
@@ -24243,11 +24243,11 @@
       <c r="AV22" s="72"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="73"/>
       <c r="E23" s="73"/>
       <c r="F23" s="73"/>
@@ -24305,11 +24305,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
@@ -24323,6 +24318,11 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="20" priority="5" operator="greaterThanOrEqual">
@@ -24402,48 +24402,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="91"/>
-      <c r="AB1" s="91"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
       <c r="AR1" s="42"/>
-      <c r="AS1" s="92" t="s">
+      <c r="AS1" s="86" t="s">
         <v>245</v>
       </c>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="92"/>
-      <c r="BA1" s="92"/>
+      <c r="AT1" s="86"/>
+      <c r="AU1" s="86"/>
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="86"/>
+      <c r="AY1" s="86"/>
+      <c r="AZ1" s="86"/>
+      <c r="BA1" s="86"/>
       <c r="BB1" s="42"/>
       <c r="BC1" s="42"/>
     </row>
@@ -24451,11 +24451,11 @@
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="87" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="F2" s="5" t="s">
         <v>148</v>
       </c>
@@ -24464,20 +24464,20 @@
       </c>
       <c r="AR2" s="42"/>
       <c r="AS2" s="44"/>
-      <c r="AT2" s="94" t="s">
+      <c r="AT2" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="AU2" s="94"/>
-      <c r="AV2" s="94"/>
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="88"/>
       <c r="AW2" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="AX2" s="95" t="s">
+      <c r="AX2" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="AY2" s="95"/>
-      <c r="AZ2" s="95"/>
-      <c r="BA2" s="95"/>
+      <c r="AY2" s="89"/>
+      <c r="AZ2" s="89"/>
+      <c r="BA2" s="89"/>
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
@@ -24517,66 +24517,66 @@
       <c r="A4" s="51"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88" t="s">
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88" t="s">
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88" t="s">
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88" t="s">
+      <c r="P4" s="93"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88" t="s">
+      <c r="S4" s="93"/>
+      <c r="T4" s="93"/>
+      <c r="U4" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="V4" s="88"/>
-      <c r="W4" s="89" t="s">
+      <c r="V4" s="93"/>
+      <c r="W4" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="88" t="s">
+      <c r="X4" s="94"/>
+      <c r="Y4" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
-      <c r="AB4" s="88"/>
-      <c r="AC4" s="88"/>
-      <c r="AD4" s="89" t="s">
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
+      <c r="AB4" s="93"/>
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="90" t="s">
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="95" t="s">
         <v>170</v>
       </c>
-      <c r="AQ4" s="90"/>
+      <c r="AQ4" s="95"/>
       <c r="AR4" s="42"/>
       <c r="AS4" s="52" t="str">
         <f>'Captura Diciembre'!B6</f>
@@ -27352,16 +27352,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="42"/>
-      <c r="AS19" s="85" t="s">
+      <c r="AS19" s="90" t="s">
         <v>247</v>
       </c>
-      <c r="AT19" s="85"/>
-      <c r="AU19" s="85"/>
-      <c r="AV19" s="85"/>
-      <c r="AW19" s="85"/>
-      <c r="AX19" s="85"/>
-      <c r="AY19" s="85"/>
-      <c r="AZ19" s="85"/>
+      <c r="AT19" s="90"/>
+      <c r="AU19" s="90"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="90"/>
+      <c r="AY19" s="90"/>
+      <c r="AZ19" s="90"/>
       <c r="BA19" s="71">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -27528,9 +27528,9 @@
       <c r="BB20" s="42"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
       <c r="F22" s="51"/>
@@ -27557,11 +27557,11 @@
       <c r="AV22" s="72"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="73"/>
       <c r="E23" s="73"/>
       <c r="F23" s="73"/>
@@ -27619,11 +27619,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
@@ -27637,6 +27632,11 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThanOrEqual">
@@ -27710,11 +27710,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="85" t="s">
         <v>248</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="108" t="s">
@@ -27832,13 +27832,13 @@
       <c r="A13" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="B13" s="76" t="str">
+      <c r="B13" s="76">
         <f>IF(AVERAGE('Captura Agosto'!D6:D20)=0,"",'Captura Agosto'!AQ23)</f>
-        <v/>
+        <v>0.43205333333333323</v>
       </c>
       <c r="C13" s="12" t="str">
         <f>IF(B13="","",IF(B13&gt;=Parametros!$C$37,"Verde",IF(B13&gt;=Parametros!$C$38,"Amarillo","Rojo")))</f>
-        <v/>
+        <v>Rojo</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28025,9 +28025,9 @@
         <f>IFERROR(IF('Captura Julio'!D8=0,"",'Captura Julio'!AQ8),"")</f>
         <v>1</v>
       </c>
-      <c r="I4" s="10" t="str">
+      <c r="I4" s="10">
         <f>IFERROR(IF('Captura Agosto'!D8=0,"",'Captura Agosto'!AQ8),"")</f>
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="J4" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
@@ -28047,7 +28047,7 @@
       </c>
       <c r="N4" s="81">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.97571428571428576</v>
+        <v>0.90749999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28082,9 +28082,9 @@
         <f>IFERROR(IF('Captura Julio'!D6=0,"",'Captura Julio'!AQ6),"")</f>
         <v>1</v>
       </c>
-      <c r="I5" s="10" t="str">
+      <c r="I5" s="10">
         <f>IFERROR(IF('Captura Agosto'!D6=0,"",'Captura Agosto'!AQ6),"")</f>
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="J5" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D6=0,"",'Captura Septiembre'!AQ6),"")</f>
@@ -28104,7 +28104,7 @@
       </c>
       <c r="N5" s="81">
         <f t="shared" si="0"/>
-        <v>0.92999999999999994</v>
+        <v>0.86749999999999994</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28139,9 +28139,9 @@
         <f>IFERROR(IF('Captura Julio'!D16=0,"",'Captura Julio'!AQ16),"")</f>
         <v>1</v>
       </c>
-      <c r="I6" s="10" t="str">
+      <c r="I6" s="10">
         <f>IFERROR(IF('Captura Agosto'!D16=0,"",'Captura Agosto'!AQ16),"")</f>
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="J6" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="N6" s="81">
         <f t="shared" si="0"/>
-        <v>0.93204081632653057</v>
+        <v>0.86928571428571422</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28196,9 +28196,9 @@
         <f>IFERROR(IF('Captura Julio'!D17=0,"",'Captura Julio'!AQ17),"")</f>
         <v>0.83</v>
       </c>
-      <c r="I7" s="10" t="str">
+      <c r="I7" s="10">
         <f>IFERROR(IF('Captura Agosto'!D17=0,"",'Captura Agosto'!AQ17),"")</f>
-        <v/>
+        <v>0.42200000000000004</v>
       </c>
       <c r="J7" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
@@ -28218,7 +28218,7 @@
       </c>
       <c r="N7" s="81">
         <f t="shared" si="0"/>
-        <v>0.86882260596546312</v>
+        <v>0.81296978021978017</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28253,9 +28253,9 @@
         <f>IFERROR(IF('Captura Julio'!D14=0,"",'Captura Julio'!AQ14),"")</f>
         <v>0.79</v>
       </c>
-      <c r="I8" s="10" t="str">
+      <c r="I8" s="10">
         <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
-        <v/>
+        <v>0.50039999999999996</v>
       </c>
       <c r="J8" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
@@ -28275,7 +28275,7 @@
       </c>
       <c r="N8" s="81">
         <f t="shared" si="0"/>
-        <v>0.93714285714285717</v>
+        <v>0.88255000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28310,9 +28310,9 @@
         <f>IFERROR(IF('Captura Julio'!D11=0,"",'Captura Julio'!AQ11),"")</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="I9" s="10" t="str">
+      <c r="I9" s="10">
         <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="J9" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
@@ -28332,7 +28332,7 @@
       </c>
       <c r="N9" s="81">
         <f t="shared" si="0"/>
-        <v>0.94000000000000006</v>
+        <v>0.87624999999999997</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28367,9 +28367,9 @@
         <f>IFERROR(IF('Captura Julio'!D13=0,"",'Captura Julio'!AQ13),"")</f>
         <v>0.64</v>
       </c>
-      <c r="I10" s="10" t="str">
+      <c r="I10" s="10">
         <f>IFERROR(IF('Captura Agosto'!D13=0,"",'Captura Agosto'!AQ13),"")</f>
-        <v/>
+        <v>0.49419999999999997</v>
       </c>
       <c r="J10" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
@@ -28389,7 +28389,7 @@
       </c>
       <c r="N10" s="81">
         <f t="shared" si="0"/>
-        <v>0.82714285714285707</v>
+        <v>0.78552499999999992</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28424,9 +28424,9 @@
         <f>IFERROR(IF('Captura Julio'!D10=0,"",'Captura Julio'!AQ10),"")</f>
         <v>1</v>
       </c>
-      <c r="I11" s="10" t="str">
+      <c r="I11" s="10">
         <f>IFERROR(IF('Captura Agosto'!D10=0,"",'Captura Agosto'!AQ10),"")</f>
-        <v/>
+        <v>0.41000000000000003</v>
       </c>
       <c r="J11" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
@@ -28446,7 +28446,7 @@
       </c>
       <c r="N11" s="81">
         <f t="shared" si="0"/>
-        <v>0.95071428571428573</v>
+        <v>0.88312500000000005</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28481,9 +28481,9 @@
         <f>IFERROR(IF('Captura Julio'!D9=0,"",'Captura Julio'!AQ9),"")</f>
         <v>1</v>
       </c>
-      <c r="I12" s="10" t="str">
+      <c r="I12" s="10">
         <f>IFERROR(IF('Captura Agosto'!D9=0,"",'Captura Agosto'!AQ9),"")</f>
-        <v/>
+        <v>0.42520000000000002</v>
       </c>
       <c r="J12" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
@@ -28503,7 +28503,7 @@
       </c>
       <c r="N12" s="81">
         <f t="shared" si="0"/>
-        <v>0.98250000000000004</v>
+        <v>0.91283750000000008</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28538,9 +28538,9 @@
         <f>IFERROR(IF('Captura Julio'!D12=0,"",'Captura Julio'!AQ12),"")</f>
         <v>0.9</v>
       </c>
-      <c r="I13" s="10" t="str">
+      <c r="I13" s="10">
         <f>IFERROR(IF('Captura Agosto'!D12=0,"",'Captura Agosto'!AQ12),"")</f>
-        <v/>
+        <v>0.42000000000000004</v>
       </c>
       <c r="J13" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
@@ -28560,7 +28560,7 @@
       </c>
       <c r="N13" s="81">
         <f t="shared" si="0"/>
-        <v>0.84875776397515534</v>
+        <v>0.79516304347826094</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28595,9 +28595,9 @@
         <f>IFERROR(IF('Captura Julio'!D15=0,"",'Captura Julio'!AQ15),"")</f>
         <v>0.75</v>
       </c>
-      <c r="I14" s="10" t="str">
+      <c r="I14" s="10">
         <f>IFERROR(IF('Captura Agosto'!D15=0,"",'Captura Agosto'!AQ15),"")</f>
-        <v/>
+        <v>0.38200000000000001</v>
       </c>
       <c r="J14" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
@@ -28617,7 +28617,7 @@
       </c>
       <c r="N14" s="81">
         <f t="shared" si="0"/>
-        <v>0.85416875522138691</v>
+        <v>0.79514766081871346</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28652,9 +28652,9 @@
         <f>IFERROR(IF('Captura Julio'!D7=0,"",'Captura Julio'!AQ7),"")</f>
         <v>0.64</v>
       </c>
-      <c r="I15" s="10" t="str">
+      <c r="I15" s="10">
         <f>IFERROR(IF('Captura Agosto'!D7=0,"",'Captura Agosto'!AQ7),"")</f>
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="J15" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D7=0,"",'Captura Septiembre'!AQ7),"")</f>
@@ -28674,7 +28674,7 @@
       </c>
       <c r="N15" s="81">
         <f t="shared" si="0"/>
-        <v>0.80285714285714282</v>
+        <v>0.74624999999999997</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28709,9 +28709,9 @@
         <f>IFERROR(IF('Captura Julio'!D20=0,"",'Captura Julio'!AQ20),"")</f>
         <v>1</v>
       </c>
-      <c r="I16" s="10" t="str">
+      <c r="I16" s="10">
         <f>IFERROR(IF('Captura Agosto'!D20=0,"",'Captura Agosto'!AQ20),"")</f>
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="J16" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
@@ -28731,7 +28731,7 @@
       </c>
       <c r="N16" s="81">
         <f t="shared" si="0"/>
-        <v>0.94428571428571428</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28766,9 +28766,9 @@
         <f>IFERROR(IF('Captura Julio'!D18=0,"",'Captura Julio'!AQ18),"")</f>
         <v>0.97666666666666679</v>
       </c>
-      <c r="I17" s="10" t="str">
+      <c r="I17" s="10">
         <f>IFERROR(IF('Captura Agosto'!D18=0,"",'Captura Agosto'!AQ18),"")</f>
-        <v/>
+        <v>0.41700000000000004</v>
       </c>
       <c r="J17" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
@@ -28788,7 +28788,7 @@
       </c>
       <c r="N17" s="81">
         <f t="shared" si="0"/>
-        <v>0.9338935574229692</v>
+        <v>0.869281862745098</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28823,9 +28823,9 @@
         <f>IFERROR(IF('Captura Julio'!D19=0,"",'Captura Julio'!AQ19),"")</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I18" s="10" t="str">
+      <c r="I18" s="10">
         <f>IFERROR(IF('Captura Agosto'!D19=0,"",'Captura Agosto'!AQ19),"")</f>
-        <v/>
+        <v>0.51</v>
       </c>
       <c r="J18" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
@@ -28845,7 +28845,7 @@
       </c>
       <c r="N18" s="81">
         <f t="shared" si="0"/>
-        <v>0.89892857142857141</v>
+        <v>0.85031249999999992</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -28880,9 +28880,9 @@
         <f t="shared" si="1"/>
         <v>0.88027777777777783</v>
       </c>
-      <c r="I19" s="83" t="str">
+      <c r="I19" s="83">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.43205333333333329</v>
       </c>
       <c r="J19" s="83" t="str">
         <f t="shared" si="1"/>
@@ -29037,9 +29037,9 @@
         <f>IFERROR(IF('Captura Julio'!D9=0,"",'Captura Julio'!AQ9),"")</f>
         <v>1</v>
       </c>
-      <c r="I4" s="10" t="str">
+      <c r="I4" s="10">
         <f>IFERROR(IF('Captura Agosto'!D9=0,"",'Captura Agosto'!AQ9),"")</f>
-        <v/>
+        <v>0.42520000000000002</v>
       </c>
       <c r="J4" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
@@ -29059,7 +29059,7 @@
       </c>
       <c r="N4" s="81">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.98250000000000004</v>
+        <v>0.91283750000000008</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29094,9 +29094,9 @@
         <f>IFERROR(IF('Captura Julio'!D8=0,"",'Captura Julio'!AQ8),"")</f>
         <v>1</v>
       </c>
-      <c r="I5" s="10" t="str">
+      <c r="I5" s="10">
         <f>IFERROR(IF('Captura Agosto'!D8=0,"",'Captura Agosto'!AQ8),"")</f>
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="J5" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
@@ -29116,7 +29116,7 @@
       </c>
       <c r="N5" s="81">
         <f t="shared" si="0"/>
-        <v>0.97571428571428576</v>
+        <v>0.90749999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29151,9 +29151,9 @@
         <f>IFERROR(IF('Captura Julio'!D10=0,"",'Captura Julio'!AQ10),"")</f>
         <v>1</v>
       </c>
-      <c r="I6" s="10" t="str">
+      <c r="I6" s="10">
         <f>IFERROR(IF('Captura Agosto'!D10=0,"",'Captura Agosto'!AQ10),"")</f>
-        <v/>
+        <v>0.41000000000000003</v>
       </c>
       <c r="J6" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="N6" s="81">
         <f t="shared" si="0"/>
-        <v>0.95071428571428573</v>
+        <v>0.88312500000000005</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29208,9 +29208,9 @@
         <f>IFERROR(IF('Captura Julio'!D20=0,"",'Captura Julio'!AQ20),"")</f>
         <v>1</v>
       </c>
-      <c r="I7" s="10" t="str">
+      <c r="I7" s="10">
         <f>IFERROR(IF('Captura Agosto'!D20=0,"",'Captura Agosto'!AQ20),"")</f>
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="J7" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
@@ -29230,7 +29230,7 @@
       </c>
       <c r="N7" s="81">
         <f t="shared" si="0"/>
-        <v>0.94428571428571428</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29265,9 +29265,9 @@
         <f>IFERROR(IF('Captura Julio'!D11=0,"",'Captura Julio'!AQ11),"")</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="I8" s="10" t="str">
+      <c r="I8" s="10">
         <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="J8" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
@@ -29287,7 +29287,7 @@
       </c>
       <c r="N8" s="81">
         <f t="shared" si="0"/>
-        <v>0.94000000000000006</v>
+        <v>0.87624999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29322,9 +29322,9 @@
         <f>IFERROR(IF('Captura Julio'!D14=0,"",'Captura Julio'!AQ14),"")</f>
         <v>0.79</v>
       </c>
-      <c r="I9" s="10" t="str">
+      <c r="I9" s="10">
         <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
-        <v/>
+        <v>0.50039999999999996</v>
       </c>
       <c r="J9" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
@@ -29344,7 +29344,7 @@
       </c>
       <c r="N9" s="81">
         <f t="shared" si="0"/>
-        <v>0.93714285714285717</v>
+        <v>0.88255000000000006</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29379,9 +29379,9 @@
         <f>IFERROR(IF('Captura Julio'!D18=0,"",'Captura Julio'!AQ18),"")</f>
         <v>0.97666666666666679</v>
       </c>
-      <c r="I10" s="10" t="str">
+      <c r="I10" s="10">
         <f>IFERROR(IF('Captura Agosto'!D18=0,"",'Captura Agosto'!AQ18),"")</f>
-        <v/>
+        <v>0.41700000000000004</v>
       </c>
       <c r="J10" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
@@ -29401,7 +29401,7 @@
       </c>
       <c r="N10" s="81">
         <f t="shared" si="0"/>
-        <v>0.9338935574229692</v>
+        <v>0.869281862745098</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29436,9 +29436,9 @@
         <f>IFERROR(IF('Captura Julio'!D16=0,"",'Captura Julio'!AQ16),"")</f>
         <v>1</v>
       </c>
-      <c r="I11" s="10" t="str">
+      <c r="I11" s="10">
         <f>IFERROR(IF('Captura Agosto'!D16=0,"",'Captura Agosto'!AQ16),"")</f>
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="J11" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
@@ -29458,7 +29458,7 @@
       </c>
       <c r="N11" s="81">
         <f t="shared" si="0"/>
-        <v>0.93204081632653057</v>
+        <v>0.86928571428571422</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29493,9 +29493,9 @@
         <f>IFERROR(IF('Captura Julio'!D6=0,"",'Captura Julio'!AQ6),"")</f>
         <v>1</v>
       </c>
-      <c r="I12" s="10" t="str">
+      <c r="I12" s="10">
         <f>IFERROR(IF('Captura Agosto'!D6=0,"",'Captura Agosto'!AQ6),"")</f>
-        <v/>
+        <v>0.43</v>
       </c>
       <c r="J12" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D6=0,"",'Captura Septiembre'!AQ6),"")</f>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="N12" s="81">
         <f t="shared" si="0"/>
-        <v>0.92999999999999994</v>
+        <v>0.86749999999999994</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29550,9 +29550,9 @@
         <f>IFERROR(IF('Captura Julio'!D19=0,"",'Captura Julio'!AQ19),"")</f>
         <v>0.73750000000000004</v>
       </c>
-      <c r="I13" s="10" t="str">
+      <c r="I13" s="10">
         <f>IFERROR(IF('Captura Agosto'!D19=0,"",'Captura Agosto'!AQ19),"")</f>
-        <v/>
+        <v>0.51</v>
       </c>
       <c r="J13" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
@@ -29572,7 +29572,7 @@
       </c>
       <c r="N13" s="81">
         <f t="shared" si="0"/>
-        <v>0.89892857142857141</v>
+        <v>0.85031249999999992</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29607,9 +29607,9 @@
         <f>IFERROR(IF('Captura Julio'!D17=0,"",'Captura Julio'!AQ17),"")</f>
         <v>0.83</v>
       </c>
-      <c r="I14" s="10" t="str">
+      <c r="I14" s="10">
         <f>IFERROR(IF('Captura Agosto'!D17=0,"",'Captura Agosto'!AQ17),"")</f>
-        <v/>
+        <v>0.42200000000000004</v>
       </c>
       <c r="J14" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
@@ -29629,7 +29629,7 @@
       </c>
       <c r="N14" s="81">
         <f t="shared" si="0"/>
-        <v>0.86882260596546312</v>
+        <v>0.81296978021978017</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29664,9 +29664,9 @@
         <f>IFERROR(IF('Captura Julio'!D15=0,"",'Captura Julio'!AQ15),"")</f>
         <v>0.75</v>
       </c>
-      <c r="I15" s="10" t="str">
+      <c r="I15" s="10">
         <f>IFERROR(IF('Captura Agosto'!D15=0,"",'Captura Agosto'!AQ15),"")</f>
-        <v/>
+        <v>0.38200000000000001</v>
       </c>
       <c r="J15" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="N15" s="81">
         <f t="shared" si="0"/>
-        <v>0.85416875522138691</v>
+        <v>0.79514766081871346</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29721,9 +29721,9 @@
         <f>IFERROR(IF('Captura Julio'!D12=0,"",'Captura Julio'!AQ12),"")</f>
         <v>0.9</v>
       </c>
-      <c r="I16" s="10" t="str">
+      <c r="I16" s="10">
         <f>IFERROR(IF('Captura Agosto'!D12=0,"",'Captura Agosto'!AQ12),"")</f>
-        <v/>
+        <v>0.42000000000000004</v>
       </c>
       <c r="J16" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
@@ -29743,7 +29743,7 @@
       </c>
       <c r="N16" s="81">
         <f t="shared" si="0"/>
-        <v>0.84875776397515534</v>
+        <v>0.79516304347826094</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29778,9 +29778,9 @@
         <f>IFERROR(IF('Captura Julio'!D13=0,"",'Captura Julio'!AQ13),"")</f>
         <v>0.64</v>
       </c>
-      <c r="I17" s="10" t="str">
+      <c r="I17" s="10">
         <f>IFERROR(IF('Captura Agosto'!D13=0,"",'Captura Agosto'!AQ13),"")</f>
-        <v/>
+        <v>0.49419999999999997</v>
       </c>
       <c r="J17" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
@@ -29800,7 +29800,7 @@
       </c>
       <c r="N17" s="81">
         <f t="shared" si="0"/>
-        <v>0.82714285714285707</v>
+        <v>0.78552499999999992</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29835,9 +29835,9 @@
         <f>IFERROR(IF('Captura Julio'!D7=0,"",'Captura Julio'!AQ7),"")</f>
         <v>0.64</v>
       </c>
-      <c r="I18" s="10" t="str">
+      <c r="I18" s="10">
         <f>IFERROR(IF('Captura Agosto'!D7=0,"",'Captura Agosto'!AQ7),"")</f>
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="J18" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D7=0,"",'Captura Septiembre'!AQ7),"")</f>
@@ -29857,7 +29857,7 @@
       </c>
       <c r="N18" s="81">
         <f t="shared" si="0"/>
-        <v>0.80285714285714282</v>
+        <v>0.74624999999999997</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -29892,9 +29892,9 @@
         <f t="shared" si="1"/>
         <v>0.88027777777777794</v>
       </c>
-      <c r="I19" s="83" t="str">
+      <c r="I19" s="83">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.43205333333333329</v>
       </c>
       <c r="J19" s="83" t="str">
         <f t="shared" si="1"/>
@@ -29942,16 +29942,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -30603,44 +30603,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="102" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="105"/>
-      <c r="O2" s="105"/>
-      <c r="P2" s="105"/>
-      <c r="Q2" s="105"/>
-      <c r="R2" s="105"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="102"/>
+      <c r="O2" s="102"/>
+      <c r="P2" s="102"/>
+      <c r="Q2" s="102"/>
+      <c r="R2" s="102"/>
     </row>
     <row r="3" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="105"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="105"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="105"/>
-      <c r="M3" s="105"/>
-      <c r="N3" s="105"/>
-      <c r="O3" s="105"/>
-      <c r="P3" s="105"/>
-      <c r="Q3" s="105"/>
-      <c r="R3" s="105"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="102"/>
     </row>
     <row r="4" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
@@ -30650,141 +30650,141 @@
         <f>Calculos!$B$2</f>
         <v>Enero</v>
       </c>
-      <c r="F4" s="106" t="s">
+      <c r="F4" s="103" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="106"/>
-      <c r="K4" s="106"/>
-      <c r="L4" s="106"/>
-      <c r="M4" s="106"/>
-      <c r="N4" s="106"/>
-      <c r="O4" s="106"/>
-      <c r="P4" s="106"/>
-      <c r="Q4" s="106"/>
-      <c r="R4" s="106"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="103"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="103"/>
+      <c r="R4" s="103"/>
     </row>
     <row r="6" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="107" t="s">
+      <c r="B6" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="107" t="s">
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="107"/>
-      <c r="H6" s="107"/>
-      <c r="I6" s="107"/>
-      <c r="J6" s="107" t="s">
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="107"/>
-      <c r="L6" s="107"/>
-      <c r="M6" s="107" t="s">
+      <c r="K6" s="104"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="N6" s="107"/>
-      <c r="O6" s="107"/>
-      <c r="P6" s="107" t="s">
+      <c r="N6" s="104"/>
+      <c r="O6" s="104"/>
+      <c r="P6" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="Q6" s="107"/>
-      <c r="R6" s="107"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="104"/>
     </row>
     <row r="7" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="107"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="107"/>
-      <c r="F7" s="107"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="107"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="107"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="107"/>
-      <c r="M7" s="107"/>
-      <c r="N7" s="107"/>
-      <c r="O7" s="107"/>
-      <c r="P7" s="107"/>
-      <c r="Q7" s="107"/>
-      <c r="R7" s="107"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="104"/>
+      <c r="L7" s="104"/>
+      <c r="M7" s="104"/>
+      <c r="N7" s="104"/>
+      <c r="O7" s="104"/>
+      <c r="P7" s="104"/>
+      <c r="Q7" s="104"/>
+      <c r="R7" s="104"/>
     </row>
     <row r="8" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="100">
+      <c r="B8" s="105">
         <f ca="1">Calculos!B44</f>
         <v>0.93030769230769228</v>
       </c>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="101" t="str">
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="106" t="str">
         <f ca="1">Calculos!B45</f>
         <v>Verde</v>
       </c>
-      <c r="G8" s="101"/>
-      <c r="H8" s="101"/>
-      <c r="I8" s="101"/>
-      <c r="J8" s="102">
+      <c r="G8" s="106"/>
+      <c r="H8" s="106"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="107">
         <f ca="1">Calculos!B40</f>
         <v>0</v>
       </c>
-      <c r="K8" s="102"/>
-      <c r="L8" s="102"/>
-      <c r="M8" s="103">
+      <c r="K8" s="107"/>
+      <c r="L8" s="107"/>
+      <c r="M8" s="100">
         <f ca="1">Calculos!B41</f>
         <v>0</v>
       </c>
-      <c r="N8" s="103"/>
-      <c r="O8" s="103"/>
-      <c r="P8" s="104">
+      <c r="N8" s="100"/>
+      <c r="O8" s="100"/>
+      <c r="P8" s="101">
         <f ca="1">Calculos!B42</f>
         <v>15</v>
       </c>
-      <c r="Q8" s="104"/>
-      <c r="R8" s="104"/>
+      <c r="Q8" s="101"/>
+      <c r="R8" s="101"/>
     </row>
     <row r="9" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="100"/>
-      <c r="C9" s="100"/>
-      <c r="D9" s="100"/>
-      <c r="E9" s="100"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="101"/>
-      <c r="J9" s="102"/>
-      <c r="K9" s="102"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="103"/>
-      <c r="N9" s="103"/>
-      <c r="O9" s="103"/>
-      <c r="P9" s="104"/>
-      <c r="Q9" s="104"/>
-      <c r="R9" s="104"/>
+      <c r="B9" s="105"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="106"/>
+      <c r="I9" s="106"/>
+      <c r="J9" s="107"/>
+      <c r="K9" s="107"/>
+      <c r="L9" s="107"/>
+      <c r="M9" s="100"/>
+      <c r="N9" s="100"/>
+      <c r="O9" s="100"/>
+      <c r="P9" s="101"/>
+      <c r="Q9" s="101"/>
+      <c r="R9" s="101"/>
     </row>
     <row r="10" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="100"/>
-      <c r="C10" s="100"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="101"/>
-      <c r="H10" s="101"/>
-      <c r="I10" s="101"/>
-      <c r="J10" s="102"/>
-      <c r="K10" s="102"/>
-      <c r="L10" s="102"/>
-      <c r="M10" s="103"/>
-      <c r="N10" s="103"/>
-      <c r="O10" s="103"/>
-      <c r="P10" s="104"/>
-      <c r="Q10" s="104"/>
-      <c r="R10" s="104"/>
+      <c r="B10" s="105"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="106"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="106"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="107"/>
+      <c r="K10" s="107"/>
+      <c r="L10" s="107"/>
+      <c r="M10" s="100"/>
+      <c r="N10" s="100"/>
+      <c r="O10" s="100"/>
+      <c r="P10" s="101"/>
+      <c r="Q10" s="101"/>
+      <c r="R10" s="101"/>
     </row>
     <row r="12" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="99" t="s">
@@ -31047,6 +31047,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B8:E10"/>
+    <mergeCell ref="F8:I10"/>
+    <mergeCell ref="J8:L10"/>
     <mergeCell ref="M8:O10"/>
     <mergeCell ref="P8:R10"/>
     <mergeCell ref="B2:R3"/>
@@ -31056,11 +31061,6 @@
     <mergeCell ref="J6:L7"/>
     <mergeCell ref="M6:O7"/>
     <mergeCell ref="P6:R7"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B8:E10"/>
-    <mergeCell ref="F8:I10"/>
-    <mergeCell ref="J8:L10"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -31090,13 +31090,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="99" t="s">
@@ -31688,48 +31688,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="85" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="91"/>
-      <c r="AB1" s="91"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
       <c r="AR1" s="42"/>
-      <c r="AS1" s="92" t="s">
+      <c r="AS1" s="86" t="s">
         <v>145</v>
       </c>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="92"/>
-      <c r="BA1" s="92"/>
+      <c r="AT1" s="86"/>
+      <c r="AU1" s="86"/>
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="86"/>
+      <c r="AY1" s="86"/>
+      <c r="AZ1" s="86"/>
+      <c r="BA1" s="86"/>
       <c r="BB1" s="42"/>
       <c r="BC1" s="42"/>
     </row>
@@ -31737,11 +31737,11 @@
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="87" t="s">
         <v>147</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="F2" s="5" t="s">
         <v>148</v>
       </c>
@@ -31750,20 +31750,20 @@
       </c>
       <c r="AR2" s="42"/>
       <c r="AS2" s="44"/>
-      <c r="AT2" s="94" t="s">
+      <c r="AT2" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="AU2" s="94"/>
-      <c r="AV2" s="94"/>
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="88"/>
       <c r="AW2" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="AX2" s="95" t="s">
+      <c r="AX2" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="AY2" s="95"/>
-      <c r="AZ2" s="95"/>
-      <c r="BA2" s="95"/>
+      <c r="AY2" s="89"/>
+      <c r="AZ2" s="89"/>
+      <c r="BA2" s="89"/>
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
@@ -31803,66 +31803,66 @@
       <c r="A4" s="51"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88" t="s">
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88" t="s">
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88" t="s">
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88" t="s">
+      <c r="P4" s="93"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88" t="s">
+      <c r="S4" s="93"/>
+      <c r="T4" s="93"/>
+      <c r="U4" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="V4" s="88"/>
-      <c r="W4" s="89" t="s">
+      <c r="V4" s="93"/>
+      <c r="W4" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="88" t="s">
+      <c r="X4" s="94"/>
+      <c r="Y4" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
-      <c r="AB4" s="88"/>
-      <c r="AC4" s="88"/>
-      <c r="AD4" s="89" t="s">
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
+      <c r="AB4" s="93"/>
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="90" t="s">
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="95" t="s">
         <v>170</v>
       </c>
-      <c r="AQ4" s="90"/>
+      <c r="AQ4" s="95"/>
       <c r="AR4" s="42"/>
       <c r="AS4" s="52" t="str">
         <f>'Captura Enero'!B6</f>
@@ -34638,16 +34638,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="42"/>
-      <c r="AS19" s="85" t="s">
+      <c r="AS19" s="90" t="s">
         <v>202</v>
       </c>
-      <c r="AT19" s="85"/>
-      <c r="AU19" s="85"/>
-      <c r="AV19" s="85"/>
-      <c r="AW19" s="85"/>
-      <c r="AX19" s="85"/>
-      <c r="AY19" s="85"/>
-      <c r="AZ19" s="85"/>
+      <c r="AT19" s="90"/>
+      <c r="AU19" s="90"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="90"/>
+      <c r="AY19" s="90"/>
+      <c r="AZ19" s="90"/>
       <c r="BA19" s="71">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93030769230769228</v>
@@ -34819,9 +34819,9 @@
       </c>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
       <c r="F22" s="51"/>
@@ -34848,11 +34848,11 @@
       <c r="AV22" s="72"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="73"/>
       <c r="E23" s="73"/>
       <c r="F23" s="73"/>
@@ -34910,11 +34910,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
@@ -34928,6 +34923,11 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="110" priority="5" operator="greaterThanOrEqual">
@@ -35007,48 +35007,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="85" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="91"/>
-      <c r="AB1" s="91"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
       <c r="AR1" s="42"/>
-      <c r="AS1" s="92" t="s">
+      <c r="AS1" s="86" t="s">
         <v>205</v>
       </c>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="92"/>
-      <c r="BA1" s="92"/>
+      <c r="AT1" s="86"/>
+      <c r="AU1" s="86"/>
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="86"/>
+      <c r="AY1" s="86"/>
+      <c r="AZ1" s="86"/>
+      <c r="BA1" s="86"/>
       <c r="BB1" s="42"/>
       <c r="BC1" s="42"/>
     </row>
@@ -35056,11 +35056,11 @@
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="87" t="s">
         <v>206</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="F2" s="5" t="s">
         <v>148</v>
       </c>
@@ -35069,20 +35069,20 @@
       </c>
       <c r="AR2" s="42"/>
       <c r="AS2" s="44"/>
-      <c r="AT2" s="94" t="s">
+      <c r="AT2" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="AU2" s="94"/>
-      <c r="AV2" s="94"/>
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="88"/>
       <c r="AW2" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="AX2" s="95" t="s">
+      <c r="AX2" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="AY2" s="95"/>
-      <c r="AZ2" s="95"/>
-      <c r="BA2" s="95"/>
+      <c r="AY2" s="89"/>
+      <c r="AZ2" s="89"/>
+      <c r="BA2" s="89"/>
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
@@ -35122,66 +35122,66 @@
       <c r="A4" s="51"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88" t="s">
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88" t="s">
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88" t="s">
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88" t="s">
+      <c r="P4" s="93"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88" t="s">
+      <c r="S4" s="93"/>
+      <c r="T4" s="93"/>
+      <c r="U4" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="V4" s="88"/>
-      <c r="W4" s="89" t="s">
+      <c r="V4" s="93"/>
+      <c r="W4" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="88" t="s">
+      <c r="X4" s="94"/>
+      <c r="Y4" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
-      <c r="AB4" s="88"/>
-      <c r="AC4" s="88"/>
-      <c r="AD4" s="89" t="s">
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
+      <c r="AB4" s="93"/>
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="90" t="s">
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="95" t="s">
         <v>170</v>
       </c>
-      <c r="AQ4" s="90"/>
+      <c r="AQ4" s="95"/>
       <c r="AR4" s="42"/>
       <c r="AS4" s="52" t="str">
         <f>'Captura Febrero'!B6</f>
@@ -37957,16 +37957,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="42"/>
-      <c r="AS19" s="85" t="s">
+      <c r="AS19" s="90" t="s">
         <v>207</v>
       </c>
-      <c r="AT19" s="85"/>
-      <c r="AU19" s="85"/>
-      <c r="AV19" s="85"/>
-      <c r="AW19" s="85"/>
-      <c r="AX19" s="85"/>
-      <c r="AY19" s="85"/>
-      <c r="AZ19" s="85"/>
+      <c r="AT19" s="90"/>
+      <c r="AU19" s="90"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="90"/>
+      <c r="AY19" s="90"/>
+      <c r="AZ19" s="90"/>
       <c r="BA19" s="71">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.91092643373138726</v>
@@ -38133,9 +38133,9 @@
       <c r="BB20" s="42"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
       <c r="F22" s="51"/>
@@ -38162,11 +38162,11 @@
       <c r="AV22" s="72"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="73"/>
       <c r="E23" s="73"/>
       <c r="F23" s="73"/>
@@ -38224,11 +38224,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
@@ -38242,6 +38237,11 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="101" priority="5" operator="greaterThanOrEqual">
@@ -38321,48 +38321,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="85" t="s">
         <v>208</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="91"/>
-      <c r="AB1" s="91"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
       <c r="AR1" s="42"/>
-      <c r="AS1" s="92" t="s">
+      <c r="AS1" s="86" t="s">
         <v>209</v>
       </c>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="92"/>
-      <c r="BA1" s="92"/>
+      <c r="AT1" s="86"/>
+      <c r="AU1" s="86"/>
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="86"/>
+      <c r="AY1" s="86"/>
+      <c r="AZ1" s="86"/>
+      <c r="BA1" s="86"/>
       <c r="BB1" s="42"/>
       <c r="BC1" s="42"/>
     </row>
@@ -38370,11 +38370,11 @@
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="87" t="s">
         <v>210</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="F2" s="5" t="s">
         <v>148</v>
       </c>
@@ -38383,20 +38383,20 @@
       </c>
       <c r="AR2" s="42"/>
       <c r="AS2" s="44"/>
-      <c r="AT2" s="94" t="s">
+      <c r="AT2" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="AU2" s="94"/>
-      <c r="AV2" s="94"/>
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="88"/>
       <c r="AW2" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="AX2" s="95" t="s">
+      <c r="AX2" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="AY2" s="95"/>
-      <c r="AZ2" s="95"/>
-      <c r="BA2" s="95"/>
+      <c r="AY2" s="89"/>
+      <c r="AZ2" s="89"/>
+      <c r="BA2" s="89"/>
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
@@ -38436,66 +38436,66 @@
       <c r="A4" s="51"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88" t="s">
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88" t="s">
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88" t="s">
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88" t="s">
+      <c r="P4" s="93"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88" t="s">
+      <c r="S4" s="93"/>
+      <c r="T4" s="93"/>
+      <c r="U4" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="V4" s="88"/>
-      <c r="W4" s="89" t="s">
+      <c r="V4" s="93"/>
+      <c r="W4" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="88" t="s">
+      <c r="X4" s="94"/>
+      <c r="Y4" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
-      <c r="AB4" s="88"/>
-      <c r="AC4" s="88"/>
-      <c r="AD4" s="89" t="s">
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
+      <c r="AB4" s="93"/>
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="90" t="s">
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="95" t="s">
         <v>170</v>
       </c>
-      <c r="AQ4" s="90"/>
+      <c r="AQ4" s="95"/>
       <c r="AR4" s="42"/>
       <c r="AS4" s="52" t="str">
         <f>'Captura Marzo'!B6</f>
@@ -41271,16 +41271,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="42"/>
-      <c r="AS19" s="85" t="s">
+      <c r="AS19" s="90" t="s">
         <v>211</v>
       </c>
-      <c r="AT19" s="85"/>
-      <c r="AU19" s="85"/>
-      <c r="AV19" s="85"/>
-      <c r="AW19" s="85"/>
-      <c r="AX19" s="85"/>
-      <c r="AY19" s="85"/>
-      <c r="AZ19" s="85"/>
+      <c r="AT19" s="90"/>
+      <c r="AU19" s="90"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="90"/>
+      <c r="AY19" s="90"/>
+      <c r="AZ19" s="90"/>
       <c r="BA19" s="71">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.99283333333333335</v>
@@ -41447,9 +41447,9 @@
       <c r="BB20" s="42"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
       <c r="F22" s="51"/>
@@ -41476,11 +41476,11 @@
       <c r="AV22" s="72"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="73"/>
       <c r="E23" s="73"/>
       <c r="F23" s="73"/>
@@ -41538,11 +41538,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
@@ -41556,6 +41551,11 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="92" priority="5" operator="greaterThanOrEqual">
@@ -41635,48 +41635,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="91"/>
-      <c r="AB1" s="91"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
       <c r="AR1" s="42"/>
-      <c r="AS1" s="92" t="s">
+      <c r="AS1" s="86" t="s">
         <v>213</v>
       </c>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="92"/>
-      <c r="BA1" s="92"/>
+      <c r="AT1" s="86"/>
+      <c r="AU1" s="86"/>
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="86"/>
+      <c r="AY1" s="86"/>
+      <c r="AZ1" s="86"/>
+      <c r="BA1" s="86"/>
       <c r="BB1" s="42"/>
       <c r="BC1" s="42"/>
     </row>
@@ -41684,11 +41684,11 @@
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="87" t="s">
         <v>214</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="F2" s="5" t="s">
         <v>148</v>
       </c>
@@ -41697,20 +41697,20 @@
       </c>
       <c r="AR2" s="42"/>
       <c r="AS2" s="44"/>
-      <c r="AT2" s="94" t="s">
+      <c r="AT2" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="AU2" s="94"/>
-      <c r="AV2" s="94"/>
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="88"/>
       <c r="AW2" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="AX2" s="95" t="s">
+      <c r="AX2" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="AY2" s="95"/>
-      <c r="AZ2" s="95"/>
-      <c r="BA2" s="95"/>
+      <c r="AY2" s="89"/>
+      <c r="AZ2" s="89"/>
+      <c r="BA2" s="89"/>
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
@@ -41750,66 +41750,66 @@
       <c r="A4" s="51"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88" t="s">
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88" t="s">
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88" t="s">
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88" t="s">
+      <c r="P4" s="93"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88" t="s">
+      <c r="S4" s="93"/>
+      <c r="T4" s="93"/>
+      <c r="U4" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="V4" s="88"/>
-      <c r="W4" s="89" t="s">
+      <c r="V4" s="93"/>
+      <c r="W4" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="88" t="s">
+      <c r="X4" s="94"/>
+      <c r="Y4" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
-      <c r="AB4" s="88"/>
-      <c r="AC4" s="88"/>
-      <c r="AD4" s="89" t="s">
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
+      <c r="AB4" s="93"/>
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="90" t="s">
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="95" t="s">
         <v>170</v>
       </c>
-      <c r="AQ4" s="90"/>
+      <c r="AQ4" s="95"/>
       <c r="AR4" s="42"/>
       <c r="AS4" s="52" t="str">
         <f>'Captura Abril'!B6</f>
@@ -44585,16 +44585,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="42"/>
-      <c r="AS19" s="85" t="s">
+      <c r="AS19" s="90" t="s">
         <v>215</v>
       </c>
-      <c r="AT19" s="85"/>
-      <c r="AU19" s="85"/>
-      <c r="AV19" s="85"/>
-      <c r="AW19" s="85"/>
-      <c r="AX19" s="85"/>
-      <c r="AY19" s="85"/>
-      <c r="AZ19" s="85"/>
+      <c r="AT19" s="90"/>
+      <c r="AU19" s="90"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="90"/>
+      <c r="AY19" s="90"/>
+      <c r="AZ19" s="90"/>
       <c r="BA19" s="71">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93466666666666676</v>
@@ -44761,9 +44761,9 @@
       <c r="BB20" s="42"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
       <c r="F22" s="51"/>
@@ -44790,11 +44790,11 @@
       <c r="AV22" s="72"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="73"/>
       <c r="E23" s="73"/>
       <c r="F23" s="73"/>
@@ -44852,11 +44852,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
@@ -44870,6 +44865,11 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="83" priority="5" operator="greaterThanOrEqual">
@@ -44949,48 +44949,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="85" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
-      <c r="Z1" s="91"/>
-      <c r="AA1" s="91"/>
-      <c r="AB1" s="91"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="85"/>
+      <c r="AA1" s="85"/>
+      <c r="AB1" s="85"/>
       <c r="AR1" s="42"/>
-      <c r="AS1" s="92" t="s">
+      <c r="AS1" s="86" t="s">
         <v>217</v>
       </c>
-      <c r="AT1" s="92"/>
-      <c r="AU1" s="92"/>
-      <c r="AV1" s="92"/>
-      <c r="AW1" s="92"/>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="92"/>
-      <c r="AZ1" s="92"/>
-      <c r="BA1" s="92"/>
+      <c r="AT1" s="86"/>
+      <c r="AU1" s="86"/>
+      <c r="AV1" s="86"/>
+      <c r="AW1" s="86"/>
+      <c r="AX1" s="86"/>
+      <c r="AY1" s="86"/>
+      <c r="AZ1" s="86"/>
+      <c r="BA1" s="86"/>
       <c r="BB1" s="42"/>
       <c r="BC1" s="42"/>
     </row>
@@ -44998,11 +44998,11 @@
       <c r="A2" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="87" t="s">
         <v>218</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
       <c r="F2" s="5" t="s">
         <v>148</v>
       </c>
@@ -45011,20 +45011,20 @@
       </c>
       <c r="AR2" s="42"/>
       <c r="AS2" s="44"/>
-      <c r="AT2" s="94" t="s">
+      <c r="AT2" s="88" t="s">
         <v>150</v>
       </c>
-      <c r="AU2" s="94"/>
-      <c r="AV2" s="94"/>
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="88"/>
       <c r="AW2" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="AX2" s="95" t="s">
+      <c r="AX2" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="AY2" s="95"/>
-      <c r="AZ2" s="95"/>
-      <c r="BA2" s="95"/>
+      <c r="AY2" s="89"/>
+      <c r="AZ2" s="89"/>
+      <c r="BA2" s="89"/>
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
@@ -45064,66 +45064,66 @@
       <c r="A4" s="51"/>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="93" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88" t="s">
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88" t="s">
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88" t="s">
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88" t="s">
+      <c r="P4" s="93"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="93" t="s">
         <v>165</v>
       </c>
-      <c r="S4" s="88"/>
-      <c r="T4" s="88"/>
-      <c r="U4" s="88" t="s">
+      <c r="S4" s="93"/>
+      <c r="T4" s="93"/>
+      <c r="U4" s="93" t="s">
         <v>166</v>
       </c>
-      <c r="V4" s="88"/>
-      <c r="W4" s="89" t="s">
+      <c r="V4" s="93"/>
+      <c r="W4" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="88" t="s">
+      <c r="X4" s="94"/>
+      <c r="Y4" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="Z4" s="88"/>
-      <c r="AA4" s="88"/>
-      <c r="AB4" s="88"/>
-      <c r="AC4" s="88"/>
-      <c r="AD4" s="89" t="s">
+      <c r="Z4" s="93"/>
+      <c r="AA4" s="93"/>
+      <c r="AB4" s="93"/>
+      <c r="AC4" s="93"/>
+      <c r="AD4" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="90" t="s">
+      <c r="AE4" s="94"/>
+      <c r="AF4" s="94"/>
+      <c r="AG4" s="94"/>
+      <c r="AH4" s="94"/>
+      <c r="AI4" s="94"/>
+      <c r="AJ4" s="94"/>
+      <c r="AK4" s="94"/>
+      <c r="AL4" s="94"/>
+      <c r="AM4" s="94"/>
+      <c r="AN4" s="94"/>
+      <c r="AO4" s="94"/>
+      <c r="AP4" s="95" t="s">
         <v>170</v>
       </c>
-      <c r="AQ4" s="90"/>
+      <c r="AQ4" s="95"/>
       <c r="AR4" s="42"/>
       <c r="AS4" s="52" t="str">
         <f>'Captura Mayo'!B6</f>
@@ -47899,16 +47899,16 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="AR19" s="42"/>
-      <c r="AS19" s="85" t="s">
+      <c r="AS19" s="90" t="s">
         <v>219</v>
       </c>
-      <c r="AT19" s="85"/>
-      <c r="AU19" s="85"/>
-      <c r="AV19" s="85"/>
-      <c r="AW19" s="85"/>
-      <c r="AX19" s="85"/>
-      <c r="AY19" s="85"/>
-      <c r="AZ19" s="85"/>
+      <c r="AT19" s="90"/>
+      <c r="AU19" s="90"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="90"/>
+      <c r="AY19" s="90"/>
+      <c r="AZ19" s="90"/>
       <c r="BA19" s="71">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.87666666666666671</v>
@@ -48075,9 +48075,9 @@
       <c r="BB20" s="42"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="86"/>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
       <c r="F22" s="51"/>
@@ -48104,11 +48104,11 @@
       <c r="AV22" s="72"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="73"/>
       <c r="E23" s="73"/>
       <c r="F23" s="73"/>
@@ -48166,11 +48166,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
@@ -48184,6 +48179,11 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="74" priority="5" operator="greaterThanOrEqual">
@@ -48244,26 +48244,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003E33BA48D1B17740BD20DC3C1E7D6897" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c5918174441eb6b55e4531b53824222f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbb49d05-d3df-47ef-b263-f54790ad9dd3" xmlns:ns3="4bae7dba-0f75-4d38-a352-dd7a188b5c30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9432285c6019c8f9bf7f2f5b0ebbd793" ns2:_="" ns3:_="">
     <xsd:import namespace="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
@@ -48510,13 +48490,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE74165-F1C6-4E67-B303-57398CFB5869}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F98439B8-0535-46FB-9AA1-827C12A2EA64}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
     <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -48530,5 +48538,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F98439B8-0535-46FB-9AA1-827C12A2EA64}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE74165-F1C6-4E67-B303-57398CFB5869}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
+    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
+++ b/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc.sharepoint.com/sites/CharlascortasSSOsemanalesCuyotenango/Shared Documents/General/04. Registros 2026/09. Nivel De Seguridad/NUEVO NIVEL DE SEGURIDAD - 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{B31B9B4D-0810-47E6-ACB2-FA5D1859CF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27FE309F-596F-46A3-BEDE-089DF08A5ABE}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{B31B9B4D-0810-47E6-ACB2-FA5D1859CF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED49828E-5BEA-4C4E-8CA1-598BAA16749C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
     <sheet name="ACUMULADO - 2026" sheetId="19" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'ACUMULADO - 2026'!$A$3:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'ACUMULADO - 2026'!$A$3:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Dashboard Ejecutivo'!$A$1:$Y$75</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -3771,7 +3771,7 @@
                   <c:v>0.93030769230769228</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.91092643373138726</c:v>
+                  <c:v>0.9572597670647206</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.99283333333333335</c:v>
@@ -3789,7 +3789,7 @@
                   <c:v>0.88027777777777783</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.43205333333333323</c:v>
+                  <c:v>0.45861333333333326</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="C13" s="4">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4500,7 +4500,7 @@
     <mergeCell ref="C20:E20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4603,7 +4603,7 @@
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
-    <row r="3" spans="1:55" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:55" ht="5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AR3" s="42"/>
       <c r="AS3" s="46" t="s">
         <v>152</v>
@@ -7814,7 +7814,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup scale="25" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11130,7 +11130,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup scale="24" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11233,7 +11233,7 @@
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
-    <row r="3" spans="1:55" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:55" ht="2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AR3" s="42"/>
       <c r="AS3" s="46" t="s">
         <v>152</v>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="AT6" s="53">
         <f>'Captura Agosto'!K8+'Captura Agosto'!N8+'Captura Agosto'!Q8</f>
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AU6" s="53">
         <f>'Captura Agosto'!T8</f>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="BA6" s="55">
         <f>'Captura Agosto'!AQ8</f>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="BB6" s="42"/>
       <c r="BC6" s="42"/>
@@ -11946,14 +11946,14 @@
         <v>0.08</v>
       </c>
       <c r="L8" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="68" t="s">
         <v>200</v>
       </c>
       <c r="N8" s="66">
         <f>IF(M8="NO",0,L8*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O8" s="65">
         <v>0</v>
@@ -12047,11 +12047,11 @@
       </c>
       <c r="AP8" s="11">
         <f t="shared" si="3"/>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="AQ8" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP8-IF(S8="NO",Parametros!$E$17,0))+AC8)-AN8-IF(AO8="SI",Parametros!$E$33,0))</f>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="AR8" s="42"/>
       <c r="AS8" s="52" t="str">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="AT8" s="53">
         <f>'Captura Agosto'!K10+'Captura Agosto'!N10+'Captura Agosto'!Q10</f>
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AU8" s="53">
         <f>'Captura Agosto'!T10</f>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="BA8" s="55">
         <f>'Captura Agosto'!AQ10</f>
-        <v>0.41000000000000003</v>
+        <v>0.49000000000000005</v>
       </c>
       <c r="BB8" s="42"/>
       <c r="BC8" s="42"/>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="AT9" s="60">
         <f>'Captura Agosto'!K11+'Captura Agosto'!N11+'Captura Agosto'!Q11</f>
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AU9" s="60">
         <f>'Captura Agosto'!T11</f>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="BA9" s="62">
         <f>'Captura Agosto'!AQ11</f>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="BB9" s="42"/>
       <c r="BC9" s="42"/>
@@ -12314,14 +12314,14 @@
         <v>0.08</v>
       </c>
       <c r="L10" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="68" t="s">
         <v>200</v>
       </c>
       <c r="N10" s="66">
         <f>IF(M10="NO",0,L10*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O10" s="65">
         <v>0</v>
@@ -12415,11 +12415,11 @@
       </c>
       <c r="AP10" s="11">
         <f t="shared" si="3"/>
-        <v>0.41000000000000003</v>
+        <v>0.49000000000000005</v>
       </c>
       <c r="AQ10" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP10-IF(S10="NO",Parametros!$E$17,0))+AC10)-AN10-IF(AO10="SI",Parametros!$E$33,0))</f>
-        <v>0.41000000000000003</v>
+        <v>0.49000000000000005</v>
       </c>
       <c r="AR10" s="42"/>
       <c r="AS10" s="52" t="str">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="AT10" s="53">
         <f>'Captura Agosto'!K12+'Captura Agosto'!N12+'Captura Agosto'!Q12</f>
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AU10" s="53">
         <f>'Captura Agosto'!T12</f>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="BA10" s="55">
         <f>'Captura Agosto'!AQ12</f>
-        <v>0.42000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="BB10" s="42"/>
       <c r="BC10" s="42"/>
@@ -12500,14 +12500,14 @@
         <v>0.08</v>
       </c>
       <c r="L11" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="68" t="s">
         <v>200</v>
       </c>
       <c r="N11" s="66">
         <f>IF(M11="NO",0,L11*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O11" s="65">
         <v>0</v>
@@ -12601,11 +12601,11 @@
       </c>
       <c r="AP11" s="11">
         <f t="shared" si="3"/>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="AQ11" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP11-IF(S11="NO",Parametros!$E$17,0))+AC11)-AN11-IF(AO11="SI",Parametros!$E$33,0))</f>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="AR11" s="42"/>
       <c r="AS11" s="59" t="str">
@@ -12638,11 +12638,11 @@
       </c>
       <c r="AZ11" s="61">
         <f>-'Captura Agosto'!AN13</f>
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="BA11" s="62">
         <f>'Captura Agosto'!AQ13</f>
-        <v>0.49419999999999997</v>
+        <v>0.39419999999999999</v>
       </c>
       <c r="BB11" s="42"/>
       <c r="BC11" s="42"/>
@@ -12686,14 +12686,14 @@
         <v>0.08</v>
       </c>
       <c r="L12" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="68" t="s">
         <v>200</v>
       </c>
       <c r="N12" s="66">
         <f>IF(M12="NO",0,L12*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O12" s="65">
         <v>0</v>
@@ -12787,11 +12787,11 @@
       </c>
       <c r="AP12" s="11">
         <f t="shared" si="3"/>
-        <v>0.42000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="AQ12" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP12-IF(S12="NO",Parametros!$E$17,0))+AC12)-AN12-IF(AO12="SI",Parametros!$E$33,0))</f>
-        <v>0.42000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="AR12" s="42"/>
       <c r="AS12" s="52" t="str">
@@ -12940,7 +12940,7 @@
         <v>200</v>
       </c>
       <c r="AF13" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" s="68" t="s">
         <v>200</v>
@@ -12965,7 +12965,7 @@
       </c>
       <c r="AN13" s="69">
         <f>AD13*Parametros!$E$28+AF13*Parametros!$E$29+AH13*Parametros!$E$30+AJ13*Parametros!$E$31+AL13*Parametros!$E$32</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AO13" s="12" t="str">
         <f t="shared" si="2"/>
@@ -12977,7 +12977,7 @@
       </c>
       <c r="AQ13" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP13-IF(S13="NO",Parametros!$E$17,0))+AC13)-AN13-IF(AO13="SI",Parametros!$E$33,0))</f>
-        <v>0.49419999999999997</v>
+        <v>0.39419999999999999</v>
       </c>
       <c r="AR13" s="42"/>
       <c r="AS13" s="59" t="str">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="AT13" s="60">
         <f>'Captura Agosto'!K15+'Captura Agosto'!N15+'Captura Agosto'!Q15</f>
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AU13" s="60">
         <f>'Captura Agosto'!T15</f>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="BA13" s="62">
         <f>'Captura Agosto'!AQ15</f>
-        <v>0.38200000000000001</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="BB13" s="42"/>
       <c r="BC13" s="42"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="AT14" s="53">
         <f>'Captura Agosto'!K16+'Captura Agosto'!N16+'Captura Agosto'!Q16</f>
-        <v>0.08</v>
+        <v>0.15839999999999999</v>
       </c>
       <c r="AU14" s="53">
         <f>'Captura Agosto'!T16</f>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="BA14" s="55">
         <f>'Captura Agosto'!AQ16</f>
-        <v>0.43</v>
+        <v>0.50839999999999996</v>
       </c>
       <c r="BB14" s="42"/>
       <c r="BC14" s="42"/>
@@ -13244,14 +13244,14 @@
         <v>0.08</v>
       </c>
       <c r="L15" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="68" t="s">
         <v>200</v>
       </c>
       <c r="N15" s="66">
         <f>IF(M15="NO",0,L15*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O15" s="65">
         <v>0</v>
@@ -13345,11 +13345,11 @@
       </c>
       <c r="AP15" s="11">
         <f t="shared" si="3"/>
-        <v>0.38200000000000001</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="AQ15" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP15-IF(S15="NO",Parametros!$E$17,0))+AC15)-AN15-IF(AO15="SI",Parametros!$E$33,0))</f>
-        <v>0.38200000000000001</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="AR15" s="42"/>
       <c r="AS15" s="59" t="str">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AT15" s="60">
         <f>'Captura Agosto'!K17+'Captura Agosto'!N17+'Captura Agosto'!Q17</f>
-        <v>0.08</v>
+        <v>0.14960000000000001</v>
       </c>
       <c r="AU15" s="60">
         <f>'Captura Agosto'!T17</f>
@@ -13382,11 +13382,11 @@
       </c>
       <c r="AZ15" s="61">
         <f>-'Captura Agosto'!AN17</f>
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="BA15" s="62">
         <f>'Captura Agosto'!AQ17</f>
-        <v>0.42200000000000004</v>
+        <v>0.39160000000000006</v>
       </c>
       <c r="BB15" s="42"/>
       <c r="BC15" s="42"/>
@@ -13430,14 +13430,14 @@
         <v>0.08</v>
       </c>
       <c r="L16" s="65">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="M16" s="68" t="s">
         <v>200</v>
       </c>
       <c r="N16" s="66">
         <f>IF(M16="NO",0,L16*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>7.8399999999999997E-2</v>
       </c>
       <c r="O16" s="65">
         <v>0</v>
@@ -13531,11 +13531,11 @@
       </c>
       <c r="AP16" s="11">
         <f t="shared" si="3"/>
-        <v>0.43</v>
+        <v>0.50839999999999996</v>
       </c>
       <c r="AQ16" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP16-IF(S16="NO",Parametros!$E$17,0))+AC16)-AN16-IF(AO16="SI",Parametros!$E$33,0))</f>
-        <v>0.43</v>
+        <v>0.50839999999999996</v>
       </c>
       <c r="AR16" s="42"/>
       <c r="AS16" s="52" t="str">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="AT16" s="53">
         <f>'Captura Agosto'!K18+'Captura Agosto'!N18+'Captura Agosto'!Q18</f>
-        <v>0.08</v>
+        <v>0.15040000000000001</v>
       </c>
       <c r="AU16" s="53">
         <f>'Captura Agosto'!T18</f>
@@ -13568,11 +13568,11 @@
       </c>
       <c r="AZ16" s="54">
         <f>-'Captura Agosto'!AN18</f>
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="BA16" s="55">
         <f>'Captura Agosto'!AQ18</f>
-        <v>0.41700000000000004</v>
+        <v>0.38739999999999997</v>
       </c>
       <c r="BB16" s="42"/>
       <c r="BC16" s="42"/>
@@ -13616,14 +13616,14 @@
         <v>0.08</v>
       </c>
       <c r="L17" s="65">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="M17" s="68" t="s">
         <v>200</v>
       </c>
       <c r="N17" s="66">
         <f>IF(M17="NO",0,L17*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>6.9599999999999995E-2</v>
       </c>
       <c r="O17" s="65">
         <v>0</v>
@@ -13684,7 +13684,7 @@
         <v>200</v>
       </c>
       <c r="AF17" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" s="68" t="s">
         <v>200</v>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="AN17" s="69">
         <f>AD17*Parametros!$E$28+AF17*Parametros!$E$29+AH17*Parametros!$E$30+AJ17*Parametros!$E$31+AL17*Parametros!$E$32</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AO17" s="12" t="str">
         <f t="shared" si="2"/>
@@ -13717,11 +13717,11 @@
       </c>
       <c r="AP17" s="11">
         <f t="shared" si="3"/>
-        <v>0.42200000000000004</v>
+        <v>0.49160000000000004</v>
       </c>
       <c r="AQ17" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP17-IF(S17="NO",Parametros!$E$17,0))+AC17)-AN17-IF(AO17="SI",Parametros!$E$33,0))</f>
-        <v>0.42200000000000004</v>
+        <v>0.39160000000000006</v>
       </c>
       <c r="AR17" s="42"/>
       <c r="AS17" s="59" t="str">
@@ -13802,14 +13802,14 @@
         <v>0.08</v>
       </c>
       <c r="L18" s="65">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="M18" s="68" t="s">
         <v>200</v>
       </c>
       <c r="N18" s="66">
         <f>IF(M18="NO",0,L18*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>7.0400000000000004E-2</v>
       </c>
       <c r="O18" s="65">
         <v>0</v>
@@ -13870,7 +13870,7 @@
         <v>200</v>
       </c>
       <c r="AF18" s="67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" s="68" t="s">
         <v>200</v>
@@ -13895,7 +13895,7 @@
       </c>
       <c r="AN18" s="69">
         <f>AD18*Parametros!$E$28+AF18*Parametros!$E$29+AH18*Parametros!$E$30+AJ18*Parametros!$E$31+AL18*Parametros!$E$32</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AO18" s="12" t="str">
         <f t="shared" si="2"/>
@@ -13903,11 +13903,11 @@
       </c>
       <c r="AP18" s="11">
         <f t="shared" si="3"/>
-        <v>0.41700000000000004</v>
+        <v>0.4874</v>
       </c>
       <c r="AQ18" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP18-IF(S18="NO",Parametros!$E$17,0))+AC18)-AN18-IF(AO18="SI",Parametros!$E$33,0))</f>
-        <v>0.41700000000000004</v>
+        <v>0.38739999999999997</v>
       </c>
       <c r="AR18" s="42"/>
       <c r="AS18" s="52" t="str">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="AT18" s="53">
         <f>'Captura Agosto'!K20+'Captura Agosto'!N20+'Captura Agosto'!Q20</f>
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AU18" s="53">
         <f>'Captura Agosto'!T20</f>
@@ -13944,7 +13944,7 @@
       </c>
       <c r="BA18" s="55">
         <f>'Captura Agosto'!AQ20</f>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="BB18" s="42"/>
       <c r="BC18" s="42"/>
@@ -14108,7 +14108,7 @@
       <c r="AZ19" s="90"/>
       <c r="BA19" s="71">
         <f>AVERAGE(BA4:BA18)</f>
-        <v>0.43205333333333323</v>
+        <v>0.45861333333333326</v>
       </c>
       <c r="BB19" s="42"/>
       <c r="BC19" s="42"/>
@@ -14152,14 +14152,14 @@
         <v>0.08</v>
       </c>
       <c r="L20" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="68" t="s">
         <v>200</v>
       </c>
       <c r="N20" s="66">
         <f>IF(M20="NO",0,L20*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O20" s="65">
         <v>0</v>
@@ -14253,11 +14253,11 @@
       </c>
       <c r="AP20" s="11">
         <f t="shared" si="3"/>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="AQ20" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP20-IF(S20="NO",Parametros!$E$17,0))+AC20)-AN20-IF(AO20="SI",Parametros!$E$33,0))</f>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="AR20" s="42"/>
       <c r="AS20" s="42"/>
@@ -14347,7 +14347,7 @@
       <c r="AP23" s="73"/>
       <c r="AQ23" s="74">
         <f>AVERAGE(AQ6:AQ20)</f>
-        <v>0.43205333333333323</v>
+        <v>0.45861333333333326</v>
       </c>
       <c r="AR23" s="42"/>
       <c r="AS23" s="42"/>
@@ -14394,12 +14394,12 @@
       <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV6:AV20">
+  <conditionalFormatting sqref="AV19:AV20">
     <cfRule type="cellIs" dxfId="44" priority="2" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="expression" dxfId="43" priority="3">
-      <formula>AND(AV6&gt;=0.7,AV6&lt;0.9)</formula>
+      <formula>AND(AV19&gt;=0.7,AV19&lt;0.9)</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="42" priority="4" operator="lessThan">
       <formula>0.7</formula>
@@ -14436,7 +14436,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup scale="25" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -17750,7 +17750,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -21064,7 +21064,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -24378,7 +24378,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -27692,7 +27692,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -27756,7 +27756,7 @@
       </c>
       <c r="B7" s="76">
         <f>IF(AVERAGE('Captura Febrero'!D6:D20)=0,"",'Captura Febrero'!AQ23)</f>
-        <v>0.91092643373138726</v>
+        <v>0.9572597670647206</v>
       </c>
       <c r="C7" s="12" t="str">
         <f>IF(B7="","",IF(B7&gt;=Parametros!$C$37,"Verde",IF(B7&gt;=Parametros!$C$38,"Amarillo","Rojo")))</f>
@@ -27834,7 +27834,7 @@
       </c>
       <c r="B13" s="76">
         <f>IF(AVERAGE('Captura Agosto'!D6:D20)=0,"",'Captura Agosto'!AQ23)</f>
-        <v>0.43205333333333323</v>
+        <v>0.45861333333333326</v>
       </c>
       <c r="C13" s="12" t="str">
         <f>IF(B13="","",IF(B13&gt;=Parametros!$C$37,"Verde",IF(B13&gt;=Parametros!$C$38,"Amarillo","Rojo")))</f>
@@ -27913,8 +27913,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -28003,7 +28003,7 @@
       </c>
       <c r="C4" s="10">
         <f>IFERROR(IF('Captura Febrero'!D8=0,"",'Captura Febrero'!AQ8),"")</f>
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="D4" s="10">
         <f>IFERROR(IF('Captura Marzo'!D8=0,"",'Captura Marzo'!AQ8),"")</f>
@@ -28027,7 +28027,7 @@
       </c>
       <c r="I4" s="10">
         <f>IFERROR(IF('Captura Agosto'!D8=0,"",'Captura Agosto'!AQ8),"")</f>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="J4" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
@@ -28047,7 +28047,7 @@
       </c>
       <c r="N4" s="81">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.90749999999999997</v>
+        <v>0.93874999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="C5" s="10">
         <f>IFERROR(IF('Captura Febrero'!D6=0,"",'Captura Febrero'!AQ6),"")</f>
-        <v>0.75000000000000011</v>
+        <v>1</v>
       </c>
       <c r="D5" s="10">
         <f>IFERROR(IF('Captura Marzo'!D6=0,"",'Captura Marzo'!AQ6),"")</f>
@@ -28104,7 +28104,7 @@
       </c>
       <c r="N5" s="81">
         <f t="shared" si="0"/>
-        <v>0.86749999999999994</v>
+        <v>0.89874999999999994</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28117,7 +28117,7 @@
       </c>
       <c r="C6" s="10">
         <f>IFERROR(IF('Captura Febrero'!D16=0,"",'Captura Febrero'!AQ16),"")</f>
-        <v>0.66428571428571437</v>
+        <v>0.91428571428571437</v>
       </c>
       <c r="D6" s="10">
         <f>IFERROR(IF('Captura Marzo'!D16=0,"",'Captura Marzo'!AQ16),"")</f>
@@ -28141,7 +28141,7 @@
       </c>
       <c r="I6" s="10">
         <f>IFERROR(IF('Captura Agosto'!D16=0,"",'Captura Agosto'!AQ16),"")</f>
-        <v>0.43</v>
+        <v>0.50839999999999996</v>
       </c>
       <c r="J6" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="N6" s="81">
         <f t="shared" si="0"/>
-        <v>0.86928571428571422</v>
+        <v>0.91033571428571425</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28198,7 +28198,7 @@
       </c>
       <c r="I7" s="10">
         <f>IFERROR(IF('Captura Agosto'!D17=0,"",'Captura Agosto'!AQ17),"")</f>
-        <v>0.42200000000000004</v>
+        <v>0.39160000000000006</v>
       </c>
       <c r="J7" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
@@ -28218,7 +28218,7 @@
       </c>
       <c r="N7" s="81">
         <f t="shared" si="0"/>
-        <v>0.81296978021978017</v>
+        <v>0.80916978021978025</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28288,7 +28288,7 @@
       </c>
       <c r="C9" s="10">
         <f>IFERROR(IF('Captura Febrero'!D11=0,"",'Captura Febrero'!AQ11),"")</f>
-        <v>0.97500000000000009</v>
+        <v>1</v>
       </c>
       <c r="D9" s="10">
         <f>IFERROR(IF('Captura Marzo'!D11=0,"",'Captura Marzo'!AQ11),"")</f>
@@ -28312,7 +28312,7 @@
       </c>
       <c r="I9" s="10">
         <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="J9" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
@@ -28332,7 +28332,7 @@
       </c>
       <c r="N9" s="81">
         <f t="shared" si="0"/>
-        <v>0.87624999999999997</v>
+        <v>0.88937500000000003</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28369,7 +28369,7 @@
       </c>
       <c r="I10" s="10">
         <f>IFERROR(IF('Captura Agosto'!D13=0,"",'Captura Agosto'!AQ13),"")</f>
-        <v>0.49419999999999997</v>
+        <v>0.39419999999999999</v>
       </c>
       <c r="J10" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
@@ -28389,7 +28389,7 @@
       </c>
       <c r="N10" s="81">
         <f t="shared" si="0"/>
-        <v>0.78552499999999992</v>
+        <v>0.77302499999999985</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="I11" s="10">
         <f>IFERROR(IF('Captura Agosto'!D10=0,"",'Captura Agosto'!AQ10),"")</f>
-        <v>0.41000000000000003</v>
+        <v>0.49000000000000005</v>
       </c>
       <c r="J11" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
@@ -28446,7 +28446,7 @@
       </c>
       <c r="N11" s="81">
         <f t="shared" si="0"/>
-        <v>0.88312500000000005</v>
+        <v>0.89312500000000006</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28540,7 +28540,7 @@
       </c>
       <c r="I13" s="10">
         <f>IFERROR(IF('Captura Agosto'!D12=0,"",'Captura Agosto'!AQ12),"")</f>
-        <v>0.42000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="J13" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
@@ -28560,7 +28560,7 @@
       </c>
       <c r="N13" s="81">
         <f t="shared" si="0"/>
-        <v>0.79516304347826094</v>
+        <v>0.80516304347826095</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28597,7 +28597,7 @@
       </c>
       <c r="I14" s="10">
         <f>IFERROR(IF('Captura Agosto'!D15=0,"",'Captura Agosto'!AQ15),"")</f>
-        <v>0.38200000000000001</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="J14" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
@@ -28617,7 +28617,7 @@
       </c>
       <c r="N14" s="81">
         <f t="shared" si="0"/>
-        <v>0.79514766081871346</v>
+        <v>0.80514766081871347</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28711,7 +28711,7 @@
       </c>
       <c r="I16" s="10">
         <f>IFERROR(IF('Captura Agosto'!D20=0,"",'Captura Agosto'!AQ20),"")</f>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="J16" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
@@ -28731,7 +28731,7 @@
       </c>
       <c r="N16" s="81">
         <f t="shared" si="0"/>
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28768,7 +28768,7 @@
       </c>
       <c r="I17" s="10">
         <f>IFERROR(IF('Captura Agosto'!D18=0,"",'Captura Agosto'!AQ18),"")</f>
-        <v>0.41700000000000004</v>
+        <v>0.38739999999999997</v>
       </c>
       <c r="J17" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
@@ -28788,7 +28788,7 @@
       </c>
       <c r="N17" s="81">
         <f t="shared" si="0"/>
-        <v>0.869281862745098</v>
+        <v>0.86558186274509796</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28858,7 +28858,7 @@
       </c>
       <c r="C19" s="83">
         <f t="shared" si="1"/>
-        <v>0.91092643373138726</v>
+        <v>0.95725976706472082</v>
       </c>
       <c r="D19" s="83">
         <f t="shared" si="1"/>
@@ -28882,7 +28882,7 @@
       </c>
       <c r="I19" s="83">
         <f t="shared" si="1"/>
-        <v>0.43205333333333329</v>
+        <v>0.45861333333333326</v>
       </c>
       <c r="J19" s="83" t="str">
         <f t="shared" si="1"/>
@@ -28902,7 +28902,7 @@
       </c>
       <c r="N19" s="84">
         <f>AVERAGE(B19:H19)</f>
-        <v>0.90846461421314806</v>
+        <v>0.91508366183219558</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -28928,7 +28928,7 @@
     <mergeCell ref="A20:M20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -29072,7 +29072,7 @@
       </c>
       <c r="C5" s="10">
         <f>IFERROR(IF('Captura Febrero'!D8=0,"",'Captura Febrero'!AQ8),"")</f>
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="D5" s="10">
         <f>IFERROR(IF('Captura Marzo'!D8=0,"",'Captura Marzo'!AQ8),"")</f>
@@ -29096,7 +29096,7 @@
       </c>
       <c r="I5" s="10">
         <f>IFERROR(IF('Captura Agosto'!D8=0,"",'Captura Agosto'!AQ8),"")</f>
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="J5" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
@@ -29116,7 +29116,7 @@
       </c>
       <c r="N5" s="81">
         <f t="shared" si="0"/>
-        <v>0.90749999999999997</v>
+        <v>0.93874999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29153,7 +29153,7 @@
       </c>
       <c r="I6" s="10">
         <f>IFERROR(IF('Captura Agosto'!D10=0,"",'Captura Agosto'!AQ10),"")</f>
-        <v>0.41000000000000003</v>
+        <v>0.49000000000000005</v>
       </c>
       <c r="J6" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
@@ -29173,292 +29173,292 @@
       </c>
       <c r="N6" s="81">
         <f t="shared" si="0"/>
-        <v>0.88312500000000005</v>
+        <v>0.89312500000000006</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="80" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="B7" s="10">
-        <f>IFERROR(IF('Captura Enero'!D20=0,"",'Captura Enero'!AQ20),"")</f>
+        <f>IFERROR(IF('Captura Enero'!D14=0,"",'Captura Enero'!AQ14),"")</f>
+        <v>0.99</v>
+      </c>
+      <c r="C7" s="10">
+        <f>IFERROR(IF('Captura Febrero'!D14=0,"",'Captura Febrero'!AQ14),"")</f>
         <v>0.95</v>
       </c>
-      <c r="C7" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D20=0,"",'Captura Febrero'!AQ20),"")</f>
-        <v>1</v>
-      </c>
       <c r="D7" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D20=0,"",'Captura Marzo'!AQ20),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Marzo'!D14=0,"",'Captura Marzo'!AQ14),"")</f>
+        <v>0.99</v>
       </c>
       <c r="E7" s="10">
-        <f>IFERROR(IF('Captura Abril'!D20=0,"",'Captura Abril'!AQ20),"")</f>
+        <f>IFERROR(IF('Captura Abril'!D14=0,"",'Captura Abril'!AQ14),"")</f>
         <v>1</v>
       </c>
       <c r="F7" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D20=0,"",'Captura Mayo'!AQ20),"")</f>
-        <v>0.95</v>
+        <f>IFERROR(IF('Captura Mayo'!D14=0,"",'Captura Mayo'!AQ14),"")</f>
+        <v>0.9</v>
       </c>
       <c r="G7" s="10">
-        <f>IFERROR(IF('Captura Junio'!D20=0,"",'Captura Junio'!AQ20),"")</f>
-        <v>0.71000000000000008</v>
+        <f>IFERROR(IF('Captura Junio'!D14=0,"",'Captura Junio'!AQ14),"")</f>
+        <v>0.94000000000000006</v>
       </c>
       <c r="H7" s="10">
-        <f>IFERROR(IF('Captura Julio'!D20=0,"",'Captura Julio'!AQ20),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Julio'!D14=0,"",'Captura Julio'!AQ14),"")</f>
+        <v>0.79</v>
       </c>
       <c r="I7" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D20=0,"",'Captura Agosto'!AQ20),"")</f>
-        <v>0.43</v>
+        <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
+        <v>0.50039999999999996</v>
       </c>
       <c r="J7" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
         <v/>
       </c>
       <c r="K7" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D20=0,"",'Captura Octubre'!AQ20),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D14=0,"",'Captura Octubre'!AQ14),"")</f>
         <v/>
       </c>
       <c r="L7" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D20=0,"",'Captura Noviembre'!AQ20),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D14=0,"",'Captura Noviembre'!AQ14),"")</f>
         <v/>
       </c>
       <c r="M7" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D20=0,"",'Captura Diciembre'!AQ20),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D14=0,"",'Captura Diciembre'!AQ14),"")</f>
         <v/>
       </c>
       <c r="N7" s="81">
         <f t="shared" si="0"/>
-        <v>0.88</v>
+        <v>0.88255000000000006</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="80" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="B8" s="10">
-        <f>IFERROR(IF('Captura Enero'!D11=0,"",'Captura Enero'!AQ11),"")</f>
-        <v>0.84000000000000008</v>
+        <f>IFERROR(IF('Captura Enero'!D20=0,"",'Captura Enero'!AQ20),"")</f>
+        <v>0.95</v>
       </c>
       <c r="C8" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D11=0,"",'Captura Febrero'!AQ11),"")</f>
-        <v>0.97500000000000009</v>
+        <f>IFERROR(IF('Captura Febrero'!D20=0,"",'Captura Febrero'!AQ20),"")</f>
+        <v>1</v>
       </c>
       <c r="D8" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D11=0,"",'Captura Marzo'!AQ11),"")</f>
-        <v>0.97500000000000009</v>
+        <f>IFERROR(IF('Captura Marzo'!D20=0,"",'Captura Marzo'!AQ20),"")</f>
+        <v>1</v>
       </c>
       <c r="E8" s="10">
-        <f>IFERROR(IF('Captura Abril'!D11=0,"",'Captura Abril'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Abril'!D20=0,"",'Captura Abril'!AQ20),"")</f>
         <v>1</v>
       </c>
       <c r="F8" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D11=0,"",'Captura Mayo'!AQ11),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Mayo'!D20=0,"",'Captura Mayo'!AQ20),"")</f>
+        <v>0.95</v>
       </c>
       <c r="G8" s="10">
-        <f>IFERROR(IF('Captura Junio'!D11=0,"",'Captura Junio'!AQ11),"")</f>
-        <v>0.85</v>
+        <f>IFERROR(IF('Captura Junio'!D20=0,"",'Captura Junio'!AQ20),"")</f>
+        <v>0.71000000000000008</v>
       </c>
       <c r="H8" s="10">
-        <f>IFERROR(IF('Captura Julio'!D11=0,"",'Captura Julio'!AQ11),"")</f>
-        <v>0.94000000000000006</v>
+        <f>IFERROR(IF('Captura Julio'!D20=0,"",'Captura Julio'!AQ20),"")</f>
+        <v>1</v>
       </c>
       <c r="I8" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
-        <v>0.43</v>
+        <f>IFERROR(IF('Captura Agosto'!D20=0,"",'Captura Agosto'!AQ20),"")</f>
+        <v>0.51</v>
       </c>
       <c r="J8" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
         <v/>
       </c>
       <c r="K8" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D11=0,"",'Captura Octubre'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D20=0,"",'Captura Octubre'!AQ20),"")</f>
         <v/>
       </c>
       <c r="L8" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D11=0,"",'Captura Noviembre'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D20=0,"",'Captura Noviembre'!AQ20),"")</f>
         <v/>
       </c>
       <c r="M8" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D11=0,"",'Captura Diciembre'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D20=0,"",'Captura Diciembre'!AQ20),"")</f>
         <v/>
       </c>
       <c r="N8" s="81">
         <f t="shared" si="0"/>
-        <v>0.87624999999999997</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="80" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B9" s="10">
-        <f>IFERROR(IF('Captura Enero'!D14=0,"",'Captura Enero'!AQ14),"")</f>
-        <v>0.99</v>
+        <f>IFERROR(IF('Captura Enero'!D11=0,"",'Captura Enero'!AQ11),"")</f>
+        <v>0.84000000000000008</v>
       </c>
       <c r="C9" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D14=0,"",'Captura Febrero'!AQ14),"")</f>
-        <v>0.95</v>
+        <f>IFERROR(IF('Captura Febrero'!D11=0,"",'Captura Febrero'!AQ11),"")</f>
+        <v>1</v>
       </c>
       <c r="D9" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D14=0,"",'Captura Marzo'!AQ14),"")</f>
-        <v>0.99</v>
+        <f>IFERROR(IF('Captura Marzo'!D11=0,"",'Captura Marzo'!AQ11),"")</f>
+        <v>0.97500000000000009</v>
       </c>
       <c r="E9" s="10">
-        <f>IFERROR(IF('Captura Abril'!D14=0,"",'Captura Abril'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Abril'!D11=0,"",'Captura Abril'!AQ11),"")</f>
         <v>1</v>
       </c>
       <c r="F9" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D14=0,"",'Captura Mayo'!AQ14),"")</f>
-        <v>0.9</v>
+        <f>IFERROR(IF('Captura Mayo'!D11=0,"",'Captura Mayo'!AQ11),"")</f>
+        <v>1</v>
       </c>
       <c r="G9" s="10">
-        <f>IFERROR(IF('Captura Junio'!D14=0,"",'Captura Junio'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Junio'!D11=0,"",'Captura Junio'!AQ11),"")</f>
+        <v>0.85</v>
+      </c>
+      <c r="H9" s="10">
+        <f>IFERROR(IF('Captura Julio'!D11=0,"",'Captura Julio'!AQ11),"")</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="H9" s="10">
-        <f>IFERROR(IF('Captura Julio'!D14=0,"",'Captura Julio'!AQ14),"")</f>
-        <v>0.79</v>
-      </c>
       <c r="I9" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
-        <v>0.50039999999999996</v>
+        <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
+        <v>0.51</v>
       </c>
       <c r="J9" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
         <v/>
       </c>
       <c r="K9" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D14=0,"",'Captura Octubre'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D11=0,"",'Captura Octubre'!AQ11),"")</f>
         <v/>
       </c>
       <c r="L9" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D14=0,"",'Captura Noviembre'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D11=0,"",'Captura Noviembre'!AQ11),"")</f>
         <v/>
       </c>
       <c r="M9" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D14=0,"",'Captura Diciembre'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D11=0,"",'Captura Diciembre'!AQ11),"")</f>
         <v/>
       </c>
       <c r="N9" s="81">
         <f t="shared" si="0"/>
-        <v>0.88255000000000006</v>
+        <v>0.88937500000000003</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="80" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="B10" s="10">
-        <f>IFERROR(IF('Captura Enero'!D18=0,"",'Captura Enero'!AQ18),"")</f>
-        <v>0.84000000000000008</v>
+        <f>IFERROR(IF('Captura Enero'!D16=0,"",'Captura Enero'!AQ16),"")</f>
+        <v>0.9</v>
       </c>
       <c r="C10" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D18=0,"",'Captura Febrero'!AQ18),"")</f>
-        <v>0.81058823529411772</v>
+        <f>IFERROR(IF('Captura Febrero'!D16=0,"",'Captura Febrero'!AQ16),"")</f>
+        <v>0.91428571428571437</v>
       </c>
       <c r="D10" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D18=0,"",'Captura Marzo'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Marzo'!D16=0,"",'Captura Marzo'!AQ16),"")</f>
         <v>1</v>
       </c>
       <c r="E10" s="10">
-        <f>IFERROR(IF('Captura Abril'!D18=0,"",'Captura Abril'!AQ18),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Abril'!D16=0,"",'Captura Abril'!AQ16),"")</f>
+        <v>0.96000000000000008</v>
       </c>
       <c r="F10" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D18=0,"",'Captura Mayo'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Mayo'!D16=0,"",'Captura Mayo'!AQ16),"")</f>
         <v>1</v>
       </c>
       <c r="G10" s="10">
-        <f>IFERROR(IF('Captura Junio'!D18=0,"",'Captura Junio'!AQ18),"")</f>
-        <v>0.91000000000000014</v>
+        <f>IFERROR(IF('Captura Junio'!D16=0,"",'Captura Junio'!AQ16),"")</f>
+        <v>1</v>
       </c>
       <c r="H10" s="10">
-        <f>IFERROR(IF('Captura Julio'!D18=0,"",'Captura Julio'!AQ18),"")</f>
-        <v>0.97666666666666679</v>
+        <f>IFERROR(IF('Captura Julio'!D16=0,"",'Captura Julio'!AQ16),"")</f>
+        <v>1</v>
       </c>
       <c r="I10" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D18=0,"",'Captura Agosto'!AQ18),"")</f>
-        <v>0.41700000000000004</v>
+        <f>IFERROR(IF('Captura Agosto'!D16=0,"",'Captura Agosto'!AQ16),"")</f>
+        <v>0.50839999999999996</v>
       </c>
       <c r="J10" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
         <v/>
       </c>
       <c r="K10" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D18=0,"",'Captura Octubre'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D16=0,"",'Captura Octubre'!AQ16),"")</f>
         <v/>
       </c>
       <c r="L10" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D18=0,"",'Captura Noviembre'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D16=0,"",'Captura Noviembre'!AQ16),"")</f>
         <v/>
       </c>
       <c r="M10" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D18=0,"",'Captura Diciembre'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D16=0,"",'Captura Diciembre'!AQ16),"")</f>
         <v/>
       </c>
       <c r="N10" s="81">
         <f t="shared" si="0"/>
-        <v>0.869281862745098</v>
+        <v>0.91033571428571425</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="80" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="B11" s="10">
-        <f>IFERROR(IF('Captura Enero'!D16=0,"",'Captura Enero'!AQ16),"")</f>
-        <v>0.9</v>
+        <f>IFERROR(IF('Captura Enero'!D18=0,"",'Captura Enero'!AQ18),"")</f>
+        <v>0.84000000000000008</v>
       </c>
       <c r="C11" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D16=0,"",'Captura Febrero'!AQ16),"")</f>
-        <v>0.66428571428571437</v>
+        <f>IFERROR(IF('Captura Febrero'!D18=0,"",'Captura Febrero'!AQ18),"")</f>
+        <v>0.81058823529411772</v>
       </c>
       <c r="D11" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D16=0,"",'Captura Marzo'!AQ16),"")</f>
+        <f>IFERROR(IF('Captura Marzo'!D18=0,"",'Captura Marzo'!AQ18),"")</f>
         <v>1</v>
       </c>
       <c r="E11" s="10">
-        <f>IFERROR(IF('Captura Abril'!D16=0,"",'Captura Abril'!AQ16),"")</f>
-        <v>0.96000000000000008</v>
+        <f>IFERROR(IF('Captura Abril'!D18=0,"",'Captura Abril'!AQ18),"")</f>
+        <v>1</v>
       </c>
       <c r="F11" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D16=0,"",'Captura Mayo'!AQ16),"")</f>
+        <f>IFERROR(IF('Captura Mayo'!D18=0,"",'Captura Mayo'!AQ18),"")</f>
         <v>1</v>
       </c>
       <c r="G11" s="10">
-        <f>IFERROR(IF('Captura Junio'!D16=0,"",'Captura Junio'!AQ16),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Junio'!D18=0,"",'Captura Junio'!AQ18),"")</f>
+        <v>0.91000000000000014</v>
       </c>
       <c r="H11" s="10">
-        <f>IFERROR(IF('Captura Julio'!D16=0,"",'Captura Julio'!AQ16),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Julio'!D18=0,"",'Captura Julio'!AQ18),"")</f>
+        <v>0.97666666666666679</v>
       </c>
       <c r="I11" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D16=0,"",'Captura Agosto'!AQ16),"")</f>
-        <v>0.43</v>
+        <f>IFERROR(IF('Captura Agosto'!D18=0,"",'Captura Agosto'!AQ18),"")</f>
+        <v>0.38739999999999997</v>
       </c>
       <c r="J11" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
         <v/>
       </c>
       <c r="K11" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D16=0,"",'Captura Octubre'!AQ16),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D18=0,"",'Captura Octubre'!AQ18),"")</f>
         <v/>
       </c>
       <c r="L11" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D16=0,"",'Captura Noviembre'!AQ16),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D18=0,"",'Captura Noviembre'!AQ18),"")</f>
         <v/>
       </c>
       <c r="M11" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D16=0,"",'Captura Diciembre'!AQ16),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D18=0,"",'Captura Diciembre'!AQ18),"")</f>
         <v/>
       </c>
       <c r="N11" s="81">
         <f t="shared" si="0"/>
-        <v>0.86928571428571422</v>
+        <v>0.86558186274509796</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29471,7 +29471,7 @@
       </c>
       <c r="C12" s="10">
         <f>IFERROR(IF('Captura Febrero'!D6=0,"",'Captura Febrero'!AQ6),"")</f>
-        <v>0.75000000000000011</v>
+        <v>1</v>
       </c>
       <c r="D12" s="10">
         <f>IFERROR(IF('Captura Marzo'!D6=0,"",'Captura Marzo'!AQ6),"")</f>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="N12" s="81">
         <f t="shared" si="0"/>
-        <v>0.86749999999999994</v>
+        <v>0.89874999999999994</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29609,7 +29609,7 @@
       </c>
       <c r="I14" s="10">
         <f>IFERROR(IF('Captura Agosto'!D17=0,"",'Captura Agosto'!AQ17),"")</f>
-        <v>0.42200000000000004</v>
+        <v>0.39160000000000006</v>
       </c>
       <c r="J14" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
@@ -29629,121 +29629,121 @@
       </c>
       <c r="N14" s="81">
         <f t="shared" si="0"/>
-        <v>0.81296978021978017</v>
+        <v>0.80916978021978025</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="80" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B15" s="10">
-        <f>IFERROR(IF('Captura Enero'!D15=0,"",'Captura Enero'!AQ15),"")</f>
-        <v>0.94000000000000006</v>
+        <f>IFERROR(IF('Captura Enero'!D12=0,"",'Captura Enero'!AQ12),"")</f>
+        <v>0.79</v>
       </c>
       <c r="C15" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D15=0,"",'Captura Febrero'!AQ15),"")</f>
-        <v>0.98473684210526335</v>
+        <f>IFERROR(IF('Captura Febrero'!D12=0,"",'Captura Febrero'!AQ12),"")</f>
+        <v>0.9</v>
       </c>
       <c r="D15" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D15=0,"",'Captura Marzo'!AQ15),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Marzo'!D12=0,"",'Captura Marzo'!AQ12),"")</f>
+        <v>0.95</v>
       </c>
       <c r="E15" s="10">
-        <f>IFERROR(IF('Captura Abril'!D15=0,"",'Captura Abril'!AQ15),"")</f>
-        <v>0.87000000000000011</v>
+        <f>IFERROR(IF('Captura Abril'!D12=0,"",'Captura Abril'!AQ12),"")</f>
+        <v>1</v>
       </c>
       <c r="F15" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D15=0,"",'Captura Mayo'!AQ15),"")</f>
-        <v>0.69000000000000006</v>
+        <f>IFERROR(IF('Captura Mayo'!D12=0,"",'Captura Mayo'!AQ12),"")</f>
+        <v>0.7</v>
       </c>
       <c r="G15" s="10">
-        <f>IFERROR(IF('Captura Junio'!D15=0,"",'Captura Junio'!AQ15),"")</f>
-        <v>0.74444444444444446</v>
+        <f>IFERROR(IF('Captura Junio'!D12=0,"",'Captura Junio'!AQ12),"")</f>
+        <v>0.70130434782608708</v>
       </c>
       <c r="H15" s="10">
-        <f>IFERROR(IF('Captura Julio'!D15=0,"",'Captura Julio'!AQ15),"")</f>
-        <v>0.75</v>
+        <f>IFERROR(IF('Captura Julio'!D12=0,"",'Captura Julio'!AQ12),"")</f>
+        <v>0.9</v>
       </c>
       <c r="I15" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D15=0,"",'Captura Agosto'!AQ15),"")</f>
-        <v>0.38200000000000001</v>
+        <f>IFERROR(IF('Captura Agosto'!D12=0,"",'Captura Agosto'!AQ12),"")</f>
+        <v>0.5</v>
       </c>
       <c r="J15" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
         <v/>
       </c>
       <c r="K15" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D15=0,"",'Captura Octubre'!AQ15),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D12=0,"",'Captura Octubre'!AQ12),"")</f>
         <v/>
       </c>
       <c r="L15" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D15=0,"",'Captura Noviembre'!AQ15),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D12=0,"",'Captura Noviembre'!AQ12),"")</f>
         <v/>
       </c>
       <c r="M15" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D15=0,"",'Captura Diciembre'!AQ15),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D12=0,"",'Captura Diciembre'!AQ12),"")</f>
         <v/>
       </c>
       <c r="N15" s="81">
         <f t="shared" si="0"/>
-        <v>0.79514766081871346</v>
+        <v>0.80516304347826095</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="80" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B16" s="10">
-        <f>IFERROR(IF('Captura Enero'!D12=0,"",'Captura Enero'!AQ12),"")</f>
-        <v>0.79</v>
+        <f>IFERROR(IF('Captura Enero'!D15=0,"",'Captura Enero'!AQ15),"")</f>
+        <v>0.94000000000000006</v>
       </c>
       <c r="C16" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D12=0,"",'Captura Febrero'!AQ12),"")</f>
-        <v>0.9</v>
+        <f>IFERROR(IF('Captura Febrero'!D15=0,"",'Captura Febrero'!AQ15),"")</f>
+        <v>0.98473684210526335</v>
       </c>
       <c r="D16" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D12=0,"",'Captura Marzo'!AQ12),"")</f>
-        <v>0.95</v>
+        <f>IFERROR(IF('Captura Marzo'!D15=0,"",'Captura Marzo'!AQ15),"")</f>
+        <v>1</v>
       </c>
       <c r="E16" s="10">
-        <f>IFERROR(IF('Captura Abril'!D12=0,"",'Captura Abril'!AQ12),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Abril'!D15=0,"",'Captura Abril'!AQ15),"")</f>
+        <v>0.87000000000000011</v>
       </c>
       <c r="F16" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D12=0,"",'Captura Mayo'!AQ12),"")</f>
-        <v>0.7</v>
+        <f>IFERROR(IF('Captura Mayo'!D15=0,"",'Captura Mayo'!AQ15),"")</f>
+        <v>0.69000000000000006</v>
       </c>
       <c r="G16" s="10">
-        <f>IFERROR(IF('Captura Junio'!D12=0,"",'Captura Junio'!AQ12),"")</f>
-        <v>0.70130434782608708</v>
+        <f>IFERROR(IF('Captura Junio'!D15=0,"",'Captura Junio'!AQ15),"")</f>
+        <v>0.74444444444444446</v>
       </c>
       <c r="H16" s="10">
-        <f>IFERROR(IF('Captura Julio'!D12=0,"",'Captura Julio'!AQ12),"")</f>
-        <v>0.9</v>
+        <f>IFERROR(IF('Captura Julio'!D15=0,"",'Captura Julio'!AQ15),"")</f>
+        <v>0.75</v>
       </c>
       <c r="I16" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D12=0,"",'Captura Agosto'!AQ12),"")</f>
-        <v>0.42000000000000004</v>
+        <f>IFERROR(IF('Captura Agosto'!D15=0,"",'Captura Agosto'!AQ15),"")</f>
+        <v>0.46200000000000002</v>
       </c>
       <c r="J16" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
         <v/>
       </c>
       <c r="K16" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D12=0,"",'Captura Octubre'!AQ12),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D15=0,"",'Captura Octubre'!AQ15),"")</f>
         <v/>
       </c>
       <c r="L16" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D12=0,"",'Captura Noviembre'!AQ12),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D15=0,"",'Captura Noviembre'!AQ15),"")</f>
         <v/>
       </c>
       <c r="M16" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D12=0,"",'Captura Diciembre'!AQ12),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D15=0,"",'Captura Diciembre'!AQ15),"")</f>
         <v/>
       </c>
       <c r="N16" s="81">
         <f t="shared" si="0"/>
-        <v>0.79516304347826094</v>
+        <v>0.80514766081871347</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29780,7 +29780,7 @@
       </c>
       <c r="I17" s="10">
         <f>IFERROR(IF('Captura Agosto'!D13=0,"",'Captura Agosto'!AQ13),"")</f>
-        <v>0.49419999999999997</v>
+        <v>0.39419999999999999</v>
       </c>
       <c r="J17" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
@@ -29800,7 +29800,7 @@
       </c>
       <c r="N17" s="81">
         <f t="shared" si="0"/>
-        <v>0.78552499999999992</v>
+        <v>0.77302499999999985</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -29866,11 +29866,11 @@
       </c>
       <c r="B19" s="83">
         <f t="shared" ref="B19:M19" si="1">IFERROR(AVERAGE(B4:B18),"")</f>
-        <v>0.93030769230769239</v>
+        <v>0.93030769230769228</v>
       </c>
       <c r="C19" s="83">
         <f t="shared" si="1"/>
-        <v>0.91092643373138737</v>
+        <v>0.95725976706472082</v>
       </c>
       <c r="D19" s="83">
         <f t="shared" si="1"/>
@@ -29882,11 +29882,11 @@
       </c>
       <c r="F19" s="83">
         <f t="shared" si="1"/>
-        <v>0.87666666666666671</v>
+        <v>0.87666666666666659</v>
       </c>
       <c r="G19" s="83">
         <f t="shared" si="1"/>
-        <v>0.83357372900851179</v>
+        <v>0.83357372900851157</v>
       </c>
       <c r="H19" s="83">
         <f t="shared" si="1"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="I19" s="83">
         <f t="shared" si="1"/>
-        <v>0.43205333333333329</v>
+        <v>0.45861333333333326</v>
       </c>
       <c r="J19" s="83" t="str">
         <f t="shared" si="1"/>
@@ -29914,18 +29914,23 @@
       </c>
       <c r="N19" s="84">
         <f>AVERAGE(B19:H19)</f>
-        <v>0.90846461421314806</v>
+        <v>0.91508366183219558</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="M24" s="77"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:N19" xr:uid="{00000000-0001-0000-1200-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:N19">
+      <sortCondition descending="1" ref="N3:N19"/>
+    </sortState>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -30579,7 +30584,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -31063,8 +31068,8 @@
     <mergeCell ref="P6:R7"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
+  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -31664,7 +31669,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -31767,7 +31772,7 @@
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
-    <row r="3" spans="1:55" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:55" ht="2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AR3" s="42"/>
       <c r="AS3" s="46" t="s">
         <v>152</v>
@@ -31903,7 +31908,7 @@
       <c r="BB4" s="42"/>
       <c r="BC4" s="42"/>
     </row>
-    <row r="5" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:55" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="56" t="s">
         <v>77</v>
       </c>
@@ -34941,12 +34946,12 @@
       <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV6:AV20">
+  <conditionalFormatting sqref="AV19:AV20">
     <cfRule type="cellIs" dxfId="107" priority="2" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
     <cfRule type="expression" dxfId="106" priority="3">
-      <formula>AND(AV6&gt;=0.7,AV6&lt;0.9)</formula>
+      <formula>AND(AV19&gt;=0.7,AV19&lt;0.9)</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="105" priority="4" operator="lessThan">
       <formula>0.7</formula>
@@ -34983,7 +34988,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup scale="25" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -35086,7 +35091,7 @@
       <c r="BB2" s="42"/>
       <c r="BC2" s="42"/>
     </row>
-    <row r="3" spans="1:55" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:55" ht="8.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="AR3" s="42"/>
       <c r="AS3" s="46" t="s">
         <v>152</v>
@@ -35197,11 +35202,11 @@
       </c>
       <c r="AV4" s="53">
         <f>'Captura Febrero'!V6</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW4" s="53">
         <f>'Captura Febrero'!G6</f>
-        <v>0.16000000000000003</v>
+        <v>0.2</v>
       </c>
       <c r="AX4" s="53">
         <f>'Captura Febrero'!X6</f>
@@ -35217,7 +35222,7 @@
       </c>
       <c r="BA4" s="55">
         <f>'Captura Febrero'!AQ6</f>
-        <v>0.75000000000000011</v>
+        <v>1</v>
       </c>
       <c r="BB4" s="42"/>
       <c r="BC4" s="42"/>
@@ -35404,18 +35409,18 @@
         <v>Fredy Fuentes</v>
       </c>
       <c r="D6" s="65">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E6" s="65">
         <v>1</v>
       </c>
       <c r="F6" s="11">
         <f t="shared" ref="F6:F20" si="0">AVERAGE(D6,E6)</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G6" s="66">
         <f>F6*Parametros!$E$6</f>
-        <v>0.16000000000000003</v>
+        <v>0.2</v>
       </c>
       <c r="H6" s="67">
         <v>10</v>
@@ -35461,11 +35466,11 @@
         <v>0.06</v>
       </c>
       <c r="U6" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="66">
         <f>U6*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W6" s="67">
         <v>0</v>
@@ -35532,11 +35537,11 @@
       </c>
       <c r="AP6" s="11">
         <f t="shared" ref="AP6:AP20" si="3">G6+K6+N6+Q6+T6+V6+X6</f>
-        <v>0.71000000000000008</v>
+        <v>1</v>
       </c>
       <c r="AQ6" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP6-IF(S6="NO",Parametros!$E$17,0))+AC6)-AN6-IF(AO6="SI",Parametros!$E$33,0))</f>
-        <v>0.75000000000000011</v>
+        <v>1</v>
       </c>
       <c r="AR6" s="42"/>
       <c r="AS6" s="52" t="str">
@@ -35553,7 +35558,7 @@
       </c>
       <c r="AV6" s="53">
         <f>'Captura Febrero'!V8</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW6" s="53">
         <f>'Captura Febrero'!G8</f>
@@ -35573,7 +35578,7 @@
       </c>
       <c r="BA6" s="55">
         <f>'Captura Febrero'!AQ8</f>
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BB6" s="42"/>
       <c r="BC6" s="42"/>
@@ -35833,11 +35838,11 @@
         <v>0.06</v>
       </c>
       <c r="U8" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="66">
         <f>U8*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W8" s="67">
         <v>0</v>
@@ -35904,11 +35909,11 @@
       </c>
       <c r="AP8" s="11">
         <f t="shared" si="3"/>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ8" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP8-IF(S8="NO",Parametros!$E$17,0))+AC8)-AN8-IF(AO8="SI",Parametros!$E$33,0))</f>
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR8" s="42"/>
       <c r="AS8" s="52" t="str">
@@ -36115,7 +36120,7 @@
       </c>
       <c r="AW9" s="60">
         <f>'Captura Febrero'!G11</f>
-        <v>0.17500000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="AX9" s="60">
         <f>'Captura Febrero'!X11</f>
@@ -36131,7 +36136,7 @@
       </c>
       <c r="BA9" s="62">
         <f>'Captura Febrero'!AQ11</f>
-        <v>0.97500000000000009</v>
+        <v>1</v>
       </c>
       <c r="BB9" s="42"/>
       <c r="BC9" s="42"/>
@@ -36337,15 +36342,15 @@
         <v>1</v>
       </c>
       <c r="E11" s="65">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F11" s="11">
         <f t="shared" si="0"/>
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="G11" s="66">
         <f>F11*Parametros!$E$6</f>
-        <v>0.17500000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="H11" s="67">
         <v>10</v>
@@ -36462,11 +36467,11 @@
       </c>
       <c r="AP11" s="11">
         <f t="shared" si="3"/>
-        <v>0.97500000000000009</v>
+        <v>1</v>
       </c>
       <c r="AQ11" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP11-IF(S11="NO",Parametros!$E$17,0))+AC11)-AN11-IF(AO11="SI",Parametros!$E$33,0))</f>
-        <v>0.97500000000000009</v>
+        <v>1</v>
       </c>
       <c r="AR11" s="42"/>
       <c r="AS11" s="59" t="str">
@@ -37041,7 +37046,7 @@
       </c>
       <c r="AV14" s="53">
         <f>'Captura Febrero'!V16</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW14" s="53">
         <f>'Captura Febrero'!G16</f>
@@ -37061,7 +37066,7 @@
       </c>
       <c r="BA14" s="55">
         <f>'Captura Febrero'!AQ16</f>
-        <v>0.66428571428571437</v>
+        <v>0.91428571428571437</v>
       </c>
       <c r="BB14" s="42"/>
       <c r="BC14" s="42"/>
@@ -37321,11 +37326,11 @@
         <v>0.06</v>
       </c>
       <c r="U16" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="66">
         <f>U16*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W16" s="67">
         <v>0</v>
@@ -37392,11 +37397,11 @@
       </c>
       <c r="AP16" s="11">
         <f t="shared" si="3"/>
-        <v>0.66428571428571437</v>
+        <v>0.91428571428571437</v>
       </c>
       <c r="AQ16" s="70">
         <f>MAX(0,MIN(1,MAX(0,AP16-IF(S16="NO",Parametros!$E$17,0))+AC16)-AN16-IF(AO16="SI",Parametros!$E$33,0))</f>
-        <v>0.66428571428571437</v>
+        <v>0.91428571428571437</v>
       </c>
       <c r="AR16" s="42"/>
       <c r="AS16" s="52" t="str">
@@ -37969,7 +37974,7 @@
       <c r="AZ19" s="90"/>
       <c r="BA19" s="71">
         <f>AVERAGE(BA4:BA18)</f>
-        <v>0.91092643373138726</v>
+        <v>0.9572597670647206</v>
       </c>
       <c r="BB19" s="42"/>
       <c r="BC19" s="42"/>
@@ -38208,7 +38213,7 @@
       <c r="AP23" s="73"/>
       <c r="AQ23" s="74">
         <f>AVERAGE(AQ6:AQ20)</f>
-        <v>0.91092643373138726</v>
+        <v>0.9572597670647206</v>
       </c>
       <c r="AR23" s="42"/>
       <c r="AS23" s="42"/>
@@ -38297,7 +38302,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup scale="25" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -41611,7 +41616,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup scale="25" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -44925,7 +44930,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup scale="25" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -48239,7 +48244,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup scale="25" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -48511,22 +48516,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F98439B8-0535-46FB-9AA1-827C12A2EA64}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
-    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91643E3-530D-47F6-9656-22B4508F358B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
+++ b/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gestorssocuyo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc.sharepoint.com/sites/CharlascortasSSOsemanalesCuyotenango/Shared Documents/General/04. Registros 2026/09. Nivel De Seguridad/NUEVO NIVEL DE SEGURIDAD - 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA93C17-BEC0-435F-87D9-564EB45A6C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{1FA93C17-BEC0-435F-87D9-564EB45A6C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F51E74CC-AD1D-4D6B-8C5E-ABF6DCC1A68E}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="-90" windowWidth="19380" windowHeight="10260" tabRatio="867" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="867" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="1" r:id="rId1"/>
@@ -2067,24 +2067,6 @@
     <xf numFmtId="10" fontId="54" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -2109,6 +2091,24 @@
     <xf numFmtId="1" fontId="27" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2120,15 +2120,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2143,6 +2134,30 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2164,21 +2179,6 @@
     </xf>
     <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3208,37 +3208,37 @@
                   <c:v>Calidad</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>Linea 4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ETEI</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Jarabes</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Equipos Auxiliares</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
+                  <c:v>Centro de Distribucion</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Linea 2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Mantenimiento</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Linea 5</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Materias Primas</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>Linea 4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Linea 2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Jarabes</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>ETEI</c:v>
-                </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>Linea 3</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>Centro de Distribucion</c:v>
-                </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>Linea 1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Linea 5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Mantenimiento</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>Alrededores</c:v>
@@ -3640,7 +3640,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1</c:v>
+                  <c:v>0.53333333333333333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4306,7 +4306,7 @@
                   <c:v>0.88027777777777783</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.45861333333333326</c:v>
+                  <c:v>0.36621333333333334</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C13" s="4">
         <f ca="1">TODAY()</f>
-        <v>46252</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5074,31 +5074,31 @@
       <c r="AA1" s="124"/>
       <c r="AB1" s="124"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="133" t="s">
         <v>242</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="133"/>
+      <c r="AU1" s="133"/>
+      <c r="AV1" s="133"/>
+      <c r="AW1" s="133"/>
+      <c r="AX1" s="133"/>
+      <c r="AY1" s="133"/>
+      <c r="AZ1" s="133"/>
+      <c r="BA1" s="133"/>
+      <c r="BB1" s="134" t="s">
         <v>243</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="134"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="135" t="s">
         <v>244</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -5107,20 +5107,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="136" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="136"/>
+      <c r="AV2" s="136"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="137"/>
+      <c r="AZ2" s="137"/>
+      <c r="BA2" s="137"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -5168,66 +5168,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="142"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="142"/>
+      <c r="N4" s="142"/>
+      <c r="O4" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="142"/>
+      <c r="T4" s="142"/>
+      <c r="U4" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="142"/>
+      <c r="W4" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="143"/>
+      <c r="Y4" s="142" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="142"/>
+      <c r="AA4" s="142"/>
+      <c r="AB4" s="142"/>
+      <c r="AC4" s="142"/>
+      <c r="AD4" s="143" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="143"/>
+      <c r="AF4" s="143"/>
+      <c r="AG4" s="143"/>
+      <c r="AH4" s="143"/>
+      <c r="AI4" s="143"/>
+      <c r="AJ4" s="143"/>
+      <c r="AK4" s="143"/>
+      <c r="AL4" s="143"/>
+      <c r="AM4" s="143"/>
+      <c r="AN4" s="143"/>
+      <c r="AO4" s="143"/>
+      <c r="AP4" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="144"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Mayo'!B6</f>
@@ -5439,10 +5439,10 @@
         <f>'Captura Mayo'!AQ7</f>
         <v>0.69000000000000006</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="138"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -8009,16 +8009,16 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="139" t="s">
         <v>245</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="139"/>
+      <c r="AU19" s="139"/>
+      <c r="AV19" s="139"/>
+      <c r="AW19" s="139"/>
+      <c r="AX19" s="139"/>
+      <c r="AY19" s="139"/>
+      <c r="AZ19" s="139"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.87666666666666671</v>
@@ -8185,9 +8185,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="140"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -8214,11 +8214,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="141" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -8276,12 +8276,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -8296,6 +8290,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="74" priority="5" operator="greaterThanOrEqual">
@@ -8408,31 +8408,31 @@
       <c r="AA1" s="124"/>
       <c r="AB1" s="124"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="133" t="s">
         <v>247</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="133"/>
+      <c r="AU1" s="133"/>
+      <c r="AV1" s="133"/>
+      <c r="AW1" s="133"/>
+      <c r="AX1" s="133"/>
+      <c r="AY1" s="133"/>
+      <c r="AZ1" s="133"/>
+      <c r="BA1" s="133"/>
+      <c r="BB1" s="134" t="s">
         <v>248</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="134"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="135" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -8441,20 +8441,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="136" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="136"/>
+      <c r="AV2" s="136"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="137"/>
+      <c r="AZ2" s="137"/>
+      <c r="BA2" s="137"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -8502,66 +8502,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="142"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="142"/>
+      <c r="N4" s="142"/>
+      <c r="O4" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="142"/>
+      <c r="T4" s="142"/>
+      <c r="U4" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="142"/>
+      <c r="W4" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="143"/>
+      <c r="Y4" s="142" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="142"/>
+      <c r="AA4" s="142"/>
+      <c r="AB4" s="142"/>
+      <c r="AC4" s="142"/>
+      <c r="AD4" s="143" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="143"/>
+      <c r="AF4" s="143"/>
+      <c r="AG4" s="143"/>
+      <c r="AH4" s="143"/>
+      <c r="AI4" s="143"/>
+      <c r="AJ4" s="143"/>
+      <c r="AK4" s="143"/>
+      <c r="AL4" s="143"/>
+      <c r="AM4" s="143"/>
+      <c r="AN4" s="143"/>
+      <c r="AO4" s="143"/>
+      <c r="AP4" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="144"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Junio'!B6</f>
@@ -8773,10 +8773,10 @@
         <f>'Captura Junio'!AQ7</f>
         <v>0.64000000000000012</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="138"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -11343,16 +11343,16 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="139" t="s">
         <v>250</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="139"/>
+      <c r="AU19" s="139"/>
+      <c r="AV19" s="139"/>
+      <c r="AW19" s="139"/>
+      <c r="AX19" s="139"/>
+      <c r="AY19" s="139"/>
+      <c r="AZ19" s="139"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.83357372900851168</v>
@@ -11519,9 +11519,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="140"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -11548,11 +11548,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="141" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -11610,12 +11610,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -11630,6 +11624,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="greaterThanOrEqual">
@@ -11744,31 +11744,31 @@
       <c r="AA1" s="124"/>
       <c r="AB1" s="124"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="133" t="s">
         <v>252</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="133"/>
+      <c r="AU1" s="133"/>
+      <c r="AV1" s="133"/>
+      <c r="AW1" s="133"/>
+      <c r="AX1" s="133"/>
+      <c r="AY1" s="133"/>
+      <c r="AZ1" s="133"/>
+      <c r="BA1" s="133"/>
+      <c r="BB1" s="134" t="s">
         <v>253</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="134"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="135" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -11777,20 +11777,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="136" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="136"/>
+      <c r="AV2" s="136"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="137"/>
+      <c r="AZ2" s="137"/>
+      <c r="BA2" s="137"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -11838,66 +11838,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="142"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="142"/>
+      <c r="N4" s="142"/>
+      <c r="O4" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="142"/>
+      <c r="T4" s="142"/>
+      <c r="U4" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="142"/>
+      <c r="W4" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="143"/>
+      <c r="Y4" s="142" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="142"/>
+      <c r="AA4" s="142"/>
+      <c r="AB4" s="142"/>
+      <c r="AC4" s="142"/>
+      <c r="AD4" s="143" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="143"/>
+      <c r="AF4" s="143"/>
+      <c r="AG4" s="143"/>
+      <c r="AH4" s="143"/>
+      <c r="AI4" s="143"/>
+      <c r="AJ4" s="143"/>
+      <c r="AK4" s="143"/>
+      <c r="AL4" s="143"/>
+      <c r="AM4" s="143"/>
+      <c r="AN4" s="143"/>
+      <c r="AO4" s="143"/>
+      <c r="AP4" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="144"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Julio'!B6</f>
@@ -12109,10 +12109,10 @@
         <f>'Captura Julio'!AQ7</f>
         <v>0.64</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="138"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -14679,16 +14679,16 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="139" t="s">
         <v>255</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="139"/>
+      <c r="AU19" s="139"/>
+      <c r="AV19" s="139"/>
+      <c r="AW19" s="139"/>
+      <c r="AX19" s="139"/>
+      <c r="AY19" s="139"/>
+      <c r="AZ19" s="139"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.88027777777777783</v>
@@ -14855,9 +14855,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="140"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -14884,11 +14884,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="141" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -14946,12 +14946,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -14966,6 +14960,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="56" priority="5" operator="greaterThanOrEqual">
@@ -15078,31 +15078,31 @@
       <c r="AA1" s="124"/>
       <c r="AB1" s="124"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="133" t="s">
         <v>257</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="133"/>
+      <c r="AU1" s="133"/>
+      <c r="AV1" s="133"/>
+      <c r="AW1" s="133"/>
+      <c r="AX1" s="133"/>
+      <c r="AY1" s="133"/>
+      <c r="AZ1" s="133"/>
+      <c r="BA1" s="133"/>
+      <c r="BB1" s="134" t="s">
         <v>258</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="134"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="135" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -15111,20 +15111,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="136" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="136"/>
+      <c r="AV2" s="136"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="137"/>
+      <c r="AZ2" s="137"/>
+      <c r="BA2" s="137"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -15172,66 +15172,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="142"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="142"/>
+      <c r="N4" s="142"/>
+      <c r="O4" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="142"/>
+      <c r="T4" s="142"/>
+      <c r="U4" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="142"/>
+      <c r="W4" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="143"/>
+      <c r="Y4" s="142" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="142"/>
+      <c r="AA4" s="142"/>
+      <c r="AB4" s="142"/>
+      <c r="AC4" s="142"/>
+      <c r="AD4" s="143" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="143"/>
+      <c r="AF4" s="143"/>
+      <c r="AG4" s="143"/>
+      <c r="AH4" s="143"/>
+      <c r="AI4" s="143"/>
+      <c r="AJ4" s="143"/>
+      <c r="AK4" s="143"/>
+      <c r="AL4" s="143"/>
+      <c r="AM4" s="143"/>
+      <c r="AN4" s="143"/>
+      <c r="AO4" s="143"/>
+      <c r="AP4" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="144"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Agosto'!B6</f>
@@ -15276,7 +15276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:55" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="76" t="s">
         <v>93</v>
       </c>
@@ -15429,7 +15429,7 @@
       </c>
       <c r="AX5" s="80">
         <f>'Captura Agosto'!X7</f>
-        <v>0.25</v>
+        <v>4.9999999999999989E-2</v>
       </c>
       <c r="AY5" s="80">
         <f>'Captura Agosto'!AC7</f>
@@ -15441,12 +15441,12 @@
       </c>
       <c r="BA5" s="82">
         <f>'Captura Agosto'!AQ7</f>
-        <v>0.35</v>
-      </c>
-      <c r="BB5" s="133" t="s">
+        <v>0.15</v>
+      </c>
+      <c r="BB5" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="138"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="AT6" s="72">
         <f>'Captura Agosto'!K8+'Captura Agosto'!N8+'Captura Agosto'!Q8</f>
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="AU6" s="72">
         <f>'Captura Agosto'!T8</f>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="BA6" s="74">
         <f>'Captura Agosto'!AQ8</f>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="BB6" s="58"/>
       <c r="BC6" s="58"/>
@@ -15706,11 +15706,11 @@
         <v>0</v>
       </c>
       <c r="W7" s="87">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X7" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W7)</f>
-        <v>0.25</v>
+        <v>4.9999999999999989E-2</v>
       </c>
       <c r="Y7" s="87">
         <v>0</v>
@@ -15770,11 +15770,11 @@
       </c>
       <c r="AP7" s="11">
         <f t="shared" si="3"/>
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="AQ7" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP7-IF(S7="NO",Parametros!$E$17,0))+AC7)-AN7-IF(AO7="SI",Parametros!$E$33,0))</f>
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="AR7" s="58"/>
       <c r="AS7" s="79" t="str">
@@ -15783,7 +15783,7 @@
       </c>
       <c r="AT7" s="80">
         <f>'Captura Agosto'!K9+'Captura Agosto'!N9+'Captura Agosto'!Q9</f>
-        <v>7.5200000000000003E-2</v>
+        <v>0.1552</v>
       </c>
       <c r="AU7" s="80">
         <f>'Captura Agosto'!T9</f>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="AX7" s="80">
         <f>'Captura Agosto'!X9</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="AY7" s="80">
         <f>'Captura Agosto'!AC9</f>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="BA7" s="82">
         <f>'Captura Agosto'!AQ9</f>
-        <v>0.42520000000000002</v>
+        <v>0.4052</v>
       </c>
       <c r="BB7" s="58"/>
       <c r="BC7" s="58"/>
@@ -15865,14 +15865,14 @@
         <v>0.08</v>
       </c>
       <c r="O8" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q8" s="86">
         <f>IF(P8="NO",0,O8*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="R8" s="85">
         <v>0</v>
@@ -15956,11 +15956,11 @@
       </c>
       <c r="AP8" s="11">
         <f t="shared" si="3"/>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="AQ8" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP8-IF(S8="NO",Parametros!$E$17,0))+AC8)-AN8-IF(AO8="SI",Parametros!$E$33,0))</f>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="AR8" s="58"/>
       <c r="AS8" s="71" t="str">
@@ -16047,14 +16047,14 @@
         <v>7.5200000000000003E-2</v>
       </c>
       <c r="O9" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q9" s="86">
         <f>IF(P9="NO",0,O9*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="R9" s="85">
         <v>0</v>
@@ -16074,11 +16074,11 @@
         <v>0</v>
       </c>
       <c r="W9" s="87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W9)</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="Y9" s="87">
         <v>0</v>
@@ -16138,11 +16138,11 @@
       </c>
       <c r="AP9" s="11">
         <f t="shared" si="3"/>
-        <v>0.42520000000000002</v>
+        <v>0.4052</v>
       </c>
       <c r="AQ9" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP9-IF(S9="NO",Parametros!$E$17,0))+AC9)-AN9-IF(AO9="SI",Parametros!$E$33,0))</f>
-        <v>0.42520000000000002</v>
+        <v>0.4052</v>
       </c>
       <c r="AR9" s="58"/>
       <c r="AS9" s="79" t="str">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="AX9" s="80">
         <f>'Captura Agosto'!X11</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="AY9" s="80">
         <f>'Captura Agosto'!AC11</f>
@@ -16179,7 +16179,7 @@
       </c>
       <c r="BA9" s="82">
         <f>'Captura Agosto'!AQ11</f>
-        <v>0.51</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="BB9" s="58"/>
       <c r="BC9" s="58"/>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="AX10" s="72">
         <f>'Captura Agosto'!X12</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AY10" s="72">
         <f>'Captura Agosto'!AC12</f>
@@ -16365,7 +16365,7 @@
       </c>
       <c r="BA10" s="74">
         <f>'Captura Agosto'!AQ12</f>
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BB10" s="58"/>
       <c r="BC10" s="58"/>
@@ -16446,11 +16446,11 @@
         <v>0</v>
       </c>
       <c r="W11" s="87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X11" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W11)</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="Y11" s="87">
         <v>0</v>
@@ -16510,11 +16510,11 @@
       </c>
       <c r="AP11" s="11">
         <f t="shared" si="3"/>
-        <v>0.51</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="AQ11" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP11-IF(S11="NO",Parametros!$E$17,0))+AC11)-AN11-IF(AO11="SI",Parametros!$E$33,0))</f>
-        <v>0.51</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="AR11" s="58"/>
       <c r="AS11" s="79" t="str">
@@ -16523,7 +16523,7 @@
       </c>
       <c r="AT11" s="80">
         <f>'Captura Agosto'!K13+'Captura Agosto'!N13+'Captura Agosto'!Q13</f>
-        <v>0.1472</v>
+        <v>0.2112</v>
       </c>
       <c r="AU11" s="80">
         <f>'Captura Agosto'!T13</f>
@@ -16539,7 +16539,7 @@
       </c>
       <c r="AX11" s="80">
         <f>'Captura Agosto'!X13</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AY11" s="80">
         <f>'Captura Agosto'!AC13</f>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="BA11" s="82">
         <f>'Captura Agosto'!AQ13</f>
-        <v>0.39419999999999999</v>
+        <v>0.20819999999999997</v>
       </c>
       <c r="BB11" s="58"/>
       <c r="BC11" s="58"/>
@@ -16632,11 +16632,11 @@
         <v>0</v>
       </c>
       <c r="W12" s="87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W12)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Y12" s="87">
         <v>0</v>
@@ -16696,11 +16696,11 @@
       </c>
       <c r="AP12" s="11">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AQ12" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP12-IF(S12="NO",Parametros!$E$17,0))+AC12)-AN12-IF(AO12="SI",Parametros!$E$33,0))</f>
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR12" s="58"/>
       <c r="AS12" s="71" t="str">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="AT12" s="72">
         <f>'Captura Agosto'!K14+'Captura Agosto'!N14+'Captura Agosto'!Q14</f>
-        <v>0.15040000000000001</v>
+        <v>0.2208</v>
       </c>
       <c r="AU12" s="72">
         <f>'Captura Agosto'!T14</f>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="AX12" s="72">
         <f>'Captura Agosto'!X14</f>
-        <v>0.25</v>
+        <v>4.9999999999999989E-2</v>
       </c>
       <c r="AY12" s="72">
         <f>'Captura Agosto'!AC14</f>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="BA12" s="74">
         <f>'Captura Agosto'!AQ14</f>
-        <v>0.50039999999999996</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="BB12" s="58"/>
       <c r="BC12" s="58"/>
@@ -16791,14 +16791,14 @@
         <v>6.7199999999999996E-2</v>
       </c>
       <c r="O13" s="85">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P13" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q13" s="86">
         <f>IF(P13="NO",0,O13*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="R13" s="85">
         <v>0</v>
@@ -16818,11 +16818,11 @@
         <v>0</v>
       </c>
       <c r="W13" s="87">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X13" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W13)</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="87">
         <v>0</v>
@@ -16882,11 +16882,11 @@
       </c>
       <c r="AP13" s="11">
         <f t="shared" si="3"/>
-        <v>0.49419999999999997</v>
+        <v>0.30819999999999997</v>
       </c>
       <c r="AQ13" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP13-IF(S13="NO",Parametros!$E$17,0))+AC13)-AN13-IF(AO13="SI",Parametros!$E$33,0))</f>
-        <v>0.39419999999999999</v>
+        <v>0.20819999999999997</v>
       </c>
       <c r="AR13" s="58"/>
       <c r="AS13" s="79" t="str">
@@ -16911,7 +16911,7 @@
       </c>
       <c r="AX13" s="80">
         <f>'Captura Agosto'!X15</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AY13" s="80">
         <f>'Captura Agosto'!AC15</f>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="BA13" s="82">
         <f>'Captura Agosto'!AQ15</f>
-        <v>0.46200000000000002</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="BB13" s="58"/>
       <c r="BC13" s="58"/>
@@ -16977,14 +16977,14 @@
         <v>7.0400000000000004E-2</v>
       </c>
       <c r="O14" s="85">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="P14" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q14" s="86">
         <f>IF(P14="NO",0,O14*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>7.0400000000000004E-2</v>
       </c>
       <c r="R14" s="85">
         <v>0</v>
@@ -17004,11 +17004,11 @@
         <v>0</v>
       </c>
       <c r="W14" s="87">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X14" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W14)</f>
-        <v>0.25</v>
+        <v>4.9999999999999989E-2</v>
       </c>
       <c r="Y14" s="87">
         <v>0</v>
@@ -17068,11 +17068,11 @@
       </c>
       <c r="AP14" s="11">
         <f t="shared" si="3"/>
-        <v>0.50039999999999996</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="AQ14" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP14-IF(S14="NO",Parametros!$E$17,0))+AC14)-AN14-IF(AO14="SI",Parametros!$E$33,0))</f>
-        <v>0.50039999999999996</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="AR14" s="58"/>
       <c r="AS14" s="71" t="str">
@@ -17190,11 +17190,11 @@
         <v>0</v>
       </c>
       <c r="W15" s="87">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X15" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W15)</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="87">
         <v>0</v>
@@ -17254,11 +17254,11 @@
       </c>
       <c r="AP15" s="11">
         <f t="shared" si="3"/>
-        <v>0.46200000000000002</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="AQ15" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP15-IF(S15="NO",Parametros!$E$17,0))+AC15)-AN15-IF(AO15="SI",Parametros!$E$33,0))</f>
-        <v>0.46200000000000002</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="AR15" s="58"/>
       <c r="AS15" s="79" t="str">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="AT15" s="80">
         <f>'Captura Agosto'!K17+'Captura Agosto'!N17+'Captura Agosto'!Q17</f>
-        <v>0.14960000000000001</v>
+        <v>0.21920000000000001</v>
       </c>
       <c r="AU15" s="80">
         <f>'Captura Agosto'!T17</f>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="AX15" s="80">
         <f>'Captura Agosto'!X17</f>
-        <v>0.25</v>
+        <v>4.9999999999999989E-2</v>
       </c>
       <c r="AY15" s="80">
         <f>'Captura Agosto'!AC17</f>
@@ -17295,7 +17295,7 @@
       </c>
       <c r="BA15" s="82">
         <f>'Captura Agosto'!AQ17</f>
-        <v>0.39160000000000006</v>
+        <v>0.26119999999999999</v>
       </c>
       <c r="BB15" s="58"/>
       <c r="BC15" s="58"/>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="AX16" s="72">
         <f>'Captura Agosto'!X18</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="AY16" s="72">
         <f>'Captura Agosto'!AC18</f>
@@ -17481,7 +17481,7 @@
       </c>
       <c r="BA16" s="74">
         <f>'Captura Agosto'!AQ18</f>
-        <v>0.38739999999999997</v>
+        <v>0.28739999999999999</v>
       </c>
       <c r="BB16" s="58"/>
       <c r="BC16" s="58"/>
@@ -17535,14 +17535,14 @@
         <v>6.9599999999999995E-2</v>
       </c>
       <c r="O17" s="85">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="P17" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q17" s="86">
         <f>IF(P17="NO",0,O17*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>6.9599999999999995E-2</v>
       </c>
       <c r="R17" s="85">
         <v>0</v>
@@ -17562,11 +17562,11 @@
         <v>0</v>
       </c>
       <c r="W17" s="87">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X17" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W17)</f>
-        <v>0.25</v>
+        <v>4.9999999999999989E-2</v>
       </c>
       <c r="Y17" s="87">
         <v>0</v>
@@ -17626,11 +17626,11 @@
       </c>
       <c r="AP17" s="11">
         <f t="shared" si="3"/>
-        <v>0.49160000000000004</v>
+        <v>0.36120000000000002</v>
       </c>
       <c r="AQ17" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP17-IF(S17="NO",Parametros!$E$17,0))+AC17)-AN17-IF(AO17="SI",Parametros!$E$33,0))</f>
-        <v>0.39160000000000006</v>
+        <v>0.26119999999999999</v>
       </c>
       <c r="AR17" s="58"/>
       <c r="AS17" s="79" t="str">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="AX17" s="80">
         <f>'Captura Agosto'!X19</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AY17" s="80">
         <f>'Captura Agosto'!AC19</f>
@@ -17667,7 +17667,7 @@
       </c>
       <c r="BA17" s="82">
         <f>'Captura Agosto'!AQ19</f>
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="BB17" s="58"/>
       <c r="BC17" s="58"/>
@@ -17748,11 +17748,11 @@
         <v>0</v>
       </c>
       <c r="W18" s="87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W18)</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="Y18" s="87">
         <v>0</v>
@@ -17812,11 +17812,11 @@
       </c>
       <c r="AP18" s="11">
         <f t="shared" si="3"/>
-        <v>0.4874</v>
+        <v>0.38739999999999997</v>
       </c>
       <c r="AQ18" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP18-IF(S18="NO",Parametros!$E$17,0))+AC18)-AN18-IF(AO18="SI",Parametros!$E$33,0))</f>
-        <v>0.38739999999999997</v>
+        <v>0.28739999999999999</v>
       </c>
       <c r="AR18" s="58"/>
       <c r="AS18" s="71" t="str">
@@ -17841,7 +17841,7 @@
       </c>
       <c r="AX18" s="72">
         <f>'Captura Agosto'!X20</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AY18" s="72">
         <f>'Captura Agosto'!AC20</f>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="BA18" s="74">
         <f>'Captura Agosto'!AQ20</f>
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="BB18" s="58"/>
       <c r="BC18" s="58"/>
@@ -17934,11 +17934,11 @@
         <v>0</v>
       </c>
       <c r="W19" s="87">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X19" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W19)</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="87">
         <v>0</v>
@@ -17998,26 +17998,26 @@
       </c>
       <c r="AP19" s="11">
         <f t="shared" si="3"/>
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="AQ19" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP19-IF(S19="NO",Parametros!$E$17,0))+AC19)-AN19-IF(AO19="SI",Parametros!$E$33,0))</f>
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="139" t="s">
         <v>260</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="139"/>
+      <c r="AU19" s="139"/>
+      <c r="AV19" s="139"/>
+      <c r="AW19" s="139"/>
+      <c r="AX19" s="139"/>
+      <c r="AY19" s="139"/>
+      <c r="AZ19" s="139"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
-        <v>0.45861333333333326</v>
+        <v>0.36621333333333334</v>
       </c>
       <c r="BB19" s="58"/>
       <c r="BC19" s="58"/>
@@ -18098,11 +18098,11 @@
         <v>0</v>
       </c>
       <c r="W20" s="87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W20)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Y20" s="87">
         <v>0</v>
@@ -18162,11 +18162,11 @@
       </c>
       <c r="AP20" s="11">
         <f t="shared" si="3"/>
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="AQ20" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP20-IF(S20="NO",Parametros!$E$17,0))+AC20)-AN20-IF(AO20="SI",Parametros!$E$33,0))</f>
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="AR20" s="58"/>
       <c r="AS20" s="58"/>
@@ -18181,9 +18181,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="140"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -18210,11 +18210,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="141" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -18256,7 +18256,7 @@
       <c r="AP23" s="93"/>
       <c r="AQ23" s="96">
         <f>AVERAGE(AQ6:AQ20)</f>
-        <v>0.45861333333333326</v>
+        <v>0.36621333333333334</v>
       </c>
       <c r="AR23" s="58"/>
       <c r="AS23" s="58"/>
@@ -18272,12 +18272,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -18292,6 +18286,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="47" priority="5" operator="greaterThanOrEqual">
@@ -18404,31 +18404,31 @@
       <c r="AA1" s="124"/>
       <c r="AB1" s="124"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="133" t="s">
         <v>262</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="133"/>
+      <c r="AU1" s="133"/>
+      <c r="AV1" s="133"/>
+      <c r="AW1" s="133"/>
+      <c r="AX1" s="133"/>
+      <c r="AY1" s="133"/>
+      <c r="AZ1" s="133"/>
+      <c r="BA1" s="133"/>
+      <c r="BB1" s="134" t="s">
         <v>263</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="134"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="135" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -18437,20 +18437,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="136" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="136"/>
+      <c r="AV2" s="136"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="137"/>
+      <c r="AZ2" s="137"/>
+      <c r="BA2" s="137"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -18498,66 +18498,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="142"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="142"/>
+      <c r="N4" s="142"/>
+      <c r="O4" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="142"/>
+      <c r="T4" s="142"/>
+      <c r="U4" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="142"/>
+      <c r="W4" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="143"/>
+      <c r="Y4" s="142" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="142"/>
+      <c r="AA4" s="142"/>
+      <c r="AB4" s="142"/>
+      <c r="AC4" s="142"/>
+      <c r="AD4" s="143" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="143"/>
+      <c r="AF4" s="143"/>
+      <c r="AG4" s="143"/>
+      <c r="AH4" s="143"/>
+      <c r="AI4" s="143"/>
+      <c r="AJ4" s="143"/>
+      <c r="AK4" s="143"/>
+      <c r="AL4" s="143"/>
+      <c r="AM4" s="143"/>
+      <c r="AN4" s="143"/>
+      <c r="AO4" s="143"/>
+      <c r="AP4" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="144"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Septiembre'!B6</f>
@@ -18769,10 +18769,10 @@
         <f>'Captura Septiembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="138"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -21339,16 +21339,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="139" t="s">
         <v>265</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="139"/>
+      <c r="AU19" s="139"/>
+      <c r="AV19" s="139"/>
+      <c r="AW19" s="139"/>
+      <c r="AX19" s="139"/>
+      <c r="AY19" s="139"/>
+      <c r="AZ19" s="139"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -21515,9 +21515,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="140"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -21544,11 +21544,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="141" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -21606,12 +21606,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -21626,6 +21620,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="38" priority="5" operator="greaterThanOrEqual">
@@ -21738,31 +21738,31 @@
       <c r="AA1" s="124"/>
       <c r="AB1" s="124"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="133" t="s">
         <v>267</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="133"/>
+      <c r="AU1" s="133"/>
+      <c r="AV1" s="133"/>
+      <c r="AW1" s="133"/>
+      <c r="AX1" s="133"/>
+      <c r="AY1" s="133"/>
+      <c r="AZ1" s="133"/>
+      <c r="BA1" s="133"/>
+      <c r="BB1" s="134" t="s">
         <v>268</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="134"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="135" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -21771,20 +21771,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="136" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="136"/>
+      <c r="AV2" s="136"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="137"/>
+      <c r="AZ2" s="137"/>
+      <c r="BA2" s="137"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -21832,66 +21832,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="142"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="142"/>
+      <c r="N4" s="142"/>
+      <c r="O4" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="142"/>
+      <c r="T4" s="142"/>
+      <c r="U4" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="142"/>
+      <c r="W4" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="143"/>
+      <c r="Y4" s="142" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="142"/>
+      <c r="AA4" s="142"/>
+      <c r="AB4" s="142"/>
+      <c r="AC4" s="142"/>
+      <c r="AD4" s="143" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="143"/>
+      <c r="AF4" s="143"/>
+      <c r="AG4" s="143"/>
+      <c r="AH4" s="143"/>
+      <c r="AI4" s="143"/>
+      <c r="AJ4" s="143"/>
+      <c r="AK4" s="143"/>
+      <c r="AL4" s="143"/>
+      <c r="AM4" s="143"/>
+      <c r="AN4" s="143"/>
+      <c r="AO4" s="143"/>
+      <c r="AP4" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="144"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Octubre'!B6</f>
@@ -22103,10 +22103,10 @@
         <f>'Captura Octubre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="138"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -24673,16 +24673,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="139" t="s">
         <v>270</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="139"/>
+      <c r="AU19" s="139"/>
+      <c r="AV19" s="139"/>
+      <c r="AW19" s="139"/>
+      <c r="AX19" s="139"/>
+      <c r="AY19" s="139"/>
+      <c r="AZ19" s="139"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -24849,9 +24849,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="140"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -24878,11 +24878,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="141" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -24940,12 +24940,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -24960,6 +24954,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="29" priority="5" operator="greaterThanOrEqual">
@@ -25072,31 +25072,31 @@
       <c r="AA1" s="124"/>
       <c r="AB1" s="124"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="133" t="s">
         <v>272</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="133"/>
+      <c r="AU1" s="133"/>
+      <c r="AV1" s="133"/>
+      <c r="AW1" s="133"/>
+      <c r="AX1" s="133"/>
+      <c r="AY1" s="133"/>
+      <c r="AZ1" s="133"/>
+      <c r="BA1" s="133"/>
+      <c r="BB1" s="134" t="s">
         <v>273</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="134"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="135" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -25105,20 +25105,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="136" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="136"/>
+      <c r="AV2" s="136"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="137"/>
+      <c r="AZ2" s="137"/>
+      <c r="BA2" s="137"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -25166,66 +25166,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="142"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="142"/>
+      <c r="N4" s="142"/>
+      <c r="O4" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="142"/>
+      <c r="T4" s="142"/>
+      <c r="U4" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="142"/>
+      <c r="W4" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="143"/>
+      <c r="Y4" s="142" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="142"/>
+      <c r="AA4" s="142"/>
+      <c r="AB4" s="142"/>
+      <c r="AC4" s="142"/>
+      <c r="AD4" s="143" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="143"/>
+      <c r="AF4" s="143"/>
+      <c r="AG4" s="143"/>
+      <c r="AH4" s="143"/>
+      <c r="AI4" s="143"/>
+      <c r="AJ4" s="143"/>
+      <c r="AK4" s="143"/>
+      <c r="AL4" s="143"/>
+      <c r="AM4" s="143"/>
+      <c r="AN4" s="143"/>
+      <c r="AO4" s="143"/>
+      <c r="AP4" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="144"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Noviembre'!B6</f>
@@ -25437,10 +25437,10 @@
         <f>'Captura Noviembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="138"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -28007,16 +28007,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="139" t="s">
         <v>275</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="139"/>
+      <c r="AU19" s="139"/>
+      <c r="AV19" s="139"/>
+      <c r="AW19" s="139"/>
+      <c r="AX19" s="139"/>
+      <c r="AY19" s="139"/>
+      <c r="AZ19" s="139"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -28183,9 +28183,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="140"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -28212,11 +28212,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="141" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -28274,12 +28274,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -28294,6 +28288,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="20" priority="5" operator="greaterThanOrEqual">
@@ -28406,31 +28406,31 @@
       <c r="AA1" s="124"/>
       <c r="AB1" s="124"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="133" t="s">
         <v>277</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="133"/>
+      <c r="AU1" s="133"/>
+      <c r="AV1" s="133"/>
+      <c r="AW1" s="133"/>
+      <c r="AX1" s="133"/>
+      <c r="AY1" s="133"/>
+      <c r="AZ1" s="133"/>
+      <c r="BA1" s="133"/>
+      <c r="BB1" s="134" t="s">
         <v>278</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="134"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="135" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -28439,20 +28439,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="136" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="136"/>
+      <c r="AV2" s="136"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="137"/>
+      <c r="AZ2" s="137"/>
+      <c r="BA2" s="137"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -28500,66 +28500,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="142"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="142"/>
+      <c r="N4" s="142"/>
+      <c r="O4" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="142"/>
+      <c r="T4" s="142"/>
+      <c r="U4" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="142"/>
+      <c r="W4" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="143"/>
+      <c r="Y4" s="142" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="142"/>
+      <c r="AA4" s="142"/>
+      <c r="AB4" s="142"/>
+      <c r="AC4" s="142"/>
+      <c r="AD4" s="143" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="143"/>
+      <c r="AF4" s="143"/>
+      <c r="AG4" s="143"/>
+      <c r="AH4" s="143"/>
+      <c r="AI4" s="143"/>
+      <c r="AJ4" s="143"/>
+      <c r="AK4" s="143"/>
+      <c r="AL4" s="143"/>
+      <c r="AM4" s="143"/>
+      <c r="AN4" s="143"/>
+      <c r="AO4" s="143"/>
+      <c r="AP4" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="144"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Diciembre'!B6</f>
@@ -28771,10 +28771,10 @@
         <f>'Captura Diciembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="138"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -31341,16 +31341,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="139" t="s">
         <v>280</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="139"/>
+      <c r="AU19" s="139"/>
+      <c r="AV19" s="139"/>
+      <c r="AW19" s="139"/>
+      <c r="AX19" s="139"/>
+      <c r="AY19" s="139"/>
+      <c r="AZ19" s="139"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -31517,9 +31517,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="140"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -31546,11 +31546,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="141" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -31608,12 +31608,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -31628,6 +31622,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThanOrEqual">
@@ -31825,7 +31825,7 @@
       </c>
       <c r="B13" s="97">
         <f>IF(AVERAGE('Captura Agosto'!D6:D20)=0,"",'Captura Agosto'!AQ23)</f>
-        <v>0.45861333333333326</v>
+        <v>0.36621333333333334</v>
       </c>
       <c r="C13" s="12" t="str">
         <f>IF(B13="","",IF(B13&gt;=Parametros!$C$37,"Verde",IF(B13&gt;=Parametros!$C$38,"Amarillo","Rojo")))</f>
@@ -32018,7 +32018,7 @@
       </c>
       <c r="I4" s="10">
         <f>IFERROR(IF('Captura Agosto'!D8=0,"",'Captura Agosto'!AQ8),"")</f>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="J4" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
@@ -32038,7 +32038,7 @@
       </c>
       <c r="N4" s="102">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.93874999999999997</v>
+        <v>0.94874999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32189,7 +32189,7 @@
       </c>
       <c r="I7" s="10">
         <f>IFERROR(IF('Captura Agosto'!D17=0,"",'Captura Agosto'!AQ17),"")</f>
-        <v>0.39160000000000006</v>
+        <v>0.26119999999999999</v>
       </c>
       <c r="J7" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
@@ -32209,7 +32209,7 @@
       </c>
       <c r="N7" s="102">
         <f t="shared" si="0"/>
-        <v>0.80916978021978025</v>
+        <v>0.79286978021978016</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32246,7 +32246,7 @@
       </c>
       <c r="I8" s="10">
         <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
-        <v>0.50039999999999996</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="J8" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="N8" s="102">
         <f t="shared" si="0"/>
-        <v>0.88255000000000006</v>
+        <v>0.86635000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32303,7 +32303,7 @@
       </c>
       <c r="I9" s="10">
         <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
-        <v>0.51</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="J9" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
@@ -32323,7 +32323,7 @@
       </c>
       <c r="N9" s="102">
         <f t="shared" si="0"/>
-        <v>0.88937500000000003</v>
+        <v>0.87687500000000007</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32360,7 +32360,7 @@
       </c>
       <c r="I10" s="10">
         <f>IFERROR(IF('Captura Agosto'!D13=0,"",'Captura Agosto'!AQ13),"")</f>
-        <v>0.39419999999999999</v>
+        <v>0.20819999999999997</v>
       </c>
       <c r="J10" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
@@ -32380,7 +32380,7 @@
       </c>
       <c r="N10" s="102">
         <f t="shared" si="0"/>
-        <v>0.77302499999999985</v>
+        <v>0.74977499999999986</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32474,7 +32474,7 @@
       </c>
       <c r="I12" s="10">
         <f>IFERROR(IF('Captura Agosto'!D9=0,"",'Captura Agosto'!AQ9),"")</f>
-        <v>0.42520000000000002</v>
+        <v>0.4052</v>
       </c>
       <c r="J12" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
@@ -32494,7 +32494,7 @@
       </c>
       <c r="N12" s="102">
         <f t="shared" si="0"/>
-        <v>0.91283750000000008</v>
+        <v>0.91033750000000002</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32531,7 +32531,7 @@
       </c>
       <c r="I13" s="10">
         <f>IFERROR(IF('Captura Agosto'!D12=0,"",'Captura Agosto'!AQ12),"")</f>
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="J13" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
@@ -32551,7 +32551,7 @@
       </c>
       <c r="N13" s="102">
         <f t="shared" si="0"/>
-        <v>0.80516304347826095</v>
+        <v>0.79891304347826098</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32588,7 +32588,7 @@
       </c>
       <c r="I14" s="10">
         <f>IFERROR(IF('Captura Agosto'!D15=0,"",'Captura Agosto'!AQ15),"")</f>
-        <v>0.46200000000000002</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="J14" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
@@ -32608,7 +32608,7 @@
       </c>
       <c r="N14" s="102">
         <f t="shared" si="0"/>
-        <v>0.80514766081871347</v>
+        <v>0.77389766081871347</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32645,7 +32645,7 @@
       </c>
       <c r="I15" s="10">
         <f>IFERROR(IF('Captura Agosto'!D7=0,"",'Captura Agosto'!AQ7),"")</f>
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="J15" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D7=0,"",'Captura Septiembre'!AQ7),"")</f>
@@ -32665,7 +32665,7 @@
       </c>
       <c r="N15" s="102">
         <f t="shared" si="0"/>
-        <v>0.74624999999999997</v>
+        <v>0.72125000000000006</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32702,7 +32702,7 @@
       </c>
       <c r="I16" s="10">
         <f>IFERROR(IF('Captura Agosto'!D20=0,"",'Captura Agosto'!AQ20),"")</f>
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="J16" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
@@ -32722,7 +32722,7 @@
       </c>
       <c r="N16" s="102">
         <f t="shared" si="0"/>
-        <v>0.89</v>
+        <v>0.88375000000000004</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32759,7 +32759,7 @@
       </c>
       <c r="I17" s="10">
         <f>IFERROR(IF('Captura Agosto'!D18=0,"",'Captura Agosto'!AQ18),"")</f>
-        <v>0.38739999999999997</v>
+        <v>0.28739999999999999</v>
       </c>
       <c r="J17" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
@@ -32779,7 +32779,7 @@
       </c>
       <c r="N17" s="102">
         <f t="shared" si="0"/>
-        <v>0.86558186274509796</v>
+        <v>0.85308186274509801</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32816,7 +32816,7 @@
       </c>
       <c r="I18" s="10">
         <f>IFERROR(IF('Captura Agosto'!D19=0,"",'Captura Agosto'!AQ19),"")</f>
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="J18" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
@@ -32836,7 +32836,7 @@
       </c>
       <c r="N18" s="102">
         <f t="shared" si="0"/>
-        <v>0.85031249999999992</v>
+        <v>0.81906249999999992</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -32873,7 +32873,7 @@
       </c>
       <c r="I19" s="104">
         <f t="shared" si="1"/>
-        <v>0.45861333333333326</v>
+        <v>0.36621333333333339</v>
       </c>
       <c r="J19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -33089,11 +33089,11 @@
       </c>
       <c r="C11" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X20"))</f>
-        <v>0.25</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="D11" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0.53333333333333333</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33108,7 +33108,7 @@
       </c>
       <c r="B14" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X20"))</f>
-        <v>0.25</v>
+        <v>0.13333333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33117,7 +33117,7 @@
       </c>
       <c r="B15" s="12">
         <f ca="1">COUNTIF(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X20"),"&gt;=0.04")</f>
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33208,7 +33208,7 @@
       </c>
       <c r="B24" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,2),$E$23:$E$37,0))</f>
-        <v>Equipos Auxiliares</v>
+        <v>Linea 4</v>
       </c>
       <c r="C24" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),2)</f>
@@ -33220,7 +33220,7 @@
       </c>
       <c r="E24" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ7")*100000-7</f>
-        <v>34993</v>
+        <v>14993</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -33229,7 +33229,7 @@
       </c>
       <c r="B25" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,3),$E$23:$E$37,0))</f>
-        <v>Materias Primas</v>
+        <v>ETEI</v>
       </c>
       <c r="C25" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),3)</f>
@@ -33241,7 +33241,7 @@
       </c>
       <c r="E25" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ8")*100000-8</f>
-        <v>50992</v>
+        <v>58992.000000000007</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33250,7 +33250,7 @@
       </c>
       <c r="B26" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,4),$E$23:$E$37,0))</f>
-        <v>Linea 4</v>
+        <v>Jarabes</v>
       </c>
       <c r="C26" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),4)</f>
@@ -33262,7 +33262,7 @@
       </c>
       <c r="E26" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ9")*100000-9</f>
-        <v>42511</v>
+        <v>40511</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33271,7 +33271,7 @@
       </c>
       <c r="B27" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,5),$E$23:$E$37,0))</f>
-        <v>Linea 2</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C27" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),5)</f>
@@ -33292,7 +33292,7 @@
       </c>
       <c r="B28" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,6),$E$23:$E$37,0))</f>
-        <v>Jarabes</v>
+        <v>Centro de Distribucion</v>
       </c>
       <c r="C28" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),6)</f>
@@ -33304,7 +33304,7 @@
       </c>
       <c r="E28" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ11")*100000-11</f>
-        <v>50989</v>
+        <v>40989</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33313,7 +33313,7 @@
       </c>
       <c r="B29" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,7),$E$23:$E$37,0))</f>
-        <v>ETEI</v>
+        <v>Linea 2</v>
       </c>
       <c r="C29" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),7)</f>
@@ -33325,7 +33325,7 @@
       </c>
       <c r="E29" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ12")*100000-12</f>
-        <v>49988</v>
+        <v>44988</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="B30" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,8),$E$23:$E$37,0))</f>
-        <v>Linea 3</v>
+        <v>Mantenimiento</v>
       </c>
       <c r="C30" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),8)</f>
@@ -33346,7 +33346,7 @@
       </c>
       <c r="E30" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ13")*100000-13</f>
-        <v>39407</v>
+        <v>20806.999999999996</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33355,7 +33355,7 @@
       </c>
       <c r="B31" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,9),$E$23:$E$37,0))</f>
-        <v>Centro de Distribucion</v>
+        <v>Linea 5</v>
       </c>
       <c r="C31" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),9)</f>
@@ -33367,7 +33367,7 @@
       </c>
       <c r="E31" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ14")*100000-14</f>
-        <v>50025.999999999993</v>
+        <v>37066</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33376,7 +33376,7 @@
       </c>
       <c r="B32" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,10),$E$23:$E$37,0))</f>
-        <v>Linea 1</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C32" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),10)</f>
@@ -33388,7 +33388,7 @@
       </c>
       <c r="E32" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ15")*100000-15</f>
-        <v>46185</v>
+        <v>21185.000000000004</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33397,7 +33397,7 @@
       </c>
       <c r="B33" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,11),$E$23:$E$37,0))</f>
-        <v>Linea 5</v>
+        <v>Linea 3</v>
       </c>
       <c r="C33" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),11)</f>
@@ -33418,7 +33418,7 @@
       </c>
       <c r="B34" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,12),$E$23:$E$37,0))</f>
-        <v>Mantenimiento</v>
+        <v>Linea 1</v>
       </c>
       <c r="C34" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),12)</f>
@@ -33430,7 +33430,7 @@
       </c>
       <c r="E34" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ17")*100000-17</f>
-        <v>39143.000000000007</v>
+        <v>26103</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33451,7 +33451,7 @@
       </c>
       <c r="E35" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ18")*100000-18</f>
-        <v>38722</v>
+        <v>28722</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33472,7 +33472,7 @@
       </c>
       <c r="E36" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ19")*100000-19</f>
-        <v>50981</v>
+        <v>25981</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33535,7 +33535,7 @@
       </c>
       <c r="B44" s="17">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ23")</f>
-        <v>0.45861333333333326</v>
+        <v>0.36621333333333334</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="I4" s="10">
         <f>IFERROR(IF('Captura Agosto'!D9=0,"",'Captura Agosto'!AQ9),"")</f>
-        <v>0.42520000000000002</v>
+        <v>0.4052</v>
       </c>
       <c r="J4" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
@@ -33704,7 +33704,7 @@
       </c>
       <c r="N4" s="102">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.91283750000000008</v>
+        <v>0.91033750000000002</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33741,7 +33741,7 @@
       </c>
       <c r="I5" s="10">
         <f>IFERROR(IF('Captura Agosto'!D8=0,"",'Captura Agosto'!AQ8),"")</f>
-        <v>0.51</v>
+        <v>0.59000000000000008</v>
       </c>
       <c r="J5" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
@@ -33761,7 +33761,7 @@
       </c>
       <c r="N5" s="102">
         <f t="shared" si="0"/>
-        <v>0.93874999999999997</v>
+        <v>0.94874999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="I7" s="10">
         <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
-        <v>0.50039999999999996</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="J7" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
@@ -33875,7 +33875,7 @@
       </c>
       <c r="N7" s="102">
         <f t="shared" si="0"/>
-        <v>0.88255000000000006</v>
+        <v>0.86635000000000006</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33912,7 +33912,7 @@
       </c>
       <c r="I8" s="10">
         <f>IFERROR(IF('Captura Agosto'!D20=0,"",'Captura Agosto'!AQ20),"")</f>
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="J8" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
@@ -33932,7 +33932,7 @@
       </c>
       <c r="N8" s="102">
         <f t="shared" si="0"/>
-        <v>0.89</v>
+        <v>0.88375000000000004</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33969,7 +33969,7 @@
       </c>
       <c r="I9" s="10">
         <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
-        <v>0.51</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="J9" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
@@ -33989,7 +33989,7 @@
       </c>
       <c r="N9" s="102">
         <f t="shared" si="0"/>
-        <v>0.88937500000000003</v>
+        <v>0.87687500000000007</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34083,7 +34083,7 @@
       </c>
       <c r="I11" s="10">
         <f>IFERROR(IF('Captura Agosto'!D18=0,"",'Captura Agosto'!AQ18),"")</f>
-        <v>0.38739999999999997</v>
+        <v>0.28739999999999999</v>
       </c>
       <c r="J11" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
@@ -34103,7 +34103,7 @@
       </c>
       <c r="N11" s="102">
         <f t="shared" si="0"/>
-        <v>0.86558186274509796</v>
+        <v>0.85308186274509801</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34197,7 +34197,7 @@
       </c>
       <c r="I13" s="10">
         <f>IFERROR(IF('Captura Agosto'!D19=0,"",'Captura Agosto'!AQ19),"")</f>
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="J13" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
@@ -34217,7 +34217,7 @@
       </c>
       <c r="N13" s="102">
         <f t="shared" si="0"/>
-        <v>0.85031249999999992</v>
+        <v>0.81906249999999992</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34254,7 +34254,7 @@
       </c>
       <c r="I14" s="10">
         <f>IFERROR(IF('Captura Agosto'!D17=0,"",'Captura Agosto'!AQ17),"")</f>
-        <v>0.39160000000000006</v>
+        <v>0.26119999999999999</v>
       </c>
       <c r="J14" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
@@ -34274,7 +34274,7 @@
       </c>
       <c r="N14" s="102">
         <f t="shared" si="0"/>
-        <v>0.80916978021978025</v>
+        <v>0.79286978021978016</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34311,7 +34311,7 @@
       </c>
       <c r="I15" s="10">
         <f>IFERROR(IF('Captura Agosto'!D12=0,"",'Captura Agosto'!AQ12),"")</f>
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="J15" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
@@ -34331,7 +34331,7 @@
       </c>
       <c r="N15" s="102">
         <f t="shared" si="0"/>
-        <v>0.80516304347826095</v>
+        <v>0.79891304347826098</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34368,7 +34368,7 @@
       </c>
       <c r="I16" s="10">
         <f>IFERROR(IF('Captura Agosto'!D15=0,"",'Captura Agosto'!AQ15),"")</f>
-        <v>0.46200000000000002</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="J16" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
@@ -34388,7 +34388,7 @@
       </c>
       <c r="N16" s="102">
         <f t="shared" si="0"/>
-        <v>0.80514766081871347</v>
+        <v>0.77389766081871347</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34425,7 +34425,7 @@
       </c>
       <c r="I17" s="10">
         <f>IFERROR(IF('Captura Agosto'!D13=0,"",'Captura Agosto'!AQ13),"")</f>
-        <v>0.39419999999999999</v>
+        <v>0.20819999999999997</v>
       </c>
       <c r="J17" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
@@ -34445,7 +34445,7 @@
       </c>
       <c r="N17" s="102">
         <f t="shared" si="0"/>
-        <v>0.77302499999999985</v>
+        <v>0.74977499999999986</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34482,7 +34482,7 @@
       </c>
       <c r="I18" s="10">
         <f>IFERROR(IF('Captura Agosto'!D7=0,"",'Captura Agosto'!AQ7),"")</f>
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="J18" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D7=0,"",'Captura Septiembre'!AQ7),"")</f>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="N18" s="102">
         <f t="shared" si="0"/>
-        <v>0.74624999999999997</v>
+        <v>0.72125000000000006</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -34539,7 +34539,7 @@
       </c>
       <c r="I19" s="104">
         <f t="shared" si="1"/>
-        <v>0.45861333333333326</v>
+        <v>0.36621333333333334</v>
       </c>
       <c r="J19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -34599,44 +34599,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="130" t="s">
+      <c r="B2" s="127" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="130"/>
-      <c r="Q2" s="130"/>
-      <c r="R2" s="130"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="127"/>
     </row>
     <row r="3" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="130"/>
-      <c r="Q3" s="130"/>
-      <c r="R3" s="130"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
+      <c r="R3" s="127"/>
     </row>
     <row r="4" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
@@ -34646,141 +34646,141 @@
         <f>Calculos!$B$2</f>
         <v>Agosto</v>
       </c>
-      <c r="F4" s="131" t="s">
+      <c r="F4" s="128" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="131"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="131"/>
-      <c r="N4" s="131"/>
-      <c r="O4" s="131"/>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="131"/>
-      <c r="R4" s="131"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="128"/>
+      <c r="L4" s="128"/>
+      <c r="M4" s="128"/>
+      <c r="N4" s="128"/>
+      <c r="O4" s="128"/>
+      <c r="P4" s="128"/>
+      <c r="Q4" s="128"/>
+      <c r="R4" s="128"/>
     </row>
     <row r="6" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="132" t="s">
+      <c r="B6" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="132"/>
-      <c r="D6" s="132"/>
-      <c r="E6" s="132"/>
-      <c r="F6" s="132" t="s">
+      <c r="C6" s="129"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="132"/>
-      <c r="H6" s="132"/>
-      <c r="I6" s="132"/>
-      <c r="J6" s="132" t="s">
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="129" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="132"/>
-      <c r="L6" s="132"/>
-      <c r="M6" s="132" t="s">
+      <c r="K6" s="129"/>
+      <c r="L6" s="129"/>
+      <c r="M6" s="129" t="s">
         <v>64</v>
       </c>
-      <c r="N6" s="132"/>
-      <c r="O6" s="132"/>
-      <c r="P6" s="132" t="s">
+      <c r="N6" s="129"/>
+      <c r="O6" s="129"/>
+      <c r="P6" s="129" t="s">
         <v>65</v>
       </c>
-      <c r="Q6" s="132"/>
-      <c r="R6" s="132"/>
+      <c r="Q6" s="129"/>
+      <c r="R6" s="129"/>
     </row>
     <row r="7" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="132"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="132"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="132"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="132"/>
-      <c r="M7" s="132"/>
-      <c r="N7" s="132"/>
-      <c r="O7" s="132"/>
-      <c r="P7" s="132"/>
-      <c r="Q7" s="132"/>
-      <c r="R7" s="132"/>
+      <c r="B7" s="129"/>
+      <c r="C7" s="129"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="129"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="129"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="129"/>
+      <c r="M7" s="129"/>
+      <c r="N7" s="129"/>
+      <c r="O7" s="129"/>
+      <c r="P7" s="129"/>
+      <c r="Q7" s="129"/>
+      <c r="R7" s="129"/>
     </row>
     <row r="8" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="125">
+      <c r="B8" s="130">
         <f ca="1">Calculos!B44</f>
-        <v>0.45861333333333326</v>
-      </c>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="126" t="str">
+        <v>0.36621333333333334</v>
+      </c>
+      <c r="C8" s="130"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="131" t="str">
         <f ca="1">Calculos!B45</f>
         <v>Rojo</v>
       </c>
-      <c r="G8" s="126"/>
-      <c r="H8" s="126"/>
-      <c r="I8" s="126"/>
-      <c r="J8" s="127">
+      <c r="G8" s="131"/>
+      <c r="H8" s="131"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="132">
         <f ca="1">Calculos!B40</f>
         <v>0</v>
       </c>
-      <c r="K8" s="127"/>
-      <c r="L8" s="127"/>
-      <c r="M8" s="128">
+      <c r="K8" s="132"/>
+      <c r="L8" s="132"/>
+      <c r="M8" s="125">
         <f ca="1">Calculos!B41</f>
         <v>0</v>
       </c>
-      <c r="N8" s="128"/>
-      <c r="O8" s="128"/>
-      <c r="P8" s="129">
+      <c r="N8" s="125"/>
+      <c r="O8" s="125"/>
+      <c r="P8" s="126">
         <f ca="1">Calculos!B42</f>
         <v>15</v>
       </c>
-      <c r="Q8" s="129"/>
-      <c r="R8" s="129"/>
+      <c r="Q8" s="126"/>
+      <c r="R8" s="126"/>
     </row>
     <row r="9" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="125"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="126"/>
-      <c r="J9" s="127"/>
-      <c r="K9" s="127"/>
-      <c r="L9" s="127"/>
-      <c r="M9" s="128"/>
-      <c r="N9" s="128"/>
-      <c r="O9" s="128"/>
-      <c r="P9" s="129"/>
-      <c r="Q9" s="129"/>
-      <c r="R9" s="129"/>
+      <c r="B9" s="130"/>
+      <c r="C9" s="130"/>
+      <c r="D9" s="130"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="131"/>
+      <c r="I9" s="131"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="132"/>
+      <c r="L9" s="132"/>
+      <c r="M9" s="125"/>
+      <c r="N9" s="125"/>
+      <c r="O9" s="125"/>
+      <c r="P9" s="126"/>
+      <c r="Q9" s="126"/>
+      <c r="R9" s="126"/>
     </row>
     <row r="10" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="126"/>
-      <c r="G10" s="126"/>
-      <c r="H10" s="126"/>
-      <c r="I10" s="126"/>
-      <c r="J10" s="127"/>
-      <c r="K10" s="127"/>
-      <c r="L10" s="127"/>
-      <c r="M10" s="128"/>
-      <c r="N10" s="128"/>
-      <c r="O10" s="128"/>
-      <c r="P10" s="129"/>
-      <c r="Q10" s="129"/>
-      <c r="R10" s="129"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="130"/>
+      <c r="D10" s="130"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="131"/>
+      <c r="G10" s="131"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="132"/>
+      <c r="K10" s="132"/>
+      <c r="L10" s="132"/>
+      <c r="M10" s="125"/>
+      <c r="N10" s="125"/>
+      <c r="O10" s="125"/>
+      <c r="P10" s="126"/>
+      <c r="Q10" s="126"/>
+      <c r="R10" s="126"/>
     </row>
     <row r="12" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="123" t="s">
@@ -34829,7 +34829,7 @@
     <row r="15" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="str">
         <f ca="1">Calculos!B24</f>
-        <v>Equipos Auxiliares</v>
+        <v>Linea 4</v>
       </c>
       <c r="C15" s="21">
         <f ca="1">Calculos!C24</f>
@@ -34847,7 +34847,7 @@
     <row r="16" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="str">
         <f ca="1">Calculos!B25</f>
-        <v>Materias Primas</v>
+        <v>ETEI</v>
       </c>
       <c r="C16" s="21">
         <f ca="1">Calculos!C25</f>
@@ -34865,7 +34865,7 @@
     <row r="17" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="str">
         <f ca="1">Calculos!B26</f>
-        <v>Linea 4</v>
+        <v>Jarabes</v>
       </c>
       <c r="C17" s="21">
         <f ca="1">Calculos!C26</f>
@@ -34883,7 +34883,7 @@
     <row r="18" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="str">
         <f ca="1">Calculos!B27</f>
-        <v>Linea 2</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C18" s="21">
         <f ca="1">Calculos!C27</f>
@@ -34901,7 +34901,7 @@
     <row r="19" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="3" t="str">
         <f ca="1">Calculos!B28</f>
-        <v>Jarabes</v>
+        <v>Centro de Distribucion</v>
       </c>
       <c r="C19" s="21">
         <f ca="1">Calculos!C28</f>
@@ -34919,7 +34919,7 @@
     <row r="20" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="str">
         <f ca="1">Calculos!B29</f>
-        <v>ETEI</v>
+        <v>Linea 2</v>
       </c>
       <c r="C20" s="21">
         <f ca="1">Calculos!C29</f>
@@ -34931,13 +34931,13 @@
       </c>
       <c r="H20" s="22">
         <f ca="1">Calculos!D11</f>
-        <v>1</v>
+        <v>0.53333333333333333</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="str">
         <f ca="1">Calculos!B30</f>
-        <v>Linea 3</v>
+        <v>Mantenimiento</v>
       </c>
       <c r="C21" s="21">
         <f ca="1">Calculos!C30</f>
@@ -34947,7 +34947,7 @@
     <row r="22" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="str">
         <f ca="1">Calculos!B31</f>
-        <v>Centro de Distribucion</v>
+        <v>Linea 5</v>
       </c>
       <c r="C22" s="21">
         <f ca="1">Calculos!C31</f>
@@ -34957,7 +34957,7 @@
     <row r="23" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="str">
         <f ca="1">Calculos!B32</f>
-        <v>Linea 1</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C23" s="21">
         <f ca="1">Calculos!C32</f>
@@ -34967,7 +34967,7 @@
     <row r="24" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="str">
         <f ca="1">Calculos!B33</f>
-        <v>Linea 5</v>
+        <v>Linea 3</v>
       </c>
       <c r="C24" s="21">
         <f ca="1">Calculos!C33</f>
@@ -34977,7 +34977,7 @@
     <row r="25" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="str">
         <f ca="1">Calculos!B34</f>
-        <v>Mantenimiento</v>
+        <v>Linea 1</v>
       </c>
       <c r="C25" s="21">
         <f ca="1">Calculos!C34</f>
@@ -35043,6 +35043,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B8:E10"/>
+    <mergeCell ref="F8:I10"/>
+    <mergeCell ref="J8:L10"/>
     <mergeCell ref="M8:O10"/>
     <mergeCell ref="P8:R10"/>
     <mergeCell ref="B2:R3"/>
@@ -35052,11 +35057,6 @@
     <mergeCell ref="J6:L7"/>
     <mergeCell ref="M6:O7"/>
     <mergeCell ref="P6:R7"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B8:E10"/>
-    <mergeCell ref="F8:I10"/>
-    <mergeCell ref="J8:L10"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -35086,61 +35086,61 @@
   <sheetData>
     <row r="1" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="108" t="s">
+      <c r="B2" s="116" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="109" t="s">
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="117" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
       <c r="H2" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="110" t="s">
+      <c r="B4" s="118" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110"/>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110"/>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
     </row>
     <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="111" t="str">
+      <c r="B5" s="119" t="str">
         <f>UPPER("Planta Cuyotenango  ·  "&amp;Calculos!$B$2&amp;" 2026  ·  Acumulado Año")</f>
         <v>PLANTA CUYOTENANGO  ·  AGOSTO 2026  ·  ACUMULADO AÑO</v>
       </c>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="111"/>
-      <c r="M5" s="111"/>
-      <c r="N5" s="111"/>
-      <c r="O5" s="111"/>
-      <c r="P5" s="111"/>
-      <c r="Q5" s="111"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="119"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="119"/>
+      <c r="N5" s="119"/>
+      <c r="O5" s="119"/>
+      <c r="P5" s="119"/>
+      <c r="Q5" s="119"/>
     </row>
     <row r="6" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="P6" s="28" t="s">
@@ -35151,7 +35151,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="112" t="str">
+      <c r="A7" s="106" t="str">
         <f>UPPER(Calculos!$B$2)</f>
         <v>AGOSTO</v>
       </c>
@@ -35168,13 +35168,13 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="112"/>
-      <c r="G8" s="113">
+      <c r="A8" s="106"/>
+      <c r="G8" s="107">
         <f ca="1">X31</f>
         <v>0</v>
       </c>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
       <c r="P8" s="31" t="s">
         <v>76</v>
       </c>
@@ -35184,15 +35184,15 @@
       </c>
     </row>
     <row r="9" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="112"/>
-      <c r="F9" s="114">
+      <c r="A9" s="106"/>
+      <c r="F9" s="108">
         <f ca="1">X32</f>
         <v>0</v>
       </c>
-      <c r="G9" s="114"/>
-      <c r="H9" s="114"/>
-      <c r="I9" s="114"/>
-      <c r="J9" s="114"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="108"/>
       <c r="P9" s="31" t="s">
         <v>77</v>
       </c>
@@ -35202,17 +35202,17 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="112"/>
-      <c r="E10" s="115">
+      <c r="A10" s="106"/>
+      <c r="E10" s="109">
         <f ca="1">X33</f>
         <v>0</v>
       </c>
-      <c r="F10" s="115"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="115"/>
-      <c r="K10" s="115"/>
+      <c r="F10" s="109"/>
+      <c r="G10" s="109"/>
+      <c r="H10" s="109"/>
+      <c r="I10" s="109"/>
+      <c r="J10" s="109"/>
+      <c r="K10" s="109"/>
       <c r="P10" s="31" t="s">
         <v>78</v>
       </c>
@@ -35222,19 +35222,19 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="112"/>
-      <c r="D11" s="116">
+      <c r="A11" s="106"/>
+      <c r="D11" s="110">
         <f ca="1">X34</f>
         <v>3</v>
       </c>
-      <c r="E11" s="116"/>
-      <c r="F11" s="116"/>
-      <c r="G11" s="116"/>
-      <c r="H11" s="116"/>
-      <c r="I11" s="116"/>
-      <c r="J11" s="116"/>
-      <c r="K11" s="116"/>
-      <c r="L11" s="116"/>
+      <c r="E11" s="110"/>
+      <c r="F11" s="110"/>
+      <c r="G11" s="110"/>
+      <c r="H11" s="110"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="110"/>
+      <c r="K11" s="110"/>
+      <c r="L11" s="110"/>
       <c r="P11" s="31" t="s">
         <v>79</v>
       </c>
@@ -35244,21 +35244,21 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="112"/>
-      <c r="C12" s="117">
+      <c r="A12" s="106"/>
+      <c r="C12" s="111">
         <f ca="1">X35</f>
         <v>0</v>
       </c>
-      <c r="D12" s="117"/>
-      <c r="E12" s="117"/>
-      <c r="F12" s="117"/>
-      <c r="G12" s="117"/>
-      <c r="H12" s="117"/>
-      <c r="I12" s="117"/>
-      <c r="J12" s="117"/>
-      <c r="K12" s="117"/>
-      <c r="L12" s="117"/>
-      <c r="M12" s="117"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="111"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="111"/>
       <c r="P12" s="31" t="s">
         <v>80</v>
       </c>
@@ -35268,23 +35268,23 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="112"/>
-      <c r="B13" s="118">
+      <c r="A13" s="106"/>
+      <c r="B13" s="112">
         <f ca="1">X36</f>
         <v>0</v>
       </c>
-      <c r="C13" s="118"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="118"/>
-      <c r="G13" s="118"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="118"/>
-      <c r="K13" s="118"/>
-      <c r="L13" s="118"/>
-      <c r="M13" s="118"/>
-      <c r="N13" s="118"/>
+      <c r="C13" s="112"/>
+      <c r="D13" s="112"/>
+      <c r="E13" s="112"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="112"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="112"/>
+      <c r="J13" s="112"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="112"/>
+      <c r="M13" s="112"/>
+      <c r="N13" s="112"/>
       <c r="P13" s="31" t="s">
         <v>81</v>
       </c>
@@ -35294,23 +35294,23 @@
       </c>
     </row>
     <row r="14" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="112"/>
-      <c r="B14" s="119">
+      <c r="A14" s="106"/>
+      <c r="B14" s="113">
         <f ca="1">X37</f>
         <v>0</v>
       </c>
-      <c r="C14" s="119"/>
-      <c r="D14" s="119"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="119"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="119"/>
-      <c r="J14" s="119"/>
-      <c r="K14" s="119"/>
-      <c r="L14" s="119"/>
-      <c r="M14" s="119"/>
-      <c r="N14" s="119"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="113"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="113"/>
+      <c r="M14" s="113"/>
+      <c r="N14" s="113"/>
       <c r="P14" s="31" t="s">
         <v>82</v>
       </c>
@@ -35321,22 +35321,22 @@
     </row>
     <row r="15" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="S16" s="106" t="s">
+      <c r="S16" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="T16" s="106"/>
-      <c r="U16" s="106"/>
-      <c r="V16" s="106"/>
+      <c r="T16" s="114"/>
+      <c r="U16" s="114"/>
+      <c r="V16" s="114"/>
     </row>
     <row r="17" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S18" s="35">
         <f ca="1">IF(T20="","—",INT(TODAY()-T20))</f>
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="U18" s="35">
         <f ca="1">IF(V20="","—",INT(TODAY()-V20))</f>
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -35365,11 +35365,11 @@
     <row r="22" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S22" s="35">
         <f ca="1">IF(T24="","—",INT(TODAY()-T24))</f>
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="U22" s="35">
         <f ca="1">IF(V24="","—",INT(TODAY()-V24))</f>
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -35397,42 +35397,42 @@
     <row r="25" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="2:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="107" t="s">
+      <c r="B27" s="115" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="107"/>
-      <c r="D27" s="107"/>
-      <c r="E27" s="107"/>
-      <c r="F27" s="107"/>
-      <c r="G27" s="107"/>
-      <c r="H27" s="107"/>
-      <c r="I27" s="107"/>
-      <c r="J27" s="107"/>
-      <c r="K27" s="107"/>
-      <c r="L27" s="107"/>
-      <c r="M27" s="107"/>
-      <c r="N27" s="107"/>
-      <c r="O27" s="107"/>
-      <c r="P27" s="107"/>
-      <c r="Q27" s="107"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="115"/>
+      <c r="L27" s="115"/>
+      <c r="M27" s="115"/>
+      <c r="N27" s="115"/>
+      <c r="O27" s="115"/>
+      <c r="P27" s="115"/>
+      <c r="Q27" s="115"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="107"/>
-      <c r="C28" s="107"/>
-      <c r="D28" s="107"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="107"/>
-      <c r="G28" s="107"/>
-      <c r="H28" s="107"/>
-      <c r="I28" s="107"/>
-      <c r="J28" s="107"/>
-      <c r="K28" s="107"/>
-      <c r="L28" s="107"/>
-      <c r="M28" s="107"/>
-      <c r="N28" s="107"/>
-      <c r="O28" s="107"/>
-      <c r="P28" s="107"/>
-      <c r="Q28" s="107"/>
+      <c r="B28" s="115"/>
+      <c r="C28" s="115"/>
+      <c r="D28" s="115"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="115"/>
+      <c r="G28" s="115"/>
+      <c r="H28" s="115"/>
+      <c r="I28" s="115"/>
+      <c r="J28" s="115"/>
+      <c r="K28" s="115"/>
+      <c r="L28" s="115"/>
+      <c r="M28" s="115"/>
+      <c r="N28" s="115"/>
+      <c r="O28" s="115"/>
+      <c r="P28" s="115"/>
+      <c r="Q28" s="115"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.35">
       <c r="W30" s="39" t="s">
@@ -35538,6 +35538,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="S16:V16"/>
+    <mergeCell ref="B27:Q28"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="B5:Q5"/>
     <mergeCell ref="A7:A14"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="F9:J9"/>
@@ -35546,12 +35552,6 @@
     <mergeCell ref="C12:M12"/>
     <mergeCell ref="B13:N13"/>
     <mergeCell ref="B14:N14"/>
-    <mergeCell ref="S16:V16"/>
-    <mergeCell ref="B27:Q28"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="B5:Q5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="E2" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -36217,31 +36217,31 @@
       <c r="AA1" s="124"/>
       <c r="AB1" s="124"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="133" t="s">
         <v>161</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="133"/>
+      <c r="AU1" s="133"/>
+      <c r="AV1" s="133"/>
+      <c r="AW1" s="133"/>
+      <c r="AX1" s="133"/>
+      <c r="AY1" s="133"/>
+      <c r="AZ1" s="133"/>
+      <c r="BA1" s="133"/>
+      <c r="BB1" s="134" t="s">
         <v>162</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="134"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="135" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -36250,20 +36250,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="136" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="136"/>
+      <c r="AV2" s="136"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="137"/>
+      <c r="AZ2" s="137"/>
+      <c r="BA2" s="137"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -36311,66 +36311,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="142"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="142"/>
+      <c r="N4" s="142"/>
+      <c r="O4" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="142"/>
+      <c r="T4" s="142"/>
+      <c r="U4" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="142"/>
+      <c r="W4" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="143"/>
+      <c r="Y4" s="142" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="142"/>
+      <c r="AA4" s="142"/>
+      <c r="AB4" s="142"/>
+      <c r="AC4" s="142"/>
+      <c r="AD4" s="143" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="143"/>
+      <c r="AF4" s="143"/>
+      <c r="AG4" s="143"/>
+      <c r="AH4" s="143"/>
+      <c r="AI4" s="143"/>
+      <c r="AJ4" s="143"/>
+      <c r="AK4" s="143"/>
+      <c r="AL4" s="143"/>
+      <c r="AM4" s="143"/>
+      <c r="AN4" s="143"/>
+      <c r="AO4" s="143"/>
+      <c r="AP4" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="144"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Enero'!B6</f>
@@ -36582,10 +36582,10 @@
         <f>'Captura Enero'!AQ7</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="138"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -39152,16 +39152,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="139" t="s">
         <v>224</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="139"/>
+      <c r="AU19" s="139"/>
+      <c r="AV19" s="139"/>
+      <c r="AW19" s="139"/>
+      <c r="AX19" s="139"/>
+      <c r="AY19" s="139"/>
+      <c r="AZ19" s="139"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93030769230769228</v>
@@ -39333,9 +39333,9 @@
       </c>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="140"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -39362,11 +39362,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="141" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -39424,12 +39424,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -39444,6 +39438,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="110" priority="5" operator="greaterThanOrEqual">
@@ -39556,31 +39556,31 @@
       <c r="AA1" s="124"/>
       <c r="AB1" s="124"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="133" t="s">
         <v>227</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="133"/>
+      <c r="AU1" s="133"/>
+      <c r="AV1" s="133"/>
+      <c r="AW1" s="133"/>
+      <c r="AX1" s="133"/>
+      <c r="AY1" s="133"/>
+      <c r="AZ1" s="133"/>
+      <c r="BA1" s="133"/>
+      <c r="BB1" s="134" t="s">
         <v>228</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="134"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="135" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -39589,20 +39589,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="136" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="136"/>
+      <c r="AV2" s="136"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="137"/>
+      <c r="AZ2" s="137"/>
+      <c r="BA2" s="137"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -39650,66 +39650,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="142"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="142"/>
+      <c r="N4" s="142"/>
+      <c r="O4" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="142"/>
+      <c r="T4" s="142"/>
+      <c r="U4" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="142"/>
+      <c r="W4" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="143"/>
+      <c r="Y4" s="142" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="142"/>
+      <c r="AA4" s="142"/>
+      <c r="AB4" s="142"/>
+      <c r="AC4" s="142"/>
+      <c r="AD4" s="143" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="143"/>
+      <c r="AF4" s="143"/>
+      <c r="AG4" s="143"/>
+      <c r="AH4" s="143"/>
+      <c r="AI4" s="143"/>
+      <c r="AJ4" s="143"/>
+      <c r="AK4" s="143"/>
+      <c r="AL4" s="143"/>
+      <c r="AM4" s="143"/>
+      <c r="AN4" s="143"/>
+      <c r="AO4" s="143"/>
+      <c r="AP4" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="144"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Febrero'!B6</f>
@@ -39921,10 +39921,10 @@
         <f>'Captura Febrero'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="138"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -42491,16 +42491,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="139" t="s">
         <v>230</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="139"/>
+      <c r="AU19" s="139"/>
+      <c r="AV19" s="139"/>
+      <c r="AW19" s="139"/>
+      <c r="AX19" s="139"/>
+      <c r="AY19" s="139"/>
+      <c r="AZ19" s="139"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.9572597670647206</v>
@@ -42667,9 +42667,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="140"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -42696,11 +42696,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="141" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -42758,12 +42758,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -42778,6 +42772,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="101" priority="5" operator="greaterThanOrEqual">
@@ -42890,31 +42890,31 @@
       <c r="AA1" s="124"/>
       <c r="AB1" s="124"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="133" t="s">
         <v>232</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="133"/>
+      <c r="AU1" s="133"/>
+      <c r="AV1" s="133"/>
+      <c r="AW1" s="133"/>
+      <c r="AX1" s="133"/>
+      <c r="AY1" s="133"/>
+      <c r="AZ1" s="133"/>
+      <c r="BA1" s="133"/>
+      <c r="BB1" s="134" t="s">
         <v>233</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="134"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="135" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -42923,20 +42923,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="136" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="136"/>
+      <c r="AV2" s="136"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="137"/>
+      <c r="AZ2" s="137"/>
+      <c r="BA2" s="137"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -42984,66 +42984,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="142"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="142"/>
+      <c r="N4" s="142"/>
+      <c r="O4" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="142"/>
+      <c r="T4" s="142"/>
+      <c r="U4" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="142"/>
+      <c r="W4" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="143"/>
+      <c r="Y4" s="142" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="142"/>
+      <c r="AA4" s="142"/>
+      <c r="AB4" s="142"/>
+      <c r="AC4" s="142"/>
+      <c r="AD4" s="143" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="143"/>
+      <c r="AF4" s="143"/>
+      <c r="AG4" s="143"/>
+      <c r="AH4" s="143"/>
+      <c r="AI4" s="143"/>
+      <c r="AJ4" s="143"/>
+      <c r="AK4" s="143"/>
+      <c r="AL4" s="143"/>
+      <c r="AM4" s="143"/>
+      <c r="AN4" s="143"/>
+      <c r="AO4" s="143"/>
+      <c r="AP4" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="144"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Marzo'!B6</f>
@@ -43255,10 +43255,10 @@
         <f>'Captura Marzo'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="138"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -45825,16 +45825,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="139" t="s">
         <v>235</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="139"/>
+      <c r="AU19" s="139"/>
+      <c r="AV19" s="139"/>
+      <c r="AW19" s="139"/>
+      <c r="AX19" s="139"/>
+      <c r="AY19" s="139"/>
+      <c r="AZ19" s="139"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.99283333333333335</v>
@@ -46001,9 +46001,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="140"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -46030,11 +46030,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="141" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -46092,12 +46092,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -46112,6 +46106,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="92" priority="5" operator="greaterThanOrEqual">
@@ -46224,31 +46224,31 @@
       <c r="AA1" s="124"/>
       <c r="AB1" s="124"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="133" t="s">
         <v>237</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="133"/>
+      <c r="AU1" s="133"/>
+      <c r="AV1" s="133"/>
+      <c r="AW1" s="133"/>
+      <c r="AX1" s="133"/>
+      <c r="AY1" s="133"/>
+      <c r="AZ1" s="133"/>
+      <c r="BA1" s="133"/>
+      <c r="BB1" s="134" t="s">
         <v>238</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="134"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="135" t="s">
         <v>239</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -46257,20 +46257,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="136" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="136"/>
+      <c r="AV2" s="136"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="137" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="137"/>
+      <c r="AZ2" s="137"/>
+      <c r="BA2" s="137"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -46318,66 +46318,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="142" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="142" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="142"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="142"/>
+      <c r="N4" s="142"/>
+      <c r="O4" s="142" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
+      <c r="R4" s="142" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="142"/>
+      <c r="T4" s="142"/>
+      <c r="U4" s="142" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="142"/>
+      <c r="W4" s="143" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="143"/>
+      <c r="Y4" s="142" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="142"/>
+      <c r="AA4" s="142"/>
+      <c r="AB4" s="142"/>
+      <c r="AC4" s="142"/>
+      <c r="AD4" s="143" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="143"/>
+      <c r="AF4" s="143"/>
+      <c r="AG4" s="143"/>
+      <c r="AH4" s="143"/>
+      <c r="AI4" s="143"/>
+      <c r="AJ4" s="143"/>
+      <c r="AK4" s="143"/>
+      <c r="AL4" s="143"/>
+      <c r="AM4" s="143"/>
+      <c r="AN4" s="143"/>
+      <c r="AO4" s="143"/>
+      <c r="AP4" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="144"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Abril'!B6</f>
@@ -46589,10 +46589,10 @@
         <f>'Captura Abril'!AQ7</f>
         <v>0.71000000000000008</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="138"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -49159,16 +49159,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="139" t="s">
         <v>240</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="139"/>
+      <c r="AU19" s="139"/>
+      <c r="AV19" s="139"/>
+      <c r="AW19" s="139"/>
+      <c r="AX19" s="139"/>
+      <c r="AY19" s="139"/>
+      <c r="AZ19" s="139"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93466666666666676</v>
@@ -49335,9 +49335,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="140"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -49364,11 +49364,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="141" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -49426,12 +49426,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -49446,6 +49440,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="83" priority="5" operator="greaterThanOrEqual">
@@ -49503,4 +49503,294 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003E33BA48D1B17740BD20DC3C1E7D6897" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c5918174441eb6b55e4531b53824222f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbb49d05-d3df-47ef-b263-f54790ad9dd3" xmlns:ns3="4bae7dba-0f75-4d38-a352-dd7a188b5c30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9432285c6019c8f9bf7f2f5b0ebbd793" ns2:_="" ns3:_="">
+    <xsd:import namespace="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
+    <xsd:import namespace="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="fbb49d05-d3df-47ef-b263-f54790ad9dd3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="11" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="12" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="101546eb-6c89-4d85-9347-36ceb32eb3b1" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="24" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="4bae7dba-0f75-4d38-a352-dd7a188b5c30" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="15" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="16" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{1dc30bec-998c-489f-bd61-9ad91e547014}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="4bae7dba-0f75-4d38-a352-dd7a188b5c30">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5821DFA2-D31E-48EB-BA9F-E1C7FBC547E5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A29B98D3-CD8F-4DEC-9477-47DD9974BEE9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D19223-1C31-49B9-BB39-EF2DA560B2DA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
+    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
+++ b/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc.sharepoint.com/sites/CharlascortasSSOsemanalesCuyotenango/Shared Documents/General/04. Registros 2026/09. Nivel De Seguridad/NUEVO NIVEL DE SEGURIDAD - 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{1FA93C17-BEC0-435F-87D9-564EB45A6C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F51E74CC-AD1D-4D6B-8C5E-ABF6DCC1A68E}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{1FA93C17-BEC0-435F-87D9-564EB45A6C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7A4C16D-D173-48C3-9BE4-7F43BA5F2DD2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="867" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="Portada" sheetId="1" r:id="rId1"/>
     <sheet name="Calculos" sheetId="2" r:id="rId2"/>
     <sheet name="Dashboard Ejecutivo" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="Triángulo Accidentabilidad" sheetId="4" r:id="rId4"/>
-    <sheet name="Parametros" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="Triángulo Accidentabilidad" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Parametros" sheetId="5" r:id="rId5"/>
     <sheet name="Captura Enero" sheetId="6" state="hidden" r:id="rId6"/>
     <sheet name="Captura Febrero" sheetId="7" state="hidden" r:id="rId7"/>
     <sheet name="Captura Marzo" sheetId="8" state="hidden" r:id="rId8"/>
@@ -35,10 +35,10 @@
     <sheet name="ACUMULADO - 2026" sheetId="20" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'ACUMULADO - 2026'!$A$3:$N$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'ACUMULADO - 2026'!$A$3:$N$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Dashboard Ejecutivo'!$A$1:$Y$75</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2067,6 +2067,59 @@
     <xf numFmtId="10" fontId="54" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -2091,74 +2144,6 @@
     <xf numFmtId="1" fontId="27" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2179,6 +2164,21 @@
     </xf>
     <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3238,10 +3238,10 @@
                   <c:v>Linea 3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Linea 1</c:v>
+                  <c:v>Alrededores</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Alrededores</c:v>
+                  <c:v>Linea 1</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Almacen de Repuestos</c:v>
@@ -3628,16 +3628,16 @@
                   <c:v>0.86666666666666647</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.82599999999999996</c:v>
+                  <c:v>0.89266666666666672</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.82599999999999996</c:v>
+                  <c:v>0.89266666666666672</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1.1111111111111112</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.97786666666666677</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.53333333333333333</c:v>
@@ -4306,7 +4306,7 @@
                   <c:v>0.88027777777777783</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.36621333333333334</c:v>
+                  <c:v>0.61868000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -4852,38 +4852,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="121" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
+      <c r="B3" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
     </row>
     <row r="4" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="121"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
     </row>
     <row r="5" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="121"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
     </row>
     <row r="6" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="121"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
+      <c r="B6" s="109"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="109"/>
     </row>
     <row r="7" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="122" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
+      <c r="B7" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
     </row>
     <row r="10" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C13" s="4">
         <f ca="1">TODAY()</f>
-        <v>46255</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4937,72 +4937,72 @@
       </c>
     </row>
     <row r="18" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="123" t="s">
+      <c r="B18" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="123"/>
-      <c r="D18" s="123"/>
-      <c r="E18" s="123"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="106"/>
+      <c r="E18" s="106"/>
     </row>
     <row r="19" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="120" t="s">
+      <c r="C19" s="108" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="120"/>
-      <c r="E19" s="120"/>
+      <c r="D19" s="108"/>
+      <c r="E19" s="108"/>
     </row>
     <row r="20" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="120" t="s">
+      <c r="C20" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="120"/>
-      <c r="E20" s="120"/>
+      <c r="D20" s="108"/>
+      <c r="E20" s="108"/>
     </row>
     <row r="21" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="120" t="s">
+      <c r="C21" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="120"/>
-      <c r="E21" s="120"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="108"/>
     </row>
     <row r="22" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="120" t="s">
+      <c r="C22" s="108" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="120"/>
-      <c r="E22" s="120"/>
+      <c r="D22" s="108"/>
+      <c r="E22" s="108"/>
     </row>
     <row r="23" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="120" t="s">
+      <c r="C23" s="108" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="120"/>
-      <c r="E23" s="120"/>
+      <c r="D23" s="108"/>
+      <c r="E23" s="108"/>
     </row>
     <row r="24" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="120" t="s">
+      <c r="C24" s="108" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="120"/>
-      <c r="E24" s="120"/>
+      <c r="D24" s="108"/>
+      <c r="E24" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -5043,62 +5043,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="107" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="133" t="s">
+      <c r="AS1" s="140" t="s">
         <v>242</v>
       </c>
-      <c r="AT1" s="133"/>
-      <c r="AU1" s="133"/>
-      <c r="AV1" s="133"/>
-      <c r="AW1" s="133"/>
-      <c r="AX1" s="133"/>
-      <c r="AY1" s="133"/>
-      <c r="AZ1" s="133"/>
-      <c r="BA1" s="133"/>
-      <c r="BB1" s="134" t="s">
+      <c r="AT1" s="140"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="140"/>
+      <c r="AW1" s="140"/>
+      <c r="AX1" s="140"/>
+      <c r="AY1" s="140"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="140"/>
+      <c r="BB1" s="141" t="s">
         <v>243</v>
       </c>
-      <c r="BC1" s="134"/>
+      <c r="BC1" s="141"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="142" t="s">
         <v>244</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -5107,20 +5107,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="136" t="s">
+      <c r="AT2" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="136"/>
-      <c r="AV2" s="136"/>
+      <c r="AU2" s="143"/>
+      <c r="AV2" s="143"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="137" t="s">
+      <c r="AX2" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="137"/>
-      <c r="AZ2" s="137"/>
-      <c r="BA2" s="137"/>
+      <c r="AY2" s="144"/>
+      <c r="AZ2" s="144"/>
+      <c r="BA2" s="144"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -5168,66 +5168,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="137" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142" t="s">
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142" t="s">
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="142"/>
-      <c r="N4" s="142"/>
-      <c r="O4" s="142" t="s">
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="142"/>
-      <c r="Q4" s="142"/>
-      <c r="R4" s="142" t="s">
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="142"/>
-      <c r="T4" s="142"/>
-      <c r="U4" s="142" t="s">
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="142"/>
-      <c r="W4" s="143" t="s">
+      <c r="V4" s="137"/>
+      <c r="W4" s="138" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="143"/>
-      <c r="Y4" s="142" t="s">
+      <c r="X4" s="138"/>
+      <c r="Y4" s="137" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="142"/>
-      <c r="AA4" s="142"/>
-      <c r="AB4" s="142"/>
-      <c r="AC4" s="142"/>
-      <c r="AD4" s="143" t="s">
+      <c r="Z4" s="137"/>
+      <c r="AA4" s="137"/>
+      <c r="AB4" s="137"/>
+      <c r="AC4" s="137"/>
+      <c r="AD4" s="138" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="143"/>
-      <c r="AF4" s="143"/>
-      <c r="AG4" s="143"/>
-      <c r="AH4" s="143"/>
-      <c r="AI4" s="143"/>
-      <c r="AJ4" s="143"/>
-      <c r="AK4" s="143"/>
-      <c r="AL4" s="143"/>
-      <c r="AM4" s="143"/>
-      <c r="AN4" s="143"/>
-      <c r="AO4" s="143"/>
-      <c r="AP4" s="144" t="s">
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138"/>
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="138"/>
+      <c r="AJ4" s="138"/>
+      <c r="AK4" s="138"/>
+      <c r="AL4" s="138"/>
+      <c r="AM4" s="138"/>
+      <c r="AN4" s="138"/>
+      <c r="AO4" s="138"/>
+      <c r="AP4" s="139" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="144"/>
+      <c r="AQ4" s="139"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Mayo'!B6</f>
@@ -5439,10 +5439,10 @@
         <f>'Captura Mayo'!AQ7</f>
         <v>0.69000000000000006</v>
       </c>
-      <c r="BB5" s="138" t="s">
+      <c r="BB5" s="133" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="138"/>
+      <c r="BC5" s="133"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -8009,16 +8009,16 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="139" t="s">
+      <c r="AS19" s="134" t="s">
         <v>245</v>
       </c>
-      <c r="AT19" s="139"/>
-      <c r="AU19" s="139"/>
-      <c r="AV19" s="139"/>
-      <c r="AW19" s="139"/>
-      <c r="AX19" s="139"/>
-      <c r="AY19" s="139"/>
-      <c r="AZ19" s="139"/>
+      <c r="AT19" s="134"/>
+      <c r="AU19" s="134"/>
+      <c r="AV19" s="134"/>
+      <c r="AW19" s="134"/>
+      <c r="AX19" s="134"/>
+      <c r="AY19" s="134"/>
+      <c r="AZ19" s="134"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.87666666666666671</v>
@@ -8185,9 +8185,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="140"/>
-      <c r="B22" s="140"/>
-      <c r="C22" s="140"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -8214,11 +8214,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="141" t="s">
+      <c r="A23" s="136" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -8276,6 +8276,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -8290,12 +8296,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="74" priority="5" operator="greaterThanOrEqual">
@@ -8377,62 +8377,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="107" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="133" t="s">
+      <c r="AS1" s="140" t="s">
         <v>247</v>
       </c>
-      <c r="AT1" s="133"/>
-      <c r="AU1" s="133"/>
-      <c r="AV1" s="133"/>
-      <c r="AW1" s="133"/>
-      <c r="AX1" s="133"/>
-      <c r="AY1" s="133"/>
-      <c r="AZ1" s="133"/>
-      <c r="BA1" s="133"/>
-      <c r="BB1" s="134" t="s">
+      <c r="AT1" s="140"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="140"/>
+      <c r="AW1" s="140"/>
+      <c r="AX1" s="140"/>
+      <c r="AY1" s="140"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="140"/>
+      <c r="BB1" s="141" t="s">
         <v>248</v>
       </c>
-      <c r="BC1" s="134"/>
+      <c r="BC1" s="141"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="142" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -8441,20 +8441,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="136" t="s">
+      <c r="AT2" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="136"/>
-      <c r="AV2" s="136"/>
+      <c r="AU2" s="143"/>
+      <c r="AV2" s="143"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="137" t="s">
+      <c r="AX2" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="137"/>
-      <c r="AZ2" s="137"/>
-      <c r="BA2" s="137"/>
+      <c r="AY2" s="144"/>
+      <c r="AZ2" s="144"/>
+      <c r="BA2" s="144"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -8502,66 +8502,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="137" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142" t="s">
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142" t="s">
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="142"/>
-      <c r="N4" s="142"/>
-      <c r="O4" s="142" t="s">
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="142"/>
-      <c r="Q4" s="142"/>
-      <c r="R4" s="142" t="s">
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="142"/>
-      <c r="T4" s="142"/>
-      <c r="U4" s="142" t="s">
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="142"/>
-      <c r="W4" s="143" t="s">
+      <c r="V4" s="137"/>
+      <c r="W4" s="138" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="143"/>
-      <c r="Y4" s="142" t="s">
+      <c r="X4" s="138"/>
+      <c r="Y4" s="137" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="142"/>
-      <c r="AA4" s="142"/>
-      <c r="AB4" s="142"/>
-      <c r="AC4" s="142"/>
-      <c r="AD4" s="143" t="s">
+      <c r="Z4" s="137"/>
+      <c r="AA4" s="137"/>
+      <c r="AB4" s="137"/>
+      <c r="AC4" s="137"/>
+      <c r="AD4" s="138" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="143"/>
-      <c r="AF4" s="143"/>
-      <c r="AG4" s="143"/>
-      <c r="AH4" s="143"/>
-      <c r="AI4" s="143"/>
-      <c r="AJ4" s="143"/>
-      <c r="AK4" s="143"/>
-      <c r="AL4" s="143"/>
-      <c r="AM4" s="143"/>
-      <c r="AN4" s="143"/>
-      <c r="AO4" s="143"/>
-      <c r="AP4" s="144" t="s">
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138"/>
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="138"/>
+      <c r="AJ4" s="138"/>
+      <c r="AK4" s="138"/>
+      <c r="AL4" s="138"/>
+      <c r="AM4" s="138"/>
+      <c r="AN4" s="138"/>
+      <c r="AO4" s="138"/>
+      <c r="AP4" s="139" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="144"/>
+      <c r="AQ4" s="139"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Junio'!B6</f>
@@ -8773,10 +8773,10 @@
         <f>'Captura Junio'!AQ7</f>
         <v>0.64000000000000012</v>
       </c>
-      <c r="BB5" s="138" t="s">
+      <c r="BB5" s="133" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="138"/>
+      <c r="BC5" s="133"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -11343,16 +11343,16 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="139" t="s">
+      <c r="AS19" s="134" t="s">
         <v>250</v>
       </c>
-      <c r="AT19" s="139"/>
-      <c r="AU19" s="139"/>
-      <c r="AV19" s="139"/>
-      <c r="AW19" s="139"/>
-      <c r="AX19" s="139"/>
-      <c r="AY19" s="139"/>
-      <c r="AZ19" s="139"/>
+      <c r="AT19" s="134"/>
+      <c r="AU19" s="134"/>
+      <c r="AV19" s="134"/>
+      <c r="AW19" s="134"/>
+      <c r="AX19" s="134"/>
+      <c r="AY19" s="134"/>
+      <c r="AZ19" s="134"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.83357372900851168</v>
@@ -11519,9 +11519,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="140"/>
-      <c r="B22" s="140"/>
-      <c r="C22" s="140"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -11548,11 +11548,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="141" t="s">
+      <c r="A23" s="136" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -11610,6 +11610,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -11624,12 +11630,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="greaterThanOrEqual">
@@ -11713,62 +11713,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="107" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="133" t="s">
+      <c r="AS1" s="140" t="s">
         <v>252</v>
       </c>
-      <c r="AT1" s="133"/>
-      <c r="AU1" s="133"/>
-      <c r="AV1" s="133"/>
-      <c r="AW1" s="133"/>
-      <c r="AX1" s="133"/>
-      <c r="AY1" s="133"/>
-      <c r="AZ1" s="133"/>
-      <c r="BA1" s="133"/>
-      <c r="BB1" s="134" t="s">
+      <c r="AT1" s="140"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="140"/>
+      <c r="AW1" s="140"/>
+      <c r="AX1" s="140"/>
+      <c r="AY1" s="140"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="140"/>
+      <c r="BB1" s="141" t="s">
         <v>253</v>
       </c>
-      <c r="BC1" s="134"/>
+      <c r="BC1" s="141"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="142" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -11777,20 +11777,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="136" t="s">
+      <c r="AT2" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="136"/>
-      <c r="AV2" s="136"/>
+      <c r="AU2" s="143"/>
+      <c r="AV2" s="143"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="137" t="s">
+      <c r="AX2" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="137"/>
-      <c r="AZ2" s="137"/>
-      <c r="BA2" s="137"/>
+      <c r="AY2" s="144"/>
+      <c r="AZ2" s="144"/>
+      <c r="BA2" s="144"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -11838,66 +11838,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="137" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142" t="s">
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142" t="s">
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="142"/>
-      <c r="N4" s="142"/>
-      <c r="O4" s="142" t="s">
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="142"/>
-      <c r="Q4" s="142"/>
-      <c r="R4" s="142" t="s">
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="142"/>
-      <c r="T4" s="142"/>
-      <c r="U4" s="142" t="s">
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="142"/>
-      <c r="W4" s="143" t="s">
+      <c r="V4" s="137"/>
+      <c r="W4" s="138" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="143"/>
-      <c r="Y4" s="142" t="s">
+      <c r="X4" s="138"/>
+      <c r="Y4" s="137" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="142"/>
-      <c r="AA4" s="142"/>
-      <c r="AB4" s="142"/>
-      <c r="AC4" s="142"/>
-      <c r="AD4" s="143" t="s">
+      <c r="Z4" s="137"/>
+      <c r="AA4" s="137"/>
+      <c r="AB4" s="137"/>
+      <c r="AC4" s="137"/>
+      <c r="AD4" s="138" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="143"/>
-      <c r="AF4" s="143"/>
-      <c r="AG4" s="143"/>
-      <c r="AH4" s="143"/>
-      <c r="AI4" s="143"/>
-      <c r="AJ4" s="143"/>
-      <c r="AK4" s="143"/>
-      <c r="AL4" s="143"/>
-      <c r="AM4" s="143"/>
-      <c r="AN4" s="143"/>
-      <c r="AO4" s="143"/>
-      <c r="AP4" s="144" t="s">
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138"/>
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="138"/>
+      <c r="AJ4" s="138"/>
+      <c r="AK4" s="138"/>
+      <c r="AL4" s="138"/>
+      <c r="AM4" s="138"/>
+      <c r="AN4" s="138"/>
+      <c r="AO4" s="138"/>
+      <c r="AP4" s="139" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="144"/>
+      <c r="AQ4" s="139"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Julio'!B6</f>
@@ -12109,10 +12109,10 @@
         <f>'Captura Julio'!AQ7</f>
         <v>0.64</v>
       </c>
-      <c r="BB5" s="138" t="s">
+      <c r="BB5" s="133" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="138"/>
+      <c r="BC5" s="133"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -14679,16 +14679,16 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="139" t="s">
+      <c r="AS19" s="134" t="s">
         <v>255</v>
       </c>
-      <c r="AT19" s="139"/>
-      <c r="AU19" s="139"/>
-      <c r="AV19" s="139"/>
-      <c r="AW19" s="139"/>
-      <c r="AX19" s="139"/>
-      <c r="AY19" s="139"/>
-      <c r="AZ19" s="139"/>
+      <c r="AT19" s="134"/>
+      <c r="AU19" s="134"/>
+      <c r="AV19" s="134"/>
+      <c r="AW19" s="134"/>
+      <c r="AX19" s="134"/>
+      <c r="AY19" s="134"/>
+      <c r="AZ19" s="134"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.88027777777777783</v>
@@ -14855,9 +14855,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="140"/>
-      <c r="B22" s="140"/>
-      <c r="C22" s="140"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -14884,11 +14884,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="141" t="s">
+      <c r="A23" s="136" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -14946,6 +14946,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -14960,12 +14966,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="56" priority="5" operator="greaterThanOrEqual">
@@ -15047,62 +15047,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="107" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="133" t="s">
+      <c r="AS1" s="140" t="s">
         <v>257</v>
       </c>
-      <c r="AT1" s="133"/>
-      <c r="AU1" s="133"/>
-      <c r="AV1" s="133"/>
-      <c r="AW1" s="133"/>
-      <c r="AX1" s="133"/>
-      <c r="AY1" s="133"/>
-      <c r="AZ1" s="133"/>
-      <c r="BA1" s="133"/>
-      <c r="BB1" s="134" t="s">
+      <c r="AT1" s="140"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="140"/>
+      <c r="AW1" s="140"/>
+      <c r="AX1" s="140"/>
+      <c r="AY1" s="140"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="140"/>
+      <c r="BB1" s="141" t="s">
         <v>258</v>
       </c>
-      <c r="BC1" s="134"/>
+      <c r="BC1" s="141"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="142" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -15111,20 +15111,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="136" t="s">
+      <c r="AT2" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="136"/>
-      <c r="AV2" s="136"/>
+      <c r="AU2" s="143"/>
+      <c r="AV2" s="143"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="137" t="s">
+      <c r="AX2" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="137"/>
-      <c r="AZ2" s="137"/>
-      <c r="BA2" s="137"/>
+      <c r="AY2" s="144"/>
+      <c r="AZ2" s="144"/>
+      <c r="BA2" s="144"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -15165,73 +15165,73 @@
         <v>180</v>
       </c>
       <c r="BC3" s="69">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="137" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142" t="s">
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142" t="s">
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="142"/>
-      <c r="N4" s="142"/>
-      <c r="O4" s="142" t="s">
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="142"/>
-      <c r="Q4" s="142"/>
-      <c r="R4" s="142" t="s">
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="142"/>
-      <c r="T4" s="142"/>
-      <c r="U4" s="142" t="s">
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="142"/>
-      <c r="W4" s="143" t="s">
+      <c r="V4" s="137"/>
+      <c r="W4" s="138" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="143"/>
-      <c r="Y4" s="142" t="s">
+      <c r="X4" s="138"/>
+      <c r="Y4" s="137" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="142"/>
-      <c r="AA4" s="142"/>
-      <c r="AB4" s="142"/>
-      <c r="AC4" s="142"/>
-      <c r="AD4" s="143" t="s">
+      <c r="Z4" s="137"/>
+      <c r="AA4" s="137"/>
+      <c r="AB4" s="137"/>
+      <c r="AC4" s="137"/>
+      <c r="AD4" s="138" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="143"/>
-      <c r="AF4" s="143"/>
-      <c r="AG4" s="143"/>
-      <c r="AH4" s="143"/>
-      <c r="AI4" s="143"/>
-      <c r="AJ4" s="143"/>
-      <c r="AK4" s="143"/>
-      <c r="AL4" s="143"/>
-      <c r="AM4" s="143"/>
-      <c r="AN4" s="143"/>
-      <c r="AO4" s="143"/>
-      <c r="AP4" s="144" t="s">
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138"/>
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="138"/>
+      <c r="AJ4" s="138"/>
+      <c r="AK4" s="138"/>
+      <c r="AL4" s="138"/>
+      <c r="AM4" s="138"/>
+      <c r="AN4" s="138"/>
+      <c r="AO4" s="138"/>
+      <c r="AP4" s="139" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="144"/>
+      <c r="AQ4" s="139"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Agosto'!B6</f>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="AV4" s="72">
         <f>'Captura Agosto'!V6</f>
-        <v>0</v>
+        <v>0.23474999999999999</v>
       </c>
       <c r="AW4" s="72">
         <f>'Captura Agosto'!G6</f>
@@ -15267,13 +15267,13 @@
       </c>
       <c r="BA4" s="74">
         <f>'Captura Agosto'!AQ6</f>
-        <v>0.43</v>
+        <v>0.66474999999999995</v>
       </c>
       <c r="BB4" s="68" t="s">
         <v>191</v>
       </c>
       <c r="BC4" s="75">
-        <v>0</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:55" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="AT5" s="80">
         <f>'Captura Agosto'!K7+'Captura Agosto'!N7+'Captura Agosto'!Q7</f>
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="AU5" s="80">
         <f>'Captura Agosto'!T7</f>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="AV5" s="80">
         <f>'Captura Agosto'!V7</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW5" s="80">
         <f>'Captura Agosto'!G7</f>
@@ -15437,16 +15437,16 @@
       </c>
       <c r="AZ5" s="81">
         <f>-'Captura Agosto'!AN7</f>
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="BA5" s="82">
         <f>'Captura Agosto'!AQ7</f>
-        <v>0.15</v>
-      </c>
-      <c r="BB5" s="138" t="s">
+        <v>0.46000000000000008</v>
+      </c>
+      <c r="BB5" s="133" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="138"/>
+      <c r="BC5" s="133"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -15517,11 +15517,11 @@
         <v>0</v>
       </c>
       <c r="U6" s="85">
-        <v>0</v>
+        <v>0.93899999999999995</v>
       </c>
       <c r="V6" s="86">
         <f>U6*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.23474999999999999</v>
       </c>
       <c r="W6" s="87">
         <v>0</v>
@@ -15588,11 +15588,11 @@
       </c>
       <c r="AP6" s="11">
         <f t="shared" ref="AP6:AP20" si="3">G6+K6+N6+Q6+T6+V6+X6</f>
-        <v>0.43</v>
+        <v>0.66474999999999995</v>
       </c>
       <c r="AQ6" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP6-IF(S6="NO",Parametros!$E$17,0))+AC6)-AN6-IF(AO6="SI",Parametros!$E$33,0))</f>
-        <v>0.43</v>
+        <v>0.66474999999999995</v>
       </c>
       <c r="AR6" s="58"/>
       <c r="AS6" s="71" t="str">
@@ -15605,11 +15605,11 @@
       </c>
       <c r="AU6" s="72">
         <f>'Captura Agosto'!T8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV6" s="72">
         <f>'Captura Agosto'!V8</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW6" s="72">
         <f>'Captura Agosto'!G8</f>
@@ -15625,11 +15625,11 @@
       </c>
       <c r="AZ6" s="73">
         <f>-'Captura Agosto'!AN8</f>
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="BA6" s="74">
         <f>'Captura Agosto'!AQ8</f>
-        <v>0.59000000000000008</v>
+        <v>0.9</v>
       </c>
       <c r="BB6" s="58"/>
       <c r="BC6" s="58"/>
@@ -15669,24 +15669,24 @@
         <v>0</v>
       </c>
       <c r="L7" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="88" t="s">
         <v>222</v>
       </c>
       <c r="N7" s="86">
         <f>IF(M7="NO",0,L7*Parametros!$E$8)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="O7" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="88" t="s">
         <v>222</v>
       </c>
       <c r="Q7" s="86">
         <f>IF(P7="NO",0,O7*Parametros!$E$9)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="R7" s="85">
         <v>0</v>
@@ -15699,11 +15699,11 @@
         <v>0</v>
       </c>
       <c r="U7" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="86">
         <f>U7*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W7" s="87">
         <v>4</v>
@@ -15737,7 +15737,7 @@
         <v>222</v>
       </c>
       <c r="AF7" s="87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" s="88" t="s">
         <v>222</v>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="AN7" s="89">
         <f>AD7*Parametros!$E$28+AF7*Parametros!$E$29+AH7*Parametros!$E$30+AJ7*Parametros!$E$31+AL7*Parametros!$E$32</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AO7" s="12" t="str">
         <f t="shared" si="2"/>
@@ -15770,11 +15770,11 @@
       </c>
       <c r="AP7" s="11">
         <f t="shared" si="3"/>
-        <v>0.15</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="AQ7" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP7-IF(S7="NO",Parametros!$E$17,0))+AC7)-AN7-IF(AO7="SI",Parametros!$E$33,0))</f>
-        <v>0.15</v>
+        <v>0.46000000000000008</v>
       </c>
       <c r="AR7" s="58"/>
       <c r="AS7" s="79" t="str">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="AV7" s="80">
         <f>'Captura Agosto'!V9</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW7" s="80">
         <f>'Captura Agosto'!G9</f>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="BA7" s="82">
         <f>'Captura Agosto'!AQ9</f>
-        <v>0.4052</v>
+        <v>0.65520000000000012</v>
       </c>
       <c r="BB7" s="58"/>
       <c r="BC7" s="58"/>
@@ -15881,15 +15881,14 @@
         <v>222</v>
       </c>
       <c r="T8" s="86">
-        <f>IF(S8="NO",0,R8*Parametros!$E$10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="86">
         <f>U8*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W8" s="87">
         <v>0</v>
@@ -15923,7 +15922,7 @@
         <v>222</v>
       </c>
       <c r="AF8" s="87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" s="88" t="s">
         <v>222</v>
@@ -15948,7 +15947,7 @@
       </c>
       <c r="AN8" s="89">
         <f>AD8*Parametros!$E$28+AF8*Parametros!$E$29+AH8*Parametros!$E$30+AJ8*Parametros!$E$31+AL8*Parametros!$E$32</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AO8" s="12" t="str">
         <f t="shared" si="2"/>
@@ -15956,11 +15955,11 @@
       </c>
       <c r="AP8" s="11">
         <f t="shared" si="3"/>
-        <v>0.59000000000000008</v>
+        <v>1.84</v>
       </c>
       <c r="AQ8" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP8-IF(S8="NO",Parametros!$E$17,0))+AC8)-AN8-IF(AO8="SI",Parametros!$E$33,0))</f>
-        <v>0.59000000000000008</v>
+        <v>0.9</v>
       </c>
       <c r="AR8" s="58"/>
       <c r="AS8" s="71" t="str">
@@ -15977,7 +15976,7 @@
       </c>
       <c r="AV8" s="72">
         <f>'Captura Agosto'!V10</f>
-        <v>0</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="AW8" s="72">
         <f>'Captura Agosto'!G10</f>
@@ -15997,7 +15996,7 @@
       </c>
       <c r="BA8" s="74">
         <f>'Captura Agosto'!AQ10</f>
-        <v>0.49000000000000005</v>
+        <v>0.72300000000000009</v>
       </c>
       <c r="BB8" s="58"/>
       <c r="BC8" s="58"/>
@@ -16067,11 +16066,11 @@
         <v>0</v>
       </c>
       <c r="U9" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="86">
         <f>U9*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W9" s="87">
         <v>2</v>
@@ -16138,11 +16137,11 @@
       </c>
       <c r="AP9" s="11">
         <f t="shared" si="3"/>
-        <v>0.4052</v>
+        <v>0.65520000000000012</v>
       </c>
       <c r="AQ9" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP9-IF(S9="NO",Parametros!$E$17,0))+AC9)-AN9-IF(AO9="SI",Parametros!$E$33,0))</f>
-        <v>0.4052</v>
+        <v>0.65520000000000012</v>
       </c>
       <c r="AR9" s="58"/>
       <c r="AS9" s="79" t="str">
@@ -16159,7 +16158,7 @@
       </c>
       <c r="AV9" s="80">
         <f>'Captura Agosto'!V11</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW9" s="80">
         <f>'Captura Agosto'!G11</f>
@@ -16179,7 +16178,7 @@
       </c>
       <c r="BA9" s="82">
         <f>'Captura Agosto'!AQ11</f>
-        <v>0.41000000000000003</v>
+        <v>0.66</v>
       </c>
       <c r="BB9" s="58"/>
       <c r="BC9" s="58"/>
@@ -16253,11 +16252,11 @@
         <v>0</v>
       </c>
       <c r="U10" s="85">
-        <v>0</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="V10" s="86">
         <f>U10*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="W10" s="87">
         <v>0</v>
@@ -16324,11 +16323,11 @@
       </c>
       <c r="AP10" s="11">
         <f t="shared" si="3"/>
-        <v>0.49000000000000005</v>
+        <v>0.72300000000000009</v>
       </c>
       <c r="AQ10" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP10-IF(S10="NO",Parametros!$E$17,0))+AC10)-AN10-IF(AO10="SI",Parametros!$E$33,0))</f>
-        <v>0.49000000000000005</v>
+        <v>0.72300000000000009</v>
       </c>
       <c r="AR10" s="58"/>
       <c r="AS10" s="71" t="str">
@@ -16345,7 +16344,7 @@
       </c>
       <c r="AV10" s="72">
         <f>'Captura Agosto'!V12</f>
-        <v>0</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="AW10" s="72">
         <f>'Captura Agosto'!G12</f>
@@ -16365,7 +16364,7 @@
       </c>
       <c r="BA10" s="74">
         <f>'Captura Agosto'!AQ12</f>
-        <v>0.45</v>
+        <v>0.68399999999999994</v>
       </c>
       <c r="BB10" s="58"/>
       <c r="BC10" s="58"/>
@@ -16439,11 +16438,11 @@
         <v>0</v>
       </c>
       <c r="U11" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="86">
         <f>U11*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W11" s="87">
         <v>2</v>
@@ -16510,11 +16509,11 @@
       </c>
       <c r="AP11" s="11">
         <f t="shared" si="3"/>
-        <v>0.41000000000000003</v>
+        <v>0.66</v>
       </c>
       <c r="AQ11" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP11-IF(S11="NO",Parametros!$E$17,0))+AC11)-AN11-IF(AO11="SI",Parametros!$E$33,0))</f>
-        <v>0.41000000000000003</v>
+        <v>0.66</v>
       </c>
       <c r="AR11" s="58"/>
       <c r="AS11" s="79" t="str">
@@ -16531,7 +16530,7 @@
       </c>
       <c r="AV11" s="80">
         <f>'Captura Agosto'!V13</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW11" s="80">
         <f>'Captura Agosto'!G13</f>
@@ -16551,7 +16550,7 @@
       </c>
       <c r="BA11" s="82">
         <f>'Captura Agosto'!AQ13</f>
-        <v>0.20819999999999997</v>
+        <v>0.45820000000000005</v>
       </c>
       <c r="BB11" s="58"/>
       <c r="BC11" s="58"/>
@@ -16625,11 +16624,11 @@
         <v>0</v>
       </c>
       <c r="U12" s="85">
-        <v>0</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="V12" s="86">
         <f>U12*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="W12" s="87">
         <v>1</v>
@@ -16696,11 +16695,11 @@
       </c>
       <c r="AP12" s="11">
         <f t="shared" si="3"/>
-        <v>0.45</v>
+        <v>0.68399999999999994</v>
       </c>
       <c r="AQ12" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP12-IF(S12="NO",Parametros!$E$17,0))+AC12)-AN12-IF(AO12="SI",Parametros!$E$33,0))</f>
-        <v>0.45</v>
+        <v>0.68399999999999994</v>
       </c>
       <c r="AR12" s="58"/>
       <c r="AS12" s="71" t="str">
@@ -16717,7 +16716,7 @@
       </c>
       <c r="AV12" s="72">
         <f>'Captura Agosto'!V14</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW12" s="72">
         <f>'Captura Agosto'!G14</f>
@@ -16737,7 +16736,7 @@
       </c>
       <c r="BA12" s="74">
         <f>'Captura Agosto'!AQ14</f>
-        <v>0.37080000000000002</v>
+        <v>0.62080000000000002</v>
       </c>
       <c r="BB12" s="58"/>
       <c r="BC12" s="58"/>
@@ -16811,11 +16810,11 @@
         <v>0</v>
       </c>
       <c r="U13" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="86">
         <f>U13*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W13" s="87">
         <v>7</v>
@@ -16882,11 +16881,11 @@
       </c>
       <c r="AP13" s="11">
         <f t="shared" si="3"/>
-        <v>0.30819999999999997</v>
+        <v>0.55820000000000003</v>
       </c>
       <c r="AQ13" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP13-IF(S13="NO",Parametros!$E$17,0))+AC13)-AN13-IF(AO13="SI",Parametros!$E$33,0))</f>
-        <v>0.20819999999999997</v>
+        <v>0.45820000000000005</v>
       </c>
       <c r="AR13" s="58"/>
       <c r="AS13" s="79" t="str">
@@ -16903,7 +16902,7 @@
       </c>
       <c r="AV13" s="80">
         <f>'Captura Agosto'!V15</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW13" s="80">
         <f>'Captura Agosto'!G15</f>
@@ -16923,7 +16922,7 @@
       </c>
       <c r="BA13" s="82">
         <f>'Captura Agosto'!AQ15</f>
-        <v>0.21200000000000002</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="BB13" s="58"/>
       <c r="BC13" s="58"/>
@@ -16997,11 +16996,11 @@
         <v>0</v>
       </c>
       <c r="U14" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="86">
         <f>U14*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W14" s="87">
         <v>4</v>
@@ -17068,11 +17067,11 @@
       </c>
       <c r="AP14" s="11">
         <f t="shared" si="3"/>
-        <v>0.37080000000000002</v>
+        <v>0.62080000000000002</v>
       </c>
       <c r="AQ14" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP14-IF(S14="NO",Parametros!$E$17,0))+AC14)-AN14-IF(AO14="SI",Parametros!$E$33,0))</f>
-        <v>0.37080000000000002</v>
+        <v>0.62080000000000002</v>
       </c>
       <c r="AR14" s="58"/>
       <c r="AS14" s="71" t="str">
@@ -17089,7 +17088,7 @@
       </c>
       <c r="AV14" s="72">
         <f>'Captura Agosto'!V16</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW14" s="72">
         <f>'Captura Agosto'!G16</f>
@@ -17109,7 +17108,7 @@
       </c>
       <c r="BA14" s="74">
         <f>'Captura Agosto'!AQ16</f>
-        <v>0.50839999999999996</v>
+        <v>0.75839999999999996</v>
       </c>
       <c r="BB14" s="58"/>
       <c r="BC14" s="58"/>
@@ -17183,11 +17182,11 @@
         <v>0</v>
       </c>
       <c r="U15" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="86">
         <f>U15*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W15" s="87">
         <v>10</v>
@@ -17254,11 +17253,11 @@
       </c>
       <c r="AP15" s="11">
         <f t="shared" si="3"/>
-        <v>0.21200000000000002</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="AQ15" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP15-IF(S15="NO",Parametros!$E$17,0))+AC15)-AN15-IF(AO15="SI",Parametros!$E$33,0))</f>
-        <v>0.21200000000000002</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="AR15" s="58"/>
       <c r="AS15" s="79" t="str">
@@ -17275,7 +17274,7 @@
       </c>
       <c r="AV15" s="80">
         <f>'Captura Agosto'!V17</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW15" s="80">
         <f>'Captura Agosto'!G17</f>
@@ -17295,7 +17294,7 @@
       </c>
       <c r="BA15" s="82">
         <f>'Captura Agosto'!AQ17</f>
-        <v>0.26119999999999999</v>
+        <v>0.51119999999999999</v>
       </c>
       <c r="BB15" s="58"/>
       <c r="BC15" s="58"/>
@@ -17369,11 +17368,11 @@
         <v>0</v>
       </c>
       <c r="U16" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="86">
         <f>U16*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W16" s="87">
         <v>0</v>
@@ -17440,11 +17439,11 @@
       </c>
       <c r="AP16" s="11">
         <f t="shared" si="3"/>
-        <v>0.50839999999999996</v>
+        <v>0.75839999999999996</v>
       </c>
       <c r="AQ16" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP16-IF(S16="NO",Parametros!$E$17,0))+AC16)-AN16-IF(AO16="SI",Parametros!$E$33,0))</f>
-        <v>0.50839999999999996</v>
+        <v>0.75839999999999996</v>
       </c>
       <c r="AR16" s="58"/>
       <c r="AS16" s="71" t="str">
@@ -17461,7 +17460,7 @@
       </c>
       <c r="AV16" s="72">
         <f>'Captura Agosto'!V18</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW16" s="72">
         <f>'Captura Agosto'!G18</f>
@@ -17481,7 +17480,7 @@
       </c>
       <c r="BA16" s="74">
         <f>'Captura Agosto'!AQ18</f>
-        <v>0.28739999999999999</v>
+        <v>0.53739999999999999</v>
       </c>
       <c r="BB16" s="58"/>
       <c r="BC16" s="58"/>
@@ -17555,11 +17554,11 @@
         <v>0</v>
       </c>
       <c r="U17" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="86">
         <f>U17*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W17" s="87">
         <v>4</v>
@@ -17626,11 +17625,11 @@
       </c>
       <c r="AP17" s="11">
         <f t="shared" si="3"/>
-        <v>0.36120000000000002</v>
+        <v>0.61119999999999997</v>
       </c>
       <c r="AQ17" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP17-IF(S17="NO",Parametros!$E$17,0))+AC17)-AN17-IF(AO17="SI",Parametros!$E$33,0))</f>
-        <v>0.26119999999999999</v>
+        <v>0.51119999999999999</v>
       </c>
       <c r="AR17" s="58"/>
       <c r="AS17" s="79" t="str">
@@ -17647,7 +17646,7 @@
       </c>
       <c r="AV17" s="80">
         <f>'Captura Agosto'!V19</f>
-        <v>0</v>
+        <v>0.23125000000000001</v>
       </c>
       <c r="AW17" s="80">
         <f>'Captura Agosto'!G19</f>
@@ -17667,7 +17666,7 @@
       </c>
       <c r="BA17" s="82">
         <f>'Captura Agosto'!AQ19</f>
-        <v>0.26</v>
+        <v>0.49125000000000002</v>
       </c>
       <c r="BB17" s="58"/>
       <c r="BC17" s="58"/>
@@ -17741,11 +17740,11 @@
         <v>0</v>
       </c>
       <c r="U18" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="86">
         <f>U18*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W18" s="87">
         <v>2</v>
@@ -17812,11 +17811,11 @@
       </c>
       <c r="AP18" s="11">
         <f t="shared" si="3"/>
-        <v>0.38739999999999997</v>
+        <v>0.63739999999999997</v>
       </c>
       <c r="AQ18" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP18-IF(S18="NO",Parametros!$E$17,0))+AC18)-AN18-IF(AO18="SI",Parametros!$E$33,0))</f>
-        <v>0.28739999999999999</v>
+        <v>0.53739999999999999</v>
       </c>
       <c r="AR18" s="58"/>
       <c r="AS18" s="71" t="str">
@@ -17833,7 +17832,7 @@
       </c>
       <c r="AV18" s="72">
         <f>'Captura Agosto'!V20</f>
-        <v>0</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="AW18" s="72">
         <f>'Captura Agosto'!G20</f>
@@ -17853,7 +17852,7 @@
       </c>
       <c r="BA18" s="74">
         <f>'Captura Agosto'!AQ20</f>
-        <v>0.46</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="BB18" s="58"/>
       <c r="BC18" s="58"/>
@@ -17927,11 +17926,11 @@
         <v>0</v>
       </c>
       <c r="U19" s="85">
-        <v>0</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="V19" s="86">
         <f>U19*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.23125000000000001</v>
       </c>
       <c r="W19" s="87">
         <v>5</v>
@@ -17998,26 +17997,26 @@
       </c>
       <c r="AP19" s="11">
         <f t="shared" si="3"/>
-        <v>0.26</v>
+        <v>0.49125000000000002</v>
       </c>
       <c r="AQ19" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP19-IF(S19="NO",Parametros!$E$17,0))+AC19)-AN19-IF(AO19="SI",Parametros!$E$33,0))</f>
-        <v>0.26</v>
+        <v>0.49125000000000002</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="139" t="s">
+      <c r="AS19" s="134" t="s">
         <v>260</v>
       </c>
-      <c r="AT19" s="139"/>
-      <c r="AU19" s="139"/>
-      <c r="AV19" s="139"/>
-      <c r="AW19" s="139"/>
-      <c r="AX19" s="139"/>
-      <c r="AY19" s="139"/>
-      <c r="AZ19" s="139"/>
+      <c r="AT19" s="134"/>
+      <c r="AU19" s="134"/>
+      <c r="AV19" s="134"/>
+      <c r="AW19" s="134"/>
+      <c r="AX19" s="134"/>
+      <c r="AY19" s="134"/>
+      <c r="AZ19" s="134"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
-        <v>0.36621333333333334</v>
+        <v>0.61868000000000001</v>
       </c>
       <c r="BB19" s="58"/>
       <c r="BC19" s="58"/>
@@ -18091,11 +18090,11 @@
         <v>0</v>
       </c>
       <c r="U20" s="85">
-        <v>0</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="V20" s="86">
         <f>U20*Parametros!$E$11</f>
-        <v>0</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="W20" s="87">
         <v>1</v>
@@ -18162,11 +18161,11 @@
       </c>
       <c r="AP20" s="11">
         <f t="shared" si="3"/>
-        <v>0.46</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="AQ20" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP20-IF(S20="NO",Parametros!$E$17,0))+AC20)-AN20-IF(AO20="SI",Parametros!$E$33,0))</f>
-        <v>0.46</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="AR20" s="58"/>
       <c r="AS20" s="58"/>
@@ -18181,9 +18180,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="140"/>
-      <c r="B22" s="140"/>
-      <c r="C22" s="140"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -18210,11 +18209,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="141" t="s">
+      <c r="A23" s="136" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -18256,7 +18255,7 @@
       <c r="AP23" s="93"/>
       <c r="AQ23" s="96">
         <f>AVERAGE(AQ6:AQ20)</f>
-        <v>0.36621333333333334</v>
+        <v>0.61868000000000001</v>
       </c>
       <c r="AR23" s="58"/>
       <c r="AS23" s="58"/>
@@ -18272,6 +18271,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -18286,12 +18291,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="47" priority="5" operator="greaterThanOrEqual">
@@ -18373,62 +18372,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="107" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="133" t="s">
+      <c r="AS1" s="140" t="s">
         <v>262</v>
       </c>
-      <c r="AT1" s="133"/>
-      <c r="AU1" s="133"/>
-      <c r="AV1" s="133"/>
-      <c r="AW1" s="133"/>
-      <c r="AX1" s="133"/>
-      <c r="AY1" s="133"/>
-      <c r="AZ1" s="133"/>
-      <c r="BA1" s="133"/>
-      <c r="BB1" s="134" t="s">
+      <c r="AT1" s="140"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="140"/>
+      <c r="AW1" s="140"/>
+      <c r="AX1" s="140"/>
+      <c r="AY1" s="140"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="140"/>
+      <c r="BB1" s="141" t="s">
         <v>263</v>
       </c>
-      <c r="BC1" s="134"/>
+      <c r="BC1" s="141"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="142" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -18437,20 +18436,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="136" t="s">
+      <c r="AT2" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="136"/>
-      <c r="AV2" s="136"/>
+      <c r="AU2" s="143"/>
+      <c r="AV2" s="143"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="137" t="s">
+      <c r="AX2" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="137"/>
-      <c r="AZ2" s="137"/>
-      <c r="BA2" s="137"/>
+      <c r="AY2" s="144"/>
+      <c r="AZ2" s="144"/>
+      <c r="BA2" s="144"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -18498,66 +18497,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="137" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142" t="s">
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142" t="s">
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="142"/>
-      <c r="N4" s="142"/>
-      <c r="O4" s="142" t="s">
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="142"/>
-      <c r="Q4" s="142"/>
-      <c r="R4" s="142" t="s">
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="142"/>
-      <c r="T4" s="142"/>
-      <c r="U4" s="142" t="s">
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="142"/>
-      <c r="W4" s="143" t="s">
+      <c r="V4" s="137"/>
+      <c r="W4" s="138" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="143"/>
-      <c r="Y4" s="142" t="s">
+      <c r="X4" s="138"/>
+      <c r="Y4" s="137" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="142"/>
-      <c r="AA4" s="142"/>
-      <c r="AB4" s="142"/>
-      <c r="AC4" s="142"/>
-      <c r="AD4" s="143" t="s">
+      <c r="Z4" s="137"/>
+      <c r="AA4" s="137"/>
+      <c r="AB4" s="137"/>
+      <c r="AC4" s="137"/>
+      <c r="AD4" s="138" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="143"/>
-      <c r="AF4" s="143"/>
-      <c r="AG4" s="143"/>
-      <c r="AH4" s="143"/>
-      <c r="AI4" s="143"/>
-      <c r="AJ4" s="143"/>
-      <c r="AK4" s="143"/>
-      <c r="AL4" s="143"/>
-      <c r="AM4" s="143"/>
-      <c r="AN4" s="143"/>
-      <c r="AO4" s="143"/>
-      <c r="AP4" s="144" t="s">
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138"/>
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="138"/>
+      <c r="AJ4" s="138"/>
+      <c r="AK4" s="138"/>
+      <c r="AL4" s="138"/>
+      <c r="AM4" s="138"/>
+      <c r="AN4" s="138"/>
+      <c r="AO4" s="138"/>
+      <c r="AP4" s="139" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="144"/>
+      <c r="AQ4" s="139"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Septiembre'!B6</f>
@@ -18769,10 +18768,10 @@
         <f>'Captura Septiembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="138" t="s">
+      <c r="BB5" s="133" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="138"/>
+      <c r="BC5" s="133"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -21339,16 +21338,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="139" t="s">
+      <c r="AS19" s="134" t="s">
         <v>265</v>
       </c>
-      <c r="AT19" s="139"/>
-      <c r="AU19" s="139"/>
-      <c r="AV19" s="139"/>
-      <c r="AW19" s="139"/>
-      <c r="AX19" s="139"/>
-      <c r="AY19" s="139"/>
-      <c r="AZ19" s="139"/>
+      <c r="AT19" s="134"/>
+      <c r="AU19" s="134"/>
+      <c r="AV19" s="134"/>
+      <c r="AW19" s="134"/>
+      <c r="AX19" s="134"/>
+      <c r="AY19" s="134"/>
+      <c r="AZ19" s="134"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -21515,9 +21514,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="140"/>
-      <c r="B22" s="140"/>
-      <c r="C22" s="140"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -21544,11 +21543,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="141" t="s">
+      <c r="A23" s="136" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -21606,6 +21605,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -21620,12 +21625,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="38" priority="5" operator="greaterThanOrEqual">
@@ -21707,62 +21706,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="107" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="133" t="s">
+      <c r="AS1" s="140" t="s">
         <v>267</v>
       </c>
-      <c r="AT1" s="133"/>
-      <c r="AU1" s="133"/>
-      <c r="AV1" s="133"/>
-      <c r="AW1" s="133"/>
-      <c r="AX1" s="133"/>
-      <c r="AY1" s="133"/>
-      <c r="AZ1" s="133"/>
-      <c r="BA1" s="133"/>
-      <c r="BB1" s="134" t="s">
+      <c r="AT1" s="140"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="140"/>
+      <c r="AW1" s="140"/>
+      <c r="AX1" s="140"/>
+      <c r="AY1" s="140"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="140"/>
+      <c r="BB1" s="141" t="s">
         <v>268</v>
       </c>
-      <c r="BC1" s="134"/>
+      <c r="BC1" s="141"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="142" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -21771,20 +21770,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="136" t="s">
+      <c r="AT2" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="136"/>
-      <c r="AV2" s="136"/>
+      <c r="AU2" s="143"/>
+      <c r="AV2" s="143"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="137" t="s">
+      <c r="AX2" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="137"/>
-      <c r="AZ2" s="137"/>
-      <c r="BA2" s="137"/>
+      <c r="AY2" s="144"/>
+      <c r="AZ2" s="144"/>
+      <c r="BA2" s="144"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -21832,66 +21831,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="137" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142" t="s">
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142" t="s">
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="142"/>
-      <c r="N4" s="142"/>
-      <c r="O4" s="142" t="s">
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="142"/>
-      <c r="Q4" s="142"/>
-      <c r="R4" s="142" t="s">
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="142"/>
-      <c r="T4" s="142"/>
-      <c r="U4" s="142" t="s">
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="142"/>
-      <c r="W4" s="143" t="s">
+      <c r="V4" s="137"/>
+      <c r="W4" s="138" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="143"/>
-      <c r="Y4" s="142" t="s">
+      <c r="X4" s="138"/>
+      <c r="Y4" s="137" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="142"/>
-      <c r="AA4" s="142"/>
-      <c r="AB4" s="142"/>
-      <c r="AC4" s="142"/>
-      <c r="AD4" s="143" t="s">
+      <c r="Z4" s="137"/>
+      <c r="AA4" s="137"/>
+      <c r="AB4" s="137"/>
+      <c r="AC4" s="137"/>
+      <c r="AD4" s="138" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="143"/>
-      <c r="AF4" s="143"/>
-      <c r="AG4" s="143"/>
-      <c r="AH4" s="143"/>
-      <c r="AI4" s="143"/>
-      <c r="AJ4" s="143"/>
-      <c r="AK4" s="143"/>
-      <c r="AL4" s="143"/>
-      <c r="AM4" s="143"/>
-      <c r="AN4" s="143"/>
-      <c r="AO4" s="143"/>
-      <c r="AP4" s="144" t="s">
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138"/>
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="138"/>
+      <c r="AJ4" s="138"/>
+      <c r="AK4" s="138"/>
+      <c r="AL4" s="138"/>
+      <c r="AM4" s="138"/>
+      <c r="AN4" s="138"/>
+      <c r="AO4" s="138"/>
+      <c r="AP4" s="139" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="144"/>
+      <c r="AQ4" s="139"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Octubre'!B6</f>
@@ -22103,10 +22102,10 @@
         <f>'Captura Octubre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="138" t="s">
+      <c r="BB5" s="133" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="138"/>
+      <c r="BC5" s="133"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -24673,16 +24672,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="139" t="s">
+      <c r="AS19" s="134" t="s">
         <v>270</v>
       </c>
-      <c r="AT19" s="139"/>
-      <c r="AU19" s="139"/>
-      <c r="AV19" s="139"/>
-      <c r="AW19" s="139"/>
-      <c r="AX19" s="139"/>
-      <c r="AY19" s="139"/>
-      <c r="AZ19" s="139"/>
+      <c r="AT19" s="134"/>
+      <c r="AU19" s="134"/>
+      <c r="AV19" s="134"/>
+      <c r="AW19" s="134"/>
+      <c r="AX19" s="134"/>
+      <c r="AY19" s="134"/>
+      <c r="AZ19" s="134"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -24849,9 +24848,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="140"/>
-      <c r="B22" s="140"/>
-      <c r="C22" s="140"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -24878,11 +24877,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="141" t="s">
+      <c r="A23" s="136" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -24940,6 +24939,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -24954,12 +24959,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="29" priority="5" operator="greaterThanOrEqual">
@@ -25041,62 +25040,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="107" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="133" t="s">
+      <c r="AS1" s="140" t="s">
         <v>272</v>
       </c>
-      <c r="AT1" s="133"/>
-      <c r="AU1" s="133"/>
-      <c r="AV1" s="133"/>
-      <c r="AW1" s="133"/>
-      <c r="AX1" s="133"/>
-      <c r="AY1" s="133"/>
-      <c r="AZ1" s="133"/>
-      <c r="BA1" s="133"/>
-      <c r="BB1" s="134" t="s">
+      <c r="AT1" s="140"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="140"/>
+      <c r="AW1" s="140"/>
+      <c r="AX1" s="140"/>
+      <c r="AY1" s="140"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="140"/>
+      <c r="BB1" s="141" t="s">
         <v>273</v>
       </c>
-      <c r="BC1" s="134"/>
+      <c r="BC1" s="141"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="142" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -25105,20 +25104,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="136" t="s">
+      <c r="AT2" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="136"/>
-      <c r="AV2" s="136"/>
+      <c r="AU2" s="143"/>
+      <c r="AV2" s="143"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="137" t="s">
+      <c r="AX2" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="137"/>
-      <c r="AZ2" s="137"/>
-      <c r="BA2" s="137"/>
+      <c r="AY2" s="144"/>
+      <c r="AZ2" s="144"/>
+      <c r="BA2" s="144"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -25166,66 +25165,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="137" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142" t="s">
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142" t="s">
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="142"/>
-      <c r="N4" s="142"/>
-      <c r="O4" s="142" t="s">
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="142"/>
-      <c r="Q4" s="142"/>
-      <c r="R4" s="142" t="s">
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="142"/>
-      <c r="T4" s="142"/>
-      <c r="U4" s="142" t="s">
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="142"/>
-      <c r="W4" s="143" t="s">
+      <c r="V4" s="137"/>
+      <c r="W4" s="138" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="143"/>
-      <c r="Y4" s="142" t="s">
+      <c r="X4" s="138"/>
+      <c r="Y4" s="137" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="142"/>
-      <c r="AA4" s="142"/>
-      <c r="AB4" s="142"/>
-      <c r="AC4" s="142"/>
-      <c r="AD4" s="143" t="s">
+      <c r="Z4" s="137"/>
+      <c r="AA4" s="137"/>
+      <c r="AB4" s="137"/>
+      <c r="AC4" s="137"/>
+      <c r="AD4" s="138" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="143"/>
-      <c r="AF4" s="143"/>
-      <c r="AG4" s="143"/>
-      <c r="AH4" s="143"/>
-      <c r="AI4" s="143"/>
-      <c r="AJ4" s="143"/>
-      <c r="AK4" s="143"/>
-      <c r="AL4" s="143"/>
-      <c r="AM4" s="143"/>
-      <c r="AN4" s="143"/>
-      <c r="AO4" s="143"/>
-      <c r="AP4" s="144" t="s">
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138"/>
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="138"/>
+      <c r="AJ4" s="138"/>
+      <c r="AK4" s="138"/>
+      <c r="AL4" s="138"/>
+      <c r="AM4" s="138"/>
+      <c r="AN4" s="138"/>
+      <c r="AO4" s="138"/>
+      <c r="AP4" s="139" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="144"/>
+      <c r="AQ4" s="139"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Noviembre'!B6</f>
@@ -25437,10 +25436,10 @@
         <f>'Captura Noviembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="138" t="s">
+      <c r="BB5" s="133" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="138"/>
+      <c r="BC5" s="133"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -28007,16 +28006,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="139" t="s">
+      <c r="AS19" s="134" t="s">
         <v>275</v>
       </c>
-      <c r="AT19" s="139"/>
-      <c r="AU19" s="139"/>
-      <c r="AV19" s="139"/>
-      <c r="AW19" s="139"/>
-      <c r="AX19" s="139"/>
-      <c r="AY19" s="139"/>
-      <c r="AZ19" s="139"/>
+      <c r="AT19" s="134"/>
+      <c r="AU19" s="134"/>
+      <c r="AV19" s="134"/>
+      <c r="AW19" s="134"/>
+      <c r="AX19" s="134"/>
+      <c r="AY19" s="134"/>
+      <c r="AZ19" s="134"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -28183,9 +28182,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="140"/>
-      <c r="B22" s="140"/>
-      <c r="C22" s="140"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -28212,11 +28211,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="141" t="s">
+      <c r="A23" s="136" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -28274,6 +28273,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -28288,12 +28293,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="20" priority="5" operator="greaterThanOrEqual">
@@ -28375,62 +28374,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="107" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="133" t="s">
+      <c r="AS1" s="140" t="s">
         <v>277</v>
       </c>
-      <c r="AT1" s="133"/>
-      <c r="AU1" s="133"/>
-      <c r="AV1" s="133"/>
-      <c r="AW1" s="133"/>
-      <c r="AX1" s="133"/>
-      <c r="AY1" s="133"/>
-      <c r="AZ1" s="133"/>
-      <c r="BA1" s="133"/>
-      <c r="BB1" s="134" t="s">
+      <c r="AT1" s="140"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="140"/>
+      <c r="AW1" s="140"/>
+      <c r="AX1" s="140"/>
+      <c r="AY1" s="140"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="140"/>
+      <c r="BB1" s="141" t="s">
         <v>278</v>
       </c>
-      <c r="BC1" s="134"/>
+      <c r="BC1" s="141"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="142" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -28439,20 +28438,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="136" t="s">
+      <c r="AT2" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="136"/>
-      <c r="AV2" s="136"/>
+      <c r="AU2" s="143"/>
+      <c r="AV2" s="143"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="137" t="s">
+      <c r="AX2" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="137"/>
-      <c r="AZ2" s="137"/>
-      <c r="BA2" s="137"/>
+      <c r="AY2" s="144"/>
+      <c r="AZ2" s="144"/>
+      <c r="BA2" s="144"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -28500,66 +28499,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="137" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142" t="s">
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142" t="s">
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="142"/>
-      <c r="N4" s="142"/>
-      <c r="O4" s="142" t="s">
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="142"/>
-      <c r="Q4" s="142"/>
-      <c r="R4" s="142" t="s">
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="142"/>
-      <c r="T4" s="142"/>
-      <c r="U4" s="142" t="s">
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="142"/>
-      <c r="W4" s="143" t="s">
+      <c r="V4" s="137"/>
+      <c r="W4" s="138" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="143"/>
-      <c r="Y4" s="142" t="s">
+      <c r="X4" s="138"/>
+      <c r="Y4" s="137" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="142"/>
-      <c r="AA4" s="142"/>
-      <c r="AB4" s="142"/>
-      <c r="AC4" s="142"/>
-      <c r="AD4" s="143" t="s">
+      <c r="Z4" s="137"/>
+      <c r="AA4" s="137"/>
+      <c r="AB4" s="137"/>
+      <c r="AC4" s="137"/>
+      <c r="AD4" s="138" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="143"/>
-      <c r="AF4" s="143"/>
-      <c r="AG4" s="143"/>
-      <c r="AH4" s="143"/>
-      <c r="AI4" s="143"/>
-      <c r="AJ4" s="143"/>
-      <c r="AK4" s="143"/>
-      <c r="AL4" s="143"/>
-      <c r="AM4" s="143"/>
-      <c r="AN4" s="143"/>
-      <c r="AO4" s="143"/>
-      <c r="AP4" s="144" t="s">
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138"/>
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="138"/>
+      <c r="AJ4" s="138"/>
+      <c r="AK4" s="138"/>
+      <c r="AL4" s="138"/>
+      <c r="AM4" s="138"/>
+      <c r="AN4" s="138"/>
+      <c r="AO4" s="138"/>
+      <c r="AP4" s="139" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="144"/>
+      <c r="AQ4" s="139"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Diciembre'!B6</f>
@@ -28771,10 +28770,10 @@
         <f>'Captura Diciembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="138" t="s">
+      <c r="BB5" s="133" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="138"/>
+      <c r="BC5" s="133"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -31341,16 +31340,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="139" t="s">
+      <c r="AS19" s="134" t="s">
         <v>280</v>
       </c>
-      <c r="AT19" s="139"/>
-      <c r="AU19" s="139"/>
-      <c r="AV19" s="139"/>
-      <c r="AW19" s="139"/>
-      <c r="AX19" s="139"/>
-      <c r="AY19" s="139"/>
-      <c r="AZ19" s="139"/>
+      <c r="AT19" s="134"/>
+      <c r="AU19" s="134"/>
+      <c r="AV19" s="134"/>
+      <c r="AW19" s="134"/>
+      <c r="AX19" s="134"/>
+      <c r="AY19" s="134"/>
+      <c r="AZ19" s="134"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -31517,9 +31516,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="140"/>
-      <c r="B22" s="140"/>
-      <c r="C22" s="140"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -31546,11 +31545,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="141" t="s">
+      <c r="A23" s="136" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -31608,6 +31607,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -31622,12 +31627,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThanOrEqual">
@@ -31701,11 +31700,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="107" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="145" t="s">
@@ -31825,7 +31824,7 @@
       </c>
       <c r="B13" s="97">
         <f>IF(AVERAGE('Captura Agosto'!D6:D20)=0,"",'Captura Agosto'!AQ23)</f>
-        <v>0.36621333333333334</v>
+        <v>0.61868000000000001</v>
       </c>
       <c r="C13" s="12" t="str">
         <f>IF(B13="","",IF(B13&gt;=Parametros!$C$37,"Verde",IF(B13&gt;=Parametros!$C$38,"Amarillo","Rojo")))</f>
@@ -32018,7 +32017,7 @@
       </c>
       <c r="I4" s="10">
         <f>IFERROR(IF('Captura Agosto'!D8=0,"",'Captura Agosto'!AQ8),"")</f>
-        <v>0.59000000000000008</v>
+        <v>0.9</v>
       </c>
       <c r="J4" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
@@ -32038,7 +32037,7 @@
       </c>
       <c r="N4" s="102">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.94874999999999998</v>
+        <v>0.98750000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32075,7 +32074,7 @@
       </c>
       <c r="I5" s="10">
         <f>IFERROR(IF('Captura Agosto'!D6=0,"",'Captura Agosto'!AQ6),"")</f>
-        <v>0.43</v>
+        <v>0.66474999999999995</v>
       </c>
       <c r="J5" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D6=0,"",'Captura Septiembre'!AQ6),"")</f>
@@ -32095,7 +32094,7 @@
       </c>
       <c r="N5" s="102">
         <f t="shared" si="0"/>
-        <v>0.89874999999999994</v>
+        <v>0.92809374999999994</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32132,7 +32131,7 @@
       </c>
       <c r="I6" s="10">
         <f>IFERROR(IF('Captura Agosto'!D16=0,"",'Captura Agosto'!AQ16),"")</f>
-        <v>0.50839999999999996</v>
+        <v>0.75839999999999996</v>
       </c>
       <c r="J6" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
@@ -32152,7 +32151,7 @@
       </c>
       <c r="N6" s="102">
         <f t="shared" si="0"/>
-        <v>0.91033571428571425</v>
+        <v>0.94158571428571425</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32189,7 +32188,7 @@
       </c>
       <c r="I7" s="10">
         <f>IFERROR(IF('Captura Agosto'!D17=0,"",'Captura Agosto'!AQ17),"")</f>
-        <v>0.26119999999999999</v>
+        <v>0.51119999999999999</v>
       </c>
       <c r="J7" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
@@ -32209,7 +32208,7 @@
       </c>
       <c r="N7" s="102">
         <f t="shared" si="0"/>
-        <v>0.79286978021978016</v>
+        <v>0.82411978021978016</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32246,7 +32245,7 @@
       </c>
       <c r="I8" s="10">
         <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
-        <v>0.37080000000000002</v>
+        <v>0.62080000000000002</v>
       </c>
       <c r="J8" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
@@ -32266,7 +32265,7 @@
       </c>
       <c r="N8" s="102">
         <f t="shared" si="0"/>
-        <v>0.86635000000000006</v>
+        <v>0.89760000000000006</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32303,7 +32302,7 @@
       </c>
       <c r="I9" s="10">
         <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
-        <v>0.41000000000000003</v>
+        <v>0.66</v>
       </c>
       <c r="J9" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
@@ -32323,7 +32322,7 @@
       </c>
       <c r="N9" s="102">
         <f t="shared" si="0"/>
-        <v>0.87687500000000007</v>
+        <v>0.90812500000000007</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32360,7 +32359,7 @@
       </c>
       <c r="I10" s="10">
         <f>IFERROR(IF('Captura Agosto'!D13=0,"",'Captura Agosto'!AQ13),"")</f>
-        <v>0.20819999999999997</v>
+        <v>0.45820000000000005</v>
       </c>
       <c r="J10" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
@@ -32380,7 +32379,7 @@
       </c>
       <c r="N10" s="102">
         <f t="shared" si="0"/>
-        <v>0.74977499999999986</v>
+        <v>0.78102499999999986</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32417,7 +32416,7 @@
       </c>
       <c r="I11" s="10">
         <f>IFERROR(IF('Captura Agosto'!D10=0,"",'Captura Agosto'!AQ10),"")</f>
-        <v>0.49000000000000005</v>
+        <v>0.72300000000000009</v>
       </c>
       <c r="J11" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
@@ -32437,7 +32436,7 @@
       </c>
       <c r="N11" s="102">
         <f t="shared" si="0"/>
-        <v>0.89312500000000006</v>
+        <v>0.92225000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32474,7 +32473,7 @@
       </c>
       <c r="I12" s="10">
         <f>IFERROR(IF('Captura Agosto'!D9=0,"",'Captura Agosto'!AQ9),"")</f>
-        <v>0.4052</v>
+        <v>0.65520000000000012</v>
       </c>
       <c r="J12" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
@@ -32494,7 +32493,7 @@
       </c>
       <c r="N12" s="102">
         <f t="shared" si="0"/>
-        <v>0.91033750000000002</v>
+        <v>0.94158750000000002</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32531,7 +32530,7 @@
       </c>
       <c r="I13" s="10">
         <f>IFERROR(IF('Captura Agosto'!D12=0,"",'Captura Agosto'!AQ12),"")</f>
-        <v>0.45</v>
+        <v>0.68399999999999994</v>
       </c>
       <c r="J13" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
@@ -32551,7 +32550,7 @@
       </c>
       <c r="N13" s="102">
         <f t="shared" si="0"/>
-        <v>0.79891304347826098</v>
+        <v>0.82816304347826097</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32588,7 +32587,7 @@
       </c>
       <c r="I14" s="10">
         <f>IFERROR(IF('Captura Agosto'!D15=0,"",'Captura Agosto'!AQ15),"")</f>
-        <v>0.21200000000000002</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="J14" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
@@ -32608,7 +32607,7 @@
       </c>
       <c r="N14" s="102">
         <f t="shared" si="0"/>
-        <v>0.77389766081871347</v>
+        <v>0.80514766081871347</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32645,7 +32644,7 @@
       </c>
       <c r="I15" s="10">
         <f>IFERROR(IF('Captura Agosto'!D7=0,"",'Captura Agosto'!AQ7),"")</f>
-        <v>0.15</v>
+        <v>0.46000000000000008</v>
       </c>
       <c r="J15" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D7=0,"",'Captura Septiembre'!AQ7),"")</f>
@@ -32665,7 +32664,7 @@
       </c>
       <c r="N15" s="102">
         <f t="shared" si="0"/>
-        <v>0.72125000000000006</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32702,7 +32701,7 @@
       </c>
       <c r="I16" s="10">
         <f>IFERROR(IF('Captura Agosto'!D20=0,"",'Captura Agosto'!AQ20),"")</f>
-        <v>0.46</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="J16" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
@@ -32722,7 +32721,7 @@
       </c>
       <c r="N16" s="102">
         <f t="shared" si="0"/>
-        <v>0.88375000000000004</v>
+        <v>0.91300000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32759,7 +32758,7 @@
       </c>
       <c r="I17" s="10">
         <f>IFERROR(IF('Captura Agosto'!D18=0,"",'Captura Agosto'!AQ18),"")</f>
-        <v>0.28739999999999999</v>
+        <v>0.53739999999999999</v>
       </c>
       <c r="J17" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
@@ -32779,7 +32778,7 @@
       </c>
       <c r="N17" s="102">
         <f t="shared" si="0"/>
-        <v>0.85308186274509801</v>
+        <v>0.88433186274509801</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32816,7 +32815,7 @@
       </c>
       <c r="I18" s="10">
         <f>IFERROR(IF('Captura Agosto'!D19=0,"",'Captura Agosto'!AQ19),"")</f>
-        <v>0.26</v>
+        <v>0.49125000000000002</v>
       </c>
       <c r="J18" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
@@ -32836,7 +32835,7 @@
       </c>
       <c r="N18" s="102">
         <f t="shared" si="0"/>
-        <v>0.81906249999999992</v>
+        <v>0.84796874999999994</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -32873,7 +32872,7 @@
       </c>
       <c r="I19" s="104">
         <f t="shared" si="1"/>
-        <v>0.36621333333333339</v>
+        <v>0.6186799999999999</v>
       </c>
       <c r="J19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -32936,16 +32935,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -32956,12 +32955,12 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="123" t="s">
+      <c r="A3" s="106" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="123"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
     </row>
     <row r="4" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
@@ -33021,11 +33020,11 @@
       </c>
       <c r="C7" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N20"))</f>
-        <v>6.608E-2</v>
+        <v>7.1413333333333343E-2</v>
       </c>
       <c r="D7" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0.82599999999999996</v>
+        <v>0.89266666666666672</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33038,11 +33037,11 @@
       </c>
       <c r="C8" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N20"))</f>
-        <v>6.608E-2</v>
+        <v>7.1413333333333343E-2</v>
       </c>
       <c r="D8" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0.82599999999999996</v>
+        <v>0.89266666666666672</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33055,11 +33054,11 @@
       </c>
       <c r="C9" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"T6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"T20"))</f>
-        <v>0</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="D9" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1.1111111111111112</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33072,11 +33071,11 @@
       </c>
       <c r="C10" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"V6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"V20"))</f>
-        <v>0</v>
+        <v>0.24446666666666669</v>
       </c>
       <c r="D10" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>0.97786666666666677</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33097,10 +33096,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="123" t="s">
+      <c r="A13" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="123"/>
+      <c r="B13" s="106"/>
     </row>
     <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
@@ -33126,7 +33125,7 @@
       </c>
       <c r="B16" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AN6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AN20"))</f>
-        <v>2.0000000000000004E-2</v>
+        <v>3.3333333333333333E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33157,12 +33156,12 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="123" t="s">
+      <c r="A21" s="106" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="123"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="123"/>
+      <c r="B21" s="106"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="106"/>
     </row>
     <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
@@ -33220,7 +33219,7 @@
       </c>
       <c r="E24" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ7")*100000-7</f>
-        <v>14993</v>
+        <v>45993.000000000007</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -33241,7 +33240,7 @@
       </c>
       <c r="E25" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ8")*100000-8</f>
-        <v>58992.000000000007</v>
+        <v>89992</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33262,7 +33261,7 @@
       </c>
       <c r="E26" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ9")*100000-9</f>
-        <v>40511</v>
+        <v>65511.000000000015</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33283,7 +33282,7 @@
       </c>
       <c r="E27" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ10")*100000-10</f>
-        <v>48990.000000000007</v>
+        <v>72290.000000000015</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33304,7 +33303,7 @@
       </c>
       <c r="E28" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ11")*100000-11</f>
-        <v>40989</v>
+        <v>65989</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33325,7 +33324,7 @@
       </c>
       <c r="E29" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ12")*100000-12</f>
-        <v>44988</v>
+        <v>68388</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -33346,7 +33345,7 @@
       </c>
       <c r="E30" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ13")*100000-13</f>
-        <v>20806.999999999996</v>
+        <v>45807.000000000007</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33367,7 +33366,7 @@
       </c>
       <c r="E31" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ14")*100000-14</f>
-        <v>37066</v>
+        <v>62066</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33388,7 +33387,7 @@
       </c>
       <c r="E32" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ15")*100000-15</f>
-        <v>21185.000000000004</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33409,7 +33408,7 @@
       </c>
       <c r="E33" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ16")*100000-16</f>
-        <v>50823.999999999993</v>
+        <v>75824</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33418,7 +33417,7 @@
       </c>
       <c r="B34" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,12),$E$23:$E$37,0))</f>
-        <v>Linea 1</v>
+        <v>Alrededores</v>
       </c>
       <c r="C34" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),12)</f>
@@ -33430,7 +33429,7 @@
       </c>
       <c r="E34" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ17")*100000-17</f>
-        <v>26103</v>
+        <v>51103</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33439,7 +33438,7 @@
       </c>
       <c r="B35" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,13),$E$23:$E$37,0))</f>
-        <v>Alrededores</v>
+        <v>Linea 1</v>
       </c>
       <c r="C35" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),13)</f>
@@ -33451,7 +33450,7 @@
       </c>
       <c r="E35" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ18")*100000-18</f>
-        <v>28722</v>
+        <v>53722</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33472,7 +33471,7 @@
       </c>
       <c r="E36" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ19")*100000-19</f>
-        <v>25981</v>
+        <v>49106</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33497,10 +33496,10 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="123" t="s">
+      <c r="A39" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="123"/>
+      <c r="B39" s="106"/>
     </row>
     <row r="40" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="16" t="s">
@@ -33535,7 +33534,7 @@
       </c>
       <c r="B44" s="17">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ23")</f>
-        <v>0.36621333333333334</v>
+        <v>0.61868000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33652,515 +33651,515 @@
     </row>
     <row r="4" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="101" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="B4" s="10">
-        <f>IFERROR(IF('Captura Enero'!D9=0,"",'Captura Enero'!AQ9),"")</f>
+        <f>IFERROR(IF('Captura Enero'!D8=0,"",'Captura Enero'!AQ8),"")</f>
         <v>1</v>
       </c>
       <c r="C4" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D9=0,"",'Captura Febrero'!AQ9),"")</f>
+        <f>IFERROR(IF('Captura Febrero'!D8=0,"",'Captura Febrero'!AQ8),"")</f>
         <v>1</v>
       </c>
       <c r="D4" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D9=0,"",'Captura Marzo'!AQ9),"")</f>
+        <f>IFERROR(IF('Captura Marzo'!D8=0,"",'Captura Marzo'!AQ8),"")</f>
+        <v>1</v>
+      </c>
+      <c r="E4" s="10">
+        <f>IFERROR(IF('Captura Abril'!D8=0,"",'Captura Abril'!AQ8),"")</f>
+        <v>1</v>
+      </c>
+      <c r="F4" s="10">
+        <f>IFERROR(IF('Captura Mayo'!D8=0,"",'Captura Mayo'!AQ8),"")</f>
+        <v>1</v>
+      </c>
+      <c r="G4" s="10">
+        <f>IFERROR(IF('Captura Junio'!D8=0,"",'Captura Junio'!AQ8),"")</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="10">
+        <f>IFERROR(IF('Captura Julio'!D8=0,"",'Captura Julio'!AQ8),"")</f>
+        <v>1</v>
+      </c>
+      <c r="I4" s="10">
+        <f>IFERROR(IF('Captura Agosto'!D8=0,"",'Captura Agosto'!AQ8),"")</f>
+        <v>0.9</v>
+      </c>
+      <c r="J4" s="10" t="str">
+        <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="10" t="str">
+        <f>IFERROR(IF('Captura Octubre'!D8=0,"",'Captura Octubre'!AQ8),"")</f>
+        <v/>
+      </c>
+      <c r="L4" s="10" t="str">
+        <f>IFERROR(IF('Captura Noviembre'!D8=0,"",'Captura Noviembre'!AQ8),"")</f>
+        <v/>
+      </c>
+      <c r="M4" s="10" t="str">
+        <f>IFERROR(IF('Captura Diciembre'!D8=0,"",'Captura Diciembre'!AQ8),"")</f>
+        <v/>
+      </c>
+      <c r="N4" s="102">
+        <f>IFERROR(AVERAGE(B4:M4),"")</f>
         <v>0.98750000000000004</v>
-      </c>
-      <c r="E4" s="10">
-        <f>IFERROR(IF('Captura Abril'!D9=0,"",'Captura Abril'!AQ9),"")</f>
-        <v>0.99</v>
-      </c>
-      <c r="F4" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D9=0,"",'Captura Mayo'!AQ9),"")</f>
-        <v>0.9</v>
-      </c>
-      <c r="G4" s="10">
-        <f>IFERROR(IF('Captura Junio'!D9=0,"",'Captura Junio'!AQ9),"")</f>
-        <v>1</v>
-      </c>
-      <c r="H4" s="10">
-        <f>IFERROR(IF('Captura Julio'!D9=0,"",'Captura Julio'!AQ9),"")</f>
-        <v>1</v>
-      </c>
-      <c r="I4" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D9=0,"",'Captura Agosto'!AQ9),"")</f>
-        <v>0.4052</v>
-      </c>
-      <c r="J4" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
-        <v/>
-      </c>
-      <c r="K4" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D9=0,"",'Captura Octubre'!AQ9),"")</f>
-        <v/>
-      </c>
-      <c r="L4" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D9=0,"",'Captura Noviembre'!AQ9),"")</f>
-        <v/>
-      </c>
-      <c r="M4" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D9=0,"",'Captura Diciembre'!AQ9),"")</f>
-        <v/>
-      </c>
-      <c r="N4" s="102">
-        <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.91033750000000002</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="101" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="B5" s="10">
-        <f>IFERROR(IF('Captura Enero'!D8=0,"",'Captura Enero'!AQ8),"")</f>
+        <f>IFERROR(IF('Captura Enero'!D9=0,"",'Captura Enero'!AQ9),"")</f>
         <v>1</v>
       </c>
       <c r="C5" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D8=0,"",'Captura Febrero'!AQ8),"")</f>
+        <f>IFERROR(IF('Captura Febrero'!D9=0,"",'Captura Febrero'!AQ9),"")</f>
         <v>1</v>
       </c>
       <c r="D5" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D8=0,"",'Captura Marzo'!AQ8),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Marzo'!D9=0,"",'Captura Marzo'!AQ9),"")</f>
+        <v>0.98750000000000004</v>
       </c>
       <c r="E5" s="10">
-        <f>IFERROR(IF('Captura Abril'!D8=0,"",'Captura Abril'!AQ8),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Abril'!D9=0,"",'Captura Abril'!AQ9),"")</f>
+        <v>0.99</v>
       </c>
       <c r="F5" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D8=0,"",'Captura Mayo'!AQ8),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Mayo'!D9=0,"",'Captura Mayo'!AQ9),"")</f>
+        <v>0.9</v>
       </c>
       <c r="G5" s="10">
-        <f>IFERROR(IF('Captura Junio'!D8=0,"",'Captura Junio'!AQ8),"")</f>
+        <f>IFERROR(IF('Captura Junio'!D9=0,"",'Captura Junio'!AQ9),"")</f>
         <v>1</v>
       </c>
       <c r="H5" s="10">
-        <f>IFERROR(IF('Captura Julio'!D8=0,"",'Captura Julio'!AQ8),"")</f>
+        <f>IFERROR(IF('Captura Julio'!D9=0,"",'Captura Julio'!AQ9),"")</f>
         <v>1</v>
       </c>
       <c r="I5" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D8=0,"",'Captura Agosto'!AQ8),"")</f>
-        <v>0.59000000000000008</v>
+        <f>IFERROR(IF('Captura Agosto'!D9=0,"",'Captura Agosto'!AQ9),"")</f>
+        <v>0.65520000000000012</v>
       </c>
       <c r="J5" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D9=0,"",'Captura Septiembre'!AQ9),"")</f>
         <v/>
       </c>
       <c r="K5" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D8=0,"",'Captura Octubre'!AQ8),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D9=0,"",'Captura Octubre'!AQ9),"")</f>
         <v/>
       </c>
       <c r="L5" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D8=0,"",'Captura Noviembre'!AQ8),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D9=0,"",'Captura Noviembre'!AQ9),"")</f>
         <v/>
       </c>
       <c r="M5" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D8=0,"",'Captura Diciembre'!AQ8),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D9=0,"",'Captura Diciembre'!AQ9),"")</f>
         <v/>
       </c>
       <c r="N5" s="102">
-        <f t="shared" si="0"/>
-        <v>0.94874999999999998</v>
+        <f>IFERROR(AVERAGE(B5:M5),"")</f>
+        <v>0.94158750000000002</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="101" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B6" s="10">
-        <f>IFERROR(IF('Captura Enero'!D10=0,"",'Captura Enero'!AQ10),"")</f>
-        <v>0.95000000000000007</v>
+        <f>IFERROR(IF('Captura Enero'!D16=0,"",'Captura Enero'!AQ16),"")</f>
+        <v>0.9</v>
       </c>
       <c r="C6" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D10=0,"",'Captura Febrero'!AQ10),"")</f>
-        <v>0.84499999999999997</v>
+        <f>IFERROR(IF('Captura Febrero'!D16=0,"",'Captura Febrero'!AQ16),"")</f>
+        <v>0.91428571428571437</v>
       </c>
       <c r="D6" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D10=0,"",'Captura Marzo'!AQ10),"")</f>
+        <f>IFERROR(IF('Captura Marzo'!D16=0,"",'Captura Marzo'!AQ16),"")</f>
         <v>1</v>
       </c>
       <c r="E6" s="10">
-        <f>IFERROR(IF('Captura Abril'!D10=0,"",'Captura Abril'!AQ10),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Abril'!D16=0,"",'Captura Abril'!AQ16),"")</f>
+        <v>0.96000000000000008</v>
       </c>
       <c r="F6" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D10=0,"",'Captura Mayo'!AQ10),"")</f>
-        <v>0.99</v>
+        <f>IFERROR(IF('Captura Mayo'!D16=0,"",'Captura Mayo'!AQ16),"")</f>
+        <v>1</v>
       </c>
       <c r="G6" s="10">
-        <f>IFERROR(IF('Captura Junio'!D10=0,"",'Captura Junio'!AQ10),"")</f>
-        <v>0.87000000000000011</v>
+        <f>IFERROR(IF('Captura Junio'!D16=0,"",'Captura Junio'!AQ16),"")</f>
+        <v>1</v>
       </c>
       <c r="H6" s="10">
-        <f>IFERROR(IF('Captura Julio'!D10=0,"",'Captura Julio'!AQ10),"")</f>
+        <f>IFERROR(IF('Captura Julio'!D16=0,"",'Captura Julio'!AQ16),"")</f>
         <v>1</v>
       </c>
       <c r="I6" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D10=0,"",'Captura Agosto'!AQ10),"")</f>
-        <v>0.49000000000000005</v>
+        <f>IFERROR(IF('Captura Agosto'!D16=0,"",'Captura Agosto'!AQ16),"")</f>
+        <v>0.75839999999999996</v>
       </c>
       <c r="J6" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
         <v/>
       </c>
       <c r="K6" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D10=0,"",'Captura Octubre'!AQ10),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D16=0,"",'Captura Octubre'!AQ16),"")</f>
         <v/>
       </c>
       <c r="L6" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D10=0,"",'Captura Noviembre'!AQ10),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D16=0,"",'Captura Noviembre'!AQ16),"")</f>
         <v/>
       </c>
       <c r="M6" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D10=0,"",'Captura Diciembre'!AQ10),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D16=0,"",'Captura Diciembre'!AQ16),"")</f>
         <v/>
       </c>
       <c r="N6" s="102">
-        <f t="shared" si="0"/>
-        <v>0.89312500000000006</v>
+        <f>IFERROR(AVERAGE(B6:M6),"")</f>
+        <v>0.94158571428571425</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="101" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B7" s="10">
-        <f>IFERROR(IF('Captura Enero'!D14=0,"",'Captura Enero'!AQ14),"")</f>
-        <v>0.99</v>
+        <f>IFERROR(IF('Captura Enero'!D6=0,"",'Captura Enero'!AQ6),"")</f>
+        <v>1</v>
       </c>
       <c r="C7" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D14=0,"",'Captura Febrero'!AQ14),"")</f>
-        <v>0.95</v>
+        <f>IFERROR(IF('Captura Febrero'!D6=0,"",'Captura Febrero'!AQ6),"")</f>
+        <v>1</v>
       </c>
       <c r="D7" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D14=0,"",'Captura Marzo'!AQ14),"")</f>
-        <v>0.99</v>
+        <f>IFERROR(IF('Captura Marzo'!D6=0,"",'Captura Marzo'!AQ6),"")</f>
+        <v>1</v>
       </c>
       <c r="E7" s="10">
-        <f>IFERROR(IF('Captura Abril'!D14=0,"",'Captura Abril'!AQ14),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Abril'!D6=0,"",'Captura Abril'!AQ6),"")</f>
+        <v>0.96000000000000008</v>
       </c>
       <c r="F7" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D14=0,"",'Captura Mayo'!AQ14),"")</f>
-        <v>0.9</v>
+        <f>IFERROR(IF('Captura Mayo'!D6=0,"",'Captura Mayo'!AQ6),"")</f>
+        <v>0.96000000000000008</v>
       </c>
       <c r="G7" s="10">
-        <f>IFERROR(IF('Captura Junio'!D14=0,"",'Captura Junio'!AQ14),"")</f>
-        <v>0.94000000000000006</v>
+        <f>IFERROR(IF('Captura Junio'!D6=0,"",'Captura Junio'!AQ6),"")</f>
+        <v>0.84000000000000008</v>
       </c>
       <c r="H7" s="10">
-        <f>IFERROR(IF('Captura Julio'!D14=0,"",'Captura Julio'!AQ14),"")</f>
-        <v>0.79</v>
+        <f>IFERROR(IF('Captura Julio'!D6=0,"",'Captura Julio'!AQ6),"")</f>
+        <v>1</v>
       </c>
       <c r="I7" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
-        <v>0.37080000000000002</v>
+        <f>IFERROR(IF('Captura Agosto'!D6=0,"",'Captura Agosto'!AQ6),"")</f>
+        <v>0.66474999999999995</v>
       </c>
       <c r="J7" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D6=0,"",'Captura Septiembre'!AQ6),"")</f>
         <v/>
       </c>
       <c r="K7" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D14=0,"",'Captura Octubre'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D6=0,"",'Captura Octubre'!AQ6),"")</f>
         <v/>
       </c>
       <c r="L7" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D14=0,"",'Captura Noviembre'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D6=0,"",'Captura Noviembre'!AQ6),"")</f>
         <v/>
       </c>
       <c r="M7" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D14=0,"",'Captura Diciembre'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D6=0,"",'Captura Diciembre'!AQ6),"")</f>
         <v/>
       </c>
       <c r="N7" s="102">
-        <f t="shared" si="0"/>
-        <v>0.86635000000000006</v>
+        <f>IFERROR(AVERAGE(B7:M7),"")</f>
+        <v>0.92809374999999994</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="101" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B8" s="10">
-        <f>IFERROR(IF('Captura Enero'!D20=0,"",'Captura Enero'!AQ20),"")</f>
-        <v>0.95</v>
+        <f>IFERROR(IF('Captura Enero'!D10=0,"",'Captura Enero'!AQ10),"")</f>
+        <v>0.95000000000000007</v>
       </c>
       <c r="C8" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D20=0,"",'Captura Febrero'!AQ20),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Febrero'!D10=0,"",'Captura Febrero'!AQ10),"")</f>
+        <v>0.84499999999999997</v>
       </c>
       <c r="D8" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D20=0,"",'Captura Marzo'!AQ20),"")</f>
+        <f>IFERROR(IF('Captura Marzo'!D10=0,"",'Captura Marzo'!AQ10),"")</f>
         <v>1</v>
       </c>
       <c r="E8" s="10">
-        <f>IFERROR(IF('Captura Abril'!D20=0,"",'Captura Abril'!AQ20),"")</f>
+        <f>IFERROR(IF('Captura Abril'!D10=0,"",'Captura Abril'!AQ10),"")</f>
         <v>1</v>
       </c>
       <c r="F8" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D20=0,"",'Captura Mayo'!AQ20),"")</f>
-        <v>0.95</v>
+        <f>IFERROR(IF('Captura Mayo'!D10=0,"",'Captura Mayo'!AQ10),"")</f>
+        <v>0.99</v>
       </c>
       <c r="G8" s="10">
-        <f>IFERROR(IF('Captura Junio'!D20=0,"",'Captura Junio'!AQ20),"")</f>
-        <v>0.71000000000000008</v>
+        <f>IFERROR(IF('Captura Junio'!D10=0,"",'Captura Junio'!AQ10),"")</f>
+        <v>0.87000000000000011</v>
       </c>
       <c r="H8" s="10">
-        <f>IFERROR(IF('Captura Julio'!D20=0,"",'Captura Julio'!AQ20),"")</f>
+        <f>IFERROR(IF('Captura Julio'!D10=0,"",'Captura Julio'!AQ10),"")</f>
         <v>1</v>
       </c>
       <c r="I8" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D20=0,"",'Captura Agosto'!AQ20),"")</f>
-        <v>0.46</v>
+        <f>IFERROR(IF('Captura Agosto'!D10=0,"",'Captura Agosto'!AQ10),"")</f>
+        <v>0.72300000000000009</v>
       </c>
       <c r="J8" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D10=0,"",'Captura Septiembre'!AQ10),"")</f>
         <v/>
       </c>
       <c r="K8" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D20=0,"",'Captura Octubre'!AQ20),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D10=0,"",'Captura Octubre'!AQ10),"")</f>
         <v/>
       </c>
       <c r="L8" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D20=0,"",'Captura Noviembre'!AQ20),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D10=0,"",'Captura Noviembre'!AQ10),"")</f>
         <v/>
       </c>
       <c r="M8" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D20=0,"",'Captura Diciembre'!AQ20),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D10=0,"",'Captura Diciembre'!AQ10),"")</f>
         <v/>
       </c>
       <c r="N8" s="102">
-        <f t="shared" si="0"/>
-        <v>0.88375000000000004</v>
+        <f>IFERROR(AVERAGE(B8:M8),"")</f>
+        <v>0.92225000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="101" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B9" s="10">
-        <f>IFERROR(IF('Captura Enero'!D11=0,"",'Captura Enero'!AQ11),"")</f>
-        <v>0.84000000000000008</v>
+        <f>IFERROR(IF('Captura Enero'!D20=0,"",'Captura Enero'!AQ20),"")</f>
+        <v>0.95</v>
       </c>
       <c r="C9" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D11=0,"",'Captura Febrero'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Febrero'!D20=0,"",'Captura Febrero'!AQ20),"")</f>
         <v>1</v>
       </c>
       <c r="D9" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D11=0,"",'Captura Marzo'!AQ11),"")</f>
-        <v>0.97500000000000009</v>
+        <f>IFERROR(IF('Captura Marzo'!D20=0,"",'Captura Marzo'!AQ20),"")</f>
+        <v>1</v>
       </c>
       <c r="E9" s="10">
-        <f>IFERROR(IF('Captura Abril'!D11=0,"",'Captura Abril'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Abril'!D20=0,"",'Captura Abril'!AQ20),"")</f>
         <v>1</v>
       </c>
       <c r="F9" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D11=0,"",'Captura Mayo'!AQ11),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Mayo'!D20=0,"",'Captura Mayo'!AQ20),"")</f>
+        <v>0.95</v>
       </c>
       <c r="G9" s="10">
-        <f>IFERROR(IF('Captura Junio'!D11=0,"",'Captura Junio'!AQ11),"")</f>
-        <v>0.85</v>
+        <f>IFERROR(IF('Captura Junio'!D20=0,"",'Captura Junio'!AQ20),"")</f>
+        <v>0.71000000000000008</v>
       </c>
       <c r="H9" s="10">
-        <f>IFERROR(IF('Captura Julio'!D11=0,"",'Captura Julio'!AQ11),"")</f>
-        <v>0.94000000000000006</v>
+        <f>IFERROR(IF('Captura Julio'!D20=0,"",'Captura Julio'!AQ20),"")</f>
+        <v>1</v>
       </c>
       <c r="I9" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
-        <v>0.41000000000000003</v>
+        <f>IFERROR(IF('Captura Agosto'!D20=0,"",'Captura Agosto'!AQ20),"")</f>
+        <v>0.69399999999999995</v>
       </c>
       <c r="J9" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D20=0,"",'Captura Septiembre'!AQ20),"")</f>
         <v/>
       </c>
       <c r="K9" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D11=0,"",'Captura Octubre'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D20=0,"",'Captura Octubre'!AQ20),"")</f>
         <v/>
       </c>
       <c r="L9" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D11=0,"",'Captura Noviembre'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D20=0,"",'Captura Noviembre'!AQ20),"")</f>
         <v/>
       </c>
       <c r="M9" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D11=0,"",'Captura Diciembre'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D20=0,"",'Captura Diciembre'!AQ20),"")</f>
         <v/>
       </c>
       <c r="N9" s="102">
-        <f t="shared" si="0"/>
-        <v>0.87687500000000007</v>
+        <f>IFERROR(AVERAGE(B9:M9),"")</f>
+        <v>0.91300000000000003</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="101" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B10" s="10">
-        <f>IFERROR(IF('Captura Enero'!D16=0,"",'Captura Enero'!AQ16),"")</f>
-        <v>0.9</v>
+        <f>IFERROR(IF('Captura Enero'!D11=0,"",'Captura Enero'!AQ11),"")</f>
+        <v>0.84000000000000008</v>
       </c>
       <c r="C10" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D16=0,"",'Captura Febrero'!AQ16),"")</f>
-        <v>0.91428571428571437</v>
+        <f>IFERROR(IF('Captura Febrero'!D11=0,"",'Captura Febrero'!AQ11),"")</f>
+        <v>1</v>
       </c>
       <c r="D10" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D16=0,"",'Captura Marzo'!AQ16),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Marzo'!D11=0,"",'Captura Marzo'!AQ11),"")</f>
+        <v>0.97500000000000009</v>
       </c>
       <c r="E10" s="10">
-        <f>IFERROR(IF('Captura Abril'!D16=0,"",'Captura Abril'!AQ16),"")</f>
-        <v>0.96000000000000008</v>
+        <f>IFERROR(IF('Captura Abril'!D11=0,"",'Captura Abril'!AQ11),"")</f>
+        <v>1</v>
       </c>
       <c r="F10" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D16=0,"",'Captura Mayo'!AQ16),"")</f>
+        <f>IFERROR(IF('Captura Mayo'!D11=0,"",'Captura Mayo'!AQ11),"")</f>
         <v>1</v>
       </c>
       <c r="G10" s="10">
-        <f>IFERROR(IF('Captura Junio'!D16=0,"",'Captura Junio'!AQ16),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Junio'!D11=0,"",'Captura Junio'!AQ11),"")</f>
+        <v>0.85</v>
       </c>
       <c r="H10" s="10">
-        <f>IFERROR(IF('Captura Julio'!D16=0,"",'Captura Julio'!AQ16),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Julio'!D11=0,"",'Captura Julio'!AQ11),"")</f>
+        <v>0.94000000000000006</v>
       </c>
       <c r="I10" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D16=0,"",'Captura Agosto'!AQ16),"")</f>
-        <v>0.50839999999999996</v>
+        <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
+        <v>0.66</v>
       </c>
       <c r="J10" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D16=0,"",'Captura Septiembre'!AQ16),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
         <v/>
       </c>
       <c r="K10" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D16=0,"",'Captura Octubre'!AQ16),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D11=0,"",'Captura Octubre'!AQ11),"")</f>
         <v/>
       </c>
       <c r="L10" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D16=0,"",'Captura Noviembre'!AQ16),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D11=0,"",'Captura Noviembre'!AQ11),"")</f>
         <v/>
       </c>
       <c r="M10" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D16=0,"",'Captura Diciembre'!AQ16),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D11=0,"",'Captura Diciembre'!AQ11),"")</f>
         <v/>
       </c>
       <c r="N10" s="102">
-        <f t="shared" si="0"/>
-        <v>0.91033571428571425</v>
+        <f>IFERROR(AVERAGE(B10:M10),"")</f>
+        <v>0.90812500000000007</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="101" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="B11" s="10">
-        <f>IFERROR(IF('Captura Enero'!D18=0,"",'Captura Enero'!AQ18),"")</f>
-        <v>0.84000000000000008</v>
+        <f>IFERROR(IF('Captura Enero'!D14=0,"",'Captura Enero'!AQ14),"")</f>
+        <v>0.99</v>
       </c>
       <c r="C11" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D18=0,"",'Captura Febrero'!AQ18),"")</f>
-        <v>0.81058823529411772</v>
+        <f>IFERROR(IF('Captura Febrero'!D14=0,"",'Captura Febrero'!AQ14),"")</f>
+        <v>0.95</v>
       </c>
       <c r="D11" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D18=0,"",'Captura Marzo'!AQ18),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Marzo'!D14=0,"",'Captura Marzo'!AQ14),"")</f>
+        <v>0.99</v>
       </c>
       <c r="E11" s="10">
-        <f>IFERROR(IF('Captura Abril'!D18=0,"",'Captura Abril'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Abril'!D14=0,"",'Captura Abril'!AQ14),"")</f>
         <v>1</v>
       </c>
       <c r="F11" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D18=0,"",'Captura Mayo'!AQ18),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Mayo'!D14=0,"",'Captura Mayo'!AQ14),"")</f>
+        <v>0.9</v>
       </c>
       <c r="G11" s="10">
-        <f>IFERROR(IF('Captura Junio'!D18=0,"",'Captura Junio'!AQ18),"")</f>
-        <v>0.91000000000000014</v>
+        <f>IFERROR(IF('Captura Junio'!D14=0,"",'Captura Junio'!AQ14),"")</f>
+        <v>0.94000000000000006</v>
       </c>
       <c r="H11" s="10">
-        <f>IFERROR(IF('Captura Julio'!D18=0,"",'Captura Julio'!AQ18),"")</f>
-        <v>0.97666666666666679</v>
+        <f>IFERROR(IF('Captura Julio'!D14=0,"",'Captura Julio'!AQ14),"")</f>
+        <v>0.79</v>
       </c>
       <c r="I11" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D18=0,"",'Captura Agosto'!AQ18),"")</f>
-        <v>0.28739999999999999</v>
+        <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
+        <v>0.62080000000000002</v>
       </c>
       <c r="J11" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
         <v/>
       </c>
       <c r="K11" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D18=0,"",'Captura Octubre'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D14=0,"",'Captura Octubre'!AQ14),"")</f>
         <v/>
       </c>
       <c r="L11" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D18=0,"",'Captura Noviembre'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D14=0,"",'Captura Noviembre'!AQ14),"")</f>
         <v/>
       </c>
       <c r="M11" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D18=0,"",'Captura Diciembre'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D14=0,"",'Captura Diciembre'!AQ14),"")</f>
         <v/>
       </c>
       <c r="N11" s="102">
-        <f t="shared" si="0"/>
-        <v>0.85308186274509801</v>
+        <f>IFERROR(AVERAGE(B11:M11),"")</f>
+        <v>0.89760000000000006</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="101" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="B12" s="10">
-        <f>IFERROR(IF('Captura Enero'!D6=0,"",'Captura Enero'!AQ6),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Enero'!D18=0,"",'Captura Enero'!AQ18),"")</f>
+        <v>0.84000000000000008</v>
       </c>
       <c r="C12" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D6=0,"",'Captura Febrero'!AQ6),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Febrero'!D18=0,"",'Captura Febrero'!AQ18),"")</f>
+        <v>0.81058823529411772</v>
       </c>
       <c r="D12" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D6=0,"",'Captura Marzo'!AQ6),"")</f>
+        <f>IFERROR(IF('Captura Marzo'!D18=0,"",'Captura Marzo'!AQ18),"")</f>
         <v>1</v>
       </c>
       <c r="E12" s="10">
-        <f>IFERROR(IF('Captura Abril'!D6=0,"",'Captura Abril'!AQ6),"")</f>
-        <v>0.96000000000000008</v>
+        <f>IFERROR(IF('Captura Abril'!D18=0,"",'Captura Abril'!AQ18),"")</f>
+        <v>1</v>
       </c>
       <c r="F12" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D6=0,"",'Captura Mayo'!AQ6),"")</f>
-        <v>0.96000000000000008</v>
+        <f>IFERROR(IF('Captura Mayo'!D18=0,"",'Captura Mayo'!AQ18),"")</f>
+        <v>1</v>
       </c>
       <c r="G12" s="10">
-        <f>IFERROR(IF('Captura Junio'!D6=0,"",'Captura Junio'!AQ6),"")</f>
-        <v>0.84000000000000008</v>
+        <f>IFERROR(IF('Captura Junio'!D18=0,"",'Captura Junio'!AQ18),"")</f>
+        <v>0.91000000000000014</v>
       </c>
       <c r="H12" s="10">
-        <f>IFERROR(IF('Captura Julio'!D6=0,"",'Captura Julio'!AQ6),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Julio'!D18=0,"",'Captura Julio'!AQ18),"")</f>
+        <v>0.97666666666666679</v>
       </c>
       <c r="I12" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D6=0,"",'Captura Agosto'!AQ6),"")</f>
-        <v>0.43</v>
+        <f>IFERROR(IF('Captura Agosto'!D18=0,"",'Captura Agosto'!AQ18),"")</f>
+        <v>0.53739999999999999</v>
       </c>
       <c r="J12" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D6=0,"",'Captura Septiembre'!AQ6),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
         <v/>
       </c>
       <c r="K12" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D6=0,"",'Captura Octubre'!AQ6),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D18=0,"",'Captura Octubre'!AQ18),"")</f>
         <v/>
       </c>
       <c r="L12" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D6=0,"",'Captura Noviembre'!AQ6),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D18=0,"",'Captura Noviembre'!AQ18),"")</f>
         <v/>
       </c>
       <c r="M12" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D6=0,"",'Captura Diciembre'!AQ6),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D18=0,"",'Captura Diciembre'!AQ18),"")</f>
         <v/>
       </c>
       <c r="N12" s="102">
-        <f t="shared" si="0"/>
-        <v>0.89874999999999994</v>
+        <f>IFERROR(AVERAGE(B12:M12),"")</f>
+        <v>0.88433186274509801</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34197,7 +34196,7 @@
       </c>
       <c r="I13" s="10">
         <f>IFERROR(IF('Captura Agosto'!D19=0,"",'Captura Agosto'!AQ19),"")</f>
-        <v>0.26</v>
+        <v>0.49125000000000002</v>
       </c>
       <c r="J13" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
@@ -34216,122 +34215,122 @@
         <v/>
       </c>
       <c r="N13" s="102">
-        <f t="shared" si="0"/>
-        <v>0.81906249999999992</v>
+        <f>IFERROR(AVERAGE(B13:M13),"")</f>
+        <v>0.84796874999999994</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="101" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="B14" s="10">
-        <f>IFERROR(IF('Captura Enero'!D17=0,"",'Captura Enero'!AQ17),"")</f>
-        <v>0.86461538461538467</v>
+        <f>IFERROR(IF('Captura Enero'!D12=0,"",'Captura Enero'!AQ12),"")</f>
+        <v>0.79</v>
       </c>
       <c r="C14" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D17=0,"",'Captura Febrero'!AQ17),"")</f>
-        <v>0.96428571428571441</v>
+        <f>IFERROR(IF('Captura Febrero'!D12=0,"",'Captura Febrero'!AQ12),"")</f>
+        <v>0.9</v>
       </c>
       <c r="D14" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D17=0,"",'Captura Marzo'!AQ17),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Marzo'!D12=0,"",'Captura Marzo'!AQ12),"")</f>
+        <v>0.95</v>
       </c>
       <c r="E14" s="10">
-        <f>IFERROR(IF('Captura Abril'!D17=0,"",'Captura Abril'!AQ17),"")</f>
-        <v>0.74</v>
+        <f>IFERROR(IF('Captura Abril'!D12=0,"",'Captura Abril'!AQ12),"")</f>
+        <v>1</v>
       </c>
       <c r="F14" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D17=0,"",'Captura Mayo'!AQ17),"")</f>
-        <v>0.89</v>
+        <f>IFERROR(IF('Captura Mayo'!D12=0,"",'Captura Mayo'!AQ12),"")</f>
+        <v>0.7</v>
       </c>
       <c r="G14" s="10">
-        <f>IFERROR(IF('Captura Junio'!D17=0,"",'Captura Junio'!AQ17),"")</f>
-        <v>0.79285714285714293</v>
+        <f>IFERROR(IF('Captura Junio'!D12=0,"",'Captura Junio'!AQ12),"")</f>
+        <v>0.70130434782608708</v>
       </c>
       <c r="H14" s="10">
-        <f>IFERROR(IF('Captura Julio'!D17=0,"",'Captura Julio'!AQ17),"")</f>
-        <v>0.83</v>
+        <f>IFERROR(IF('Captura Julio'!D12=0,"",'Captura Julio'!AQ12),"")</f>
+        <v>0.9</v>
       </c>
       <c r="I14" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D17=0,"",'Captura Agosto'!AQ17),"")</f>
-        <v>0.26119999999999999</v>
+        <f>IFERROR(IF('Captura Agosto'!D12=0,"",'Captura Agosto'!AQ12),"")</f>
+        <v>0.68399999999999994</v>
       </c>
       <c r="J14" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
         <v/>
       </c>
       <c r="K14" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D17=0,"",'Captura Octubre'!AQ17),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D12=0,"",'Captura Octubre'!AQ12),"")</f>
         <v/>
       </c>
       <c r="L14" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D17=0,"",'Captura Noviembre'!AQ17),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D12=0,"",'Captura Noviembre'!AQ12),"")</f>
         <v/>
       </c>
       <c r="M14" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D17=0,"",'Captura Diciembre'!AQ17),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D12=0,"",'Captura Diciembre'!AQ12),"")</f>
         <v/>
       </c>
       <c r="N14" s="102">
-        <f t="shared" si="0"/>
-        <v>0.79286978021978016</v>
+        <f>IFERROR(AVERAGE(B14:M14),"")</f>
+        <v>0.82816304347826097</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="101" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="B15" s="10">
-        <f>IFERROR(IF('Captura Enero'!D12=0,"",'Captura Enero'!AQ12),"")</f>
-        <v>0.79</v>
+        <f>IFERROR(IF('Captura Enero'!D17=0,"",'Captura Enero'!AQ17),"")</f>
+        <v>0.86461538461538467</v>
       </c>
       <c r="C15" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D12=0,"",'Captura Febrero'!AQ12),"")</f>
-        <v>0.9</v>
+        <f>IFERROR(IF('Captura Febrero'!D17=0,"",'Captura Febrero'!AQ17),"")</f>
+        <v>0.96428571428571441</v>
       </c>
       <c r="D15" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D12=0,"",'Captura Marzo'!AQ12),"")</f>
-        <v>0.95</v>
+        <f>IFERROR(IF('Captura Marzo'!D17=0,"",'Captura Marzo'!AQ17),"")</f>
+        <v>1</v>
       </c>
       <c r="E15" s="10">
-        <f>IFERROR(IF('Captura Abril'!D12=0,"",'Captura Abril'!AQ12),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Abril'!D17=0,"",'Captura Abril'!AQ17),"")</f>
+        <v>0.74</v>
       </c>
       <c r="F15" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D12=0,"",'Captura Mayo'!AQ12),"")</f>
-        <v>0.7</v>
+        <f>IFERROR(IF('Captura Mayo'!D17=0,"",'Captura Mayo'!AQ17),"")</f>
+        <v>0.89</v>
       </c>
       <c r="G15" s="10">
-        <f>IFERROR(IF('Captura Junio'!D12=0,"",'Captura Junio'!AQ12),"")</f>
-        <v>0.70130434782608708</v>
+        <f>IFERROR(IF('Captura Junio'!D17=0,"",'Captura Junio'!AQ17),"")</f>
+        <v>0.79285714285714293</v>
       </c>
       <c r="H15" s="10">
-        <f>IFERROR(IF('Captura Julio'!D12=0,"",'Captura Julio'!AQ12),"")</f>
-        <v>0.9</v>
+        <f>IFERROR(IF('Captura Julio'!D17=0,"",'Captura Julio'!AQ17),"")</f>
+        <v>0.83</v>
       </c>
       <c r="I15" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D12=0,"",'Captura Agosto'!AQ12),"")</f>
-        <v>0.45</v>
+        <f>IFERROR(IF('Captura Agosto'!D17=0,"",'Captura Agosto'!AQ17),"")</f>
+        <v>0.51119999999999999</v>
       </c>
       <c r="J15" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D12=0,"",'Captura Septiembre'!AQ12),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D17=0,"",'Captura Septiembre'!AQ17),"")</f>
         <v/>
       </c>
       <c r="K15" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D12=0,"",'Captura Octubre'!AQ12),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D17=0,"",'Captura Octubre'!AQ17),"")</f>
         <v/>
       </c>
       <c r="L15" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D12=0,"",'Captura Noviembre'!AQ12),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D17=0,"",'Captura Noviembre'!AQ17),"")</f>
         <v/>
       </c>
       <c r="M15" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D12=0,"",'Captura Diciembre'!AQ12),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D17=0,"",'Captura Diciembre'!AQ17),"")</f>
         <v/>
       </c>
       <c r="N15" s="102">
-        <f t="shared" si="0"/>
-        <v>0.79891304347826098</v>
+        <f>IFERROR(AVERAGE(B15:M15),"")</f>
+        <v>0.82411978021978016</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34368,7 +34367,7 @@
       </c>
       <c r="I16" s="10">
         <f>IFERROR(IF('Captura Agosto'!D15=0,"",'Captura Agosto'!AQ15),"")</f>
-        <v>0.21200000000000002</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="J16" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D15=0,"",'Captura Septiembre'!AQ15),"")</f>
@@ -34387,8 +34386,8 @@
         <v/>
       </c>
       <c r="N16" s="102">
-        <f t="shared" si="0"/>
-        <v>0.77389766081871347</v>
+        <f>IFERROR(AVERAGE(B16:M16),"")</f>
+        <v>0.80514766081871347</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34425,7 +34424,7 @@
       </c>
       <c r="I17" s="10">
         <f>IFERROR(IF('Captura Agosto'!D13=0,"",'Captura Agosto'!AQ13),"")</f>
-        <v>0.20819999999999997</v>
+        <v>0.45820000000000005</v>
       </c>
       <c r="J17" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
@@ -34444,8 +34443,8 @@
         <v/>
       </c>
       <c r="N17" s="102">
-        <f t="shared" si="0"/>
-        <v>0.74977499999999986</v>
+        <f>IFERROR(AVERAGE(B17:M17),"")</f>
+        <v>0.78102499999999986</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34482,7 +34481,7 @@
       </c>
       <c r="I18" s="10">
         <f>IFERROR(IF('Captura Agosto'!D7=0,"",'Captura Agosto'!AQ7),"")</f>
-        <v>0.15</v>
+        <v>0.46000000000000008</v>
       </c>
       <c r="J18" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D7=0,"",'Captura Septiembre'!AQ7),"")</f>
@@ -34501,8 +34500,8 @@
         <v/>
       </c>
       <c r="N18" s="102">
-        <f t="shared" si="0"/>
-        <v>0.72125000000000006</v>
+        <f>IFERROR(AVERAGE(B18:M18),"")</f>
+        <v>0.76</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -34510,51 +34509,51 @@
         <v>298</v>
       </c>
       <c r="B19" s="104">
-        <f t="shared" ref="B19:M19" si="1">IFERROR(AVERAGE(B4:B18),"")</f>
-        <v>0.93030769230769228</v>
+        <f>IFERROR(AVERAGE(B4:B18),"")</f>
+        <v>0.93030769230769239</v>
       </c>
       <c r="C19" s="104">
-        <f t="shared" si="1"/>
-        <v>0.95725976706472082</v>
+        <f>IFERROR(AVERAGE(C4:C18),"")</f>
+        <v>0.9572597670647206</v>
       </c>
       <c r="D19" s="104">
-        <f t="shared" si="1"/>
+        <f>IFERROR(AVERAGE(D4:D18),"")</f>
         <v>0.99283333333333335</v>
       </c>
       <c r="E19" s="104">
-        <f t="shared" si="1"/>
+        <f>IFERROR(AVERAGE(E4:E18),"")</f>
         <v>0.93466666666666665</v>
       </c>
       <c r="F19" s="104">
-        <f t="shared" si="1"/>
+        <f>IFERROR(AVERAGE(F4:F18),"")</f>
         <v>0.87666666666666659</v>
       </c>
       <c r="G19" s="104">
-        <f t="shared" si="1"/>
+        <f>IFERROR(AVERAGE(G4:G18),"")</f>
         <v>0.83357372900851157</v>
       </c>
       <c r="H19" s="104">
-        <f t="shared" si="1"/>
+        <f>IFERROR(AVERAGE(H4:H18),"")</f>
         <v>0.88027777777777794</v>
       </c>
       <c r="I19" s="104">
-        <f t="shared" si="1"/>
-        <v>0.36621333333333334</v>
+        <f>IFERROR(AVERAGE(I4:I18),"")</f>
+        <v>0.61868000000000001</v>
       </c>
       <c r="J19" s="104" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(AVERAGE(J4:J18),"")</f>
         <v/>
       </c>
       <c r="K19" s="104" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(AVERAGE(K4:K18),"")</f>
         <v/>
       </c>
       <c r="L19" s="104" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(AVERAGE(L4:L18),"")</f>
         <v/>
       </c>
       <c r="M19" s="104" t="str">
-        <f t="shared" si="1"/>
+        <f>IFERROR(AVERAGE(M4:M18),"")</f>
         <v/>
       </c>
       <c r="N19" s="105">
@@ -34568,7 +34567,7 @@
   </sheetData>
   <autoFilter ref="A3:N19" xr:uid="{00000000-0009-0000-0000-000013000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:N19">
-      <sortCondition descending="1" ref="C4:C19"/>
+      <sortCondition descending="1" ref="N3:N19"/>
     </sortState>
   </autoFilter>
   <mergeCells count="1">
@@ -34599,44 +34598,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="116" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
-      <c r="P2" s="127"/>
-      <c r="Q2" s="127"/>
-      <c r="R2" s="127"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
     </row>
     <row r="3" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
-      <c r="M3" s="127"/>
-      <c r="N3" s="127"/>
-      <c r="O3" s="127"/>
-      <c r="P3" s="127"/>
-      <c r="Q3" s="127"/>
-      <c r="R3" s="127"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="116"/>
+      <c r="K3" s="116"/>
+      <c r="L3" s="116"/>
+      <c r="M3" s="116"/>
+      <c r="N3" s="116"/>
+      <c r="O3" s="116"/>
+      <c r="P3" s="116"/>
+      <c r="Q3" s="116"/>
+      <c r="R3" s="116"/>
     </row>
     <row r="4" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
@@ -34646,153 +34645,153 @@
         <f>Calculos!$B$2</f>
         <v>Agosto</v>
       </c>
-      <c r="F4" s="128" t="s">
+      <c r="F4" s="117" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="128"/>
-      <c r="O4" s="128"/>
-      <c r="P4" s="128"/>
-      <c r="Q4" s="128"/>
-      <c r="R4" s="128"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="117"/>
+      <c r="N4" s="117"/>
+      <c r="O4" s="117"/>
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="117"/>
     </row>
     <row r="6" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="129" t="s">
+      <c r="B6" s="118" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="129"/>
-      <c r="D6" s="129"/>
-      <c r="E6" s="129"/>
-      <c r="F6" s="129" t="s">
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="129"/>
-      <c r="H6" s="129"/>
-      <c r="I6" s="129"/>
-      <c r="J6" s="129" t="s">
+      <c r="G6" s="118"/>
+      <c r="H6" s="118"/>
+      <c r="I6" s="118"/>
+      <c r="J6" s="118" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="129"/>
-      <c r="L6" s="129"/>
-      <c r="M6" s="129" t="s">
+      <c r="K6" s="118"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="118" t="s">
         <v>64</v>
       </c>
-      <c r="N6" s="129"/>
-      <c r="O6" s="129"/>
-      <c r="P6" s="129" t="s">
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="Q6" s="129"/>
-      <c r="R6" s="129"/>
+      <c r="Q6" s="118"/>
+      <c r="R6" s="118"/>
     </row>
     <row r="7" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="129"/>
-      <c r="C7" s="129"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="129"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="129"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="129"/>
-      <c r="M7" s="129"/>
-      <c r="N7" s="129"/>
-      <c r="O7" s="129"/>
-      <c r="P7" s="129"/>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="129"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="118"/>
+      <c r="K7" s="118"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118"/>
+      <c r="N7" s="118"/>
+      <c r="O7" s="118"/>
+      <c r="P7" s="118"/>
+      <c r="Q7" s="118"/>
+      <c r="R7" s="118"/>
     </row>
     <row r="8" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="130">
+      <c r="B8" s="111">
         <f ca="1">Calculos!B44</f>
-        <v>0.36621333333333334</v>
-      </c>
-      <c r="C8" s="130"/>
-      <c r="D8" s="130"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="131" t="str">
+        <v>0.61868000000000001</v>
+      </c>
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="112" t="str">
         <f ca="1">Calculos!B45</f>
         <v>Rojo</v>
       </c>
-      <c r="G8" s="131"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="131"/>
-      <c r="J8" s="132">
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="113">
         <f ca="1">Calculos!B40</f>
         <v>0</v>
       </c>
-      <c r="K8" s="132"/>
-      <c r="L8" s="132"/>
-      <c r="M8" s="125">
+      <c r="K8" s="113"/>
+      <c r="L8" s="113"/>
+      <c r="M8" s="114">
         <f ca="1">Calculos!B41</f>
         <v>0</v>
       </c>
-      <c r="N8" s="125"/>
-      <c r="O8" s="125"/>
-      <c r="P8" s="126">
+      <c r="N8" s="114"/>
+      <c r="O8" s="114"/>
+      <c r="P8" s="115">
         <f ca="1">Calculos!B42</f>
         <v>15</v>
       </c>
-      <c r="Q8" s="126"/>
-      <c r="R8" s="126"/>
+      <c r="Q8" s="115"/>
+      <c r="R8" s="115"/>
     </row>
     <row r="9" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="130"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="130"/>
-      <c r="E9" s="130"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="131"/>
-      <c r="J9" s="132"/>
-      <c r="K9" s="132"/>
-      <c r="L9" s="132"/>
-      <c r="M9" s="125"/>
-      <c r="N9" s="125"/>
-      <c r="O9" s="125"/>
-      <c r="P9" s="126"/>
-      <c r="Q9" s="126"/>
-      <c r="R9" s="126"/>
+      <c r="B9" s="111"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="113"/>
+      <c r="K9" s="113"/>
+      <c r="L9" s="113"/>
+      <c r="M9" s="114"/>
+      <c r="N9" s="114"/>
+      <c r="O9" s="114"/>
+      <c r="P9" s="115"/>
+      <c r="Q9" s="115"/>
+      <c r="R9" s="115"/>
     </row>
     <row r="10" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="130"/>
-      <c r="C10" s="130"/>
-      <c r="D10" s="130"/>
-      <c r="E10" s="130"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="132"/>
-      <c r="K10" s="132"/>
-      <c r="L10" s="132"/>
-      <c r="M10" s="125"/>
-      <c r="N10" s="125"/>
-      <c r="O10" s="125"/>
-      <c r="P10" s="126"/>
-      <c r="Q10" s="126"/>
-      <c r="R10" s="126"/>
+      <c r="B10" s="111"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="113"/>
+      <c r="K10" s="113"/>
+      <c r="L10" s="113"/>
+      <c r="M10" s="114"/>
+      <c r="N10" s="114"/>
+      <c r="O10" s="114"/>
+      <c r="P10" s="115"/>
+      <c r="Q10" s="115"/>
+      <c r="R10" s="115"/>
     </row>
     <row r="12" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="123" t="s">
+      <c r="B12" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="123"/>
-      <c r="D12" s="123"/>
-      <c r="E12" s="123"/>
-      <c r="G12" s="123" t="s">
+      <c r="C12" s="106"/>
+      <c r="D12" s="106"/>
+      <c r="E12" s="106"/>
+      <c r="G12" s="106" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="123"/>
+      <c r="H12" s="106"/>
     </row>
     <row r="13" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="7" t="s">
@@ -34859,7 +34858,7 @@
       </c>
       <c r="H16" s="22">
         <f ca="1">Calculos!D7</f>
-        <v>0.82599999999999996</v>
+        <v>0.89266666666666672</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34877,7 +34876,7 @@
       </c>
       <c r="H17" s="22">
         <f ca="1">Calculos!D8</f>
-        <v>0.82599999999999996</v>
+        <v>0.89266666666666672</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34895,7 +34894,7 @@
       </c>
       <c r="H18" s="22">
         <f ca="1">Calculos!D9</f>
-        <v>0</v>
+        <v>1.1111111111111112</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34913,7 +34912,7 @@
       </c>
       <c r="H19" s="22">
         <f ca="1">Calculos!D10</f>
-        <v>0</v>
+        <v>0.97786666666666677</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34977,7 +34976,7 @@
     <row r="25" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="str">
         <f ca="1">Calculos!B34</f>
-        <v>Linea 1</v>
+        <v>Alrededores</v>
       </c>
       <c r="C25" s="21">
         <f ca="1">Calculos!C34</f>
@@ -34987,7 +34986,7 @@
     <row r="26" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="str">
         <f ca="1">Calculos!B35</f>
-        <v>Alrededores</v>
+        <v>Linea 1</v>
       </c>
       <c r="C26" s="21">
         <f ca="1">Calculos!C35</f>
@@ -35043,11 +35042,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B8:E10"/>
-    <mergeCell ref="F8:I10"/>
-    <mergeCell ref="J8:L10"/>
     <mergeCell ref="M8:O10"/>
     <mergeCell ref="P8:R10"/>
     <mergeCell ref="B2:R3"/>
@@ -35057,6 +35051,11 @@
     <mergeCell ref="J6:L7"/>
     <mergeCell ref="M6:O7"/>
     <mergeCell ref="P6:R7"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B8:E10"/>
+    <mergeCell ref="F8:I10"/>
+    <mergeCell ref="J8:L10"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -35086,61 +35085,61 @@
   <sheetData>
     <row r="1" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="121" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="117" t="s">
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="122" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
       <c r="H2" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="118" t="s">
+      <c r="B4" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118"/>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118"/>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="123"/>
+      <c r="M4" s="123"/>
+      <c r="N4" s="123"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="123"/>
+      <c r="Q4" s="123"/>
     </row>
     <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="119" t="str">
+      <c r="B5" s="124" t="str">
         <f>UPPER("Planta Cuyotenango  ·  "&amp;Calculos!$B$2&amp;" 2026  ·  Acumulado Año")</f>
         <v>PLANTA CUYOTENANGO  ·  AGOSTO 2026  ·  ACUMULADO AÑO</v>
       </c>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="119"/>
-      <c r="L5" s="119"/>
-      <c r="M5" s="119"/>
-      <c r="N5" s="119"/>
-      <c r="O5" s="119"/>
-      <c r="P5" s="119"/>
-      <c r="Q5" s="119"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="124"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="124"/>
+      <c r="I5" s="124"/>
+      <c r="J5" s="124"/>
+      <c r="K5" s="124"/>
+      <c r="L5" s="124"/>
+      <c r="M5" s="124"/>
+      <c r="N5" s="124"/>
+      <c r="O5" s="124"/>
+      <c r="P5" s="124"/>
+      <c r="Q5" s="124"/>
     </row>
     <row r="6" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="P6" s="28" t="s">
@@ -35151,7 +35150,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="106" t="str">
+      <c r="A7" s="125" t="str">
         <f>UPPER(Calculos!$B$2)</f>
         <v>AGOSTO</v>
       </c>
@@ -35168,13 +35167,13 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="106"/>
-      <c r="G8" s="107">
+      <c r="A8" s="125"/>
+      <c r="G8" s="126">
         <f ca="1">X31</f>
         <v>0</v>
       </c>
-      <c r="H8" s="107"/>
-      <c r="I8" s="107"/>
+      <c r="H8" s="126"/>
+      <c r="I8" s="126"/>
       <c r="P8" s="31" t="s">
         <v>76</v>
       </c>
@@ -35184,15 +35183,15 @@
       </c>
     </row>
     <row r="9" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="106"/>
-      <c r="F9" s="108">
+      <c r="A9" s="125"/>
+      <c r="F9" s="127">
         <f ca="1">X32</f>
         <v>0</v>
       </c>
-      <c r="G9" s="108"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="108"/>
+      <c r="G9" s="127"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="127"/>
+      <c r="J9" s="127"/>
       <c r="P9" s="31" t="s">
         <v>77</v>
       </c>
@@ -35202,17 +35201,17 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="106"/>
-      <c r="E10" s="109">
+      <c r="A10" s="125"/>
+      <c r="E10" s="128">
         <f ca="1">X33</f>
         <v>0</v>
       </c>
-      <c r="F10" s="109"/>
-      <c r="G10" s="109"/>
-      <c r="H10" s="109"/>
-      <c r="I10" s="109"/>
-      <c r="J10" s="109"/>
-      <c r="K10" s="109"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
       <c r="P10" s="31" t="s">
         <v>78</v>
       </c>
@@ -35222,43 +35221,43 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="106"/>
-      <c r="D11" s="110">
+      <c r="A11" s="125"/>
+      <c r="D11" s="129">
         <f ca="1">X34</f>
-        <v>3</v>
-      </c>
-      <c r="E11" s="110"/>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="110"/>
-      <c r="K11" s="110"/>
-      <c r="L11" s="110"/>
+        <v>5</v>
+      </c>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="129"/>
+      <c r="J11" s="129"/>
+      <c r="K11" s="129"/>
+      <c r="L11" s="129"/>
       <c r="P11" s="31" t="s">
         <v>79</v>
       </c>
       <c r="Q11" s="32">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="106"/>
-      <c r="C12" s="111">
+      <c r="A12" s="125"/>
+      <c r="C12" s="130">
         <f ca="1">X35</f>
         <v>0</v>
       </c>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="111"/>
-      <c r="L12" s="111"/>
-      <c r="M12" s="111"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="130"/>
+      <c r="G12" s="130"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="130"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="130"/>
+      <c r="M12" s="130"/>
       <c r="P12" s="31" t="s">
         <v>80</v>
       </c>
@@ -35268,75 +35267,75 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="106"/>
-      <c r="B13" s="112">
+      <c r="A13" s="125"/>
+      <c r="B13" s="131">
         <f ca="1">X36</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="112"/>
-      <c r="D13" s="112"/>
-      <c r="E13" s="112"/>
-      <c r="F13" s="112"/>
-      <c r="G13" s="112"/>
-      <c r="H13" s="112"/>
-      <c r="I13" s="112"/>
-      <c r="J13" s="112"/>
-      <c r="K13" s="112"/>
-      <c r="L13" s="112"/>
-      <c r="M13" s="112"/>
-      <c r="N13" s="112"/>
+        <v>27</v>
+      </c>
+      <c r="C13" s="131"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="131"/>
+      <c r="J13" s="131"/>
+      <c r="K13" s="131"/>
+      <c r="L13" s="131"/>
+      <c r="M13" s="131"/>
+      <c r="N13" s="131"/>
       <c r="P13" s="31" t="s">
         <v>81</v>
       </c>
       <c r="Q13" s="34">
         <f t="shared" si="0"/>
-        <v>411</v>
+        <v>438</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="106"/>
-      <c r="B14" s="113">
+      <c r="A14" s="125"/>
+      <c r="B14" s="132">
         <f ca="1">X37</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="113"/>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="113"/>
-      <c r="G14" s="113"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="113"/>
-      <c r="J14" s="113"/>
-      <c r="K14" s="113"/>
-      <c r="L14" s="113"/>
-      <c r="M14" s="113"/>
-      <c r="N14" s="113"/>
+        <v>196</v>
+      </c>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="132"/>
+      <c r="K14" s="132"/>
+      <c r="L14" s="132"/>
+      <c r="M14" s="132"/>
+      <c r="N14" s="132"/>
       <c r="P14" s="31" t="s">
         <v>82</v>
       </c>
       <c r="Q14" s="34">
         <f t="shared" si="0"/>
-        <v>1692</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="S16" s="114" t="s">
+      <c r="S16" s="119" t="s">
         <v>83</v>
       </c>
-      <c r="T16" s="114"/>
-      <c r="U16" s="114"/>
-      <c r="V16" s="114"/>
+      <c r="T16" s="119"/>
+      <c r="U16" s="119"/>
+      <c r="V16" s="119"/>
     </row>
     <row r="17" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S18" s="35">
         <f ca="1">IF(T20="","—",INT(TODAY()-T20))</f>
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="U18" s="35">
         <f ca="1">IF(V20="","—",INT(TODAY()-V20))</f>
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -35365,11 +35364,11 @@
     <row r="22" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S22" s="35">
         <f ca="1">IF(T24="","—",INT(TODAY()-T24))</f>
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="U22" s="35">
         <f ca="1">IF(V24="","—",INT(TODAY()-V24))</f>
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -35397,42 +35396,42 @@
     <row r="25" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="2:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="115" t="s">
+      <c r="B27" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="115"/>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="115"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
-      <c r="L27" s="115"/>
-      <c r="M27" s="115"/>
-      <c r="N27" s="115"/>
-      <c r="O27" s="115"/>
-      <c r="P27" s="115"/>
-      <c r="Q27" s="115"/>
+      <c r="C27" s="120"/>
+      <c r="D27" s="120"/>
+      <c r="E27" s="120"/>
+      <c r="F27" s="120"/>
+      <c r="G27" s="120"/>
+      <c r="H27" s="120"/>
+      <c r="I27" s="120"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="120"/>
+      <c r="M27" s="120"/>
+      <c r="N27" s="120"/>
+      <c r="O27" s="120"/>
+      <c r="P27" s="120"/>
+      <c r="Q27" s="120"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="115"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="115"/>
-      <c r="E28" s="115"/>
-      <c r="F28" s="115"/>
-      <c r="G28" s="115"/>
-      <c r="H28" s="115"/>
-      <c r="I28" s="115"/>
-      <c r="J28" s="115"/>
-      <c r="K28" s="115"/>
-      <c r="L28" s="115"/>
-      <c r="M28" s="115"/>
-      <c r="N28" s="115"/>
-      <c r="O28" s="115"/>
-      <c r="P28" s="115"/>
-      <c r="Q28" s="115"/>
+      <c r="B28" s="120"/>
+      <c r="C28" s="120"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="120"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="120"/>
+      <c r="L28" s="120"/>
+      <c r="M28" s="120"/>
+      <c r="N28" s="120"/>
+      <c r="O28" s="120"/>
+      <c r="P28" s="120"/>
+      <c r="Q28" s="120"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.35">
       <c r="W30" s="39" t="s">
@@ -35490,11 +35489,11 @@
       </c>
       <c r="X34" s="41">
         <f ca="1">IFERROR(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF6")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF7")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF8")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF9")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF10")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF11")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF12")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF13")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF14")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF15")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF16")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF17")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF18")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF19")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF20"),0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y34" s="41">
         <f>SUM('Captura Enero'!AF6:AF20)+SUM('Captura Febrero'!AF6:AF20)+SUM('Captura Marzo'!AF6:AF20)+SUM('Captura Abril'!AF6:AF20)+SUM('Captura Mayo'!AF6:AF20)+SUM('Captura Junio'!AF6:AF20)+SUM('Captura Julio'!AF6:AF20)+SUM('Captura Agosto'!AF6:AF20)+SUM('Captura Septiembre'!AF6:AF20)+SUM('Captura Octubre'!AF6:AF20)+SUM('Captura Noviembre'!AF6:AF20)+SUM('Captura Diciembre'!AF6:AF20)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="23:25" x14ac:dyDescent="0.35">
@@ -35516,11 +35515,11 @@
       </c>
       <c r="X36" s="42">
         <f ca="1">IFERROR(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!BC3"),0)</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Y36" s="41">
         <f>'Captura Enero'!BC3+'Captura Febrero'!BC3+'Captura Marzo'!BC3+'Captura Abril'!BC3+'Captura Mayo'!BC3+'Captura Junio'!BC3+'Captura Julio'!BC3+'Captura Agosto'!BC3+'Captura Septiembre'!BC3+'Captura Octubre'!BC3+'Captura Noviembre'!BC3+'Captura Diciembre'!BC3</f>
-        <v>411</v>
+        <v>438</v>
       </c>
     </row>
     <row r="37" spans="23:25" x14ac:dyDescent="0.35">
@@ -35529,21 +35528,15 @@
       </c>
       <c r="X37" s="42">
         <f ca="1">IFERROR(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!BC4"),0)</f>
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="Y37" s="41">
         <f>'Captura Enero'!BC4+'Captura Febrero'!BC4+'Captura Marzo'!BC4+'Captura Abril'!BC4+'Captura Mayo'!BC4+'Captura Junio'!BC4+'Captura Julio'!BC4+'Captura Agosto'!BC4+'Captura Septiembre'!BC4+'Captura Octubre'!BC4+'Captura Noviembre'!BC4+'Captura Diciembre'!BC4</f>
-        <v>1692</v>
+        <v>1888</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="S16:V16"/>
-    <mergeCell ref="B27:Q28"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="B5:Q5"/>
     <mergeCell ref="A7:A14"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="F9:J9"/>
@@ -35552,6 +35545,12 @@
     <mergeCell ref="C12:M12"/>
     <mergeCell ref="B13:N13"/>
     <mergeCell ref="B14:N14"/>
+    <mergeCell ref="S16:V16"/>
+    <mergeCell ref="B27:Q28"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="B5:Q5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="E2" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -35586,26 +35585,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="124" t="s">
+      <c r="B2" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="123" t="s">
+      <c r="B4" s="106" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="123"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="123"/>
-      <c r="F4" s="123"/>
-      <c r="H4" s="123" t="s">
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="H4" s="106" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="123"/>
+      <c r="I4" s="106"/>
     </row>
     <row r="5" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="7" t="s">
@@ -35866,13 +35865,13 @@
       </c>
     </row>
     <row r="16" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="123" t="s">
+      <c r="B16" s="106" t="s">
         <v>132</v>
       </c>
-      <c r="C16" s="123"/>
-      <c r="D16" s="123"/>
-      <c r="E16" s="123"/>
-      <c r="F16" s="123"/>
+      <c r="C16" s="106"/>
+      <c r="D16" s="106"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="106"/>
       <c r="H16" s="8">
         <v>11</v>
       </c>
@@ -35955,13 +35954,13 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="123" t="s">
+      <c r="B21" s="106" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="123"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="123"/>
-      <c r="F21" s="123"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="106"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="106"/>
     </row>
     <row r="22" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="52"/>
@@ -36008,13 +36007,13 @@
       <c r="F25" s="52"/>
     </row>
     <row r="27" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="123" t="s">
+      <c r="B27" s="106" t="s">
         <v>149</v>
       </c>
-      <c r="C27" s="123"/>
-      <c r="D27" s="123"/>
-      <c r="E27" s="123"/>
-      <c r="F27" s="123"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="106"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="106"/>
     </row>
     <row r="28" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="52"/>
@@ -36083,13 +36082,13 @@
       <c r="F33" s="52"/>
     </row>
     <row r="35" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="123" t="s">
+      <c r="B35" s="106" t="s">
         <v>156</v>
       </c>
-      <c r="C35" s="123"/>
-      <c r="D35" s="123"/>
-      <c r="E35" s="123"/>
-      <c r="F35" s="123"/>
+      <c r="C35" s="106"/>
+      <c r="D35" s="106"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="106"/>
     </row>
     <row r="36" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="7" t="s">
@@ -36186,62 +36185,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="107" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="133" t="s">
+      <c r="AS1" s="140" t="s">
         <v>161</v>
       </c>
-      <c r="AT1" s="133"/>
-      <c r="AU1" s="133"/>
-      <c r="AV1" s="133"/>
-      <c r="AW1" s="133"/>
-      <c r="AX1" s="133"/>
-      <c r="AY1" s="133"/>
-      <c r="AZ1" s="133"/>
-      <c r="BA1" s="133"/>
-      <c r="BB1" s="134" t="s">
+      <c r="AT1" s="140"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="140"/>
+      <c r="AW1" s="140"/>
+      <c r="AX1" s="140"/>
+      <c r="AY1" s="140"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="140"/>
+      <c r="BB1" s="141" t="s">
         <v>162</v>
       </c>
-      <c r="BC1" s="134"/>
+      <c r="BC1" s="141"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="142" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -36250,20 +36249,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="136" t="s">
+      <c r="AT2" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="136"/>
-      <c r="AV2" s="136"/>
+      <c r="AU2" s="143"/>
+      <c r="AV2" s="143"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="137" t="s">
+      <c r="AX2" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="137"/>
-      <c r="AZ2" s="137"/>
-      <c r="BA2" s="137"/>
+      <c r="AY2" s="144"/>
+      <c r="AZ2" s="144"/>
+      <c r="BA2" s="144"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -36311,66 +36310,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="137" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142" t="s">
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142" t="s">
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="142"/>
-      <c r="N4" s="142"/>
-      <c r="O4" s="142" t="s">
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="142"/>
-      <c r="Q4" s="142"/>
-      <c r="R4" s="142" t="s">
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="142"/>
-      <c r="T4" s="142"/>
-      <c r="U4" s="142" t="s">
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="142"/>
-      <c r="W4" s="143" t="s">
+      <c r="V4" s="137"/>
+      <c r="W4" s="138" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="143"/>
-      <c r="Y4" s="142" t="s">
+      <c r="X4" s="138"/>
+      <c r="Y4" s="137" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="142"/>
-      <c r="AA4" s="142"/>
-      <c r="AB4" s="142"/>
-      <c r="AC4" s="142"/>
-      <c r="AD4" s="143" t="s">
+      <c r="Z4" s="137"/>
+      <c r="AA4" s="137"/>
+      <c r="AB4" s="137"/>
+      <c r="AC4" s="137"/>
+      <c r="AD4" s="138" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="143"/>
-      <c r="AF4" s="143"/>
-      <c r="AG4" s="143"/>
-      <c r="AH4" s="143"/>
-      <c r="AI4" s="143"/>
-      <c r="AJ4" s="143"/>
-      <c r="AK4" s="143"/>
-      <c r="AL4" s="143"/>
-      <c r="AM4" s="143"/>
-      <c r="AN4" s="143"/>
-      <c r="AO4" s="143"/>
-      <c r="AP4" s="144" t="s">
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138"/>
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="138"/>
+      <c r="AJ4" s="138"/>
+      <c r="AK4" s="138"/>
+      <c r="AL4" s="138"/>
+      <c r="AM4" s="138"/>
+      <c r="AN4" s="138"/>
+      <c r="AO4" s="138"/>
+      <c r="AP4" s="139" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="144"/>
+      <c r="AQ4" s="139"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Enero'!B6</f>
@@ -36582,10 +36581,10 @@
         <f>'Captura Enero'!AQ7</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="BB5" s="138" t="s">
+      <c r="BB5" s="133" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="138"/>
+      <c r="BC5" s="133"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -39152,16 +39151,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="139" t="s">
+      <c r="AS19" s="134" t="s">
         <v>224</v>
       </c>
-      <c r="AT19" s="139"/>
-      <c r="AU19" s="139"/>
-      <c r="AV19" s="139"/>
-      <c r="AW19" s="139"/>
-      <c r="AX19" s="139"/>
-      <c r="AY19" s="139"/>
-      <c r="AZ19" s="139"/>
+      <c r="AT19" s="134"/>
+      <c r="AU19" s="134"/>
+      <c r="AV19" s="134"/>
+      <c r="AW19" s="134"/>
+      <c r="AX19" s="134"/>
+      <c r="AY19" s="134"/>
+      <c r="AZ19" s="134"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93030769230769228</v>
@@ -39333,9 +39332,9 @@
       </c>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="140"/>
-      <c r="B22" s="140"/>
-      <c r="C22" s="140"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -39362,11 +39361,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="141" t="s">
+      <c r="A23" s="136" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -39424,6 +39423,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -39438,12 +39443,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="110" priority="5" operator="greaterThanOrEqual">
@@ -39525,62 +39524,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="107" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="133" t="s">
+      <c r="AS1" s="140" t="s">
         <v>227</v>
       </c>
-      <c r="AT1" s="133"/>
-      <c r="AU1" s="133"/>
-      <c r="AV1" s="133"/>
-      <c r="AW1" s="133"/>
-      <c r="AX1" s="133"/>
-      <c r="AY1" s="133"/>
-      <c r="AZ1" s="133"/>
-      <c r="BA1" s="133"/>
-      <c r="BB1" s="134" t="s">
+      <c r="AT1" s="140"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="140"/>
+      <c r="AW1" s="140"/>
+      <c r="AX1" s="140"/>
+      <c r="AY1" s="140"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="140"/>
+      <c r="BB1" s="141" t="s">
         <v>228</v>
       </c>
-      <c r="BC1" s="134"/>
+      <c r="BC1" s="141"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="142" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -39589,20 +39588,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="136" t="s">
+      <c r="AT2" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="136"/>
-      <c r="AV2" s="136"/>
+      <c r="AU2" s="143"/>
+      <c r="AV2" s="143"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="137" t="s">
+      <c r="AX2" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="137"/>
-      <c r="AZ2" s="137"/>
-      <c r="BA2" s="137"/>
+      <c r="AY2" s="144"/>
+      <c r="AZ2" s="144"/>
+      <c r="BA2" s="144"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -39650,66 +39649,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="137" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142" t="s">
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142" t="s">
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="142"/>
-      <c r="N4" s="142"/>
-      <c r="O4" s="142" t="s">
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="142"/>
-      <c r="Q4" s="142"/>
-      <c r="R4" s="142" t="s">
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="142"/>
-      <c r="T4" s="142"/>
-      <c r="U4" s="142" t="s">
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="142"/>
-      <c r="W4" s="143" t="s">
+      <c r="V4" s="137"/>
+      <c r="W4" s="138" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="143"/>
-      <c r="Y4" s="142" t="s">
+      <c r="X4" s="138"/>
+      <c r="Y4" s="137" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="142"/>
-      <c r="AA4" s="142"/>
-      <c r="AB4" s="142"/>
-      <c r="AC4" s="142"/>
-      <c r="AD4" s="143" t="s">
+      <c r="Z4" s="137"/>
+      <c r="AA4" s="137"/>
+      <c r="AB4" s="137"/>
+      <c r="AC4" s="137"/>
+      <c r="AD4" s="138" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="143"/>
-      <c r="AF4" s="143"/>
-      <c r="AG4" s="143"/>
-      <c r="AH4" s="143"/>
-      <c r="AI4" s="143"/>
-      <c r="AJ4" s="143"/>
-      <c r="AK4" s="143"/>
-      <c r="AL4" s="143"/>
-      <c r="AM4" s="143"/>
-      <c r="AN4" s="143"/>
-      <c r="AO4" s="143"/>
-      <c r="AP4" s="144" t="s">
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138"/>
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="138"/>
+      <c r="AJ4" s="138"/>
+      <c r="AK4" s="138"/>
+      <c r="AL4" s="138"/>
+      <c r="AM4" s="138"/>
+      <c r="AN4" s="138"/>
+      <c r="AO4" s="138"/>
+      <c r="AP4" s="139" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="144"/>
+      <c r="AQ4" s="139"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Febrero'!B6</f>
@@ -39921,10 +39920,10 @@
         <f>'Captura Febrero'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="138" t="s">
+      <c r="BB5" s="133" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="138"/>
+      <c r="BC5" s="133"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -42491,16 +42490,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="139" t="s">
+      <c r="AS19" s="134" t="s">
         <v>230</v>
       </c>
-      <c r="AT19" s="139"/>
-      <c r="AU19" s="139"/>
-      <c r="AV19" s="139"/>
-      <c r="AW19" s="139"/>
-      <c r="AX19" s="139"/>
-      <c r="AY19" s="139"/>
-      <c r="AZ19" s="139"/>
+      <c r="AT19" s="134"/>
+      <c r="AU19" s="134"/>
+      <c r="AV19" s="134"/>
+      <c r="AW19" s="134"/>
+      <c r="AX19" s="134"/>
+      <c r="AY19" s="134"/>
+      <c r="AZ19" s="134"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.9572597670647206</v>
@@ -42667,9 +42666,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="140"/>
-      <c r="B22" s="140"/>
-      <c r="C22" s="140"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -42696,11 +42695,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="141" t="s">
+      <c r="A23" s="136" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -42758,6 +42757,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -42772,12 +42777,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="101" priority="5" operator="greaterThanOrEqual">
@@ -42859,62 +42858,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="107" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="133" t="s">
+      <c r="AS1" s="140" t="s">
         <v>232</v>
       </c>
-      <c r="AT1" s="133"/>
-      <c r="AU1" s="133"/>
-      <c r="AV1" s="133"/>
-      <c r="AW1" s="133"/>
-      <c r="AX1" s="133"/>
-      <c r="AY1" s="133"/>
-      <c r="AZ1" s="133"/>
-      <c r="BA1" s="133"/>
-      <c r="BB1" s="134" t="s">
+      <c r="AT1" s="140"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="140"/>
+      <c r="AW1" s="140"/>
+      <c r="AX1" s="140"/>
+      <c r="AY1" s="140"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="140"/>
+      <c r="BB1" s="141" t="s">
         <v>233</v>
       </c>
-      <c r="BC1" s="134"/>
+      <c r="BC1" s="141"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="142" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -42923,20 +42922,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="136" t="s">
+      <c r="AT2" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="136"/>
-      <c r="AV2" s="136"/>
+      <c r="AU2" s="143"/>
+      <c r="AV2" s="143"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="137" t="s">
+      <c r="AX2" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="137"/>
-      <c r="AZ2" s="137"/>
-      <c r="BA2" s="137"/>
+      <c r="AY2" s="144"/>
+      <c r="AZ2" s="144"/>
+      <c r="BA2" s="144"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -42984,66 +42983,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="137" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142" t="s">
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142" t="s">
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="142"/>
-      <c r="N4" s="142"/>
-      <c r="O4" s="142" t="s">
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="142"/>
-      <c r="Q4" s="142"/>
-      <c r="R4" s="142" t="s">
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="142"/>
-      <c r="T4" s="142"/>
-      <c r="U4" s="142" t="s">
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="142"/>
-      <c r="W4" s="143" t="s">
+      <c r="V4" s="137"/>
+      <c r="W4" s="138" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="143"/>
-      <c r="Y4" s="142" t="s">
+      <c r="X4" s="138"/>
+      <c r="Y4" s="137" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="142"/>
-      <c r="AA4" s="142"/>
-      <c r="AB4" s="142"/>
-      <c r="AC4" s="142"/>
-      <c r="AD4" s="143" t="s">
+      <c r="Z4" s="137"/>
+      <c r="AA4" s="137"/>
+      <c r="AB4" s="137"/>
+      <c r="AC4" s="137"/>
+      <c r="AD4" s="138" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="143"/>
-      <c r="AF4" s="143"/>
-      <c r="AG4" s="143"/>
-      <c r="AH4" s="143"/>
-      <c r="AI4" s="143"/>
-      <c r="AJ4" s="143"/>
-      <c r="AK4" s="143"/>
-      <c r="AL4" s="143"/>
-      <c r="AM4" s="143"/>
-      <c r="AN4" s="143"/>
-      <c r="AO4" s="143"/>
-      <c r="AP4" s="144" t="s">
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138"/>
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="138"/>
+      <c r="AJ4" s="138"/>
+      <c r="AK4" s="138"/>
+      <c r="AL4" s="138"/>
+      <c r="AM4" s="138"/>
+      <c r="AN4" s="138"/>
+      <c r="AO4" s="138"/>
+      <c r="AP4" s="139" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="144"/>
+      <c r="AQ4" s="139"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Marzo'!B6</f>
@@ -43255,10 +43254,10 @@
         <f>'Captura Marzo'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="138" t="s">
+      <c r="BB5" s="133" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="138"/>
+      <c r="BC5" s="133"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -45825,16 +45824,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="139" t="s">
+      <c r="AS19" s="134" t="s">
         <v>235</v>
       </c>
-      <c r="AT19" s="139"/>
-      <c r="AU19" s="139"/>
-      <c r="AV19" s="139"/>
-      <c r="AW19" s="139"/>
-      <c r="AX19" s="139"/>
-      <c r="AY19" s="139"/>
-      <c r="AZ19" s="139"/>
+      <c r="AT19" s="134"/>
+      <c r="AU19" s="134"/>
+      <c r="AV19" s="134"/>
+      <c r="AW19" s="134"/>
+      <c r="AX19" s="134"/>
+      <c r="AY19" s="134"/>
+      <c r="AZ19" s="134"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.99283333333333335</v>
@@ -46001,9 +46000,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="140"/>
-      <c r="B22" s="140"/>
-      <c r="C22" s="140"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -46030,11 +46029,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="141" t="s">
+      <c r="A23" s="136" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -46092,6 +46091,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -46106,12 +46111,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="92" priority="5" operator="greaterThanOrEqual">
@@ -46193,62 +46192,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="107" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="124"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="124"/>
-      <c r="T1" s="124"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
-      <c r="W1" s="124"/>
-      <c r="X1" s="124"/>
-      <c r="Y1" s="124"/>
-      <c r="Z1" s="124"/>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
+      <c r="Z1" s="107"/>
+      <c r="AA1" s="107"/>
+      <c r="AB1" s="107"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="133" t="s">
+      <c r="AS1" s="140" t="s">
         <v>237</v>
       </c>
-      <c r="AT1" s="133"/>
-      <c r="AU1" s="133"/>
-      <c r="AV1" s="133"/>
-      <c r="AW1" s="133"/>
-      <c r="AX1" s="133"/>
-      <c r="AY1" s="133"/>
-      <c r="AZ1" s="133"/>
-      <c r="BA1" s="133"/>
-      <c r="BB1" s="134" t="s">
+      <c r="AT1" s="140"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="140"/>
+      <c r="AW1" s="140"/>
+      <c r="AX1" s="140"/>
+      <c r="AY1" s="140"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="140"/>
+      <c r="BB1" s="141" t="s">
         <v>238</v>
       </c>
-      <c r="BC1" s="134"/>
+      <c r="BC1" s="141"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="142" t="s">
         <v>239</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -46257,20 +46256,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="136" t="s">
+      <c r="AT2" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="136"/>
-      <c r="AV2" s="136"/>
+      <c r="AU2" s="143"/>
+      <c r="AV2" s="143"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="137" t="s">
+      <c r="AX2" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="137"/>
-      <c r="AZ2" s="137"/>
-      <c r="BA2" s="137"/>
+      <c r="AY2" s="144"/>
+      <c r="AZ2" s="144"/>
+      <c r="BA2" s="144"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -46318,66 +46317,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="142" t="s">
+      <c r="D4" s="137" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142" t="s">
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="142"/>
-      <c r="J4" s="142"/>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142" t="s">
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="142"/>
-      <c r="N4" s="142"/>
-      <c r="O4" s="142" t="s">
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="142"/>
-      <c r="Q4" s="142"/>
-      <c r="R4" s="142" t="s">
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="142"/>
-      <c r="T4" s="142"/>
-      <c r="U4" s="142" t="s">
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="142"/>
-      <c r="W4" s="143" t="s">
+      <c r="V4" s="137"/>
+      <c r="W4" s="138" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="143"/>
-      <c r="Y4" s="142" t="s">
+      <c r="X4" s="138"/>
+      <c r="Y4" s="137" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="142"/>
-      <c r="AA4" s="142"/>
-      <c r="AB4" s="142"/>
-      <c r="AC4" s="142"/>
-      <c r="AD4" s="143" t="s">
+      <c r="Z4" s="137"/>
+      <c r="AA4" s="137"/>
+      <c r="AB4" s="137"/>
+      <c r="AC4" s="137"/>
+      <c r="AD4" s="138" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="143"/>
-      <c r="AF4" s="143"/>
-      <c r="AG4" s="143"/>
-      <c r="AH4" s="143"/>
-      <c r="AI4" s="143"/>
-      <c r="AJ4" s="143"/>
-      <c r="AK4" s="143"/>
-      <c r="AL4" s="143"/>
-      <c r="AM4" s="143"/>
-      <c r="AN4" s="143"/>
-      <c r="AO4" s="143"/>
-      <c r="AP4" s="144" t="s">
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138"/>
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="138"/>
+      <c r="AJ4" s="138"/>
+      <c r="AK4" s="138"/>
+      <c r="AL4" s="138"/>
+      <c r="AM4" s="138"/>
+      <c r="AN4" s="138"/>
+      <c r="AO4" s="138"/>
+      <c r="AP4" s="139" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="144"/>
+      <c r="AQ4" s="139"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Abril'!B6</f>
@@ -46589,10 +46588,10 @@
         <f>'Captura Abril'!AQ7</f>
         <v>0.71000000000000008</v>
       </c>
-      <c r="BB5" s="138" t="s">
+      <c r="BB5" s="133" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="138"/>
+      <c r="BC5" s="133"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -49159,16 +49158,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="139" t="s">
+      <c r="AS19" s="134" t="s">
         <v>240</v>
       </c>
-      <c r="AT19" s="139"/>
-      <c r="AU19" s="139"/>
-      <c r="AV19" s="139"/>
-      <c r="AW19" s="139"/>
-      <c r="AX19" s="139"/>
-      <c r="AY19" s="139"/>
-      <c r="AZ19" s="139"/>
+      <c r="AT19" s="134"/>
+      <c r="AU19" s="134"/>
+      <c r="AV19" s="134"/>
+      <c r="AW19" s="134"/>
+      <c r="AX19" s="134"/>
+      <c r="AY19" s="134"/>
+      <c r="AZ19" s="134"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93466666666666676</v>
@@ -49335,9 +49334,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="140"/>
-      <c r="B22" s="140"/>
-      <c r="C22" s="140"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -49364,11 +49363,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="141" t="s">
+      <c r="A23" s="136" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="141"/>
-      <c r="C23" s="141"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -49426,6 +49425,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -49440,12 +49445,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="83" priority="5" operator="greaterThanOrEqual">
@@ -49515,6 +49514,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003E33BA48D1B17740BD20DC3C1E7D6897" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c5918174441eb6b55e4531b53824222f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbb49d05-d3df-47ef-b263-f54790ad9dd3" xmlns:ns3="4bae7dba-0f75-4d38-a352-dd7a188b5c30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9432285c6019c8f9bf7f2f5b0ebbd793" ns2:_="" ns3:_="">
     <xsd:import namespace="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
@@ -49761,17 +49771,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5821DFA2-D31E-48EB-BA9F-E1C7FBC547E5}">
   <ds:schemaRefs>
@@ -49781,10 +49780,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A29B98D3-CD8F-4DEC-9477-47DD9974BEE9}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D19223-1C31-49B9-BB39-EF2DA560B2DA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -49793,4 +49788,23 @@
     <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A29B98D3-CD8F-4DEC-9477-47DD9974BEE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
+    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
+++ b/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc.sharepoint.com/sites/CharlascortasSSOsemanalesCuyotenango/Shared Documents/General/04. Registros 2026/09. Nivel De Seguridad/NUEVO NIVEL DE SEGURIDAD - 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{1FA93C17-BEC0-435F-87D9-564EB45A6C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7A4C16D-D173-48C3-9BE4-7F43BA5F2DD2}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{1FA93C17-BEC0-435F-87D9-564EB45A6C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{886A3DD0-794A-4D4A-A9C6-780167760147}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="867" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <sheet name="Captura Abril" sheetId="9" state="hidden" r:id="rId9"/>
     <sheet name="Captura Mayo" sheetId="10" state="hidden" r:id="rId10"/>
     <sheet name="Captura Junio" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet name="Captura Julio" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet name="Captura Julio" sheetId="12" r:id="rId12"/>
     <sheet name="Captura Agosto" sheetId="13" r:id="rId13"/>
     <sheet name="Captura Septiembre" sheetId="14" state="hidden" r:id="rId14"/>
     <sheet name="Captura Octubre" sheetId="15" state="hidden" r:id="rId15"/>
@@ -1025,369 +1025,369 @@
       <sz val="24"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
       <color rgb="FF1F4E79"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF1F4E79"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="8"/>
       <color rgb="FFA6A6A6"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FFA6A6A6"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="22"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1F4E79"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="36"/>
       <color rgb="FF1F4E79"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="28"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="28"/>
       <color rgb="FF1F4E79"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color rgb="FFBFBFBF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color rgb="FF00B050"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color rgb="FFC00000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FF70AD47"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color rgb="FF00B0F0"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="26"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF5B9BD5"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="7"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="8"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="8"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <i/>
       <sz val="8"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF1F4E79"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFC00000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="7"/>
       <color rgb="FFA6A6A6"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF1F4E79"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="30">
@@ -2067,17 +2067,53 @@
     <xf numFmtId="10" fontId="54" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2142,42 +2178,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="27" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3634,7 +3634,7 @@
                   <c:v>0.89266666666666672</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.1111111111111112</c:v>
+                  <c:v>6.6666666666666666E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0.97786666666666677</c:v>
@@ -4306,7 +4306,7 @@
                   <c:v>0.88027777777777783</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.61868000000000001</c:v>
+                  <c:v>0.6120133333333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -4852,38 +4852,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
+      <c r="B3" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="120"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="120"/>
     </row>
     <row r="4" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
     </row>
     <row r="5" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="109"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="109"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
     </row>
     <row r="6" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="109"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="109"/>
+      <c r="B6" s="120"/>
+      <c r="C6" s="120"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
     </row>
     <row r="7" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="110" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
+      <c r="B7" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
     </row>
     <row r="10" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
@@ -4937,72 +4937,72 @@
       </c>
     </row>
     <row r="18" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="106" t="s">
+      <c r="B18" s="122" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="106"/>
-      <c r="D18" s="106"/>
-      <c r="E18" s="106"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
     </row>
     <row r="19" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="108" t="s">
+      <c r="C19" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="108"/>
-      <c r="E19" s="108"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
     </row>
     <row r="20" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="108" t="s">
+      <c r="C20" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="108"/>
-      <c r="E20" s="108"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
     </row>
     <row r="21" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="108" t="s">
+      <c r="C21" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="108"/>
-      <c r="E21" s="108"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
     </row>
     <row r="22" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="108" t="s">
+      <c r="C22" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="108"/>
-      <c r="E22" s="108"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
     </row>
     <row r="23" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="108" t="s">
+      <c r="C23" s="119" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="108"/>
-      <c r="E23" s="108"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
     </row>
     <row r="24" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="108" t="s">
+      <c r="C24" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="108"/>
-      <c r="E24" s="108"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -5043,62 +5043,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="113" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="114" t="s">
         <v>242</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>243</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="116" t="s">
         <v>244</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -5107,20 +5107,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -5168,66 +5168,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Mayo'!B6</f>
@@ -5439,10 +5439,10 @@
         <f>'Captura Mayo'!AQ7</f>
         <v>0.69000000000000006</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -8009,16 +8009,16 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="107" t="s">
         <v>245</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.87666666666666671</v>
@@ -8185,9 +8185,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -8214,11 +8214,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -8377,62 +8377,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="113" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="114" t="s">
         <v>247</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>248</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="116" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -8441,20 +8441,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -8502,66 +8502,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Junio'!B6</f>
@@ -8773,10 +8773,10 @@
         <f>'Captura Junio'!AQ7</f>
         <v>0.64000000000000012</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -11343,16 +11343,16 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="107" t="s">
         <v>250</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.83357372900851168</v>
@@ -11519,9 +11519,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -11548,11 +11548,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -11713,62 +11713,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="113" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="114" t="s">
         <v>252</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>253</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="116" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -11777,20 +11777,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -11838,66 +11838,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Julio'!B6</f>
@@ -12109,10 +12109,10 @@
         <f>'Captura Julio'!AQ7</f>
         <v>0.64</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -14679,16 +14679,16 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="107" t="s">
         <v>255</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.88027777777777783</v>
@@ -14855,9 +14855,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -14884,11 +14884,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -15037,7 +15037,11 @@
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="48" width="9.54296875" customWidth="1"/>
+    <col min="4" max="44" width="9.54296875" customWidth="1"/>
+    <col min="45" max="45" width="15" customWidth="1"/>
+    <col min="46" max="46" width="18.7265625" customWidth="1"/>
+    <col min="47" max="47" width="11.26953125" customWidth="1"/>
+    <col min="48" max="48" width="9.54296875" customWidth="1"/>
     <col min="49" max="50" width="11" customWidth="1"/>
     <col min="51" max="51" width="13" customWidth="1"/>
     <col min="52" max="52" width="11" customWidth="1"/>
@@ -15047,62 +15051,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="113" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="114" t="s">
         <v>257</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>258</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="116" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -15111,20 +15115,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -15172,66 +15176,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Agosto'!B6</f>
@@ -15443,10 +15447,10 @@
         <f>'Captura Agosto'!AQ7</f>
         <v>0.46000000000000008</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -15605,7 +15609,7 @@
       </c>
       <c r="AU6" s="72">
         <f>'Captura Agosto'!T8</f>
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="AV6" s="72">
         <f>'Captura Agosto'!V8</f>
@@ -15629,7 +15633,7 @@
       </c>
       <c r="BA6" s="74">
         <f>'Captura Agosto'!AQ8</f>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="BB6" s="58"/>
       <c r="BC6" s="58"/>
@@ -15875,13 +15879,14 @@
         <v>0.08</v>
       </c>
       <c r="R8" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="88" t="s">
         <v>222</v>
       </c>
       <c r="T8" s="86">
-        <v>1</v>
+        <f>IF(S8="NO",0,R8*Parametros!$E$10)</f>
+        <v>0.06</v>
       </c>
       <c r="U8" s="85">
         <v>1</v>
@@ -15955,11 +15960,11 @@
       </c>
       <c r="AP8" s="11">
         <f t="shared" si="3"/>
-        <v>1.84</v>
+        <v>0.9</v>
       </c>
       <c r="AQ8" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP8-IF(S8="NO",Parametros!$E$17,0))+AC8)-AN8-IF(AO8="SI",Parametros!$E$33,0))</f>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AR8" s="58"/>
       <c r="AS8" s="71" t="str">
@@ -18004,19 +18009,19 @@
         <v>0.49125000000000002</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="107" t="s">
         <v>260</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
-        <v>0.61868000000000001</v>
+        <v>0.6120133333333333</v>
       </c>
       <c r="BB19" s="58"/>
       <c r="BC19" s="58"/>
@@ -18180,9 +18185,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -18209,11 +18214,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -18255,7 +18260,7 @@
       <c r="AP23" s="93"/>
       <c r="AQ23" s="96">
         <f>AVERAGE(AQ6:AQ20)</f>
-        <v>0.61868000000000001</v>
+        <v>0.6120133333333333</v>
       </c>
       <c r="AR23" s="58"/>
       <c r="AS23" s="58"/>
@@ -18340,7 +18345,7 @@
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="J6:J20 M6:M20 P6:P20 S6:T20 X6:X20 AE6:AE20 AG6:AG20 AI6:AN20 AP6:AP20 AR6:AR20" xr:uid="{00000000-0002-0000-0C00-000003000000}">
+    <dataValidation type="list" sqref="J6:J20 M6:M20 P6:P20 AR6:AR20 X6:X20 AE6:AE20 AG6:AG20 AI6:AN20 AP6:AP20 S6:T20" xr:uid="{00000000-0002-0000-0C00-000003000000}">
       <formula1>"SI,NO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -18372,62 +18377,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="113" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="114" t="s">
         <v>262</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>263</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="116" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -18436,20 +18441,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -18497,66 +18502,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Septiembre'!B6</f>
@@ -18768,10 +18773,10 @@
         <f>'Captura Septiembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -21338,16 +21343,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="107" t="s">
         <v>265</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -21514,9 +21519,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -21543,11 +21548,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -21706,62 +21711,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="113" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="114" t="s">
         <v>267</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>268</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="116" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -21770,20 +21775,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -21831,66 +21836,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Octubre'!B6</f>
@@ -22102,10 +22107,10 @@
         <f>'Captura Octubre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -24672,16 +24677,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -24848,9 +24853,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -24877,11 +24882,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -25040,62 +25045,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="113" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="114" t="s">
         <v>272</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>273</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="116" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -25104,20 +25109,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -25165,66 +25170,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Noviembre'!B6</f>
@@ -25436,10 +25441,10 @@
         <f>'Captura Noviembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -28006,16 +28011,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="107" t="s">
         <v>275</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -28182,9 +28187,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -28211,11 +28216,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -28374,62 +28379,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="113" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="114" t="s">
         <v>277</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>278</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="116" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -28438,20 +28443,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -28499,66 +28504,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Diciembre'!B6</f>
@@ -28770,10 +28775,10 @@
         <f>'Captura Diciembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -31340,16 +31345,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="107" t="s">
         <v>280</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -31516,9 +31521,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -31545,11 +31550,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -31700,11 +31705,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="113" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="145" t="s">
@@ -31824,7 +31829,7 @@
       </c>
       <c r="B13" s="97">
         <f>IF(AVERAGE('Captura Agosto'!D6:D20)=0,"",'Captura Agosto'!AQ23)</f>
-        <v>0.61868000000000001</v>
+        <v>0.6120133333333333</v>
       </c>
       <c r="C13" s="12" t="str">
         <f>IF(B13="","",IF(B13&gt;=Parametros!$C$37,"Verde",IF(B13&gt;=Parametros!$C$38,"Amarillo","Rojo")))</f>
@@ -32017,7 +32022,7 @@
       </c>
       <c r="I4" s="10">
         <f>IFERROR(IF('Captura Agosto'!D8=0,"",'Captura Agosto'!AQ8),"")</f>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J4" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
@@ -32037,7 +32042,7 @@
       </c>
       <c r="N4" s="102">
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.98750000000000004</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32872,7 +32877,7 @@
       </c>
       <c r="I19" s="104">
         <f t="shared" si="1"/>
-        <v>0.6186799999999999</v>
+        <v>0.61201333333333341</v>
       </c>
       <c r="J19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -32935,16 +32940,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -32955,12 +32960,12 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="122" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
     </row>
     <row r="4" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
@@ -33054,11 +33059,11 @@
       </c>
       <c r="C9" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"T6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"T20"))</f>
-        <v>6.6666666666666666E-2</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D9" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>1.1111111111111112</v>
+        <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33096,10 +33101,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="106" t="s">
+      <c r="A13" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="106"/>
+      <c r="B13" s="122"/>
     </row>
     <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
@@ -33156,12 +33161,12 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="106" t="s">
+      <c r="A21" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="106"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="106"/>
+      <c r="B21" s="122"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="122"/>
     </row>
     <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
@@ -33240,7 +33245,7 @@
       </c>
       <c r="E25" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ8")*100000-8</f>
-        <v>89992</v>
+        <v>79992</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33496,10 +33501,10 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="106" t="s">
+      <c r="A39" s="122" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="106"/>
+      <c r="B39" s="122"/>
     </row>
     <row r="40" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="16" t="s">
@@ -33534,7 +33539,7 @@
       </c>
       <c r="B44" s="17">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ23")</f>
-        <v>0.61868000000000001</v>
+        <v>0.6120133333333333</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33683,7 +33688,7 @@
       </c>
       <c r="I4" s="10">
         <f>IFERROR(IF('Captura Agosto'!D8=0,"",'Captura Agosto'!AQ8),"")</f>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J4" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D8=0,"",'Captura Septiembre'!AQ8),"")</f>
@@ -33702,8 +33707,8 @@
         <v/>
       </c>
       <c r="N4" s="102">
-        <f>IFERROR(AVERAGE(B4:M4),"")</f>
-        <v>0.98750000000000004</v>
+        <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33759,7 +33764,7 @@
         <v/>
       </c>
       <c r="N5" s="102">
-        <f>IFERROR(AVERAGE(B5:M5),"")</f>
+        <f t="shared" si="0"/>
         <v>0.94158750000000002</v>
       </c>
     </row>
@@ -33816,7 +33821,7 @@
         <v/>
       </c>
       <c r="N6" s="102">
-        <f>IFERROR(AVERAGE(B6:M6),"")</f>
+        <f t="shared" si="0"/>
         <v>0.94158571428571425</v>
       </c>
     </row>
@@ -33873,7 +33878,7 @@
         <v/>
       </c>
       <c r="N7" s="102">
-        <f>IFERROR(AVERAGE(B7:M7),"")</f>
+        <f t="shared" si="0"/>
         <v>0.92809374999999994</v>
       </c>
     </row>
@@ -33930,7 +33935,7 @@
         <v/>
       </c>
       <c r="N8" s="102">
-        <f>IFERROR(AVERAGE(B8:M8),"")</f>
+        <f t="shared" si="0"/>
         <v>0.92225000000000001</v>
       </c>
     </row>
@@ -33987,7 +33992,7 @@
         <v/>
       </c>
       <c r="N9" s="102">
-        <f>IFERROR(AVERAGE(B9:M9),"")</f>
+        <f t="shared" si="0"/>
         <v>0.91300000000000003</v>
       </c>
     </row>
@@ -34044,7 +34049,7 @@
         <v/>
       </c>
       <c r="N10" s="102">
-        <f>IFERROR(AVERAGE(B10:M10),"")</f>
+        <f t="shared" si="0"/>
         <v>0.90812500000000007</v>
       </c>
     </row>
@@ -34101,7 +34106,7 @@
         <v/>
       </c>
       <c r="N11" s="102">
-        <f>IFERROR(AVERAGE(B11:M11),"")</f>
+        <f t="shared" si="0"/>
         <v>0.89760000000000006</v>
       </c>
     </row>
@@ -34158,7 +34163,7 @@
         <v/>
       </c>
       <c r="N12" s="102">
-        <f>IFERROR(AVERAGE(B12:M12),"")</f>
+        <f t="shared" si="0"/>
         <v>0.88433186274509801</v>
       </c>
     </row>
@@ -34215,7 +34220,7 @@
         <v/>
       </c>
       <c r="N13" s="102">
-        <f>IFERROR(AVERAGE(B13:M13),"")</f>
+        <f t="shared" si="0"/>
         <v>0.84796874999999994</v>
       </c>
     </row>
@@ -34272,7 +34277,7 @@
         <v/>
       </c>
       <c r="N14" s="102">
-        <f>IFERROR(AVERAGE(B14:M14),"")</f>
+        <f t="shared" si="0"/>
         <v>0.82816304347826097</v>
       </c>
     </row>
@@ -34329,7 +34334,7 @@
         <v/>
       </c>
       <c r="N15" s="102">
-        <f>IFERROR(AVERAGE(B15:M15),"")</f>
+        <f t="shared" si="0"/>
         <v>0.82411978021978016</v>
       </c>
     </row>
@@ -34386,7 +34391,7 @@
         <v/>
       </c>
       <c r="N16" s="102">
-        <f>IFERROR(AVERAGE(B16:M16),"")</f>
+        <f t="shared" si="0"/>
         <v>0.80514766081871347</v>
       </c>
     </row>
@@ -34443,7 +34448,7 @@
         <v/>
       </c>
       <c r="N17" s="102">
-        <f>IFERROR(AVERAGE(B17:M17),"")</f>
+        <f t="shared" si="0"/>
         <v>0.78102499999999986</v>
       </c>
     </row>
@@ -34500,7 +34505,7 @@
         <v/>
       </c>
       <c r="N18" s="102">
-        <f>IFERROR(AVERAGE(B18:M18),"")</f>
+        <f t="shared" si="0"/>
         <v>0.76</v>
       </c>
     </row>
@@ -34509,51 +34514,51 @@
         <v>298</v>
       </c>
       <c r="B19" s="104">
-        <f>IFERROR(AVERAGE(B4:B18),"")</f>
+        <f t="shared" ref="B19:M19" si="1">IFERROR(AVERAGE(B4:B18),"")</f>
         <v>0.93030769230769239</v>
       </c>
       <c r="C19" s="104">
-        <f>IFERROR(AVERAGE(C4:C18),"")</f>
+        <f t="shared" si="1"/>
         <v>0.9572597670647206</v>
       </c>
       <c r="D19" s="104">
-        <f>IFERROR(AVERAGE(D4:D18),"")</f>
+        <f t="shared" si="1"/>
         <v>0.99283333333333335</v>
       </c>
       <c r="E19" s="104">
-        <f>IFERROR(AVERAGE(E4:E18),"")</f>
+        <f t="shared" si="1"/>
         <v>0.93466666666666665</v>
       </c>
       <c r="F19" s="104">
-        <f>IFERROR(AVERAGE(F4:F18),"")</f>
+        <f t="shared" si="1"/>
         <v>0.87666666666666659</v>
       </c>
       <c r="G19" s="104">
-        <f>IFERROR(AVERAGE(G4:G18),"")</f>
+        <f t="shared" si="1"/>
         <v>0.83357372900851157</v>
       </c>
       <c r="H19" s="104">
-        <f>IFERROR(AVERAGE(H4:H18),"")</f>
+        <f t="shared" si="1"/>
         <v>0.88027777777777794</v>
       </c>
       <c r="I19" s="104">
-        <f>IFERROR(AVERAGE(I4:I18),"")</f>
-        <v>0.61868000000000001</v>
+        <f t="shared" si="1"/>
+        <v>0.61201333333333341</v>
       </c>
       <c r="J19" s="104" t="str">
-        <f>IFERROR(AVERAGE(J4:J18),"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K19" s="104" t="str">
-        <f>IFERROR(AVERAGE(K4:K18),"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L19" s="104" t="str">
-        <f>IFERROR(AVERAGE(L4:L18),"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M19" s="104" t="str">
-        <f>IFERROR(AVERAGE(M4:M18),"")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N19" s="105">
@@ -34598,44 +34603,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="128" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="116"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128"/>
+      <c r="R2" s="128"/>
     </row>
     <row r="3" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="116"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="116"/>
-      <c r="J3" s="116"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="116"/>
-      <c r="M3" s="116"/>
-      <c r="N3" s="116"/>
-      <c r="O3" s="116"/>
-      <c r="P3" s="116"/>
-      <c r="Q3" s="116"/>
-      <c r="R3" s="116"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="128"/>
     </row>
     <row r="4" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
@@ -34645,153 +34650,153 @@
         <f>Calculos!$B$2</f>
         <v>Agosto</v>
       </c>
-      <c r="F4" s="117" t="s">
+      <c r="F4" s="129" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
-      <c r="N4" s="117"/>
-      <c r="O4" s="117"/>
-      <c r="P4" s="117"/>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="117"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="129"/>
+      <c r="K4" s="129"/>
+      <c r="L4" s="129"/>
+      <c r="M4" s="129"/>
+      <c r="N4" s="129"/>
+      <c r="O4" s="129"/>
+      <c r="P4" s="129"/>
+      <c r="Q4" s="129"/>
+      <c r="R4" s="129"/>
     </row>
     <row r="6" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="118" t="s">
+      <c r="B6" s="130" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="118" t="s">
+      <c r="C6" s="130"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="118"/>
-      <c r="H6" s="118"/>
-      <c r="I6" s="118"/>
-      <c r="J6" s="118" t="s">
+      <c r="G6" s="130"/>
+      <c r="H6" s="130"/>
+      <c r="I6" s="130"/>
+      <c r="J6" s="130" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="118"/>
-      <c r="L6" s="118"/>
-      <c r="M6" s="118" t="s">
+      <c r="K6" s="130"/>
+      <c r="L6" s="130"/>
+      <c r="M6" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="N6" s="118"/>
-      <c r="O6" s="118"/>
-      <c r="P6" s="118" t="s">
+      <c r="N6" s="130"/>
+      <c r="O6" s="130"/>
+      <c r="P6" s="130" t="s">
         <v>65</v>
       </c>
-      <c r="Q6" s="118"/>
-      <c r="R6" s="118"/>
+      <c r="Q6" s="130"/>
+      <c r="R6" s="130"/>
     </row>
     <row r="7" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="118"/>
-      <c r="K7" s="118"/>
-      <c r="L7" s="118"/>
-      <c r="M7" s="118"/>
-      <c r="N7" s="118"/>
-      <c r="O7" s="118"/>
-      <c r="P7" s="118"/>
-      <c r="Q7" s="118"/>
-      <c r="R7" s="118"/>
+      <c r="B7" s="130"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="130"/>
+      <c r="J7" s="130"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="130"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="130"/>
+      <c r="O7" s="130"/>
+      <c r="P7" s="130"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="130"/>
     </row>
     <row r="8" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="111">
+      <c r="B8" s="123">
         <f ca="1">Calculos!B44</f>
-        <v>0.61868000000000001</v>
-      </c>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="111"/>
-      <c r="F8" s="112" t="str">
+        <v>0.6120133333333333</v>
+      </c>
+      <c r="C8" s="123"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="124" t="str">
         <f ca="1">Calculos!B45</f>
         <v>Rojo</v>
       </c>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="113">
+      <c r="G8" s="124"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="124"/>
+      <c r="J8" s="125">
         <f ca="1">Calculos!B40</f>
         <v>0</v>
       </c>
-      <c r="K8" s="113"/>
-      <c r="L8" s="113"/>
-      <c r="M8" s="114">
+      <c r="K8" s="125"/>
+      <c r="L8" s="125"/>
+      <c r="M8" s="126">
         <f ca="1">Calculos!B41</f>
         <v>0</v>
       </c>
-      <c r="N8" s="114"/>
-      <c r="O8" s="114"/>
-      <c r="P8" s="115">
+      <c r="N8" s="126"/>
+      <c r="O8" s="126"/>
+      <c r="P8" s="127">
         <f ca="1">Calculos!B42</f>
         <v>15</v>
       </c>
-      <c r="Q8" s="115"/>
-      <c r="R8" s="115"/>
+      <c r="Q8" s="127"/>
+      <c r="R8" s="127"/>
     </row>
     <row r="9" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="111"/>
-      <c r="C9" s="111"/>
-      <c r="D9" s="111"/>
-      <c r="E9" s="111"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="113"/>
-      <c r="K9" s="113"/>
-      <c r="L9" s="113"/>
-      <c r="M9" s="114"/>
-      <c r="N9" s="114"/>
-      <c r="O9" s="114"/>
-      <c r="P9" s="115"/>
-      <c r="Q9" s="115"/>
-      <c r="R9" s="115"/>
+      <c r="B9" s="123"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="123"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="124"/>
+      <c r="I9" s="124"/>
+      <c r="J9" s="125"/>
+      <c r="K9" s="125"/>
+      <c r="L9" s="125"/>
+      <c r="M9" s="126"/>
+      <c r="N9" s="126"/>
+      <c r="O9" s="126"/>
+      <c r="P9" s="127"/>
+      <c r="Q9" s="127"/>
+      <c r="R9" s="127"/>
     </row>
     <row r="10" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="111"/>
-      <c r="C10" s="111"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="113"/>
-      <c r="K10" s="113"/>
-      <c r="L10" s="113"/>
-      <c r="M10" s="114"/>
-      <c r="N10" s="114"/>
-      <c r="O10" s="114"/>
-      <c r="P10" s="115"/>
-      <c r="Q10" s="115"/>
-      <c r="R10" s="115"/>
+      <c r="B10" s="123"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="124"/>
+      <c r="I10" s="124"/>
+      <c r="J10" s="125"/>
+      <c r="K10" s="125"/>
+      <c r="L10" s="125"/>
+      <c r="M10" s="126"/>
+      <c r="N10" s="126"/>
+      <c r="O10" s="126"/>
+      <c r="P10" s="127"/>
+      <c r="Q10" s="127"/>
+      <c r="R10" s="127"/>
     </row>
     <row r="12" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="106" t="s">
+      <c r="B12" s="122" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="106"/>
-      <c r="D12" s="106"/>
-      <c r="E12" s="106"/>
-      <c r="G12" s="106" t="s">
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="G12" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="106"/>
+      <c r="H12" s="122"/>
     </row>
     <row r="13" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="7" t="s">
@@ -34894,7 +34899,7 @@
       </c>
       <c r="H18" s="22">
         <f ca="1">Calculos!D9</f>
-        <v>1.1111111111111112</v>
+        <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -35085,61 +35090,61 @@
   <sheetData>
     <row r="1" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="133" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="122" t="s">
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="122"/>
-      <c r="G2" s="122"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
       <c r="H2" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="123" t="s">
+      <c r="B4" s="135" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="123"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="123"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="123"/>
-      <c r="H4" s="123"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="123"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="123"/>
-      <c r="M4" s="123"/>
-      <c r="N4" s="123"/>
-      <c r="O4" s="123"/>
-      <c r="P4" s="123"/>
-      <c r="Q4" s="123"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
+      <c r="M4" s="135"/>
+      <c r="N4" s="135"/>
+      <c r="O4" s="135"/>
+      <c r="P4" s="135"/>
+      <c r="Q4" s="135"/>
     </row>
     <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="124" t="str">
+      <c r="B5" s="136" t="str">
         <f>UPPER("Planta Cuyotenango  ·  "&amp;Calculos!$B$2&amp;" 2026  ·  Acumulado Año")</f>
         <v>PLANTA CUYOTENANGO  ·  AGOSTO 2026  ·  ACUMULADO AÑO</v>
       </c>
-      <c r="C5" s="124"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="124"/>
-      <c r="F5" s="124"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="124"/>
-      <c r="I5" s="124"/>
-      <c r="J5" s="124"/>
-      <c r="K5" s="124"/>
-      <c r="L5" s="124"/>
-      <c r="M5" s="124"/>
-      <c r="N5" s="124"/>
-      <c r="O5" s="124"/>
-      <c r="P5" s="124"/>
-      <c r="Q5" s="124"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
+      <c r="M5" s="136"/>
+      <c r="N5" s="136"/>
+      <c r="O5" s="136"/>
+      <c r="P5" s="136"/>
+      <c r="Q5" s="136"/>
     </row>
     <row r="6" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="P6" s="28" t="s">
@@ -35150,7 +35155,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="125" t="str">
+      <c r="A7" s="137" t="str">
         <f>UPPER(Calculos!$B$2)</f>
         <v>AGOSTO</v>
       </c>
@@ -35167,13 +35172,13 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="125"/>
-      <c r="G8" s="126">
+      <c r="A8" s="137"/>
+      <c r="G8" s="138">
         <f ca="1">X31</f>
         <v>0</v>
       </c>
-      <c r="H8" s="126"/>
-      <c r="I8" s="126"/>
+      <c r="H8" s="138"/>
+      <c r="I8" s="138"/>
       <c r="P8" s="31" t="s">
         <v>76</v>
       </c>
@@ -35183,15 +35188,15 @@
       </c>
     </row>
     <row r="9" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="125"/>
-      <c r="F9" s="127">
+      <c r="A9" s="137"/>
+      <c r="F9" s="139">
         <f ca="1">X32</f>
         <v>0</v>
       </c>
-      <c r="G9" s="127"/>
-      <c r="H9" s="127"/>
-      <c r="I9" s="127"/>
-      <c r="J9" s="127"/>
+      <c r="G9" s="139"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="139"/>
+      <c r="J9" s="139"/>
       <c r="P9" s="31" t="s">
         <v>77</v>
       </c>
@@ -35201,17 +35206,17 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="125"/>
-      <c r="E10" s="128">
+      <c r="A10" s="137"/>
+      <c r="E10" s="140">
         <f ca="1">X33</f>
         <v>0</v>
       </c>
-      <c r="F10" s="128"/>
-      <c r="G10" s="128"/>
-      <c r="H10" s="128"/>
-      <c r="I10" s="128"/>
-      <c r="J10" s="128"/>
-      <c r="K10" s="128"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="140"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="140"/>
       <c r="P10" s="31" t="s">
         <v>78</v>
       </c>
@@ -35221,19 +35226,19 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="125"/>
-      <c r="D11" s="129">
+      <c r="A11" s="137"/>
+      <c r="D11" s="141">
         <f ca="1">X34</f>
         <v>5</v>
       </c>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="129"/>
-      <c r="J11" s="129"/>
-      <c r="K11" s="129"/>
-      <c r="L11" s="129"/>
+      <c r="E11" s="141"/>
+      <c r="F11" s="141"/>
+      <c r="G11" s="141"/>
+      <c r="H11" s="141"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="141"/>
+      <c r="K11" s="141"/>
+      <c r="L11" s="141"/>
       <c r="P11" s="31" t="s">
         <v>79</v>
       </c>
@@ -35243,21 +35248,21 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="125"/>
-      <c r="C12" s="130">
+      <c r="A12" s="137"/>
+      <c r="C12" s="142">
         <f ca="1">X35</f>
         <v>0</v>
       </c>
-      <c r="D12" s="130"/>
-      <c r="E12" s="130"/>
-      <c r="F12" s="130"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="130"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="130"/>
-      <c r="M12" s="130"/>
+      <c r="D12" s="142"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="142"/>
+      <c r="L12" s="142"/>
+      <c r="M12" s="142"/>
       <c r="P12" s="31" t="s">
         <v>80</v>
       </c>
@@ -35267,23 +35272,23 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="125"/>
-      <c r="B13" s="131">
+      <c r="A13" s="137"/>
+      <c r="B13" s="143">
         <f ca="1">X36</f>
         <v>27</v>
       </c>
-      <c r="C13" s="131"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="131"/>
-      <c r="I13" s="131"/>
-      <c r="J13" s="131"/>
-      <c r="K13" s="131"/>
-      <c r="L13" s="131"/>
-      <c r="M13" s="131"/>
-      <c r="N13" s="131"/>
+      <c r="C13" s="143"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="143"/>
+      <c r="F13" s="143"/>
+      <c r="G13" s="143"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143"/>
+      <c r="K13" s="143"/>
+      <c r="L13" s="143"/>
+      <c r="M13" s="143"/>
+      <c r="N13" s="143"/>
       <c r="P13" s="31" t="s">
         <v>81</v>
       </c>
@@ -35293,23 +35298,23 @@
       </c>
     </row>
     <row r="14" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="125"/>
-      <c r="B14" s="132">
+      <c r="A14" s="137"/>
+      <c r="B14" s="144">
         <f ca="1">X37</f>
         <v>196</v>
       </c>
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="132"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="132"/>
-      <c r="J14" s="132"/>
-      <c r="K14" s="132"/>
-      <c r="L14" s="132"/>
-      <c r="M14" s="132"/>
-      <c r="N14" s="132"/>
+      <c r="C14" s="144"/>
+      <c r="D14" s="144"/>
+      <c r="E14" s="144"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="144"/>
+      <c r="H14" s="144"/>
+      <c r="I14" s="144"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="144"/>
+      <c r="L14" s="144"/>
+      <c r="M14" s="144"/>
+      <c r="N14" s="144"/>
       <c r="P14" s="31" t="s">
         <v>82</v>
       </c>
@@ -35320,12 +35325,12 @@
     </row>
     <row r="15" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="S16" s="119" t="s">
+      <c r="S16" s="131" t="s">
         <v>83</v>
       </c>
-      <c r="T16" s="119"/>
-      <c r="U16" s="119"/>
-      <c r="V16" s="119"/>
+      <c r="T16" s="131"/>
+      <c r="U16" s="131"/>
+      <c r="V16" s="131"/>
     </row>
     <row r="17" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -35396,42 +35401,42 @@
     <row r="25" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="2:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="120" t="s">
+      <c r="B27" s="132" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="120"/>
-      <c r="D27" s="120"/>
-      <c r="E27" s="120"/>
-      <c r="F27" s="120"/>
-      <c r="G27" s="120"/>
-      <c r="H27" s="120"/>
-      <c r="I27" s="120"/>
-      <c r="J27" s="120"/>
-      <c r="K27" s="120"/>
-      <c r="L27" s="120"/>
-      <c r="M27" s="120"/>
-      <c r="N27" s="120"/>
-      <c r="O27" s="120"/>
-      <c r="P27" s="120"/>
-      <c r="Q27" s="120"/>
+      <c r="C27" s="132"/>
+      <c r="D27" s="132"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="132"/>
+      <c r="I27" s="132"/>
+      <c r="J27" s="132"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="132"/>
+      <c r="M27" s="132"/>
+      <c r="N27" s="132"/>
+      <c r="O27" s="132"/>
+      <c r="P27" s="132"/>
+      <c r="Q27" s="132"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="120"/>
-      <c r="C28" s="120"/>
-      <c r="D28" s="120"/>
-      <c r="E28" s="120"/>
-      <c r="F28" s="120"/>
-      <c r="G28" s="120"/>
-      <c r="H28" s="120"/>
-      <c r="I28" s="120"/>
-      <c r="J28" s="120"/>
-      <c r="K28" s="120"/>
-      <c r="L28" s="120"/>
-      <c r="M28" s="120"/>
-      <c r="N28" s="120"/>
-      <c r="O28" s="120"/>
-      <c r="P28" s="120"/>
-      <c r="Q28" s="120"/>
+      <c r="B28" s="132"/>
+      <c r="C28" s="132"/>
+      <c r="D28" s="132"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="132"/>
+      <c r="H28" s="132"/>
+      <c r="I28" s="132"/>
+      <c r="J28" s="132"/>
+      <c r="K28" s="132"/>
+      <c r="L28" s="132"/>
+      <c r="M28" s="132"/>
+      <c r="N28" s="132"/>
+      <c r="O28" s="132"/>
+      <c r="P28" s="132"/>
+      <c r="Q28" s="132"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.35">
       <c r="W30" s="39" t="s">
@@ -35585,26 +35590,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="122" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="H4" s="106" t="s">
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="H4" s="122" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="106"/>
+      <c r="I4" s="122"/>
     </row>
     <row r="5" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="7" t="s">
@@ -35865,13 +35870,13 @@
       </c>
     </row>
     <row r="16" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="106" t="s">
+      <c r="B16" s="122" t="s">
         <v>132</v>
       </c>
-      <c r="C16" s="106"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="106"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
       <c r="H16" s="8">
         <v>11</v>
       </c>
@@ -35954,13 +35959,13 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="106" t="s">
+      <c r="B21" s="122" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="106"/>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="106"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="122"/>
     </row>
     <row r="22" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="52"/>
@@ -36007,13 +36012,13 @@
       <c r="F25" s="52"/>
     </row>
     <row r="27" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="106" t="s">
+      <c r="B27" s="122" t="s">
         <v>149</v>
       </c>
-      <c r="C27" s="106"/>
-      <c r="D27" s="106"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="106"/>
+      <c r="C27" s="122"/>
+      <c r="D27" s="122"/>
+      <c r="E27" s="122"/>
+      <c r="F27" s="122"/>
     </row>
     <row r="28" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="52"/>
@@ -36082,13 +36087,13 @@
       <c r="F33" s="52"/>
     </row>
     <row r="35" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="106" t="s">
+      <c r="B35" s="122" t="s">
         <v>156</v>
       </c>
-      <c r="C35" s="106"/>
-      <c r="D35" s="106"/>
-      <c r="E35" s="106"/>
-      <c r="F35" s="106"/>
+      <c r="C35" s="122"/>
+      <c r="D35" s="122"/>
+      <c r="E35" s="122"/>
+      <c r="F35" s="122"/>
     </row>
     <row r="36" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="7" t="s">
@@ -36185,62 +36190,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="113" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="114" t="s">
         <v>161</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>162</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="116" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -36249,20 +36254,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -36310,66 +36315,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Enero'!B6</f>
@@ -36581,10 +36586,10 @@
         <f>'Captura Enero'!AQ7</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -39151,16 +39156,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="107" t="s">
         <v>224</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93030769230769228</v>
@@ -39332,9 +39337,9 @@
       </c>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -39361,11 +39366,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -39524,62 +39529,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="113" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="114" t="s">
         <v>227</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>228</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="116" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -39588,20 +39593,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -39649,66 +39654,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Febrero'!B6</f>
@@ -39920,10 +39925,10 @@
         <f>'Captura Febrero'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -42490,16 +42495,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="107" t="s">
         <v>230</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.9572597670647206</v>
@@ -42666,9 +42671,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -42695,11 +42700,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -42858,62 +42863,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="113" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="114" t="s">
         <v>232</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>233</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="116" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -42922,20 +42927,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -42983,66 +42988,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Marzo'!B6</f>
@@ -43254,10 +43259,10 @@
         <f>'Captura Marzo'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -45824,16 +45829,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="107" t="s">
         <v>235</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.99283333333333335</v>
@@ -46000,9 +46005,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -46029,11 +46034,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -46192,62 +46197,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="113" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
-      <c r="Z1" s="107"/>
-      <c r="AA1" s="107"/>
-      <c r="AB1" s="107"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="140" t="s">
+      <c r="AS1" s="114" t="s">
         <v>237</v>
       </c>
-      <c r="AT1" s="140"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="140"/>
-      <c r="AW1" s="140"/>
-      <c r="AX1" s="140"/>
-      <c r="AY1" s="140"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="140"/>
-      <c r="BB1" s="141" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>238</v>
       </c>
-      <c r="BC1" s="141"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="116" t="s">
         <v>239</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -46256,20 +46261,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="143" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="144" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -46317,66 +46322,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="137" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="137"/>
-      <c r="AB4" s="137"/>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="138" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138"/>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138"/>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138"/>
-      <c r="AP4" s="139" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="139"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Abril'!B6</f>
@@ -46588,10 +46593,10 @@
         <f>'Captura Abril'!AQ7</f>
         <v>0.71000000000000008</v>
       </c>
-      <c r="BB5" s="133" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="133"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -49158,16 +49163,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="134" t="s">
+      <c r="AS19" s="107" t="s">
         <v>240</v>
       </c>
-      <c r="AT19" s="134"/>
-      <c r="AU19" s="134"/>
-      <c r="AV19" s="134"/>
-      <c r="AW19" s="134"/>
-      <c r="AX19" s="134"/>
-      <c r="AY19" s="134"/>
-      <c r="AZ19" s="134"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93466666666666676</v>
@@ -49334,9 +49339,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="135"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -49363,11 +49368,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="136" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>

--- a/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
+++ b/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc.sharepoint.com/sites/CharlascortasSSOsemanalesCuyotenango/Shared Documents/General/04. Registros 2026/09. Nivel De Seguridad/NUEVO NIVEL DE SEGURIDAD - 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{1FA93C17-BEC0-435F-87D9-564EB45A6C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{886A3DD0-794A-4D4A-A9C6-780167760147}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{1FA93C17-BEC0-435F-87D9-564EB45A6C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87BA2384-B2FA-4BF1-844B-23D0D5315494}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="867" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2067,6 +2067,24 @@
     <xf numFmtId="10" fontId="54" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2088,24 +2106,6 @@
     <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2114,15 +2114,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2138,23 +2129,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -2178,6 +2160,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="27" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3223,25 +3223,25 @@
                   <c:v>Centro de Distribucion</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Linea 2</c:v>
+                  <c:v>Linea 1</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>Mantenimiento</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Linea 2</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Linea 5</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>Materias Primas</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>Linea 3</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>Alrededores</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Linea 1</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Almacen de Repuestos</c:v>
@@ -5043,62 +5043,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="106" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="113"/>
-      <c r="Z1" s="113"/>
-      <c r="AA1" s="113"/>
-      <c r="AB1" s="113"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="114" t="s">
+      <c r="AS1" s="107" t="s">
         <v>242</v>
       </c>
-      <c r="AT1" s="114"/>
-      <c r="AU1" s="114"/>
-      <c r="AV1" s="114"/>
-      <c r="AW1" s="114"/>
-      <c r="AX1" s="114"/>
-      <c r="AY1" s="114"/>
-      <c r="AZ1" s="114"/>
-      <c r="BA1" s="114"/>
-      <c r="BB1" s="115" t="s">
+      <c r="AT1" s="107"/>
+      <c r="AU1" s="107"/>
+      <c r="AV1" s="107"/>
+      <c r="AW1" s="107"/>
+      <c r="AX1" s="107"/>
+      <c r="AY1" s="107"/>
+      <c r="AZ1" s="107"/>
+      <c r="BA1" s="107"/>
+      <c r="BB1" s="108" t="s">
         <v>243</v>
       </c>
-      <c r="BC1" s="115"/>
+      <c r="BC1" s="108"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="109" t="s">
         <v>244</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -5107,20 +5107,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="117" t="s">
+      <c r="AT2" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="117"/>
-      <c r="AV2" s="117"/>
+      <c r="AU2" s="110"/>
+      <c r="AV2" s="110"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="118" t="s">
+      <c r="AX2" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="118"/>
-      <c r="AZ2" s="118"/>
-      <c r="BA2" s="118"/>
+      <c r="AY2" s="111"/>
+      <c r="AZ2" s="111"/>
+      <c r="BA2" s="111"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -5168,66 +5168,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110" t="s">
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110" t="s">
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110" t="s">
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110" t="s">
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110" t="s">
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="110"/>
-      <c r="W4" s="111" t="s">
+      <c r="V4" s="116"/>
+      <c r="W4" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="111"/>
-      <c r="Y4" s="110" t="s">
+      <c r="X4" s="117"/>
+      <c r="Y4" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="111" t="s">
+      <c r="Z4" s="116"/>
+      <c r="AA4" s="116"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="111"/>
-      <c r="AF4" s="111"/>
-      <c r="AG4" s="111"/>
-      <c r="AH4" s="111"/>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
-      <c r="AO4" s="111"/>
-      <c r="AP4" s="112" t="s">
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
+      <c r="AJ4" s="117"/>
+      <c r="AK4" s="117"/>
+      <c r="AL4" s="117"/>
+      <c r="AM4" s="117"/>
+      <c r="AN4" s="117"/>
+      <c r="AO4" s="117"/>
+      <c r="AP4" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="112"/>
+      <c r="AQ4" s="118"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Mayo'!B6</f>
@@ -5439,10 +5439,10 @@
         <f>'Captura Mayo'!AQ7</f>
         <v>0.69000000000000006</v>
       </c>
-      <c r="BB5" s="106" t="s">
+      <c r="BB5" s="112" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="106"/>
+      <c r="BC5" s="112"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -8009,16 +8009,16 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="107" t="s">
+      <c r="AS19" s="113" t="s">
         <v>245</v>
       </c>
-      <c r="AT19" s="107"/>
-      <c r="AU19" s="107"/>
-      <c r="AV19" s="107"/>
-      <c r="AW19" s="107"/>
-      <c r="AX19" s="107"/>
-      <c r="AY19" s="107"/>
-      <c r="AZ19" s="107"/>
+      <c r="AT19" s="113"/>
+      <c r="AU19" s="113"/>
+      <c r="AV19" s="113"/>
+      <c r="AW19" s="113"/>
+      <c r="AX19" s="113"/>
+      <c r="AY19" s="113"/>
+      <c r="AZ19" s="113"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.87666666666666671</v>
@@ -8185,9 +8185,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="108"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="108"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="114"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -8214,11 +8214,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="115" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -8276,12 +8276,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -8296,6 +8290,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="74" priority="5" operator="greaterThanOrEqual">
@@ -8377,62 +8377,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="106" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="113"/>
-      <c r="Z1" s="113"/>
-      <c r="AA1" s="113"/>
-      <c r="AB1" s="113"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="114" t="s">
+      <c r="AS1" s="107" t="s">
         <v>247</v>
       </c>
-      <c r="AT1" s="114"/>
-      <c r="AU1" s="114"/>
-      <c r="AV1" s="114"/>
-      <c r="AW1" s="114"/>
-      <c r="AX1" s="114"/>
-      <c r="AY1" s="114"/>
-      <c r="AZ1" s="114"/>
-      <c r="BA1" s="114"/>
-      <c r="BB1" s="115" t="s">
+      <c r="AT1" s="107"/>
+      <c r="AU1" s="107"/>
+      <c r="AV1" s="107"/>
+      <c r="AW1" s="107"/>
+      <c r="AX1" s="107"/>
+      <c r="AY1" s="107"/>
+      <c r="AZ1" s="107"/>
+      <c r="BA1" s="107"/>
+      <c r="BB1" s="108" t="s">
         <v>248</v>
       </c>
-      <c r="BC1" s="115"/>
+      <c r="BC1" s="108"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="109" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -8441,20 +8441,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="117" t="s">
+      <c r="AT2" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="117"/>
-      <c r="AV2" s="117"/>
+      <c r="AU2" s="110"/>
+      <c r="AV2" s="110"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="118" t="s">
+      <c r="AX2" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="118"/>
-      <c r="AZ2" s="118"/>
-      <c r="BA2" s="118"/>
+      <c r="AY2" s="111"/>
+      <c r="AZ2" s="111"/>
+      <c r="BA2" s="111"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -8502,66 +8502,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110" t="s">
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110" t="s">
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110" t="s">
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110" t="s">
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110" t="s">
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="110"/>
-      <c r="W4" s="111" t="s">
+      <c r="V4" s="116"/>
+      <c r="W4" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="111"/>
-      <c r="Y4" s="110" t="s">
+      <c r="X4" s="117"/>
+      <c r="Y4" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="111" t="s">
+      <c r="Z4" s="116"/>
+      <c r="AA4" s="116"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="111"/>
-      <c r="AF4" s="111"/>
-      <c r="AG4" s="111"/>
-      <c r="AH4" s="111"/>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
-      <c r="AO4" s="111"/>
-      <c r="AP4" s="112" t="s">
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
+      <c r="AJ4" s="117"/>
+      <c r="AK4" s="117"/>
+      <c r="AL4" s="117"/>
+      <c r="AM4" s="117"/>
+      <c r="AN4" s="117"/>
+      <c r="AO4" s="117"/>
+      <c r="AP4" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="112"/>
+      <c r="AQ4" s="118"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Junio'!B6</f>
@@ -8773,10 +8773,10 @@
         <f>'Captura Junio'!AQ7</f>
         <v>0.64000000000000012</v>
       </c>
-      <c r="BB5" s="106" t="s">
+      <c r="BB5" s="112" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="106"/>
+      <c r="BC5" s="112"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -11343,16 +11343,16 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="107" t="s">
+      <c r="AS19" s="113" t="s">
         <v>250</v>
       </c>
-      <c r="AT19" s="107"/>
-      <c r="AU19" s="107"/>
-      <c r="AV19" s="107"/>
-      <c r="AW19" s="107"/>
-      <c r="AX19" s="107"/>
-      <c r="AY19" s="107"/>
-      <c r="AZ19" s="107"/>
+      <c r="AT19" s="113"/>
+      <c r="AU19" s="113"/>
+      <c r="AV19" s="113"/>
+      <c r="AW19" s="113"/>
+      <c r="AX19" s="113"/>
+      <c r="AY19" s="113"/>
+      <c r="AZ19" s="113"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.83357372900851168</v>
@@ -11519,9 +11519,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="108"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="108"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="114"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -11548,11 +11548,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="115" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -11610,12 +11610,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -11630,6 +11624,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="greaterThanOrEqual">
@@ -11713,62 +11713,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="106" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="113"/>
-      <c r="Z1" s="113"/>
-      <c r="AA1" s="113"/>
-      <c r="AB1" s="113"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="114" t="s">
+      <c r="AS1" s="107" t="s">
         <v>252</v>
       </c>
-      <c r="AT1" s="114"/>
-      <c r="AU1" s="114"/>
-      <c r="AV1" s="114"/>
-      <c r="AW1" s="114"/>
-      <c r="AX1" s="114"/>
-      <c r="AY1" s="114"/>
-      <c r="AZ1" s="114"/>
-      <c r="BA1" s="114"/>
-      <c r="BB1" s="115" t="s">
+      <c r="AT1" s="107"/>
+      <c r="AU1" s="107"/>
+      <c r="AV1" s="107"/>
+      <c r="AW1" s="107"/>
+      <c r="AX1" s="107"/>
+      <c r="AY1" s="107"/>
+      <c r="AZ1" s="107"/>
+      <c r="BA1" s="107"/>
+      <c r="BB1" s="108" t="s">
         <v>253</v>
       </c>
-      <c r="BC1" s="115"/>
+      <c r="BC1" s="108"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="109" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -11777,20 +11777,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="117" t="s">
+      <c r="AT2" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="117"/>
-      <c r="AV2" s="117"/>
+      <c r="AU2" s="110"/>
+      <c r="AV2" s="110"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="118" t="s">
+      <c r="AX2" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="118"/>
-      <c r="AZ2" s="118"/>
-      <c r="BA2" s="118"/>
+      <c r="AY2" s="111"/>
+      <c r="AZ2" s="111"/>
+      <c r="BA2" s="111"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -11838,66 +11838,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110" t="s">
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110" t="s">
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110" t="s">
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110" t="s">
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110" t="s">
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="110"/>
-      <c r="W4" s="111" t="s">
+      <c r="V4" s="116"/>
+      <c r="W4" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="111"/>
-      <c r="Y4" s="110" t="s">
+      <c r="X4" s="117"/>
+      <c r="Y4" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="111" t="s">
+      <c r="Z4" s="116"/>
+      <c r="AA4" s="116"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="111"/>
-      <c r="AF4" s="111"/>
-      <c r="AG4" s="111"/>
-      <c r="AH4" s="111"/>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
-      <c r="AO4" s="111"/>
-      <c r="AP4" s="112" t="s">
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
+      <c r="AJ4" s="117"/>
+      <c r="AK4" s="117"/>
+      <c r="AL4" s="117"/>
+      <c r="AM4" s="117"/>
+      <c r="AN4" s="117"/>
+      <c r="AO4" s="117"/>
+      <c r="AP4" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="112"/>
+      <c r="AQ4" s="118"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Julio'!B6</f>
@@ -12109,10 +12109,10 @@
         <f>'Captura Julio'!AQ7</f>
         <v>0.64</v>
       </c>
-      <c r="BB5" s="106" t="s">
+      <c r="BB5" s="112" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="106"/>
+      <c r="BC5" s="112"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -14679,16 +14679,16 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="107" t="s">
+      <c r="AS19" s="113" t="s">
         <v>255</v>
       </c>
-      <c r="AT19" s="107"/>
-      <c r="AU19" s="107"/>
-      <c r="AV19" s="107"/>
-      <c r="AW19" s="107"/>
-      <c r="AX19" s="107"/>
-      <c r="AY19" s="107"/>
-      <c r="AZ19" s="107"/>
+      <c r="AT19" s="113"/>
+      <c r="AU19" s="113"/>
+      <c r="AV19" s="113"/>
+      <c r="AW19" s="113"/>
+      <c r="AX19" s="113"/>
+      <c r="AY19" s="113"/>
+      <c r="AZ19" s="113"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.88027777777777783</v>
@@ -14855,9 +14855,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="108"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="108"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="114"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -14884,11 +14884,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="115" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -14946,12 +14946,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -14966,6 +14960,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="56" priority="5" operator="greaterThanOrEqual">
@@ -15051,62 +15051,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="106" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="113"/>
-      <c r="Z1" s="113"/>
-      <c r="AA1" s="113"/>
-      <c r="AB1" s="113"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="114" t="s">
+      <c r="AS1" s="107" t="s">
         <v>257</v>
       </c>
-      <c r="AT1" s="114"/>
-      <c r="AU1" s="114"/>
-      <c r="AV1" s="114"/>
-      <c r="AW1" s="114"/>
-      <c r="AX1" s="114"/>
-      <c r="AY1" s="114"/>
-      <c r="AZ1" s="114"/>
-      <c r="BA1" s="114"/>
-      <c r="BB1" s="115" t="s">
+      <c r="AT1" s="107"/>
+      <c r="AU1" s="107"/>
+      <c r="AV1" s="107"/>
+      <c r="AW1" s="107"/>
+      <c r="AX1" s="107"/>
+      <c r="AY1" s="107"/>
+      <c r="AZ1" s="107"/>
+      <c r="BA1" s="107"/>
+      <c r="BB1" s="108" t="s">
         <v>258</v>
       </c>
-      <c r="BC1" s="115"/>
+      <c r="BC1" s="108"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="109" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -15115,20 +15115,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="117" t="s">
+      <c r="AT2" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="117"/>
-      <c r="AV2" s="117"/>
+      <c r="AU2" s="110"/>
+      <c r="AV2" s="110"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="118" t="s">
+      <c r="AX2" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="118"/>
-      <c r="AZ2" s="118"/>
-      <c r="BA2" s="118"/>
+      <c r="AY2" s="111"/>
+      <c r="AZ2" s="111"/>
+      <c r="BA2" s="111"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -15176,66 +15176,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110" t="s">
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110" t="s">
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110" t="s">
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110" t="s">
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110" t="s">
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="110"/>
-      <c r="W4" s="111" t="s">
+      <c r="V4" s="116"/>
+      <c r="W4" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="111"/>
-      <c r="Y4" s="110" t="s">
+      <c r="X4" s="117"/>
+      <c r="Y4" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="111" t="s">
+      <c r="Z4" s="116"/>
+      <c r="AA4" s="116"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="111"/>
-      <c r="AF4" s="111"/>
-      <c r="AG4" s="111"/>
-      <c r="AH4" s="111"/>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
-      <c r="AO4" s="111"/>
-      <c r="AP4" s="112" t="s">
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
+      <c r="AJ4" s="117"/>
+      <c r="AK4" s="117"/>
+      <c r="AL4" s="117"/>
+      <c r="AM4" s="117"/>
+      <c r="AN4" s="117"/>
+      <c r="AO4" s="117"/>
+      <c r="AP4" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="112"/>
+      <c r="AQ4" s="118"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Agosto'!B6</f>
@@ -15447,10 +15447,10 @@
         <f>'Captura Agosto'!AQ7</f>
         <v>0.46000000000000008</v>
       </c>
-      <c r="BB5" s="106" t="s">
+      <c r="BB5" s="112" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="106"/>
+      <c r="BC5" s="112"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -16551,11 +16551,11 @@
       </c>
       <c r="AZ11" s="81">
         <f>-'Captura Agosto'!AN13</f>
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="BA11" s="82">
         <f>'Captura Agosto'!AQ13</f>
-        <v>0.45820000000000005</v>
+        <v>0.55820000000000003</v>
       </c>
       <c r="BB11" s="58"/>
       <c r="BC11" s="58"/>
@@ -16737,11 +16737,11 @@
       </c>
       <c r="AZ12" s="73">
         <f>-'Captura Agosto'!AN14</f>
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="BA12" s="74">
         <f>'Captura Agosto'!AQ14</f>
-        <v>0.62080000000000002</v>
+        <v>0.52080000000000004</v>
       </c>
       <c r="BB12" s="58"/>
       <c r="BC12" s="58"/>
@@ -16853,7 +16853,7 @@
         <v>222</v>
       </c>
       <c r="AF13" s="87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13" s="88" t="s">
         <v>222</v>
@@ -16878,7 +16878,7 @@
       </c>
       <c r="AN13" s="89">
         <f>AD13*Parametros!$E$28+AF13*Parametros!$E$29+AH13*Parametros!$E$30+AJ13*Parametros!$E$31+AL13*Parametros!$E$32</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="12" t="str">
         <f t="shared" si="2"/>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="AQ13" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP13-IF(S13="NO",Parametros!$E$17,0))+AC13)-AN13-IF(AO13="SI",Parametros!$E$33,0))</f>
-        <v>0.45820000000000005</v>
+        <v>0.55820000000000003</v>
       </c>
       <c r="AR13" s="58"/>
       <c r="AS13" s="79" t="str">
@@ -17039,7 +17039,7 @@
         <v>222</v>
       </c>
       <c r="AF14" s="87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" s="88" t="s">
         <v>222</v>
@@ -17064,7 +17064,7 @@
       </c>
       <c r="AN14" s="89">
         <f>AD14*Parametros!$E$28+AF14*Parametros!$E$29+AH14*Parametros!$E$30+AJ14*Parametros!$E$31+AL14*Parametros!$E$32</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AO14" s="12" t="str">
         <f t="shared" si="2"/>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="AQ14" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP14-IF(S14="NO",Parametros!$E$17,0))+AC14)-AN14-IF(AO14="SI",Parametros!$E$33,0))</f>
-        <v>0.62080000000000002</v>
+        <v>0.52080000000000004</v>
       </c>
       <c r="AR14" s="58"/>
       <c r="AS14" s="71" t="str">
@@ -18009,16 +18009,16 @@
         <v>0.49125000000000002</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="107" t="s">
+      <c r="AS19" s="113" t="s">
         <v>260</v>
       </c>
-      <c r="AT19" s="107"/>
-      <c r="AU19" s="107"/>
-      <c r="AV19" s="107"/>
-      <c r="AW19" s="107"/>
-      <c r="AX19" s="107"/>
-      <c r="AY19" s="107"/>
-      <c r="AZ19" s="107"/>
+      <c r="AT19" s="113"/>
+      <c r="AU19" s="113"/>
+      <c r="AV19" s="113"/>
+      <c r="AW19" s="113"/>
+      <c r="AX19" s="113"/>
+      <c r="AY19" s="113"/>
+      <c r="AZ19" s="113"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.6120133333333333</v>
@@ -18185,9 +18185,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="108"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="108"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="114"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -18214,11 +18214,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="115" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -18276,12 +18276,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -18296,6 +18290,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="47" priority="5" operator="greaterThanOrEqual">
@@ -18377,62 +18377,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="106" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="113"/>
-      <c r="Z1" s="113"/>
-      <c r="AA1" s="113"/>
-      <c r="AB1" s="113"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="114" t="s">
+      <c r="AS1" s="107" t="s">
         <v>262</v>
       </c>
-      <c r="AT1" s="114"/>
-      <c r="AU1" s="114"/>
-      <c r="AV1" s="114"/>
-      <c r="AW1" s="114"/>
-      <c r="AX1" s="114"/>
-      <c r="AY1" s="114"/>
-      <c r="AZ1" s="114"/>
-      <c r="BA1" s="114"/>
-      <c r="BB1" s="115" t="s">
+      <c r="AT1" s="107"/>
+      <c r="AU1" s="107"/>
+      <c r="AV1" s="107"/>
+      <c r="AW1" s="107"/>
+      <c r="AX1" s="107"/>
+      <c r="AY1" s="107"/>
+      <c r="AZ1" s="107"/>
+      <c r="BA1" s="107"/>
+      <c r="BB1" s="108" t="s">
         <v>263</v>
       </c>
-      <c r="BC1" s="115"/>
+      <c r="BC1" s="108"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="109" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -18441,20 +18441,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="117" t="s">
+      <c r="AT2" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="117"/>
-      <c r="AV2" s="117"/>
+      <c r="AU2" s="110"/>
+      <c r="AV2" s="110"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="118" t="s">
+      <c r="AX2" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="118"/>
-      <c r="AZ2" s="118"/>
-      <c r="BA2" s="118"/>
+      <c r="AY2" s="111"/>
+      <c r="AZ2" s="111"/>
+      <c r="BA2" s="111"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -18502,66 +18502,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110" t="s">
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110" t="s">
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110" t="s">
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110" t="s">
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110" t="s">
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="110"/>
-      <c r="W4" s="111" t="s">
+      <c r="V4" s="116"/>
+      <c r="W4" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="111"/>
-      <c r="Y4" s="110" t="s">
+      <c r="X4" s="117"/>
+      <c r="Y4" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="111" t="s">
+      <c r="Z4" s="116"/>
+      <c r="AA4" s="116"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="111"/>
-      <c r="AF4" s="111"/>
-      <c r="AG4" s="111"/>
-      <c r="AH4" s="111"/>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
-      <c r="AO4" s="111"/>
-      <c r="AP4" s="112" t="s">
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
+      <c r="AJ4" s="117"/>
+      <c r="AK4" s="117"/>
+      <c r="AL4" s="117"/>
+      <c r="AM4" s="117"/>
+      <c r="AN4" s="117"/>
+      <c r="AO4" s="117"/>
+      <c r="AP4" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="112"/>
+      <c r="AQ4" s="118"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Septiembre'!B6</f>
@@ -18773,10 +18773,10 @@
         <f>'Captura Septiembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="106" t="s">
+      <c r="BB5" s="112" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="106"/>
+      <c r="BC5" s="112"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -21343,16 +21343,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="107" t="s">
+      <c r="AS19" s="113" t="s">
         <v>265</v>
       </c>
-      <c r="AT19" s="107"/>
-      <c r="AU19" s="107"/>
-      <c r="AV19" s="107"/>
-      <c r="AW19" s="107"/>
-      <c r="AX19" s="107"/>
-      <c r="AY19" s="107"/>
-      <c r="AZ19" s="107"/>
+      <c r="AT19" s="113"/>
+      <c r="AU19" s="113"/>
+      <c r="AV19" s="113"/>
+      <c r="AW19" s="113"/>
+      <c r="AX19" s="113"/>
+      <c r="AY19" s="113"/>
+      <c r="AZ19" s="113"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -21519,9 +21519,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="108"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="108"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="114"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -21548,11 +21548,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="115" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -21610,12 +21610,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -21630,6 +21624,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="38" priority="5" operator="greaterThanOrEqual">
@@ -21711,62 +21711,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="106" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="113"/>
-      <c r="Z1" s="113"/>
-      <c r="AA1" s="113"/>
-      <c r="AB1" s="113"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="114" t="s">
+      <c r="AS1" s="107" t="s">
         <v>267</v>
       </c>
-      <c r="AT1" s="114"/>
-      <c r="AU1" s="114"/>
-      <c r="AV1" s="114"/>
-      <c r="AW1" s="114"/>
-      <c r="AX1" s="114"/>
-      <c r="AY1" s="114"/>
-      <c r="AZ1" s="114"/>
-      <c r="BA1" s="114"/>
-      <c r="BB1" s="115" t="s">
+      <c r="AT1" s="107"/>
+      <c r="AU1" s="107"/>
+      <c r="AV1" s="107"/>
+      <c r="AW1" s="107"/>
+      <c r="AX1" s="107"/>
+      <c r="AY1" s="107"/>
+      <c r="AZ1" s="107"/>
+      <c r="BA1" s="107"/>
+      <c r="BB1" s="108" t="s">
         <v>268</v>
       </c>
-      <c r="BC1" s="115"/>
+      <c r="BC1" s="108"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="109" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -21775,20 +21775,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="117" t="s">
+      <c r="AT2" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="117"/>
-      <c r="AV2" s="117"/>
+      <c r="AU2" s="110"/>
+      <c r="AV2" s="110"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="118" t="s">
+      <c r="AX2" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="118"/>
-      <c r="AZ2" s="118"/>
-      <c r="BA2" s="118"/>
+      <c r="AY2" s="111"/>
+      <c r="AZ2" s="111"/>
+      <c r="BA2" s="111"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -21836,66 +21836,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110" t="s">
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110" t="s">
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110" t="s">
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110" t="s">
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110" t="s">
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="110"/>
-      <c r="W4" s="111" t="s">
+      <c r="V4" s="116"/>
+      <c r="W4" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="111"/>
-      <c r="Y4" s="110" t="s">
+      <c r="X4" s="117"/>
+      <c r="Y4" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="111" t="s">
+      <c r="Z4" s="116"/>
+      <c r="AA4" s="116"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="111"/>
-      <c r="AF4" s="111"/>
-      <c r="AG4" s="111"/>
-      <c r="AH4" s="111"/>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
-      <c r="AO4" s="111"/>
-      <c r="AP4" s="112" t="s">
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
+      <c r="AJ4" s="117"/>
+      <c r="AK4" s="117"/>
+      <c r="AL4" s="117"/>
+      <c r="AM4" s="117"/>
+      <c r="AN4" s="117"/>
+      <c r="AO4" s="117"/>
+      <c r="AP4" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="112"/>
+      <c r="AQ4" s="118"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Octubre'!B6</f>
@@ -22107,10 +22107,10 @@
         <f>'Captura Octubre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="106" t="s">
+      <c r="BB5" s="112" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="106"/>
+      <c r="BC5" s="112"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -24677,16 +24677,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="107" t="s">
+      <c r="AS19" s="113" t="s">
         <v>270</v>
       </c>
-      <c r="AT19" s="107"/>
-      <c r="AU19" s="107"/>
-      <c r="AV19" s="107"/>
-      <c r="AW19" s="107"/>
-      <c r="AX19" s="107"/>
-      <c r="AY19" s="107"/>
-      <c r="AZ19" s="107"/>
+      <c r="AT19" s="113"/>
+      <c r="AU19" s="113"/>
+      <c r="AV19" s="113"/>
+      <c r="AW19" s="113"/>
+      <c r="AX19" s="113"/>
+      <c r="AY19" s="113"/>
+      <c r="AZ19" s="113"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -24853,9 +24853,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="108"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="108"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="114"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -24882,11 +24882,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="115" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -24944,12 +24944,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -24964,6 +24958,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="29" priority="5" operator="greaterThanOrEqual">
@@ -25045,62 +25045,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="106" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="113"/>
-      <c r="Z1" s="113"/>
-      <c r="AA1" s="113"/>
-      <c r="AB1" s="113"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="114" t="s">
+      <c r="AS1" s="107" t="s">
         <v>272</v>
       </c>
-      <c r="AT1" s="114"/>
-      <c r="AU1" s="114"/>
-      <c r="AV1" s="114"/>
-      <c r="AW1" s="114"/>
-      <c r="AX1" s="114"/>
-      <c r="AY1" s="114"/>
-      <c r="AZ1" s="114"/>
-      <c r="BA1" s="114"/>
-      <c r="BB1" s="115" t="s">
+      <c r="AT1" s="107"/>
+      <c r="AU1" s="107"/>
+      <c r="AV1" s="107"/>
+      <c r="AW1" s="107"/>
+      <c r="AX1" s="107"/>
+      <c r="AY1" s="107"/>
+      <c r="AZ1" s="107"/>
+      <c r="BA1" s="107"/>
+      <c r="BB1" s="108" t="s">
         <v>273</v>
       </c>
-      <c r="BC1" s="115"/>
+      <c r="BC1" s="108"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="109" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -25109,20 +25109,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="117" t="s">
+      <c r="AT2" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="117"/>
-      <c r="AV2" s="117"/>
+      <c r="AU2" s="110"/>
+      <c r="AV2" s="110"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="118" t="s">
+      <c r="AX2" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="118"/>
-      <c r="AZ2" s="118"/>
-      <c r="BA2" s="118"/>
+      <c r="AY2" s="111"/>
+      <c r="AZ2" s="111"/>
+      <c r="BA2" s="111"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -25170,66 +25170,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110" t="s">
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110" t="s">
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110" t="s">
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110" t="s">
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110" t="s">
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="110"/>
-      <c r="W4" s="111" t="s">
+      <c r="V4" s="116"/>
+      <c r="W4" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="111"/>
-      <c r="Y4" s="110" t="s">
+      <c r="X4" s="117"/>
+      <c r="Y4" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="111" t="s">
+      <c r="Z4" s="116"/>
+      <c r="AA4" s="116"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="111"/>
-      <c r="AF4" s="111"/>
-      <c r="AG4" s="111"/>
-      <c r="AH4" s="111"/>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
-      <c r="AO4" s="111"/>
-      <c r="AP4" s="112" t="s">
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
+      <c r="AJ4" s="117"/>
+      <c r="AK4" s="117"/>
+      <c r="AL4" s="117"/>
+      <c r="AM4" s="117"/>
+      <c r="AN4" s="117"/>
+      <c r="AO4" s="117"/>
+      <c r="AP4" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="112"/>
+      <c r="AQ4" s="118"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Noviembre'!B6</f>
@@ -25441,10 +25441,10 @@
         <f>'Captura Noviembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="106" t="s">
+      <c r="BB5" s="112" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="106"/>
+      <c r="BC5" s="112"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -28011,16 +28011,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="107" t="s">
+      <c r="AS19" s="113" t="s">
         <v>275</v>
       </c>
-      <c r="AT19" s="107"/>
-      <c r="AU19" s="107"/>
-      <c r="AV19" s="107"/>
-      <c r="AW19" s="107"/>
-      <c r="AX19" s="107"/>
-      <c r="AY19" s="107"/>
-      <c r="AZ19" s="107"/>
+      <c r="AT19" s="113"/>
+      <c r="AU19" s="113"/>
+      <c r="AV19" s="113"/>
+      <c r="AW19" s="113"/>
+      <c r="AX19" s="113"/>
+      <c r="AY19" s="113"/>
+      <c r="AZ19" s="113"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -28187,9 +28187,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="108"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="108"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="114"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -28216,11 +28216,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="115" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -28278,12 +28278,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -28298,6 +28292,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="20" priority="5" operator="greaterThanOrEqual">
@@ -28379,62 +28379,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="106" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="113"/>
-      <c r="Z1" s="113"/>
-      <c r="AA1" s="113"/>
-      <c r="AB1" s="113"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="114" t="s">
+      <c r="AS1" s="107" t="s">
         <v>277</v>
       </c>
-      <c r="AT1" s="114"/>
-      <c r="AU1" s="114"/>
-      <c r="AV1" s="114"/>
-      <c r="AW1" s="114"/>
-      <c r="AX1" s="114"/>
-      <c r="AY1" s="114"/>
-      <c r="AZ1" s="114"/>
-      <c r="BA1" s="114"/>
-      <c r="BB1" s="115" t="s">
+      <c r="AT1" s="107"/>
+      <c r="AU1" s="107"/>
+      <c r="AV1" s="107"/>
+      <c r="AW1" s="107"/>
+      <c r="AX1" s="107"/>
+      <c r="AY1" s="107"/>
+      <c r="AZ1" s="107"/>
+      <c r="BA1" s="107"/>
+      <c r="BB1" s="108" t="s">
         <v>278</v>
       </c>
-      <c r="BC1" s="115"/>
+      <c r="BC1" s="108"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="109" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -28443,20 +28443,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="117" t="s">
+      <c r="AT2" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="117"/>
-      <c r="AV2" s="117"/>
+      <c r="AU2" s="110"/>
+      <c r="AV2" s="110"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="118" t="s">
+      <c r="AX2" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="118"/>
-      <c r="AZ2" s="118"/>
-      <c r="BA2" s="118"/>
+      <c r="AY2" s="111"/>
+      <c r="AZ2" s="111"/>
+      <c r="BA2" s="111"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -28504,66 +28504,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110" t="s">
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110" t="s">
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110" t="s">
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110" t="s">
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110" t="s">
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="110"/>
-      <c r="W4" s="111" t="s">
+      <c r="V4" s="116"/>
+      <c r="W4" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="111"/>
-      <c r="Y4" s="110" t="s">
+      <c r="X4" s="117"/>
+      <c r="Y4" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="111" t="s">
+      <c r="Z4" s="116"/>
+      <c r="AA4" s="116"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="111"/>
-      <c r="AF4" s="111"/>
-      <c r="AG4" s="111"/>
-      <c r="AH4" s="111"/>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
-      <c r="AO4" s="111"/>
-      <c r="AP4" s="112" t="s">
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
+      <c r="AJ4" s="117"/>
+      <c r="AK4" s="117"/>
+      <c r="AL4" s="117"/>
+      <c r="AM4" s="117"/>
+      <c r="AN4" s="117"/>
+      <c r="AO4" s="117"/>
+      <c r="AP4" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="112"/>
+      <c r="AQ4" s="118"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Diciembre'!B6</f>
@@ -28775,10 +28775,10 @@
         <f>'Captura Diciembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="106" t="s">
+      <c r="BB5" s="112" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="106"/>
+      <c r="BC5" s="112"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -31345,16 +31345,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="107" t="s">
+      <c r="AS19" s="113" t="s">
         <v>280</v>
       </c>
-      <c r="AT19" s="107"/>
-      <c r="AU19" s="107"/>
-      <c r="AV19" s="107"/>
-      <c r="AW19" s="107"/>
-      <c r="AX19" s="107"/>
-      <c r="AY19" s="107"/>
-      <c r="AZ19" s="107"/>
+      <c r="AT19" s="113"/>
+      <c r="AU19" s="113"/>
+      <c r="AV19" s="113"/>
+      <c r="AW19" s="113"/>
+      <c r="AX19" s="113"/>
+      <c r="AY19" s="113"/>
+      <c r="AZ19" s="113"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -31521,9 +31521,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="108"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="108"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="114"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -31550,11 +31550,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="115" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -31612,12 +31612,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -31632,6 +31626,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThanOrEqual">
@@ -31705,11 +31705,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="106" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="145" t="s">
@@ -32250,7 +32250,7 @@
       </c>
       <c r="I8" s="10">
         <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
-        <v>0.62080000000000002</v>
+        <v>0.52080000000000004</v>
       </c>
       <c r="J8" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
@@ -32270,7 +32270,7 @@
       </c>
       <c r="N8" s="102">
         <f t="shared" si="0"/>
-        <v>0.89760000000000006</v>
+        <v>0.88510000000000011</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32364,7 +32364,7 @@
       </c>
       <c r="I10" s="10">
         <f>IFERROR(IF('Captura Agosto'!D13=0,"",'Captura Agosto'!AQ13),"")</f>
-        <v>0.45820000000000005</v>
+        <v>0.55820000000000003</v>
       </c>
       <c r="J10" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
@@ -32384,7 +32384,7 @@
       </c>
       <c r="N10" s="102">
         <f t="shared" si="0"/>
-        <v>0.78102499999999986</v>
+        <v>0.79352499999999992</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32940,16 +32940,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -33317,7 +33317,7 @@
       </c>
       <c r="B29" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,7),$E$23:$E$37,0))</f>
-        <v>Linea 2</v>
+        <v>Linea 1</v>
       </c>
       <c r="C29" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),7)</f>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="E30" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ13")*100000-13</f>
-        <v>45807.000000000007</v>
+        <v>55807</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33359,7 +33359,7 @@
       </c>
       <c r="B31" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,9),$E$23:$E$37,0))</f>
-        <v>Linea 5</v>
+        <v>Linea 2</v>
       </c>
       <c r="C31" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),9)</f>
@@ -33371,7 +33371,7 @@
       </c>
       <c r="E31" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ14")*100000-14</f>
-        <v>62066</v>
+        <v>52066.000000000007</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33380,7 +33380,7 @@
       </c>
       <c r="B32" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,10),$E$23:$E$37,0))</f>
-        <v>Materias Primas</v>
+        <v>Linea 5</v>
       </c>
       <c r="C32" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),10)</f>
@@ -33401,7 +33401,7 @@
       </c>
       <c r="B33" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,11),$E$23:$E$37,0))</f>
-        <v>Linea 3</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C33" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),11)</f>
@@ -33422,7 +33422,7 @@
       </c>
       <c r="B34" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,12),$E$23:$E$37,0))</f>
-        <v>Alrededores</v>
+        <v>Linea 3</v>
       </c>
       <c r="C34" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),12)</f>
@@ -33443,7 +33443,7 @@
       </c>
       <c r="B35" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,13),$E$23:$E$37,0))</f>
-        <v>Linea 1</v>
+        <v>Alrededores</v>
       </c>
       <c r="C35" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),13)</f>
@@ -34087,7 +34087,7 @@
       </c>
       <c r="I11" s="10">
         <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
-        <v>0.62080000000000002</v>
+        <v>0.52080000000000004</v>
       </c>
       <c r="J11" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
@@ -34107,7 +34107,7 @@
       </c>
       <c r="N11" s="102">
         <f t="shared" si="0"/>
-        <v>0.89760000000000006</v>
+        <v>0.88510000000000011</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34429,7 +34429,7 @@
       </c>
       <c r="I17" s="10">
         <f>IFERROR(IF('Captura Agosto'!D13=0,"",'Captura Agosto'!AQ13),"")</f>
-        <v>0.45820000000000005</v>
+        <v>0.55820000000000003</v>
       </c>
       <c r="J17" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D13=0,"",'Captura Septiembre'!AQ13),"")</f>
@@ -34449,7 +34449,7 @@
       </c>
       <c r="N17" s="102">
         <f t="shared" si="0"/>
-        <v>0.78102499999999986</v>
+        <v>0.79352499999999992</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34603,44 +34603,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="128" t="s">
+      <c r="B2" s="125" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="128"/>
-      <c r="R2" s="128"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="125"/>
+      <c r="P2" s="125"/>
+      <c r="Q2" s="125"/>
+      <c r="R2" s="125"/>
     </row>
     <row r="3" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="128"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="128"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="128"/>
-      <c r="G3" s="128"/>
-      <c r="H3" s="128"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="128"/>
-      <c r="K3" s="128"/>
-      <c r="L3" s="128"/>
-      <c r="M3" s="128"/>
-      <c r="N3" s="128"/>
-      <c r="O3" s="128"/>
-      <c r="P3" s="128"/>
-      <c r="Q3" s="128"/>
-      <c r="R3" s="128"/>
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="125"/>
     </row>
     <row r="4" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
@@ -34650,141 +34650,141 @@
         <f>Calculos!$B$2</f>
         <v>Agosto</v>
       </c>
-      <c r="F4" s="129" t="s">
+      <c r="F4" s="126" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="129"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="129"/>
-      <c r="J4" s="129"/>
-      <c r="K4" s="129"/>
-      <c r="L4" s="129"/>
-      <c r="M4" s="129"/>
-      <c r="N4" s="129"/>
-      <c r="O4" s="129"/>
-      <c r="P4" s="129"/>
-      <c r="Q4" s="129"/>
-      <c r="R4" s="129"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="126"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="126"/>
+      <c r="M4" s="126"/>
+      <c r="N4" s="126"/>
+      <c r="O4" s="126"/>
+      <c r="P4" s="126"/>
+      <c r="Q4" s="126"/>
+      <c r="R4" s="126"/>
     </row>
     <row r="6" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="130" t="s">
+      <c r="B6" s="127" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="130"/>
-      <c r="D6" s="130"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="130" t="s">
+      <c r="C6" s="127"/>
+      <c r="D6" s="127"/>
+      <c r="E6" s="127"/>
+      <c r="F6" s="127" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="130"/>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="130" t="s">
+      <c r="G6" s="127"/>
+      <c r="H6" s="127"/>
+      <c r="I6" s="127"/>
+      <c r="J6" s="127" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
-      <c r="M6" s="130" t="s">
+      <c r="K6" s="127"/>
+      <c r="L6" s="127"/>
+      <c r="M6" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="N6" s="130"/>
-      <c r="O6" s="130"/>
-      <c r="P6" s="130" t="s">
+      <c r="N6" s="127"/>
+      <c r="O6" s="127"/>
+      <c r="P6" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="Q6" s="130"/>
-      <c r="R6" s="130"/>
+      <c r="Q6" s="127"/>
+      <c r="R6" s="127"/>
     </row>
     <row r="7" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="130"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="130"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="130"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="130"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="127"/>
+      <c r="K7" s="127"/>
+      <c r="L7" s="127"/>
+      <c r="M7" s="127"/>
+      <c r="N7" s="127"/>
+      <c r="O7" s="127"/>
+      <c r="P7" s="127"/>
+      <c r="Q7" s="127"/>
+      <c r="R7" s="127"/>
     </row>
     <row r="8" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="123">
+      <c r="B8" s="128">
         <f ca="1">Calculos!B44</f>
         <v>0.6120133333333333</v>
       </c>
-      <c r="C8" s="123"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="124" t="str">
+      <c r="C8" s="128"/>
+      <c r="D8" s="128"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="129" t="str">
         <f ca="1">Calculos!B45</f>
         <v>Rojo</v>
       </c>
-      <c r="G8" s="124"/>
-      <c r="H8" s="124"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="125">
+      <c r="G8" s="129"/>
+      <c r="H8" s="129"/>
+      <c r="I8" s="129"/>
+      <c r="J8" s="130">
         <f ca="1">Calculos!B40</f>
         <v>0</v>
       </c>
-      <c r="K8" s="125"/>
-      <c r="L8" s="125"/>
-      <c r="M8" s="126">
+      <c r="K8" s="130"/>
+      <c r="L8" s="130"/>
+      <c r="M8" s="123">
         <f ca="1">Calculos!B41</f>
         <v>0</v>
       </c>
-      <c r="N8" s="126"/>
-      <c r="O8" s="126"/>
-      <c r="P8" s="127">
+      <c r="N8" s="123"/>
+      <c r="O8" s="123"/>
+      <c r="P8" s="124">
         <f ca="1">Calculos!B42</f>
         <v>15</v>
       </c>
-      <c r="Q8" s="127"/>
-      <c r="R8" s="127"/>
+      <c r="Q8" s="124"/>
+      <c r="R8" s="124"/>
     </row>
     <row r="9" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="123"/>
-      <c r="C9" s="123"/>
-      <c r="D9" s="123"/>
-      <c r="E9" s="123"/>
-      <c r="F9" s="124"/>
-      <c r="G9" s="124"/>
-      <c r="H9" s="124"/>
-      <c r="I9" s="124"/>
-      <c r="J9" s="125"/>
-      <c r="K9" s="125"/>
-      <c r="L9" s="125"/>
-      <c r="M9" s="126"/>
-      <c r="N9" s="126"/>
-      <c r="O9" s="126"/>
-      <c r="P9" s="127"/>
-      <c r="Q9" s="127"/>
-      <c r="R9" s="127"/>
+      <c r="B9" s="128"/>
+      <c r="C9" s="128"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="128"/>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="130"/>
+      <c r="K9" s="130"/>
+      <c r="L9" s="130"/>
+      <c r="M9" s="123"/>
+      <c r="N9" s="123"/>
+      <c r="O9" s="123"/>
+      <c r="P9" s="124"/>
+      <c r="Q9" s="124"/>
+      <c r="R9" s="124"/>
     </row>
     <row r="10" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="123"/>
-      <c r="C10" s="123"/>
-      <c r="D10" s="123"/>
-      <c r="E10" s="123"/>
-      <c r="F10" s="124"/>
-      <c r="G10" s="124"/>
-      <c r="H10" s="124"/>
-      <c r="I10" s="124"/>
-      <c r="J10" s="125"/>
-      <c r="K10" s="125"/>
-      <c r="L10" s="125"/>
-      <c r="M10" s="126"/>
-      <c r="N10" s="126"/>
-      <c r="O10" s="126"/>
-      <c r="P10" s="127"/>
-      <c r="Q10" s="127"/>
-      <c r="R10" s="127"/>
+      <c r="B10" s="128"/>
+      <c r="C10" s="128"/>
+      <c r="D10" s="128"/>
+      <c r="E10" s="128"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="130"/>
+      <c r="K10" s="130"/>
+      <c r="L10" s="130"/>
+      <c r="M10" s="123"/>
+      <c r="N10" s="123"/>
+      <c r="O10" s="123"/>
+      <c r="P10" s="124"/>
+      <c r="Q10" s="124"/>
+      <c r="R10" s="124"/>
     </row>
     <row r="12" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
@@ -34923,7 +34923,7 @@
     <row r="20" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="str">
         <f ca="1">Calculos!B29</f>
-        <v>Linea 2</v>
+        <v>Linea 1</v>
       </c>
       <c r="C20" s="21">
         <f ca="1">Calculos!C29</f>
@@ -34951,7 +34951,7 @@
     <row r="22" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="str">
         <f ca="1">Calculos!B31</f>
-        <v>Linea 5</v>
+        <v>Linea 2</v>
       </c>
       <c r="C22" s="21">
         <f ca="1">Calculos!C31</f>
@@ -34961,7 +34961,7 @@
     <row r="23" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="str">
         <f ca="1">Calculos!B32</f>
-        <v>Materias Primas</v>
+        <v>Linea 5</v>
       </c>
       <c r="C23" s="21">
         <f ca="1">Calculos!C32</f>
@@ -34971,7 +34971,7 @@
     <row r="24" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="str">
         <f ca="1">Calculos!B33</f>
-        <v>Linea 3</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C24" s="21">
         <f ca="1">Calculos!C33</f>
@@ -34981,7 +34981,7 @@
     <row r="25" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="str">
         <f ca="1">Calculos!B34</f>
-        <v>Alrededores</v>
+        <v>Linea 3</v>
       </c>
       <c r="C25" s="21">
         <f ca="1">Calculos!C34</f>
@@ -34991,7 +34991,7 @@
     <row r="26" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="str">
         <f ca="1">Calculos!B35</f>
-        <v>Linea 1</v>
+        <v>Alrededores</v>
       </c>
       <c r="C26" s="21">
         <f ca="1">Calculos!C35</f>
@@ -35047,6 +35047,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B8:E10"/>
+    <mergeCell ref="F8:I10"/>
+    <mergeCell ref="J8:L10"/>
     <mergeCell ref="M8:O10"/>
     <mergeCell ref="P8:R10"/>
     <mergeCell ref="B2:R3"/>
@@ -35056,11 +35061,6 @@
     <mergeCell ref="J6:L7"/>
     <mergeCell ref="M6:O7"/>
     <mergeCell ref="P6:R7"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B8:E10"/>
-    <mergeCell ref="F8:I10"/>
-    <mergeCell ref="J8:L10"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -35090,61 +35090,61 @@
   <sheetData>
     <row r="1" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="141" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134" t="s">
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="142" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="142"/>
       <c r="H2" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="135" t="s">
+      <c r="B4" s="143" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="135"/>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="135"/>
-      <c r="M4" s="135"/>
-      <c r="N4" s="135"/>
-      <c r="O4" s="135"/>
-      <c r="P4" s="135"/>
-      <c r="Q4" s="135"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+      <c r="I4" s="143"/>
+      <c r="J4" s="143"/>
+      <c r="K4" s="143"/>
+      <c r="L4" s="143"/>
+      <c r="M4" s="143"/>
+      <c r="N4" s="143"/>
+      <c r="O4" s="143"/>
+      <c r="P4" s="143"/>
+      <c r="Q4" s="143"/>
     </row>
     <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="136" t="str">
+      <c r="B5" s="144" t="str">
         <f>UPPER("Planta Cuyotenango  ·  "&amp;Calculos!$B$2&amp;" 2026  ·  Acumulado Año")</f>
         <v>PLANTA CUYOTENANGO  ·  AGOSTO 2026  ·  ACUMULADO AÑO</v>
       </c>
-      <c r="C5" s="136"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="136"/>
-      <c r="L5" s="136"/>
-      <c r="M5" s="136"/>
-      <c r="N5" s="136"/>
-      <c r="O5" s="136"/>
-      <c r="P5" s="136"/>
-      <c r="Q5" s="136"/>
+      <c r="C5" s="144"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="144"/>
+      <c r="F5" s="144"/>
+      <c r="G5" s="144"/>
+      <c r="H5" s="144"/>
+      <c r="I5" s="144"/>
+      <c r="J5" s="144"/>
+      <c r="K5" s="144"/>
+      <c r="L5" s="144"/>
+      <c r="M5" s="144"/>
+      <c r="N5" s="144"/>
+      <c r="O5" s="144"/>
+      <c r="P5" s="144"/>
+      <c r="Q5" s="144"/>
     </row>
     <row r="6" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="P6" s="28" t="s">
@@ -35155,7 +35155,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="137" t="str">
+      <c r="A7" s="131" t="str">
         <f>UPPER(Calculos!$B$2)</f>
         <v>AGOSTO</v>
       </c>
@@ -35172,13 +35172,13 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="137"/>
-      <c r="G8" s="138">
+      <c r="A8" s="131"/>
+      <c r="G8" s="132">
         <f ca="1">X31</f>
         <v>0</v>
       </c>
-      <c r="H8" s="138"/>
-      <c r="I8" s="138"/>
+      <c r="H8" s="132"/>
+      <c r="I8" s="132"/>
       <c r="P8" s="31" t="s">
         <v>76</v>
       </c>
@@ -35188,15 +35188,15 @@
       </c>
     </row>
     <row r="9" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="137"/>
-      <c r="F9" s="139">
+      <c r="A9" s="131"/>
+      <c r="F9" s="133">
         <f ca="1">X32</f>
         <v>0</v>
       </c>
-      <c r="G9" s="139"/>
-      <c r="H9" s="139"/>
-      <c r="I9" s="139"/>
-      <c r="J9" s="139"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="133"/>
       <c r="P9" s="31" t="s">
         <v>77</v>
       </c>
@@ -35206,17 +35206,17 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="137"/>
-      <c r="E10" s="140">
+      <c r="A10" s="131"/>
+      <c r="E10" s="134">
         <f ca="1">X33</f>
         <v>0</v>
       </c>
-      <c r="F10" s="140"/>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="140"/>
+      <c r="F10" s="134"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="134"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="134"/>
+      <c r="K10" s="134"/>
       <c r="P10" s="31" t="s">
         <v>78</v>
       </c>
@@ -35226,19 +35226,19 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="137"/>
-      <c r="D11" s="141">
+      <c r="A11" s="131"/>
+      <c r="D11" s="135">
         <f ca="1">X34</f>
         <v>5</v>
       </c>
-      <c r="E11" s="141"/>
-      <c r="F11" s="141"/>
-      <c r="G11" s="141"/>
-      <c r="H11" s="141"/>
-      <c r="I11" s="141"/>
-      <c r="J11" s="141"/>
-      <c r="K11" s="141"/>
-      <c r="L11" s="141"/>
+      <c r="E11" s="135"/>
+      <c r="F11" s="135"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="135"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="135"/>
+      <c r="K11" s="135"/>
+      <c r="L11" s="135"/>
       <c r="P11" s="31" t="s">
         <v>79</v>
       </c>
@@ -35248,21 +35248,21 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="137"/>
-      <c r="C12" s="142">
+      <c r="A12" s="131"/>
+      <c r="C12" s="136">
         <f ca="1">X35</f>
         <v>0</v>
       </c>
-      <c r="D12" s="142"/>
-      <c r="E12" s="142"/>
-      <c r="F12" s="142"/>
-      <c r="G12" s="142"/>
-      <c r="H12" s="142"/>
-      <c r="I12" s="142"/>
-      <c r="J12" s="142"/>
-      <c r="K12" s="142"/>
-      <c r="L12" s="142"/>
-      <c r="M12" s="142"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="136"/>
+      <c r="L12" s="136"/>
+      <c r="M12" s="136"/>
       <c r="P12" s="31" t="s">
         <v>80</v>
       </c>
@@ -35272,23 +35272,23 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="137"/>
-      <c r="B13" s="143">
+      <c r="A13" s="131"/>
+      <c r="B13" s="137">
         <f ca="1">X36</f>
         <v>27</v>
       </c>
-      <c r="C13" s="143"/>
-      <c r="D13" s="143"/>
-      <c r="E13" s="143"/>
-      <c r="F13" s="143"/>
-      <c r="G13" s="143"/>
-      <c r="H13" s="143"/>
-      <c r="I13" s="143"/>
-      <c r="J13" s="143"/>
-      <c r="K13" s="143"/>
-      <c r="L13" s="143"/>
-      <c r="M13" s="143"/>
-      <c r="N13" s="143"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="137"/>
+      <c r="L13" s="137"/>
+      <c r="M13" s="137"/>
+      <c r="N13" s="137"/>
       <c r="P13" s="31" t="s">
         <v>81</v>
       </c>
@@ -35298,23 +35298,23 @@
       </c>
     </row>
     <row r="14" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="137"/>
-      <c r="B14" s="144">
+      <c r="A14" s="131"/>
+      <c r="B14" s="138">
         <f ca="1">X37</f>
         <v>196</v>
       </c>
-      <c r="C14" s="144"/>
-      <c r="D14" s="144"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="144"/>
-      <c r="J14" s="144"/>
-      <c r="K14" s="144"/>
-      <c r="L14" s="144"/>
-      <c r="M14" s="144"/>
-      <c r="N14" s="144"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="138"/>
+      <c r="L14" s="138"/>
+      <c r="M14" s="138"/>
+      <c r="N14" s="138"/>
       <c r="P14" s="31" t="s">
         <v>82</v>
       </c>
@@ -35325,12 +35325,12 @@
     </row>
     <row r="15" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="S16" s="131" t="s">
+      <c r="S16" s="139" t="s">
         <v>83</v>
       </c>
-      <c r="T16" s="131"/>
-      <c r="U16" s="131"/>
-      <c r="V16" s="131"/>
+      <c r="T16" s="139"/>
+      <c r="U16" s="139"/>
+      <c r="V16" s="139"/>
     </row>
     <row r="17" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -35401,42 +35401,42 @@
     <row r="25" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="2:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="132" t="s">
+      <c r="B27" s="140" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="132"/>
-      <c r="D27" s="132"/>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="132"/>
-      <c r="I27" s="132"/>
-      <c r="J27" s="132"/>
-      <c r="K27" s="132"/>
-      <c r="L27" s="132"/>
-      <c r="M27" s="132"/>
-      <c r="N27" s="132"/>
-      <c r="O27" s="132"/>
-      <c r="P27" s="132"/>
-      <c r="Q27" s="132"/>
+      <c r="C27" s="140"/>
+      <c r="D27" s="140"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="140"/>
+      <c r="I27" s="140"/>
+      <c r="J27" s="140"/>
+      <c r="K27" s="140"/>
+      <c r="L27" s="140"/>
+      <c r="M27" s="140"/>
+      <c r="N27" s="140"/>
+      <c r="O27" s="140"/>
+      <c r="P27" s="140"/>
+      <c r="Q27" s="140"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="132"/>
-      <c r="C28" s="132"/>
-      <c r="D28" s="132"/>
-      <c r="E28" s="132"/>
-      <c r="F28" s="132"/>
-      <c r="G28" s="132"/>
-      <c r="H28" s="132"/>
-      <c r="I28" s="132"/>
-      <c r="J28" s="132"/>
-      <c r="K28" s="132"/>
-      <c r="L28" s="132"/>
-      <c r="M28" s="132"/>
-      <c r="N28" s="132"/>
-      <c r="O28" s="132"/>
-      <c r="P28" s="132"/>
-      <c r="Q28" s="132"/>
+      <c r="B28" s="140"/>
+      <c r="C28" s="140"/>
+      <c r="D28" s="140"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="140"/>
+      <c r="I28" s="140"/>
+      <c r="J28" s="140"/>
+      <c r="K28" s="140"/>
+      <c r="L28" s="140"/>
+      <c r="M28" s="140"/>
+      <c r="N28" s="140"/>
+      <c r="O28" s="140"/>
+      <c r="P28" s="140"/>
+      <c r="Q28" s="140"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.35">
       <c r="W30" s="39" t="s">
@@ -35542,6 +35542,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="S16:V16"/>
+    <mergeCell ref="B27:Q28"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="B5:Q5"/>
     <mergeCell ref="A7:A14"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="F9:J9"/>
@@ -35550,12 +35556,6 @@
     <mergeCell ref="C12:M12"/>
     <mergeCell ref="B13:N13"/>
     <mergeCell ref="B14:N14"/>
-    <mergeCell ref="S16:V16"/>
-    <mergeCell ref="B27:Q28"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="B5:Q5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="E2" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -35590,13 +35590,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="106" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="122" t="s">
@@ -36190,62 +36190,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="106" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="113"/>
-      <c r="Z1" s="113"/>
-      <c r="AA1" s="113"/>
-      <c r="AB1" s="113"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="114" t="s">
+      <c r="AS1" s="107" t="s">
         <v>161</v>
       </c>
-      <c r="AT1" s="114"/>
-      <c r="AU1" s="114"/>
-      <c r="AV1" s="114"/>
-      <c r="AW1" s="114"/>
-      <c r="AX1" s="114"/>
-      <c r="AY1" s="114"/>
-      <c r="AZ1" s="114"/>
-      <c r="BA1" s="114"/>
-      <c r="BB1" s="115" t="s">
+      <c r="AT1" s="107"/>
+      <c r="AU1" s="107"/>
+      <c r="AV1" s="107"/>
+      <c r="AW1" s="107"/>
+      <c r="AX1" s="107"/>
+      <c r="AY1" s="107"/>
+      <c r="AZ1" s="107"/>
+      <c r="BA1" s="107"/>
+      <c r="BB1" s="108" t="s">
         <v>162</v>
       </c>
-      <c r="BC1" s="115"/>
+      <c r="BC1" s="108"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="109" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -36254,20 +36254,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="117" t="s">
+      <c r="AT2" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="117"/>
-      <c r="AV2" s="117"/>
+      <c r="AU2" s="110"/>
+      <c r="AV2" s="110"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="118" t="s">
+      <c r="AX2" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="118"/>
-      <c r="AZ2" s="118"/>
-      <c r="BA2" s="118"/>
+      <c r="AY2" s="111"/>
+      <c r="AZ2" s="111"/>
+      <c r="BA2" s="111"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -36315,66 +36315,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110" t="s">
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110" t="s">
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110" t="s">
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110" t="s">
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110" t="s">
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="110"/>
-      <c r="W4" s="111" t="s">
+      <c r="V4" s="116"/>
+      <c r="W4" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="111"/>
-      <c r="Y4" s="110" t="s">
+      <c r="X4" s="117"/>
+      <c r="Y4" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="111" t="s">
+      <c r="Z4" s="116"/>
+      <c r="AA4" s="116"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="111"/>
-      <c r="AF4" s="111"/>
-      <c r="AG4" s="111"/>
-      <c r="AH4" s="111"/>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
-      <c r="AO4" s="111"/>
-      <c r="AP4" s="112" t="s">
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
+      <c r="AJ4" s="117"/>
+      <c r="AK4" s="117"/>
+      <c r="AL4" s="117"/>
+      <c r="AM4" s="117"/>
+      <c r="AN4" s="117"/>
+      <c r="AO4" s="117"/>
+      <c r="AP4" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="112"/>
+      <c r="AQ4" s="118"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Enero'!B6</f>
@@ -36586,10 +36586,10 @@
         <f>'Captura Enero'!AQ7</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="BB5" s="106" t="s">
+      <c r="BB5" s="112" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="106"/>
+      <c r="BC5" s="112"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -39156,16 +39156,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="107" t="s">
+      <c r="AS19" s="113" t="s">
         <v>224</v>
       </c>
-      <c r="AT19" s="107"/>
-      <c r="AU19" s="107"/>
-      <c r="AV19" s="107"/>
-      <c r="AW19" s="107"/>
-      <c r="AX19" s="107"/>
-      <c r="AY19" s="107"/>
-      <c r="AZ19" s="107"/>
+      <c r="AT19" s="113"/>
+      <c r="AU19" s="113"/>
+      <c r="AV19" s="113"/>
+      <c r="AW19" s="113"/>
+      <c r="AX19" s="113"/>
+      <c r="AY19" s="113"/>
+      <c r="AZ19" s="113"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93030769230769228</v>
@@ -39337,9 +39337,9 @@
       </c>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="108"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="108"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="114"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -39366,11 +39366,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="115" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -39428,12 +39428,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -39448,6 +39442,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="110" priority="5" operator="greaterThanOrEqual">
@@ -39529,62 +39529,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="106" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="113"/>
-      <c r="Z1" s="113"/>
-      <c r="AA1" s="113"/>
-      <c r="AB1" s="113"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="114" t="s">
+      <c r="AS1" s="107" t="s">
         <v>227</v>
       </c>
-      <c r="AT1" s="114"/>
-      <c r="AU1" s="114"/>
-      <c r="AV1" s="114"/>
-      <c r="AW1" s="114"/>
-      <c r="AX1" s="114"/>
-      <c r="AY1" s="114"/>
-      <c r="AZ1" s="114"/>
-      <c r="BA1" s="114"/>
-      <c r="BB1" s="115" t="s">
+      <c r="AT1" s="107"/>
+      <c r="AU1" s="107"/>
+      <c r="AV1" s="107"/>
+      <c r="AW1" s="107"/>
+      <c r="AX1" s="107"/>
+      <c r="AY1" s="107"/>
+      <c r="AZ1" s="107"/>
+      <c r="BA1" s="107"/>
+      <c r="BB1" s="108" t="s">
         <v>228</v>
       </c>
-      <c r="BC1" s="115"/>
+      <c r="BC1" s="108"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="109" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -39593,20 +39593,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="117" t="s">
+      <c r="AT2" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="117"/>
-      <c r="AV2" s="117"/>
+      <c r="AU2" s="110"/>
+      <c r="AV2" s="110"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="118" t="s">
+      <c r="AX2" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="118"/>
-      <c r="AZ2" s="118"/>
-      <c r="BA2" s="118"/>
+      <c r="AY2" s="111"/>
+      <c r="AZ2" s="111"/>
+      <c r="BA2" s="111"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -39654,66 +39654,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110" t="s">
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110" t="s">
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110" t="s">
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110" t="s">
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110" t="s">
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="110"/>
-      <c r="W4" s="111" t="s">
+      <c r="V4" s="116"/>
+      <c r="W4" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="111"/>
-      <c r="Y4" s="110" t="s">
+      <c r="X4" s="117"/>
+      <c r="Y4" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="111" t="s">
+      <c r="Z4" s="116"/>
+      <c r="AA4" s="116"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="111"/>
-      <c r="AF4" s="111"/>
-      <c r="AG4" s="111"/>
-      <c r="AH4" s="111"/>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
-      <c r="AO4" s="111"/>
-      <c r="AP4" s="112" t="s">
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
+      <c r="AJ4" s="117"/>
+      <c r="AK4" s="117"/>
+      <c r="AL4" s="117"/>
+      <c r="AM4" s="117"/>
+      <c r="AN4" s="117"/>
+      <c r="AO4" s="117"/>
+      <c r="AP4" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="112"/>
+      <c r="AQ4" s="118"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Febrero'!B6</f>
@@ -39925,10 +39925,10 @@
         <f>'Captura Febrero'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="106" t="s">
+      <c r="BB5" s="112" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="106"/>
+      <c r="BC5" s="112"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -42495,16 +42495,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="107" t="s">
+      <c r="AS19" s="113" t="s">
         <v>230</v>
       </c>
-      <c r="AT19" s="107"/>
-      <c r="AU19" s="107"/>
-      <c r="AV19" s="107"/>
-      <c r="AW19" s="107"/>
-      <c r="AX19" s="107"/>
-      <c r="AY19" s="107"/>
-      <c r="AZ19" s="107"/>
+      <c r="AT19" s="113"/>
+      <c r="AU19" s="113"/>
+      <c r="AV19" s="113"/>
+      <c r="AW19" s="113"/>
+      <c r="AX19" s="113"/>
+      <c r="AY19" s="113"/>
+      <c r="AZ19" s="113"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.9572597670647206</v>
@@ -42671,9 +42671,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="108"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="108"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="114"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -42700,11 +42700,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="115" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -42762,12 +42762,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -42782,6 +42776,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="101" priority="5" operator="greaterThanOrEqual">
@@ -42863,62 +42863,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="106" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="113"/>
-      <c r="Z1" s="113"/>
-      <c r="AA1" s="113"/>
-      <c r="AB1" s="113"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="114" t="s">
+      <c r="AS1" s="107" t="s">
         <v>232</v>
       </c>
-      <c r="AT1" s="114"/>
-      <c r="AU1" s="114"/>
-      <c r="AV1" s="114"/>
-      <c r="AW1" s="114"/>
-      <c r="AX1" s="114"/>
-      <c r="AY1" s="114"/>
-      <c r="AZ1" s="114"/>
-      <c r="BA1" s="114"/>
-      <c r="BB1" s="115" t="s">
+      <c r="AT1" s="107"/>
+      <c r="AU1" s="107"/>
+      <c r="AV1" s="107"/>
+      <c r="AW1" s="107"/>
+      <c r="AX1" s="107"/>
+      <c r="AY1" s="107"/>
+      <c r="AZ1" s="107"/>
+      <c r="BA1" s="107"/>
+      <c r="BB1" s="108" t="s">
         <v>233</v>
       </c>
-      <c r="BC1" s="115"/>
+      <c r="BC1" s="108"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="109" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -42927,20 +42927,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="117" t="s">
+      <c r="AT2" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="117"/>
-      <c r="AV2" s="117"/>
+      <c r="AU2" s="110"/>
+      <c r="AV2" s="110"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="118" t="s">
+      <c r="AX2" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="118"/>
-      <c r="AZ2" s="118"/>
-      <c r="BA2" s="118"/>
+      <c r="AY2" s="111"/>
+      <c r="AZ2" s="111"/>
+      <c r="BA2" s="111"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -42988,66 +42988,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110" t="s">
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110" t="s">
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110" t="s">
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110" t="s">
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110" t="s">
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="110"/>
-      <c r="W4" s="111" t="s">
+      <c r="V4" s="116"/>
+      <c r="W4" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="111"/>
-      <c r="Y4" s="110" t="s">
+      <c r="X4" s="117"/>
+      <c r="Y4" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="111" t="s">
+      <c r="Z4" s="116"/>
+      <c r="AA4" s="116"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="111"/>
-      <c r="AF4" s="111"/>
-      <c r="AG4" s="111"/>
-      <c r="AH4" s="111"/>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
-      <c r="AO4" s="111"/>
-      <c r="AP4" s="112" t="s">
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
+      <c r="AJ4" s="117"/>
+      <c r="AK4" s="117"/>
+      <c r="AL4" s="117"/>
+      <c r="AM4" s="117"/>
+      <c r="AN4" s="117"/>
+      <c r="AO4" s="117"/>
+      <c r="AP4" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="112"/>
+      <c r="AQ4" s="118"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Marzo'!B6</f>
@@ -43259,10 +43259,10 @@
         <f>'Captura Marzo'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="106" t="s">
+      <c r="BB5" s="112" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="106"/>
+      <c r="BC5" s="112"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -45829,16 +45829,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="107" t="s">
+      <c r="AS19" s="113" t="s">
         <v>235</v>
       </c>
-      <c r="AT19" s="107"/>
-      <c r="AU19" s="107"/>
-      <c r="AV19" s="107"/>
-      <c r="AW19" s="107"/>
-      <c r="AX19" s="107"/>
-      <c r="AY19" s="107"/>
-      <c r="AZ19" s="107"/>
+      <c r="AT19" s="113"/>
+      <c r="AU19" s="113"/>
+      <c r="AV19" s="113"/>
+      <c r="AW19" s="113"/>
+      <c r="AX19" s="113"/>
+      <c r="AY19" s="113"/>
+      <c r="AZ19" s="113"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.99283333333333335</v>
@@ -46005,9 +46005,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="108"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="108"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="114"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -46034,11 +46034,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="115" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -46096,12 +46096,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -46116,6 +46110,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="92" priority="5" operator="greaterThanOrEqual">
@@ -46197,62 +46197,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="106" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="113"/>
-      <c r="W1" s="113"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="113"/>
-      <c r="Z1" s="113"/>
-      <c r="AA1" s="113"/>
-      <c r="AB1" s="113"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
+      <c r="Z1" s="106"/>
+      <c r="AA1" s="106"/>
+      <c r="AB1" s="106"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="114" t="s">
+      <c r="AS1" s="107" t="s">
         <v>237</v>
       </c>
-      <c r="AT1" s="114"/>
-      <c r="AU1" s="114"/>
-      <c r="AV1" s="114"/>
-      <c r="AW1" s="114"/>
-      <c r="AX1" s="114"/>
-      <c r="AY1" s="114"/>
-      <c r="AZ1" s="114"/>
-      <c r="BA1" s="114"/>
-      <c r="BB1" s="115" t="s">
+      <c r="AT1" s="107"/>
+      <c r="AU1" s="107"/>
+      <c r="AV1" s="107"/>
+      <c r="AW1" s="107"/>
+      <c r="AX1" s="107"/>
+      <c r="AY1" s="107"/>
+      <c r="AZ1" s="107"/>
+      <c r="BA1" s="107"/>
+      <c r="BB1" s="108" t="s">
         <v>238</v>
       </c>
-      <c r="BC1" s="115"/>
+      <c r="BC1" s="108"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="109" t="s">
         <v>239</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -46261,20 +46261,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="117" t="s">
+      <c r="AT2" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="117"/>
-      <c r="AV2" s="117"/>
+      <c r="AU2" s="110"/>
+      <c r="AV2" s="110"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="118" t="s">
+      <c r="AX2" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="118"/>
-      <c r="AZ2" s="118"/>
-      <c r="BA2" s="118"/>
+      <c r="AY2" s="111"/>
+      <c r="AZ2" s="111"/>
+      <c r="BA2" s="111"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -46322,66 +46322,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="110" t="s">
+      <c r="D4" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110" t="s">
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110" t="s">
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110" t="s">
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
-      <c r="R4" s="110" t="s">
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="110"/>
-      <c r="T4" s="110"/>
-      <c r="U4" s="110" t="s">
+      <c r="S4" s="116"/>
+      <c r="T4" s="116"/>
+      <c r="U4" s="116" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="110"/>
-      <c r="W4" s="111" t="s">
+      <c r="V4" s="116"/>
+      <c r="W4" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="111"/>
-      <c r="Y4" s="110" t="s">
+      <c r="X4" s="117"/>
+      <c r="Y4" s="116" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="110"/>
-      <c r="AA4" s="110"/>
-      <c r="AB4" s="110"/>
-      <c r="AC4" s="110"/>
-      <c r="AD4" s="111" t="s">
+      <c r="Z4" s="116"/>
+      <c r="AA4" s="116"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="116"/>
+      <c r="AD4" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="111"/>
-      <c r="AF4" s="111"/>
-      <c r="AG4" s="111"/>
-      <c r="AH4" s="111"/>
-      <c r="AI4" s="111"/>
-      <c r="AJ4" s="111"/>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
-      <c r="AN4" s="111"/>
-      <c r="AO4" s="111"/>
-      <c r="AP4" s="112" t="s">
+      <c r="AE4" s="117"/>
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="117"/>
+      <c r="AH4" s="117"/>
+      <c r="AI4" s="117"/>
+      <c r="AJ4" s="117"/>
+      <c r="AK4" s="117"/>
+      <c r="AL4" s="117"/>
+      <c r="AM4" s="117"/>
+      <c r="AN4" s="117"/>
+      <c r="AO4" s="117"/>
+      <c r="AP4" s="118" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="112"/>
+      <c r="AQ4" s="118"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Abril'!B6</f>
@@ -46593,10 +46593,10 @@
         <f>'Captura Abril'!AQ7</f>
         <v>0.71000000000000008</v>
       </c>
-      <c r="BB5" s="106" t="s">
+      <c r="BB5" s="112" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="106"/>
+      <c r="BC5" s="112"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -49163,16 +49163,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="107" t="s">
+      <c r="AS19" s="113" t="s">
         <v>240</v>
       </c>
-      <c r="AT19" s="107"/>
-      <c r="AU19" s="107"/>
-      <c r="AV19" s="107"/>
-      <c r="AW19" s="107"/>
-      <c r="AX19" s="107"/>
-      <c r="AY19" s="107"/>
-      <c r="AZ19" s="107"/>
+      <c r="AT19" s="113"/>
+      <c r="AU19" s="113"/>
+      <c r="AV19" s="113"/>
+      <c r="AW19" s="113"/>
+      <c r="AX19" s="113"/>
+      <c r="AY19" s="113"/>
+      <c r="AZ19" s="113"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93466666666666676</v>
@@ -49339,9 +49339,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="108"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="108"/>
+      <c r="A22" s="114"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="114"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -49368,11 +49368,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="115" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -49430,12 +49430,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -49450,6 +49444,12 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="83" priority="5" operator="greaterThanOrEqual">
@@ -49510,26 +49510,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003E33BA48D1B17740BD20DC3C1E7D6897" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c5918174441eb6b55e4531b53824222f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbb49d05-d3df-47ef-b263-f54790ad9dd3" xmlns:ns3="4bae7dba-0f75-4d38-a352-dd7a188b5c30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9432285c6019c8f9bf7f2f5b0ebbd793" ns2:_="" ns3:_="">
     <xsd:import namespace="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
@@ -49776,10 +49756,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5821DFA2-D31E-48EB-BA9F-E1C7FBC547E5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A29B98D3-CD8F-4DEC-9477-47DD9974BEE9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
+    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -49796,20 +49807,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A29B98D3-CD8F-4DEC-9477-47DD9974BEE9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5821DFA2-D31E-48EB-BA9F-E1C7FBC547E5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
-    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
+++ b/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc.sharepoint.com/sites/CharlascortasSSOsemanalesCuyotenango/Shared Documents/General/04. Registros 2026/09. Nivel De Seguridad/NUEVO NIVEL DE SEGURIDAD - 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{1FA93C17-BEC0-435F-87D9-564EB45A6C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87BA2384-B2FA-4BF1-844B-23D0D5315494}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{1FA93C17-BEC0-435F-87D9-564EB45A6C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8B284B2-8E85-4962-ABCB-2B599B4A9BDC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="867" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2067,24 +2067,6 @@
     <xf numFmtId="10" fontId="54" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2106,6 +2088,24 @@
     <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2114,6 +2114,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2129,14 +2138,23 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -2160,24 +2178,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="27" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3214,10 +3214,10 @@
                   <c:v>ETEI</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Jarabes</c:v>
+                  <c:v>Equipos Auxiliares</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Equipos Auxiliares</c:v>
+                  <c:v>Jarabes</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>Centro de Distribucion</c:v>
@@ -3232,16 +3232,16 @@
                   <c:v>Linea 2</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>Alrededores</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Linea 5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>Materias Primas</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>Linea 3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Alrededores</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Almacen de Repuestos</c:v>
@@ -3634,7 +3634,7 @@
                   <c:v>0.89266666666666672</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.6666666666666666E-2</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0.97786666666666677</c:v>
@@ -4306,7 +4306,7 @@
                   <c:v>0.88027777777777783</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.6120133333333333</c:v>
+                  <c:v>0.62001333333333331</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -5043,62 +5043,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="113" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="107" t="s">
+      <c r="AS1" s="114" t="s">
         <v>242</v>
       </c>
-      <c r="AT1" s="107"/>
-      <c r="AU1" s="107"/>
-      <c r="AV1" s="107"/>
-      <c r="AW1" s="107"/>
-      <c r="AX1" s="107"/>
-      <c r="AY1" s="107"/>
-      <c r="AZ1" s="107"/>
-      <c r="BA1" s="107"/>
-      <c r="BB1" s="108" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>243</v>
       </c>
-      <c r="BC1" s="108"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="116" t="s">
         <v>244</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -5107,20 +5107,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="110" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="110"/>
-      <c r="AV2" s="110"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="111" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="111"/>
-      <c r="AZ2" s="111"/>
-      <c r="BA2" s="111"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -5168,66 +5168,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="116"/>
-      <c r="W4" s="117" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="116" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="116"/>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
-      <c r="AC4" s="116"/>
-      <c r="AD4" s="117" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
-      <c r="AO4" s="117"/>
-      <c r="AP4" s="118" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="118"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Mayo'!B6</f>
@@ -5439,10 +5439,10 @@
         <f>'Captura Mayo'!AQ7</f>
         <v>0.69000000000000006</v>
       </c>
-      <c r="BB5" s="112" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="112"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -8009,16 +8009,16 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="113" t="s">
+      <c r="AS19" s="107" t="s">
         <v>245</v>
       </c>
-      <c r="AT19" s="113"/>
-      <c r="AU19" s="113"/>
-      <c r="AV19" s="113"/>
-      <c r="AW19" s="113"/>
-      <c r="AX19" s="113"/>
-      <c r="AY19" s="113"/>
-      <c r="AZ19" s="113"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.87666666666666671</v>
@@ -8185,9 +8185,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="114"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -8214,11 +8214,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="115" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -8276,6 +8276,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -8290,12 +8296,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="74" priority="5" operator="greaterThanOrEqual">
@@ -8377,62 +8377,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="113" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="107" t="s">
+      <c r="AS1" s="114" t="s">
         <v>247</v>
       </c>
-      <c r="AT1" s="107"/>
-      <c r="AU1" s="107"/>
-      <c r="AV1" s="107"/>
-      <c r="AW1" s="107"/>
-      <c r="AX1" s="107"/>
-      <c r="AY1" s="107"/>
-      <c r="AZ1" s="107"/>
-      <c r="BA1" s="107"/>
-      <c r="BB1" s="108" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>248</v>
       </c>
-      <c r="BC1" s="108"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="116" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -8441,20 +8441,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="110" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="110"/>
-      <c r="AV2" s="110"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="111" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="111"/>
-      <c r="AZ2" s="111"/>
-      <c r="BA2" s="111"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -8502,66 +8502,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="116"/>
-      <c r="W4" s="117" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="116" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="116"/>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
-      <c r="AC4" s="116"/>
-      <c r="AD4" s="117" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
-      <c r="AO4" s="117"/>
-      <c r="AP4" s="118" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="118"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Junio'!B6</f>
@@ -8773,10 +8773,10 @@
         <f>'Captura Junio'!AQ7</f>
         <v>0.64000000000000012</v>
       </c>
-      <c r="BB5" s="112" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="112"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -11343,16 +11343,16 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="113" t="s">
+      <c r="AS19" s="107" t="s">
         <v>250</v>
       </c>
-      <c r="AT19" s="113"/>
-      <c r="AU19" s="113"/>
-      <c r="AV19" s="113"/>
-      <c r="AW19" s="113"/>
-      <c r="AX19" s="113"/>
-      <c r="AY19" s="113"/>
-      <c r="AZ19" s="113"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.83357372900851168</v>
@@ -11519,9 +11519,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="114"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -11548,11 +11548,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="115" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -11610,6 +11610,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -11624,12 +11630,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="greaterThanOrEqual">
@@ -11713,62 +11713,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="113" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="107" t="s">
+      <c r="AS1" s="114" t="s">
         <v>252</v>
       </c>
-      <c r="AT1" s="107"/>
-      <c r="AU1" s="107"/>
-      <c r="AV1" s="107"/>
-      <c r="AW1" s="107"/>
-      <c r="AX1" s="107"/>
-      <c r="AY1" s="107"/>
-      <c r="AZ1" s="107"/>
-      <c r="BA1" s="107"/>
-      <c r="BB1" s="108" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>253</v>
       </c>
-      <c r="BC1" s="108"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="116" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -11777,20 +11777,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="110" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="110"/>
-      <c r="AV2" s="110"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="111" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="111"/>
-      <c r="AZ2" s="111"/>
-      <c r="BA2" s="111"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -11838,66 +11838,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="116"/>
-      <c r="W4" s="117" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="116" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="116"/>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
-      <c r="AC4" s="116"/>
-      <c r="AD4" s="117" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
-      <c r="AO4" s="117"/>
-      <c r="AP4" s="118" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="118"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Julio'!B6</f>
@@ -12109,10 +12109,10 @@
         <f>'Captura Julio'!AQ7</f>
         <v>0.64</v>
       </c>
-      <c r="BB5" s="112" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="112"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -14679,16 +14679,16 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="113" t="s">
+      <c r="AS19" s="107" t="s">
         <v>255</v>
       </c>
-      <c r="AT19" s="113"/>
-      <c r="AU19" s="113"/>
-      <c r="AV19" s="113"/>
-      <c r="AW19" s="113"/>
-      <c r="AX19" s="113"/>
-      <c r="AY19" s="113"/>
-      <c r="AZ19" s="113"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.88027777777777783</v>
@@ -14855,9 +14855,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="114"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -14884,11 +14884,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="115" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -14946,6 +14946,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -14960,12 +14966,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="56" priority="5" operator="greaterThanOrEqual">
@@ -15051,62 +15051,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="113" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="107" t="s">
+      <c r="AS1" s="114" t="s">
         <v>257</v>
       </c>
-      <c r="AT1" s="107"/>
-      <c r="AU1" s="107"/>
-      <c r="AV1" s="107"/>
-      <c r="AW1" s="107"/>
-      <c r="AX1" s="107"/>
-      <c r="AY1" s="107"/>
-      <c r="AZ1" s="107"/>
-      <c r="BA1" s="107"/>
-      <c r="BB1" s="108" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>258</v>
       </c>
-      <c r="BC1" s="108"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="116" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -15115,20 +15115,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="110" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="110"/>
-      <c r="AV2" s="110"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="111" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="111"/>
-      <c r="AZ2" s="111"/>
-      <c r="BA2" s="111"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -15176,66 +15176,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="116"/>
-      <c r="W4" s="117" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="116" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="116"/>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
-      <c r="AC4" s="116"/>
-      <c r="AD4" s="117" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
-      <c r="AO4" s="117"/>
-      <c r="AP4" s="118" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="118"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Agosto'!B6</f>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="AU5" s="80">
         <f>'Captura Agosto'!T7</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AV5" s="80">
         <f>'Captura Agosto'!V7</f>
@@ -15445,12 +15445,12 @@
       </c>
       <c r="BA5" s="82">
         <f>'Captura Agosto'!AQ7</f>
-        <v>0.46000000000000008</v>
-      </c>
-      <c r="BB5" s="112" t="s">
+        <v>0.52000000000000013</v>
+      </c>
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="112"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -15693,14 +15693,14 @@
         <v>0.08</v>
       </c>
       <c r="R7" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="88" t="s">
         <v>222</v>
       </c>
       <c r="T7" s="86">
         <f>IF(S7="NO",0,R7*Parametros!$E$10)</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="U7" s="85">
         <v>1</v>
@@ -15774,11 +15774,11 @@
       </c>
       <c r="AP7" s="11">
         <f t="shared" si="3"/>
-        <v>0.56000000000000005</v>
+        <v>0.62000000000000011</v>
       </c>
       <c r="AQ7" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP7-IF(S7="NO",Parametros!$E$17,0))+AC7)-AN7-IF(AO7="SI",Parametros!$E$33,0))</f>
-        <v>0.46000000000000008</v>
+        <v>0.52000000000000013</v>
       </c>
       <c r="AR7" s="58"/>
       <c r="AS7" s="79" t="str">
@@ -16159,7 +16159,7 @@
       </c>
       <c r="AU9" s="80">
         <f>'Captura Agosto'!T11</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AV9" s="80">
         <f>'Captura Agosto'!V11</f>
@@ -16183,7 +16183,7 @@
       </c>
       <c r="BA9" s="82">
         <f>'Captura Agosto'!AQ11</f>
-        <v>0.66</v>
+        <v>0.72000000000000008</v>
       </c>
       <c r="BB9" s="58"/>
       <c r="BC9" s="58"/>
@@ -16433,14 +16433,14 @@
         <v>0</v>
       </c>
       <c r="R11" s="85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="88" t="s">
         <v>222</v>
       </c>
       <c r="T11" s="86">
         <f>IF(S11="NO",0,R11*Parametros!$E$10)</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="U11" s="85">
         <v>1</v>
@@ -16514,11 +16514,11 @@
       </c>
       <c r="AP11" s="11">
         <f t="shared" si="3"/>
-        <v>0.66</v>
+        <v>0.72000000000000008</v>
       </c>
       <c r="AQ11" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP11-IF(S11="NO",Parametros!$E$17,0))+AC11)-AN11-IF(AO11="SI",Parametros!$E$33,0))</f>
-        <v>0.66</v>
+        <v>0.72000000000000008</v>
       </c>
       <c r="AR11" s="58"/>
       <c r="AS11" s="79" t="str">
@@ -18009,19 +18009,19 @@
         <v>0.49125000000000002</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="113" t="s">
+      <c r="AS19" s="107" t="s">
         <v>260</v>
       </c>
-      <c r="AT19" s="113"/>
-      <c r="AU19" s="113"/>
-      <c r="AV19" s="113"/>
-      <c r="AW19" s="113"/>
-      <c r="AX19" s="113"/>
-      <c r="AY19" s="113"/>
-      <c r="AZ19" s="113"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
-        <v>0.6120133333333333</v>
+        <v>0.62001333333333331</v>
       </c>
       <c r="BB19" s="58"/>
       <c r="BC19" s="58"/>
@@ -18185,9 +18185,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="114"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -18214,11 +18214,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="115" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -18260,7 +18260,7 @@
       <c r="AP23" s="93"/>
       <c r="AQ23" s="96">
         <f>AVERAGE(AQ6:AQ20)</f>
-        <v>0.6120133333333333</v>
+        <v>0.62001333333333331</v>
       </c>
       <c r="AR23" s="58"/>
       <c r="AS23" s="58"/>
@@ -18276,6 +18276,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -18290,12 +18296,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="47" priority="5" operator="greaterThanOrEqual">
@@ -18377,62 +18377,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="113" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="107" t="s">
+      <c r="AS1" s="114" t="s">
         <v>262</v>
       </c>
-      <c r="AT1" s="107"/>
-      <c r="AU1" s="107"/>
-      <c r="AV1" s="107"/>
-      <c r="AW1" s="107"/>
-      <c r="AX1" s="107"/>
-      <c r="AY1" s="107"/>
-      <c r="AZ1" s="107"/>
-      <c r="BA1" s="107"/>
-      <c r="BB1" s="108" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>263</v>
       </c>
-      <c r="BC1" s="108"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="116" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -18441,20 +18441,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="110" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="110"/>
-      <c r="AV2" s="110"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="111" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="111"/>
-      <c r="AZ2" s="111"/>
-      <c r="BA2" s="111"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -18502,66 +18502,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="116"/>
-      <c r="W4" s="117" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="116" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="116"/>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
-      <c r="AC4" s="116"/>
-      <c r="AD4" s="117" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
-      <c r="AO4" s="117"/>
-      <c r="AP4" s="118" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="118"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Septiembre'!B6</f>
@@ -18773,10 +18773,10 @@
         <f>'Captura Septiembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="112" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="112"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -21343,16 +21343,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="113" t="s">
+      <c r="AS19" s="107" t="s">
         <v>265</v>
       </c>
-      <c r="AT19" s="113"/>
-      <c r="AU19" s="113"/>
-      <c r="AV19" s="113"/>
-      <c r="AW19" s="113"/>
-      <c r="AX19" s="113"/>
-      <c r="AY19" s="113"/>
-      <c r="AZ19" s="113"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -21519,9 +21519,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="114"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -21548,11 +21548,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="115" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -21610,6 +21610,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -21624,12 +21630,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="38" priority="5" operator="greaterThanOrEqual">
@@ -21711,62 +21711,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="113" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="107" t="s">
+      <c r="AS1" s="114" t="s">
         <v>267</v>
       </c>
-      <c r="AT1" s="107"/>
-      <c r="AU1" s="107"/>
-      <c r="AV1" s="107"/>
-      <c r="AW1" s="107"/>
-      <c r="AX1" s="107"/>
-      <c r="AY1" s="107"/>
-      <c r="AZ1" s="107"/>
-      <c r="BA1" s="107"/>
-      <c r="BB1" s="108" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>268</v>
       </c>
-      <c r="BC1" s="108"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="116" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -21775,20 +21775,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="110" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="110"/>
-      <c r="AV2" s="110"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="111" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="111"/>
-      <c r="AZ2" s="111"/>
-      <c r="BA2" s="111"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -21836,66 +21836,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="116"/>
-      <c r="W4" s="117" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="116" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="116"/>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
-      <c r="AC4" s="116"/>
-      <c r="AD4" s="117" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
-      <c r="AO4" s="117"/>
-      <c r="AP4" s="118" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="118"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Octubre'!B6</f>
@@ -22107,10 +22107,10 @@
         <f>'Captura Octubre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="112" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="112"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -24677,16 +24677,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="113" t="s">
+      <c r="AS19" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="AT19" s="113"/>
-      <c r="AU19" s="113"/>
-      <c r="AV19" s="113"/>
-      <c r="AW19" s="113"/>
-      <c r="AX19" s="113"/>
-      <c r="AY19" s="113"/>
-      <c r="AZ19" s="113"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -24853,9 +24853,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="114"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -24882,11 +24882,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="115" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -24944,6 +24944,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -24958,12 +24964,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="29" priority="5" operator="greaterThanOrEqual">
@@ -25045,62 +25045,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="113" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="107" t="s">
+      <c r="AS1" s="114" t="s">
         <v>272</v>
       </c>
-      <c r="AT1" s="107"/>
-      <c r="AU1" s="107"/>
-      <c r="AV1" s="107"/>
-      <c r="AW1" s="107"/>
-      <c r="AX1" s="107"/>
-      <c r="AY1" s="107"/>
-      <c r="AZ1" s="107"/>
-      <c r="BA1" s="107"/>
-      <c r="BB1" s="108" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>273</v>
       </c>
-      <c r="BC1" s="108"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="116" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -25109,20 +25109,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="110" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="110"/>
-      <c r="AV2" s="110"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="111" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="111"/>
-      <c r="AZ2" s="111"/>
-      <c r="BA2" s="111"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -25170,66 +25170,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="116"/>
-      <c r="W4" s="117" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="116" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="116"/>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
-      <c r="AC4" s="116"/>
-      <c r="AD4" s="117" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
-      <c r="AO4" s="117"/>
-      <c r="AP4" s="118" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="118"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Noviembre'!B6</f>
@@ -25441,10 +25441,10 @@
         <f>'Captura Noviembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="112" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="112"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -28011,16 +28011,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="113" t="s">
+      <c r="AS19" s="107" t="s">
         <v>275</v>
       </c>
-      <c r="AT19" s="113"/>
-      <c r="AU19" s="113"/>
-      <c r="AV19" s="113"/>
-      <c r="AW19" s="113"/>
-      <c r="AX19" s="113"/>
-      <c r="AY19" s="113"/>
-      <c r="AZ19" s="113"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -28187,9 +28187,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="114"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -28216,11 +28216,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="115" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -28278,6 +28278,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -28292,12 +28298,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="20" priority="5" operator="greaterThanOrEqual">
@@ -28379,62 +28379,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="113" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="107" t="s">
+      <c r="AS1" s="114" t="s">
         <v>277</v>
       </c>
-      <c r="AT1" s="107"/>
-      <c r="AU1" s="107"/>
-      <c r="AV1" s="107"/>
-      <c r="AW1" s="107"/>
-      <c r="AX1" s="107"/>
-      <c r="AY1" s="107"/>
-      <c r="AZ1" s="107"/>
-      <c r="BA1" s="107"/>
-      <c r="BB1" s="108" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>278</v>
       </c>
-      <c r="BC1" s="108"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="116" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -28443,20 +28443,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="110" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="110"/>
-      <c r="AV2" s="110"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="111" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="111"/>
-      <c r="AZ2" s="111"/>
-      <c r="BA2" s="111"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -28504,66 +28504,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="116"/>
-      <c r="W4" s="117" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="116" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="116"/>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
-      <c r="AC4" s="116"/>
-      <c r="AD4" s="117" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
-      <c r="AO4" s="117"/>
-      <c r="AP4" s="118" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="118"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Diciembre'!B6</f>
@@ -28775,10 +28775,10 @@
         <f>'Captura Diciembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="112" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="112"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -31345,16 +31345,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="113" t="s">
+      <c r="AS19" s="107" t="s">
         <v>280</v>
       </c>
-      <c r="AT19" s="113"/>
-      <c r="AU19" s="113"/>
-      <c r="AV19" s="113"/>
-      <c r="AW19" s="113"/>
-      <c r="AX19" s="113"/>
-      <c r="AY19" s="113"/>
-      <c r="AZ19" s="113"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -31521,9 +31521,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="114"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -31550,11 +31550,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="115" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -31612,6 +31612,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -31626,12 +31632,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThanOrEqual">
@@ -31705,11 +31705,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="113" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="145" t="s">
@@ -31829,7 +31829,7 @@
       </c>
       <c r="B13" s="97">
         <f>IF(AVERAGE('Captura Agosto'!D6:D20)=0,"",'Captura Agosto'!AQ23)</f>
-        <v>0.6120133333333333</v>
+        <v>0.62001333333333331</v>
       </c>
       <c r="C13" s="12" t="str">
         <f>IF(B13="","",IF(B13&gt;=Parametros!$C$37,"Verde",IF(B13&gt;=Parametros!$C$38,"Amarillo","Rojo")))</f>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="I9" s="10">
         <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
-        <v>0.66</v>
+        <v>0.72000000000000008</v>
       </c>
       <c r="J9" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
@@ -32327,7 +32327,7 @@
       </c>
       <c r="N9" s="102">
         <f t="shared" si="0"/>
-        <v>0.90812500000000007</v>
+        <v>0.91562500000000002</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32649,7 +32649,7 @@
       </c>
       <c r="I15" s="10">
         <f>IFERROR(IF('Captura Agosto'!D7=0,"",'Captura Agosto'!AQ7),"")</f>
-        <v>0.46000000000000008</v>
+        <v>0.52000000000000013</v>
       </c>
       <c r="J15" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D7=0,"",'Captura Septiembre'!AQ7),"")</f>
@@ -32669,7 +32669,7 @@
       </c>
       <c r="N15" s="102">
         <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.76750000000000007</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -32877,7 +32877,7 @@
       </c>
       <c r="I19" s="104">
         <f t="shared" si="1"/>
-        <v>0.61201333333333341</v>
+        <v>0.62001333333333342</v>
       </c>
       <c r="J19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -32940,16 +32940,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -33059,11 +33059,11 @@
       </c>
       <c r="C9" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"T6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"T20"))</f>
-        <v>4.0000000000000001E-3</v>
+        <v>1.2E-2</v>
       </c>
       <c r="D9" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>6.6666666666666666E-2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33224,7 +33224,7 @@
       </c>
       <c r="E24" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ7")*100000-7</f>
-        <v>45993.000000000007</v>
+        <v>51993.000000000015</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -33254,7 +33254,7 @@
       </c>
       <c r="B26" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,4),$E$23:$E$37,0))</f>
-        <v>Jarabes</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C26" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),4)</f>
@@ -33275,7 +33275,7 @@
       </c>
       <c r="B27" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,5),$E$23:$E$37,0))</f>
-        <v>Equipos Auxiliares</v>
+        <v>Jarabes</v>
       </c>
       <c r="C27" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),5)</f>
@@ -33308,7 +33308,7 @@
       </c>
       <c r="E28" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ11")*100000-11</f>
-        <v>65989</v>
+        <v>71989.000000000015</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33380,7 +33380,7 @@
       </c>
       <c r="B32" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,10),$E$23:$E$37,0))</f>
-        <v>Linea 5</v>
+        <v>Alrededores</v>
       </c>
       <c r="C32" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),10)</f>
@@ -33401,7 +33401,7 @@
       </c>
       <c r="B33" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,11),$E$23:$E$37,0))</f>
-        <v>Materias Primas</v>
+        <v>Linea 5</v>
       </c>
       <c r="C33" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),11)</f>
@@ -33422,7 +33422,7 @@
       </c>
       <c r="B34" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,12),$E$23:$E$37,0))</f>
-        <v>Linea 3</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C34" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),12)</f>
@@ -33443,7 +33443,7 @@
       </c>
       <c r="B35" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,13),$E$23:$E$37,0))</f>
-        <v>Alrededores</v>
+        <v>Linea 3</v>
       </c>
       <c r="C35" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),13)</f>
@@ -33539,7 +33539,7 @@
       </c>
       <c r="B44" s="17">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ23")</f>
-        <v>0.6120133333333333</v>
+        <v>0.62001333333333331</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34030,7 +34030,7 @@
       </c>
       <c r="I10" s="10">
         <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
-        <v>0.66</v>
+        <v>0.72000000000000008</v>
       </c>
       <c r="J10" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
@@ -34050,7 +34050,7 @@
       </c>
       <c r="N10" s="102">
         <f t="shared" si="0"/>
-        <v>0.90812500000000007</v>
+        <v>0.91562500000000002</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34486,7 +34486,7 @@
       </c>
       <c r="I18" s="10">
         <f>IFERROR(IF('Captura Agosto'!D7=0,"",'Captura Agosto'!AQ7),"")</f>
-        <v>0.46000000000000008</v>
+        <v>0.52000000000000013</v>
       </c>
       <c r="J18" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D7=0,"",'Captura Septiembre'!AQ7),"")</f>
@@ -34506,7 +34506,7 @@
       </c>
       <c r="N18" s="102">
         <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.76750000000000007</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -34543,7 +34543,7 @@
       </c>
       <c r="I19" s="104">
         <f t="shared" si="1"/>
-        <v>0.61201333333333341</v>
+        <v>0.62001333333333319</v>
       </c>
       <c r="J19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -34603,44 +34603,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="125" t="s">
+      <c r="B2" s="128" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="125"/>
-      <c r="M2" s="125"/>
-      <c r="N2" s="125"/>
-      <c r="O2" s="125"/>
-      <c r="P2" s="125"/>
-      <c r="Q2" s="125"/>
-      <c r="R2" s="125"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128"/>
+      <c r="R2" s="128"/>
     </row>
     <row r="3" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="125"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="125"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="125"/>
-      <c r="K3" s="125"/>
-      <c r="L3" s="125"/>
-      <c r="M3" s="125"/>
-      <c r="N3" s="125"/>
-      <c r="O3" s="125"/>
-      <c r="P3" s="125"/>
-      <c r="Q3" s="125"/>
-      <c r="R3" s="125"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="128"/>
     </row>
     <row r="4" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
@@ -34650,141 +34650,141 @@
         <f>Calculos!$B$2</f>
         <v>Agosto</v>
       </c>
-      <c r="F4" s="126" t="s">
+      <c r="F4" s="129" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="126"/>
-      <c r="K4" s="126"/>
-      <c r="L4" s="126"/>
-      <c r="M4" s="126"/>
-      <c r="N4" s="126"/>
-      <c r="O4" s="126"/>
-      <c r="P4" s="126"/>
-      <c r="Q4" s="126"/>
-      <c r="R4" s="126"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="129"/>
+      <c r="K4" s="129"/>
+      <c r="L4" s="129"/>
+      <c r="M4" s="129"/>
+      <c r="N4" s="129"/>
+      <c r="O4" s="129"/>
+      <c r="P4" s="129"/>
+      <c r="Q4" s="129"/>
+      <c r="R4" s="129"/>
     </row>
     <row r="6" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="127" t="s">
+      <c r="B6" s="130" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="127"/>
-      <c r="D6" s="127"/>
-      <c r="E6" s="127"/>
-      <c r="F6" s="127" t="s">
+      <c r="C6" s="130"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="127"/>
-      <c r="H6" s="127"/>
-      <c r="I6" s="127"/>
-      <c r="J6" s="127" t="s">
+      <c r="G6" s="130"/>
+      <c r="H6" s="130"/>
+      <c r="I6" s="130"/>
+      <c r="J6" s="130" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="127"/>
-      <c r="L6" s="127"/>
-      <c r="M6" s="127" t="s">
+      <c r="K6" s="130"/>
+      <c r="L6" s="130"/>
+      <c r="M6" s="130" t="s">
         <v>64</v>
       </c>
-      <c r="N6" s="127"/>
-      <c r="O6" s="127"/>
-      <c r="P6" s="127" t="s">
+      <c r="N6" s="130"/>
+      <c r="O6" s="130"/>
+      <c r="P6" s="130" t="s">
         <v>65</v>
       </c>
-      <c r="Q6" s="127"/>
-      <c r="R6" s="127"/>
+      <c r="Q6" s="130"/>
+      <c r="R6" s="130"/>
     </row>
     <row r="7" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="127"/>
-      <c r="K7" s="127"/>
-      <c r="L7" s="127"/>
-      <c r="M7" s="127"/>
-      <c r="N7" s="127"/>
-      <c r="O7" s="127"/>
-      <c r="P7" s="127"/>
-      <c r="Q7" s="127"/>
-      <c r="R7" s="127"/>
+      <c r="B7" s="130"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="130"/>
+      <c r="J7" s="130"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="130"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="130"/>
+      <c r="O7" s="130"/>
+      <c r="P7" s="130"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="130"/>
     </row>
     <row r="8" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="128">
+      <c r="B8" s="123">
         <f ca="1">Calculos!B44</f>
-        <v>0.6120133333333333</v>
-      </c>
-      <c r="C8" s="128"/>
-      <c r="D8" s="128"/>
-      <c r="E8" s="128"/>
-      <c r="F8" s="129" t="str">
+        <v>0.62001333333333331</v>
+      </c>
+      <c r="C8" s="123"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="124" t="str">
         <f ca="1">Calculos!B45</f>
         <v>Rojo</v>
       </c>
-      <c r="G8" s="129"/>
-      <c r="H8" s="129"/>
-      <c r="I8" s="129"/>
-      <c r="J8" s="130">
+      <c r="G8" s="124"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="124"/>
+      <c r="J8" s="125">
         <f ca="1">Calculos!B40</f>
         <v>0</v>
       </c>
-      <c r="K8" s="130"/>
-      <c r="L8" s="130"/>
-      <c r="M8" s="123">
+      <c r="K8" s="125"/>
+      <c r="L8" s="125"/>
+      <c r="M8" s="126">
         <f ca="1">Calculos!B41</f>
         <v>0</v>
       </c>
-      <c r="N8" s="123"/>
-      <c r="O8" s="123"/>
-      <c r="P8" s="124">
+      <c r="N8" s="126"/>
+      <c r="O8" s="126"/>
+      <c r="P8" s="127">
         <f ca="1">Calculos!B42</f>
         <v>15</v>
       </c>
-      <c r="Q8" s="124"/>
-      <c r="R8" s="124"/>
+      <c r="Q8" s="127"/>
+      <c r="R8" s="127"/>
     </row>
     <row r="9" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="128"/>
-      <c r="C9" s="128"/>
-      <c r="D9" s="128"/>
-      <c r="E9" s="128"/>
-      <c r="F9" s="129"/>
-      <c r="G9" s="129"/>
-      <c r="H9" s="129"/>
-      <c r="I9" s="129"/>
-      <c r="J9" s="130"/>
-      <c r="K9" s="130"/>
-      <c r="L9" s="130"/>
-      <c r="M9" s="123"/>
-      <c r="N9" s="123"/>
-      <c r="O9" s="123"/>
-      <c r="P9" s="124"/>
-      <c r="Q9" s="124"/>
-      <c r="R9" s="124"/>
+      <c r="B9" s="123"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="123"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="124"/>
+      <c r="I9" s="124"/>
+      <c r="J9" s="125"/>
+      <c r="K9" s="125"/>
+      <c r="L9" s="125"/>
+      <c r="M9" s="126"/>
+      <c r="N9" s="126"/>
+      <c r="O9" s="126"/>
+      <c r="P9" s="127"/>
+      <c r="Q9" s="127"/>
+      <c r="R9" s="127"/>
     </row>
     <row r="10" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="128"/>
-      <c r="C10" s="128"/>
-      <c r="D10" s="128"/>
-      <c r="E10" s="128"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="129"/>
-      <c r="H10" s="129"/>
-      <c r="I10" s="129"/>
-      <c r="J10" s="130"/>
-      <c r="K10" s="130"/>
-      <c r="L10" s="130"/>
-      <c r="M10" s="123"/>
-      <c r="N10" s="123"/>
-      <c r="O10" s="123"/>
-      <c r="P10" s="124"/>
-      <c r="Q10" s="124"/>
-      <c r="R10" s="124"/>
+      <c r="B10" s="123"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="124"/>
+      <c r="I10" s="124"/>
+      <c r="J10" s="125"/>
+      <c r="K10" s="125"/>
+      <c r="L10" s="125"/>
+      <c r="M10" s="126"/>
+      <c r="N10" s="126"/>
+      <c r="O10" s="126"/>
+      <c r="P10" s="127"/>
+      <c r="Q10" s="127"/>
+      <c r="R10" s="127"/>
     </row>
     <row r="12" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
@@ -34869,7 +34869,7 @@
     <row r="17" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="str">
         <f ca="1">Calculos!B26</f>
-        <v>Jarabes</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C17" s="21">
         <f ca="1">Calculos!C26</f>
@@ -34887,7 +34887,7 @@
     <row r="18" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="str">
         <f ca="1">Calculos!B27</f>
-        <v>Equipos Auxiliares</v>
+        <v>Jarabes</v>
       </c>
       <c r="C18" s="21">
         <f ca="1">Calculos!C27</f>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="H18" s="22">
         <f ca="1">Calculos!D9</f>
-        <v>6.6666666666666666E-2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -34961,7 +34961,7 @@
     <row r="23" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="str">
         <f ca="1">Calculos!B32</f>
-        <v>Linea 5</v>
+        <v>Alrededores</v>
       </c>
       <c r="C23" s="21">
         <f ca="1">Calculos!C32</f>
@@ -34971,7 +34971,7 @@
     <row r="24" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="str">
         <f ca="1">Calculos!B33</f>
-        <v>Materias Primas</v>
+        <v>Linea 5</v>
       </c>
       <c r="C24" s="21">
         <f ca="1">Calculos!C33</f>
@@ -34981,7 +34981,7 @@
     <row r="25" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="str">
         <f ca="1">Calculos!B34</f>
-        <v>Linea 3</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C25" s="21">
         <f ca="1">Calculos!C34</f>
@@ -34991,7 +34991,7 @@
     <row r="26" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="str">
         <f ca="1">Calculos!B35</f>
-        <v>Alrededores</v>
+        <v>Linea 3</v>
       </c>
       <c r="C26" s="21">
         <f ca="1">Calculos!C35</f>
@@ -35047,11 +35047,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B8:E10"/>
-    <mergeCell ref="F8:I10"/>
-    <mergeCell ref="J8:L10"/>
     <mergeCell ref="M8:O10"/>
     <mergeCell ref="P8:R10"/>
     <mergeCell ref="B2:R3"/>
@@ -35061,6 +35056,11 @@
     <mergeCell ref="J6:L7"/>
     <mergeCell ref="M6:O7"/>
     <mergeCell ref="P6:R7"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B8:E10"/>
+    <mergeCell ref="F8:I10"/>
+    <mergeCell ref="J8:L10"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -35090,61 +35090,61 @@
   <sheetData>
     <row r="1" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="133" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="142" t="s">
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="142"/>
-      <c r="G2" s="142"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
       <c r="H2" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="143" t="s">
+      <c r="B4" s="135" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="143"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="143"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="143"/>
-      <c r="I4" s="143"/>
-      <c r="J4" s="143"/>
-      <c r="K4" s="143"/>
-      <c r="L4" s="143"/>
-      <c r="M4" s="143"/>
-      <c r="N4" s="143"/>
-      <c r="O4" s="143"/>
-      <c r="P4" s="143"/>
-      <c r="Q4" s="143"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
+      <c r="M4" s="135"/>
+      <c r="N4" s="135"/>
+      <c r="O4" s="135"/>
+      <c r="P4" s="135"/>
+      <c r="Q4" s="135"/>
     </row>
     <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="144" t="str">
+      <c r="B5" s="136" t="str">
         <f>UPPER("Planta Cuyotenango  ·  "&amp;Calculos!$B$2&amp;" 2026  ·  Acumulado Año")</f>
         <v>PLANTA CUYOTENANGO  ·  AGOSTO 2026  ·  ACUMULADO AÑO</v>
       </c>
-      <c r="C5" s="144"/>
-      <c r="D5" s="144"/>
-      <c r="E5" s="144"/>
-      <c r="F5" s="144"/>
-      <c r="G5" s="144"/>
-      <c r="H5" s="144"/>
-      <c r="I5" s="144"/>
-      <c r="J5" s="144"/>
-      <c r="K5" s="144"/>
-      <c r="L5" s="144"/>
-      <c r="M5" s="144"/>
-      <c r="N5" s="144"/>
-      <c r="O5" s="144"/>
-      <c r="P5" s="144"/>
-      <c r="Q5" s="144"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
+      <c r="M5" s="136"/>
+      <c r="N5" s="136"/>
+      <c r="O5" s="136"/>
+      <c r="P5" s="136"/>
+      <c r="Q5" s="136"/>
     </row>
     <row r="6" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="P6" s="28" t="s">
@@ -35155,7 +35155,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="131" t="str">
+      <c r="A7" s="137" t="str">
         <f>UPPER(Calculos!$B$2)</f>
         <v>AGOSTO</v>
       </c>
@@ -35172,13 +35172,13 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="131"/>
-      <c r="G8" s="132">
+      <c r="A8" s="137"/>
+      <c r="G8" s="138">
         <f ca="1">X31</f>
         <v>0</v>
       </c>
-      <c r="H8" s="132"/>
-      <c r="I8" s="132"/>
+      <c r="H8" s="138"/>
+      <c r="I8" s="138"/>
       <c r="P8" s="31" t="s">
         <v>76</v>
       </c>
@@ -35188,15 +35188,15 @@
       </c>
     </row>
     <row r="9" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="131"/>
-      <c r="F9" s="133">
+      <c r="A9" s="137"/>
+      <c r="F9" s="139">
         <f ca="1">X32</f>
         <v>0</v>
       </c>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="133"/>
+      <c r="G9" s="139"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="139"/>
+      <c r="J9" s="139"/>
       <c r="P9" s="31" t="s">
         <v>77</v>
       </c>
@@ -35206,17 +35206,17 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="131"/>
-      <c r="E10" s="134">
+      <c r="A10" s="137"/>
+      <c r="E10" s="140">
         <f ca="1">X33</f>
         <v>0</v>
       </c>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="134"/>
-      <c r="I10" s="134"/>
-      <c r="J10" s="134"/>
-      <c r="K10" s="134"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="140"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="140"/>
       <c r="P10" s="31" t="s">
         <v>78</v>
       </c>
@@ -35226,19 +35226,19 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="131"/>
-      <c r="D11" s="135">
+      <c r="A11" s="137"/>
+      <c r="D11" s="141">
         <f ca="1">X34</f>
         <v>5</v>
       </c>
-      <c r="E11" s="135"/>
-      <c r="F11" s="135"/>
-      <c r="G11" s="135"/>
-      <c r="H11" s="135"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="135"/>
-      <c r="K11" s="135"/>
-      <c r="L11" s="135"/>
+      <c r="E11" s="141"/>
+      <c r="F11" s="141"/>
+      <c r="G11" s="141"/>
+      <c r="H11" s="141"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="141"/>
+      <c r="K11" s="141"/>
+      <c r="L11" s="141"/>
       <c r="P11" s="31" t="s">
         <v>79</v>
       </c>
@@ -35248,21 +35248,21 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="131"/>
-      <c r="C12" s="136">
+      <c r="A12" s="137"/>
+      <c r="C12" s="142">
         <f ca="1">X35</f>
         <v>0</v>
       </c>
-      <c r="D12" s="136"/>
-      <c r="E12" s="136"/>
-      <c r="F12" s="136"/>
-      <c r="G12" s="136"/>
-      <c r="H12" s="136"/>
-      <c r="I12" s="136"/>
-      <c r="J12" s="136"/>
-      <c r="K12" s="136"/>
-      <c r="L12" s="136"/>
-      <c r="M12" s="136"/>
+      <c r="D12" s="142"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="142"/>
+      <c r="L12" s="142"/>
+      <c r="M12" s="142"/>
       <c r="P12" s="31" t="s">
         <v>80</v>
       </c>
@@ -35272,23 +35272,23 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="131"/>
-      <c r="B13" s="137">
+      <c r="A13" s="137"/>
+      <c r="B13" s="143">
         <f ca="1">X36</f>
         <v>27</v>
       </c>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="137"/>
-      <c r="L13" s="137"/>
-      <c r="M13" s="137"/>
-      <c r="N13" s="137"/>
+      <c r="C13" s="143"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="143"/>
+      <c r="F13" s="143"/>
+      <c r="G13" s="143"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143"/>
+      <c r="K13" s="143"/>
+      <c r="L13" s="143"/>
+      <c r="M13" s="143"/>
+      <c r="N13" s="143"/>
       <c r="P13" s="31" t="s">
         <v>81</v>
       </c>
@@ -35298,23 +35298,23 @@
       </c>
     </row>
     <row r="14" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="131"/>
-      <c r="B14" s="138">
+      <c r="A14" s="137"/>
+      <c r="B14" s="144">
         <f ca="1">X37</f>
         <v>196</v>
       </c>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="138"/>
-      <c r="L14" s="138"/>
-      <c r="M14" s="138"/>
-      <c r="N14" s="138"/>
+      <c r="C14" s="144"/>
+      <c r="D14" s="144"/>
+      <c r="E14" s="144"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="144"/>
+      <c r="H14" s="144"/>
+      <c r="I14" s="144"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="144"/>
+      <c r="L14" s="144"/>
+      <c r="M14" s="144"/>
+      <c r="N14" s="144"/>
       <c r="P14" s="31" t="s">
         <v>82</v>
       </c>
@@ -35325,12 +35325,12 @@
     </row>
     <row r="15" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="S16" s="139" t="s">
+      <c r="S16" s="131" t="s">
         <v>83</v>
       </c>
-      <c r="T16" s="139"/>
-      <c r="U16" s="139"/>
-      <c r="V16" s="139"/>
+      <c r="T16" s="131"/>
+      <c r="U16" s="131"/>
+      <c r="V16" s="131"/>
     </row>
     <row r="17" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -35401,42 +35401,42 @@
     <row r="25" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="2:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="140" t="s">
+      <c r="B27" s="132" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="140"/>
-      <c r="D27" s="140"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="140"/>
-      <c r="G27" s="140"/>
-      <c r="H27" s="140"/>
-      <c r="I27" s="140"/>
-      <c r="J27" s="140"/>
-      <c r="K27" s="140"/>
-      <c r="L27" s="140"/>
-      <c r="M27" s="140"/>
-      <c r="N27" s="140"/>
-      <c r="O27" s="140"/>
-      <c r="P27" s="140"/>
-      <c r="Q27" s="140"/>
+      <c r="C27" s="132"/>
+      <c r="D27" s="132"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="132"/>
+      <c r="I27" s="132"/>
+      <c r="J27" s="132"/>
+      <c r="K27" s="132"/>
+      <c r="L27" s="132"/>
+      <c r="M27" s="132"/>
+      <c r="N27" s="132"/>
+      <c r="O27" s="132"/>
+      <c r="P27" s="132"/>
+      <c r="Q27" s="132"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="140"/>
-      <c r="C28" s="140"/>
-      <c r="D28" s="140"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="140"/>
-      <c r="G28" s="140"/>
-      <c r="H28" s="140"/>
-      <c r="I28" s="140"/>
-      <c r="J28" s="140"/>
-      <c r="K28" s="140"/>
-      <c r="L28" s="140"/>
-      <c r="M28" s="140"/>
-      <c r="N28" s="140"/>
-      <c r="O28" s="140"/>
-      <c r="P28" s="140"/>
-      <c r="Q28" s="140"/>
+      <c r="B28" s="132"/>
+      <c r="C28" s="132"/>
+      <c r="D28" s="132"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="132"/>
+      <c r="H28" s="132"/>
+      <c r="I28" s="132"/>
+      <c r="J28" s="132"/>
+      <c r="K28" s="132"/>
+      <c r="L28" s="132"/>
+      <c r="M28" s="132"/>
+      <c r="N28" s="132"/>
+      <c r="O28" s="132"/>
+      <c r="P28" s="132"/>
+      <c r="Q28" s="132"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.35">
       <c r="W30" s="39" t="s">
@@ -35542,12 +35542,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="S16:V16"/>
-    <mergeCell ref="B27:Q28"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="B5:Q5"/>
     <mergeCell ref="A7:A14"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="F9:J9"/>
@@ -35556,6 +35550,12 @@
     <mergeCell ref="C12:M12"/>
     <mergeCell ref="B13:N13"/>
     <mergeCell ref="B14:N14"/>
+    <mergeCell ref="S16:V16"/>
+    <mergeCell ref="B27:Q28"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="B5:Q5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="E2" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -35590,13 +35590,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="113" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="122" t="s">
@@ -36190,62 +36190,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="113" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="107" t="s">
+      <c r="AS1" s="114" t="s">
         <v>161</v>
       </c>
-      <c r="AT1" s="107"/>
-      <c r="AU1" s="107"/>
-      <c r="AV1" s="107"/>
-      <c r="AW1" s="107"/>
-      <c r="AX1" s="107"/>
-      <c r="AY1" s="107"/>
-      <c r="AZ1" s="107"/>
-      <c r="BA1" s="107"/>
-      <c r="BB1" s="108" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>162</v>
       </c>
-      <c r="BC1" s="108"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="116" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -36254,20 +36254,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="110" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="110"/>
-      <c r="AV2" s="110"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="111" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="111"/>
-      <c r="AZ2" s="111"/>
-      <c r="BA2" s="111"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -36315,66 +36315,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="116"/>
-      <c r="W4" s="117" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="116" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="116"/>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
-      <c r="AC4" s="116"/>
-      <c r="AD4" s="117" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
-      <c r="AO4" s="117"/>
-      <c r="AP4" s="118" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="118"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Enero'!B6</f>
@@ -36586,10 +36586,10 @@
         <f>'Captura Enero'!AQ7</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="BB5" s="112" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="112"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -39156,16 +39156,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="113" t="s">
+      <c r="AS19" s="107" t="s">
         <v>224</v>
       </c>
-      <c r="AT19" s="113"/>
-      <c r="AU19" s="113"/>
-      <c r="AV19" s="113"/>
-      <c r="AW19" s="113"/>
-      <c r="AX19" s="113"/>
-      <c r="AY19" s="113"/>
-      <c r="AZ19" s="113"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93030769230769228</v>
@@ -39337,9 +39337,9 @@
       </c>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="114"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -39366,11 +39366,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="115" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -39428,6 +39428,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -39442,12 +39448,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="110" priority="5" operator="greaterThanOrEqual">
@@ -39529,62 +39529,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="113" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="107" t="s">
+      <c r="AS1" s="114" t="s">
         <v>227</v>
       </c>
-      <c r="AT1" s="107"/>
-      <c r="AU1" s="107"/>
-      <c r="AV1" s="107"/>
-      <c r="AW1" s="107"/>
-      <c r="AX1" s="107"/>
-      <c r="AY1" s="107"/>
-      <c r="AZ1" s="107"/>
-      <c r="BA1" s="107"/>
-      <c r="BB1" s="108" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>228</v>
       </c>
-      <c r="BC1" s="108"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="116" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -39593,20 +39593,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="110" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="110"/>
-      <c r="AV2" s="110"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="111" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="111"/>
-      <c r="AZ2" s="111"/>
-      <c r="BA2" s="111"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -39654,66 +39654,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="116"/>
-      <c r="W4" s="117" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="116" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="116"/>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
-      <c r="AC4" s="116"/>
-      <c r="AD4" s="117" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
-      <c r="AO4" s="117"/>
-      <c r="AP4" s="118" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="118"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Febrero'!B6</f>
@@ -39925,10 +39925,10 @@
         <f>'Captura Febrero'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="112" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="112"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -42495,16 +42495,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="113" t="s">
+      <c r="AS19" s="107" t="s">
         <v>230</v>
       </c>
-      <c r="AT19" s="113"/>
-      <c r="AU19" s="113"/>
-      <c r="AV19" s="113"/>
-      <c r="AW19" s="113"/>
-      <c r="AX19" s="113"/>
-      <c r="AY19" s="113"/>
-      <c r="AZ19" s="113"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.9572597670647206</v>
@@ -42671,9 +42671,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="114"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -42700,11 +42700,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="115" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -42762,6 +42762,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -42776,12 +42782,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="101" priority="5" operator="greaterThanOrEqual">
@@ -42863,62 +42863,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="113" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="107" t="s">
+      <c r="AS1" s="114" t="s">
         <v>232</v>
       </c>
-      <c r="AT1" s="107"/>
-      <c r="AU1" s="107"/>
-      <c r="AV1" s="107"/>
-      <c r="AW1" s="107"/>
-      <c r="AX1" s="107"/>
-      <c r="AY1" s="107"/>
-      <c r="AZ1" s="107"/>
-      <c r="BA1" s="107"/>
-      <c r="BB1" s="108" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>233</v>
       </c>
-      <c r="BC1" s="108"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="116" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -42927,20 +42927,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="110" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="110"/>
-      <c r="AV2" s="110"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="111" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="111"/>
-      <c r="AZ2" s="111"/>
-      <c r="BA2" s="111"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -42988,66 +42988,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="116"/>
-      <c r="W4" s="117" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="116" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="116"/>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
-      <c r="AC4" s="116"/>
-      <c r="AD4" s="117" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
-      <c r="AO4" s="117"/>
-      <c r="AP4" s="118" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="118"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Marzo'!B6</f>
@@ -43259,10 +43259,10 @@
         <f>'Captura Marzo'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="112" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="112"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -45829,16 +45829,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="113" t="s">
+      <c r="AS19" s="107" t="s">
         <v>235</v>
       </c>
-      <c r="AT19" s="113"/>
-      <c r="AU19" s="113"/>
-      <c r="AV19" s="113"/>
-      <c r="AW19" s="113"/>
-      <c r="AX19" s="113"/>
-      <c r="AY19" s="113"/>
-      <c r="AZ19" s="113"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.99283333333333335</v>
@@ -46005,9 +46005,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="114"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -46034,11 +46034,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="115" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -46096,6 +46096,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -46110,12 +46116,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="92" priority="5" operator="greaterThanOrEqual">
@@ -46197,62 +46197,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="113" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="106"/>
-      <c r="AB1" s="106"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="107" t="s">
+      <c r="AS1" s="114" t="s">
         <v>237</v>
       </c>
-      <c r="AT1" s="107"/>
-      <c r="AU1" s="107"/>
-      <c r="AV1" s="107"/>
-      <c r="AW1" s="107"/>
-      <c r="AX1" s="107"/>
-      <c r="AY1" s="107"/>
-      <c r="AZ1" s="107"/>
-      <c r="BA1" s="107"/>
-      <c r="BB1" s="108" t="s">
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="114"/>
+      <c r="AX1" s="114"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="114"/>
+      <c r="BA1" s="114"/>
+      <c r="BB1" s="115" t="s">
         <v>238</v>
       </c>
-      <c r="BC1" s="108"/>
+      <c r="BC1" s="115"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="116" t="s">
         <v>239</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -46261,20 +46261,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="110" t="s">
+      <c r="AT2" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="110"/>
-      <c r="AV2" s="110"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="111" t="s">
+      <c r="AX2" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="111"/>
-      <c r="AZ2" s="111"/>
-      <c r="BA2" s="111"/>
+      <c r="AY2" s="118"/>
+      <c r="AZ2" s="118"/>
+      <c r="BA2" s="118"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -46322,66 +46322,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116" t="s">
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116" t="s">
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116" t="s">
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116" t="s">
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116" t="s">
+      <c r="S4" s="110"/>
+      <c r="T4" s="110"/>
+      <c r="U4" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="116"/>
-      <c r="W4" s="117" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="116" t="s">
+      <c r="X4" s="111"/>
+      <c r="Y4" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="116"/>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
-      <c r="AC4" s="116"/>
-      <c r="AD4" s="117" t="s">
+      <c r="Z4" s="110"/>
+      <c r="AA4" s="110"/>
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="117"/>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="117"/>
-      <c r="AH4" s="117"/>
-      <c r="AI4" s="117"/>
-      <c r="AJ4" s="117"/>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
-      <c r="AN4" s="117"/>
-      <c r="AO4" s="117"/>
-      <c r="AP4" s="118" t="s">
+      <c r="AE4" s="111"/>
+      <c r="AF4" s="111"/>
+      <c r="AG4" s="111"/>
+      <c r="AH4" s="111"/>
+      <c r="AI4" s="111"/>
+      <c r="AJ4" s="111"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
+      <c r="AN4" s="111"/>
+      <c r="AO4" s="111"/>
+      <c r="AP4" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="118"/>
+      <c r="AQ4" s="112"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Abril'!B6</f>
@@ -46593,10 +46593,10 @@
         <f>'Captura Abril'!AQ7</f>
         <v>0.71000000000000008</v>
       </c>
-      <c r="BB5" s="112" t="s">
+      <c r="BB5" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="112"/>
+      <c r="BC5" s="106"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -49163,16 +49163,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="113" t="s">
+      <c r="AS19" s="107" t="s">
         <v>240</v>
       </c>
-      <c r="AT19" s="113"/>
-      <c r="AU19" s="113"/>
-      <c r="AV19" s="113"/>
-      <c r="AW19" s="113"/>
-      <c r="AX19" s="113"/>
-      <c r="AY19" s="113"/>
-      <c r="AZ19" s="113"/>
+      <c r="AT19" s="107"/>
+      <c r="AU19" s="107"/>
+      <c r="AV19" s="107"/>
+      <c r="AW19" s="107"/>
+      <c r="AX19" s="107"/>
+      <c r="AY19" s="107"/>
+      <c r="AZ19" s="107"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93466666666666676</v>
@@ -49339,9 +49339,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="114"/>
-      <c r="B22" s="114"/>
-      <c r="C22" s="114"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -49368,11 +49368,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="115" t="s">
+      <c r="A23" s="109" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="115"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -49430,6 +49430,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -49444,12 +49450,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="83" priority="5" operator="greaterThanOrEqual">
@@ -49510,6 +49510,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003E33BA48D1B17740BD20DC3C1E7D6897" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c5918174441eb6b55e4531b53824222f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbb49d05-d3df-47ef-b263-f54790ad9dd3" xmlns:ns3="4bae7dba-0f75-4d38-a352-dd7a188b5c30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9432285c6019c8f9bf7f2f5b0ebbd793" ns2:_="" ns3:_="">
     <xsd:import namespace="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
@@ -49756,27 +49776,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5821DFA2-D31E-48EB-BA9F-E1C7FBC547E5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D19223-1C31-49B9-BB39-EF2DA560B2DA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
+    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A29B98D3-CD8F-4DEC-9477-47DD9974BEE9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -49793,23 +49812,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D19223-1C31-49B9-BB39-EF2DA560B2DA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
-    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5821DFA2-D31E-48EB-BA9F-E1C7FBC547E5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
+++ b/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc.sharepoint.com/sites/CharlascortasSSOsemanalesCuyotenango/Shared Documents/General/04. Registros 2026/09. Nivel De Seguridad/NUEVO NIVEL DE SEGURIDAD - 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="11_425E79763165A80B9DB442E442D9E0A19AA5C458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01200A99-A1A2-48CF-87DF-BB8D59C990EB}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="11_425E79763165A80B9DB442E442D9E0A19AA5C458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83EE0A04-74F0-43B1-AA23-14AF25B1D2FB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="950" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2131,8 +2131,44 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="53" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2144,7 +2180,13 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2160,14 +2202,23 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -2193,62 +2244,11 @@
     <xf numFmtId="1" fontId="27" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4983,38 +4983,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="109"/>
+      <c r="B3" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
     </row>
     <row r="4" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="109"/>
+      <c r="B4" s="121"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
     </row>
     <row r="5" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="109"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="109"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
     </row>
     <row r="6" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="109"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="109"/>
+      <c r="B6" s="121"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="121"/>
     </row>
     <row r="7" spans="2:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="110" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
+      <c r="B7" s="122" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
     </row>
     <row r="10" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
@@ -5068,72 +5068,72 @@
       </c>
     </row>
     <row r="18" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="111" t="s">
+      <c r="B18" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="111"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="111"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="123"/>
     </row>
     <row r="19" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="108" t="s">
+      <c r="C19" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="108"/>
-      <c r="E19" s="108"/>
+      <c r="D19" s="120"/>
+      <c r="E19" s="120"/>
     </row>
     <row r="20" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="108" t="s">
+      <c r="C20" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="108"/>
-      <c r="E20" s="108"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="120"/>
     </row>
     <row r="21" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="108" t="s">
+      <c r="C21" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="108"/>
-      <c r="E21" s="108"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="120"/>
     </row>
     <row r="22" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="108" t="s">
+      <c r="C22" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="108"/>
-      <c r="E22" s="108"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="120"/>
     </row>
     <row r="23" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="108" t="s">
+      <c r="C23" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="108"/>
-      <c r="E23" s="108"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="120"/>
     </row>
     <row r="24" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="108" t="s">
+      <c r="C24" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="108"/>
-      <c r="E24" s="108"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -5174,62 +5174,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="114"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="135" t="s">
+      <c r="AS1" s="115" t="s">
         <v>242</v>
       </c>
-      <c r="AT1" s="135"/>
-      <c r="AU1" s="135"/>
-      <c r="AV1" s="135"/>
-      <c r="AW1" s="135"/>
-      <c r="AX1" s="135"/>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="135"/>
-      <c r="BB1" s="136" t="s">
+      <c r="AT1" s="115"/>
+      <c r="AU1" s="115"/>
+      <c r="AV1" s="115"/>
+      <c r="AW1" s="115"/>
+      <c r="AX1" s="115"/>
+      <c r="AY1" s="115"/>
+      <c r="AZ1" s="115"/>
+      <c r="BA1" s="115"/>
+      <c r="BB1" s="116" t="s">
         <v>243</v>
       </c>
-      <c r="BC1" s="136"/>
+      <c r="BC1" s="116"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="117" t="s">
         <v>244</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -5238,20 +5238,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="138" t="s">
+      <c r="AT2" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="138"/>
-      <c r="AV2" s="138"/>
+      <c r="AU2" s="118"/>
+      <c r="AV2" s="118"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="139" t="s">
+      <c r="AX2" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="139"/>
-      <c r="AZ2" s="139"/>
-      <c r="BA2" s="139"/>
+      <c r="AY2" s="119"/>
+      <c r="AZ2" s="119"/>
+      <c r="BA2" s="119"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -5299,66 +5299,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144" t="s">
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="144"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="144"/>
-      <c r="L4" s="144" t="s">
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="144"/>
-      <c r="N4" s="144"/>
-      <c r="O4" s="144" t="s">
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144" t="s">
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="144"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144" t="s">
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="144"/>
-      <c r="W4" s="145" t="s">
+      <c r="V4" s="111"/>
+      <c r="W4" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="145"/>
-      <c r="Y4" s="144" t="s">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="111" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="144"/>
-      <c r="AA4" s="144"/>
-      <c r="AB4" s="144"/>
-      <c r="AC4" s="144"/>
-      <c r="AD4" s="145" t="s">
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="145"/>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="145"/>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="145"/>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="145"/>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="145"/>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="146" t="s">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112"/>
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="146"/>
+      <c r="AQ4" s="113"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Mayo'!B6</f>
@@ -5570,10 +5570,10 @@
         <f>'Captura Mayo'!AQ7</f>
         <v>0.69000000000000006</v>
       </c>
-      <c r="BB5" s="140" t="s">
+      <c r="BB5" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="140"/>
+      <c r="BC5" s="107"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -8140,16 +8140,16 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="141" t="s">
+      <c r="AS19" s="108" t="s">
         <v>245</v>
       </c>
-      <c r="AT19" s="141"/>
-      <c r="AU19" s="141"/>
-      <c r="AV19" s="141"/>
-      <c r="AW19" s="141"/>
-      <c r="AX19" s="141"/>
-      <c r="AY19" s="141"/>
-      <c r="AZ19" s="141"/>
+      <c r="AT19" s="108"/>
+      <c r="AU19" s="108"/>
+      <c r="AV19" s="108"/>
+      <c r="AW19" s="108"/>
+      <c r="AX19" s="108"/>
+      <c r="AY19" s="108"/>
+      <c r="AZ19" s="108"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.8793333333333333</v>
@@ -8316,9 +8316,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="142"/>
-      <c r="B22" s="142"/>
-      <c r="C22" s="142"/>
+      <c r="A22" s="109"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -8345,11 +8345,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="143" t="s">
+      <c r="A23" s="110" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="143"/>
-      <c r="C23" s="143"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -8407,6 +8407,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -8421,12 +8427,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="74" priority="5" operator="greaterThanOrEqual">
@@ -8508,62 +8508,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="114"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="135" t="s">
+      <c r="AS1" s="115" t="s">
         <v>247</v>
       </c>
-      <c r="AT1" s="135"/>
-      <c r="AU1" s="135"/>
-      <c r="AV1" s="135"/>
-      <c r="AW1" s="135"/>
-      <c r="AX1" s="135"/>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="135"/>
-      <c r="BB1" s="136" t="s">
+      <c r="AT1" s="115"/>
+      <c r="AU1" s="115"/>
+      <c r="AV1" s="115"/>
+      <c r="AW1" s="115"/>
+      <c r="AX1" s="115"/>
+      <c r="AY1" s="115"/>
+      <c r="AZ1" s="115"/>
+      <c r="BA1" s="115"/>
+      <c r="BB1" s="116" t="s">
         <v>248</v>
       </c>
-      <c r="BC1" s="136"/>
+      <c r="BC1" s="116"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="117" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -8572,20 +8572,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="138" t="s">
+      <c r="AT2" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="138"/>
-      <c r="AV2" s="138"/>
+      <c r="AU2" s="118"/>
+      <c r="AV2" s="118"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="139" t="s">
+      <c r="AX2" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="139"/>
-      <c r="AZ2" s="139"/>
-      <c r="BA2" s="139"/>
+      <c r="AY2" s="119"/>
+      <c r="AZ2" s="119"/>
+      <c r="BA2" s="119"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -8633,66 +8633,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144" t="s">
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="144"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="144"/>
-      <c r="L4" s="144" t="s">
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="144"/>
-      <c r="N4" s="144"/>
-      <c r="O4" s="144" t="s">
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144" t="s">
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="144"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144" t="s">
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="144"/>
-      <c r="W4" s="145" t="s">
+      <c r="V4" s="111"/>
+      <c r="W4" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="145"/>
-      <c r="Y4" s="144" t="s">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="111" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="144"/>
-      <c r="AA4" s="144"/>
-      <c r="AB4" s="144"/>
-      <c r="AC4" s="144"/>
-      <c r="AD4" s="145" t="s">
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="145"/>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="145"/>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="145"/>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="145"/>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="145"/>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="146" t="s">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112"/>
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="146"/>
+      <c r="AQ4" s="113"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Junio'!B6</f>
@@ -8904,10 +8904,10 @@
         <f>'Captura Junio'!AQ7</f>
         <v>0.64000000000000012</v>
       </c>
-      <c r="BB5" s="140" t="s">
+      <c r="BB5" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="140"/>
+      <c r="BC5" s="107"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -11474,16 +11474,16 @@
         <v>0.71500000000000008</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="141" t="s">
+      <c r="AS19" s="108" t="s">
         <v>250</v>
       </c>
-      <c r="AT19" s="141"/>
-      <c r="AU19" s="141"/>
-      <c r="AV19" s="141"/>
-      <c r="AW19" s="141"/>
-      <c r="AX19" s="141"/>
-      <c r="AY19" s="141"/>
-      <c r="AZ19" s="141"/>
+      <c r="AT19" s="108"/>
+      <c r="AU19" s="108"/>
+      <c r="AV19" s="108"/>
+      <c r="AW19" s="108"/>
+      <c r="AX19" s="108"/>
+      <c r="AY19" s="108"/>
+      <c r="AZ19" s="108"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.83357372900851168</v>
@@ -11650,9 +11650,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="142"/>
-      <c r="B22" s="142"/>
-      <c r="C22" s="142"/>
+      <c r="A22" s="109"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -11679,11 +11679,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="143" t="s">
+      <c r="A23" s="110" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="143"/>
-      <c r="C23" s="143"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -11741,6 +11741,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -11755,12 +11761,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="65" priority="5" operator="greaterThanOrEqual">
@@ -11844,62 +11844,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="114"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="135" t="s">
+      <c r="AS1" s="115" t="s">
         <v>252</v>
       </c>
-      <c r="AT1" s="135"/>
-      <c r="AU1" s="135"/>
-      <c r="AV1" s="135"/>
-      <c r="AW1" s="135"/>
-      <c r="AX1" s="135"/>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="135"/>
-      <c r="BB1" s="136" t="s">
+      <c r="AT1" s="115"/>
+      <c r="AU1" s="115"/>
+      <c r="AV1" s="115"/>
+      <c r="AW1" s="115"/>
+      <c r="AX1" s="115"/>
+      <c r="AY1" s="115"/>
+      <c r="AZ1" s="115"/>
+      <c r="BA1" s="115"/>
+      <c r="BB1" s="116" t="s">
         <v>253</v>
       </c>
-      <c r="BC1" s="136"/>
+      <c r="BC1" s="116"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="117" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -11908,20 +11908,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="138" t="s">
+      <c r="AT2" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="138"/>
-      <c r="AV2" s="138"/>
+      <c r="AU2" s="118"/>
+      <c r="AV2" s="118"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="139" t="s">
+      <c r="AX2" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="139"/>
-      <c r="AZ2" s="139"/>
-      <c r="BA2" s="139"/>
+      <c r="AY2" s="119"/>
+      <c r="AZ2" s="119"/>
+      <c r="BA2" s="119"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -11969,66 +11969,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144" t="s">
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="144"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="144"/>
-      <c r="L4" s="144" t="s">
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="144"/>
-      <c r="N4" s="144"/>
-      <c r="O4" s="144" t="s">
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144" t="s">
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="144"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144" t="s">
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="144"/>
-      <c r="W4" s="145" t="s">
+      <c r="V4" s="111"/>
+      <c r="W4" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="145"/>
-      <c r="Y4" s="144" t="s">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="111" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="144"/>
-      <c r="AA4" s="144"/>
-      <c r="AB4" s="144"/>
-      <c r="AC4" s="144"/>
-      <c r="AD4" s="145" t="s">
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="145"/>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="145"/>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="145"/>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="145"/>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="145"/>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="146" t="s">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112"/>
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="146"/>
+      <c r="AQ4" s="113"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Julio'!B6</f>
@@ -12240,10 +12240,10 @@
         <f>'Captura Julio'!AQ7</f>
         <v>0.64</v>
       </c>
-      <c r="BB5" s="140" t="s">
+      <c r="BB5" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="140"/>
+      <c r="BC5" s="107"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -14810,16 +14810,16 @@
         <v>0.73750000000000004</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="141" t="s">
+      <c r="AS19" s="108" t="s">
         <v>255</v>
       </c>
-      <c r="AT19" s="141"/>
-      <c r="AU19" s="141"/>
-      <c r="AV19" s="141"/>
-      <c r="AW19" s="141"/>
-      <c r="AX19" s="141"/>
-      <c r="AY19" s="141"/>
-      <c r="AZ19" s="141"/>
+      <c r="AT19" s="108"/>
+      <c r="AU19" s="108"/>
+      <c r="AV19" s="108"/>
+      <c r="AW19" s="108"/>
+      <c r="AX19" s="108"/>
+      <c r="AY19" s="108"/>
+      <c r="AZ19" s="108"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.88027777777777783</v>
@@ -14986,9 +14986,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="142"/>
-      <c r="B22" s="142"/>
-      <c r="C22" s="142"/>
+      <c r="A22" s="109"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -15015,11 +15015,11 @@
       <c r="AV22" s="95"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="143" t="s">
+      <c r="A23" s="110" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="143"/>
-      <c r="C23" s="143"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -15077,6 +15077,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -15091,12 +15097,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="56" priority="5" operator="greaterThanOrEqual">
@@ -15182,62 +15182,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="114"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="135" t="s">
+      <c r="AS1" s="115" t="s">
         <v>257</v>
       </c>
-      <c r="AT1" s="135"/>
-      <c r="AU1" s="135"/>
-      <c r="AV1" s="135"/>
-      <c r="AW1" s="135"/>
-      <c r="AX1" s="135"/>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="135"/>
-      <c r="BB1" s="136" t="s">
+      <c r="AT1" s="115"/>
+      <c r="AU1" s="115"/>
+      <c r="AV1" s="115"/>
+      <c r="AW1" s="115"/>
+      <c r="AX1" s="115"/>
+      <c r="AY1" s="115"/>
+      <c r="AZ1" s="115"/>
+      <c r="BA1" s="115"/>
+      <c r="BB1" s="116" t="s">
         <v>258</v>
       </c>
-      <c r="BC1" s="136"/>
+      <c r="BC1" s="116"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="117" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -15246,20 +15246,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="138" t="s">
+      <c r="AT2" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="138"/>
-      <c r="AV2" s="138"/>
+      <c r="AU2" s="118"/>
+      <c r="AV2" s="118"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="139" t="s">
+      <c r="AX2" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="139"/>
-      <c r="AZ2" s="139"/>
-      <c r="BA2" s="139"/>
+      <c r="AY2" s="119"/>
+      <c r="AZ2" s="119"/>
+      <c r="BA2" s="119"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -15307,66 +15307,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144" t="s">
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="144"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="144"/>
-      <c r="L4" s="144" t="s">
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="144"/>
-      <c r="N4" s="144"/>
-      <c r="O4" s="144" t="s">
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144" t="s">
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="144"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144" t="s">
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="144"/>
-      <c r="W4" s="145" t="s">
+      <c r="V4" s="111"/>
+      <c r="W4" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="145"/>
-      <c r="Y4" s="144" t="s">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="111" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="144"/>
-      <c r="AA4" s="144"/>
-      <c r="AB4" s="144"/>
-      <c r="AC4" s="144"/>
-      <c r="AD4" s="145" t="s">
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="145"/>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="145"/>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="145"/>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="145"/>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="145"/>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="146" t="s">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112"/>
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="146"/>
+      <c r="AQ4" s="113"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Agosto'!B6</f>
@@ -15578,10 +15578,10 @@
         <f>'Captura Agosto'!AQ7</f>
         <v>0.64449999999999996</v>
       </c>
-      <c r="BB5" s="140" t="s">
+      <c r="BB5" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="140"/>
+      <c r="BC5" s="107"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -16968,7 +16968,7 @@
         <v>0</v>
       </c>
       <c r="Y13" s="87">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z13" s="87">
         <v>16</v>
@@ -17154,7 +17154,7 @@
         <v>0</v>
       </c>
       <c r="Y14" s="87">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z14" s="87">
         <v>19</v>
@@ -18148,16 +18148,16 @@
         <v>0.88124999999999998</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="141" t="s">
+      <c r="AS19" s="108" t="s">
         <v>260</v>
       </c>
-      <c r="AT19" s="141"/>
-      <c r="AU19" s="141"/>
-      <c r="AV19" s="141"/>
-      <c r="AW19" s="141"/>
-      <c r="AX19" s="141"/>
-      <c r="AY19" s="141"/>
-      <c r="AZ19" s="141"/>
+      <c r="AT19" s="108"/>
+      <c r="AU19" s="108"/>
+      <c r="AV19" s="108"/>
+      <c r="AW19" s="108"/>
+      <c r="AX19" s="108"/>
+      <c r="AY19" s="108"/>
+      <c r="AZ19" s="108"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.85630933333333326</v>
@@ -18248,7 +18248,7 @@
         <v>0.2</v>
       </c>
       <c r="Y20" s="87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z20" s="87">
         <v>5</v>
@@ -18324,9 +18324,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="142"/>
-      <c r="B22" s="142"/>
-      <c r="C22" s="142"/>
+      <c r="A22" s="109"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -18353,11 +18353,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="143" t="s">
+      <c r="A23" s="110" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="143"/>
-      <c r="C23" s="143"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -18415,6 +18415,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -18429,12 +18435,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="47" priority="5" operator="greaterThanOrEqual">
@@ -18517,62 +18517,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="114"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="135" t="s">
+      <c r="AS1" s="115" t="s">
         <v>262</v>
       </c>
-      <c r="AT1" s="135"/>
-      <c r="AU1" s="135"/>
-      <c r="AV1" s="135"/>
-      <c r="AW1" s="135"/>
-      <c r="AX1" s="135"/>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="135"/>
-      <c r="BB1" s="136" t="s">
+      <c r="AT1" s="115"/>
+      <c r="AU1" s="115"/>
+      <c r="AV1" s="115"/>
+      <c r="AW1" s="115"/>
+      <c r="AX1" s="115"/>
+      <c r="AY1" s="115"/>
+      <c r="AZ1" s="115"/>
+      <c r="BA1" s="115"/>
+      <c r="BB1" s="116" t="s">
         <v>263</v>
       </c>
-      <c r="BC1" s="136"/>
+      <c r="BC1" s="116"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="117" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -18581,20 +18581,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="138" t="s">
+      <c r="AT2" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="138"/>
-      <c r="AV2" s="138"/>
+      <c r="AU2" s="118"/>
+      <c r="AV2" s="118"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="139" t="s">
+      <c r="AX2" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="139"/>
-      <c r="AZ2" s="139"/>
-      <c r="BA2" s="139"/>
+      <c r="AY2" s="119"/>
+      <c r="AZ2" s="119"/>
+      <c r="BA2" s="119"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -18642,66 +18642,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144" t="s">
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="144"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="144"/>
-      <c r="L4" s="144" t="s">
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="144"/>
-      <c r="N4" s="144"/>
-      <c r="O4" s="144" t="s">
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144" t="s">
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="144"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144" t="s">
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="144"/>
-      <c r="W4" s="145" t="s">
+      <c r="V4" s="111"/>
+      <c r="W4" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="145"/>
-      <c r="Y4" s="144" t="s">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="111" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="144"/>
-      <c r="AA4" s="144"/>
-      <c r="AB4" s="144"/>
-      <c r="AC4" s="144"/>
-      <c r="AD4" s="145" t="s">
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="145"/>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="145"/>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="145"/>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="145"/>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="145"/>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="146" t="s">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112"/>
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="146"/>
+      <c r="AQ4" s="113"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Septiembre'!B6</f>
@@ -18913,10 +18913,10 @@
         <f>'Captura Septiembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="140" t="s">
+      <c r="BB5" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="140"/>
+      <c r="BC5" s="107"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -21483,16 +21483,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="141" t="s">
+      <c r="AS19" s="108" t="s">
         <v>265</v>
       </c>
-      <c r="AT19" s="141"/>
-      <c r="AU19" s="141"/>
-      <c r="AV19" s="141"/>
-      <c r="AW19" s="141"/>
-      <c r="AX19" s="141"/>
-      <c r="AY19" s="141"/>
-      <c r="AZ19" s="141"/>
+      <c r="AT19" s="108"/>
+      <c r="AU19" s="108"/>
+      <c r="AV19" s="108"/>
+      <c r="AW19" s="108"/>
+      <c r="AX19" s="108"/>
+      <c r="AY19" s="108"/>
+      <c r="AZ19" s="108"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -21659,9 +21659,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="142"/>
-      <c r="B22" s="142"/>
-      <c r="C22" s="142"/>
+      <c r="A22" s="109"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -21688,11 +21688,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="143" t="s">
+      <c r="A23" s="110" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="143"/>
-      <c r="C23" s="143"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -21750,6 +21750,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -21764,12 +21770,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="38" priority="5" operator="greaterThanOrEqual">
@@ -21851,62 +21851,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="114"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="135" t="s">
+      <c r="AS1" s="115" t="s">
         <v>267</v>
       </c>
-      <c r="AT1" s="135"/>
-      <c r="AU1" s="135"/>
-      <c r="AV1" s="135"/>
-      <c r="AW1" s="135"/>
-      <c r="AX1" s="135"/>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="135"/>
-      <c r="BB1" s="136" t="s">
+      <c r="AT1" s="115"/>
+      <c r="AU1" s="115"/>
+      <c r="AV1" s="115"/>
+      <c r="AW1" s="115"/>
+      <c r="AX1" s="115"/>
+      <c r="AY1" s="115"/>
+      <c r="AZ1" s="115"/>
+      <c r="BA1" s="115"/>
+      <c r="BB1" s="116" t="s">
         <v>268</v>
       </c>
-      <c r="BC1" s="136"/>
+      <c r="BC1" s="116"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="117" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -21915,20 +21915,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="138" t="s">
+      <c r="AT2" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="138"/>
-      <c r="AV2" s="138"/>
+      <c r="AU2" s="118"/>
+      <c r="AV2" s="118"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="139" t="s">
+      <c r="AX2" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="139"/>
-      <c r="AZ2" s="139"/>
-      <c r="BA2" s="139"/>
+      <c r="AY2" s="119"/>
+      <c r="AZ2" s="119"/>
+      <c r="BA2" s="119"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -21976,66 +21976,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144" t="s">
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="144"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="144"/>
-      <c r="L4" s="144" t="s">
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="144"/>
-      <c r="N4" s="144"/>
-      <c r="O4" s="144" t="s">
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144" t="s">
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="144"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144" t="s">
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="144"/>
-      <c r="W4" s="145" t="s">
+      <c r="V4" s="111"/>
+      <c r="W4" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="145"/>
-      <c r="Y4" s="144" t="s">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="111" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="144"/>
-      <c r="AA4" s="144"/>
-      <c r="AB4" s="144"/>
-      <c r="AC4" s="144"/>
-      <c r="AD4" s="145" t="s">
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="145"/>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="145"/>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="145"/>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="145"/>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="145"/>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="146" t="s">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112"/>
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="146"/>
+      <c r="AQ4" s="113"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Octubre'!B6</f>
@@ -22247,10 +22247,10 @@
         <f>'Captura Octubre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="140" t="s">
+      <c r="BB5" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="140"/>
+      <c r="BC5" s="107"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -24817,16 +24817,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="141" t="s">
+      <c r="AS19" s="108" t="s">
         <v>270</v>
       </c>
-      <c r="AT19" s="141"/>
-      <c r="AU19" s="141"/>
-      <c r="AV19" s="141"/>
-      <c r="AW19" s="141"/>
-      <c r="AX19" s="141"/>
-      <c r="AY19" s="141"/>
-      <c r="AZ19" s="141"/>
+      <c r="AT19" s="108"/>
+      <c r="AU19" s="108"/>
+      <c r="AV19" s="108"/>
+      <c r="AW19" s="108"/>
+      <c r="AX19" s="108"/>
+      <c r="AY19" s="108"/>
+      <c r="AZ19" s="108"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -24993,9 +24993,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="142"/>
-      <c r="B22" s="142"/>
-      <c r="C22" s="142"/>
+      <c r="A22" s="109"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -25022,11 +25022,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="143" t="s">
+      <c r="A23" s="110" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="143"/>
-      <c r="C23" s="143"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -25084,6 +25084,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -25098,12 +25104,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="29" priority="5" operator="greaterThanOrEqual">
@@ -25185,62 +25185,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="114"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="135" t="s">
+      <c r="AS1" s="115" t="s">
         <v>272</v>
       </c>
-      <c r="AT1" s="135"/>
-      <c r="AU1" s="135"/>
-      <c r="AV1" s="135"/>
-      <c r="AW1" s="135"/>
-      <c r="AX1" s="135"/>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="135"/>
-      <c r="BB1" s="136" t="s">
+      <c r="AT1" s="115"/>
+      <c r="AU1" s="115"/>
+      <c r="AV1" s="115"/>
+      <c r="AW1" s="115"/>
+      <c r="AX1" s="115"/>
+      <c r="AY1" s="115"/>
+      <c r="AZ1" s="115"/>
+      <c r="BA1" s="115"/>
+      <c r="BB1" s="116" t="s">
         <v>273</v>
       </c>
-      <c r="BC1" s="136"/>
+      <c r="BC1" s="116"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="117" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -25249,20 +25249,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="138" t="s">
+      <c r="AT2" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="138"/>
-      <c r="AV2" s="138"/>
+      <c r="AU2" s="118"/>
+      <c r="AV2" s="118"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="139" t="s">
+      <c r="AX2" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="139"/>
-      <c r="AZ2" s="139"/>
-      <c r="BA2" s="139"/>
+      <c r="AY2" s="119"/>
+      <c r="AZ2" s="119"/>
+      <c r="BA2" s="119"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -25310,66 +25310,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144" t="s">
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="144"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="144"/>
-      <c r="L4" s="144" t="s">
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="144"/>
-      <c r="N4" s="144"/>
-      <c r="O4" s="144" t="s">
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144" t="s">
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="144"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144" t="s">
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="144"/>
-      <c r="W4" s="145" t="s">
+      <c r="V4" s="111"/>
+      <c r="W4" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="145"/>
-      <c r="Y4" s="144" t="s">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="111" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="144"/>
-      <c r="AA4" s="144"/>
-      <c r="AB4" s="144"/>
-      <c r="AC4" s="144"/>
-      <c r="AD4" s="145" t="s">
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="145"/>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="145"/>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="145"/>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="145"/>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="145"/>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="146" t="s">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112"/>
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="146"/>
+      <c r="AQ4" s="113"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Noviembre'!B6</f>
@@ -25581,10 +25581,10 @@
         <f>'Captura Noviembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="140" t="s">
+      <c r="BB5" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="140"/>
+      <c r="BC5" s="107"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -28151,16 +28151,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="141" t="s">
+      <c r="AS19" s="108" t="s">
         <v>275</v>
       </c>
-      <c r="AT19" s="141"/>
-      <c r="AU19" s="141"/>
-      <c r="AV19" s="141"/>
-      <c r="AW19" s="141"/>
-      <c r="AX19" s="141"/>
-      <c r="AY19" s="141"/>
-      <c r="AZ19" s="141"/>
+      <c r="AT19" s="108"/>
+      <c r="AU19" s="108"/>
+      <c r="AV19" s="108"/>
+      <c r="AW19" s="108"/>
+      <c r="AX19" s="108"/>
+      <c r="AY19" s="108"/>
+      <c r="AZ19" s="108"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -28327,9 +28327,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="142"/>
-      <c r="B22" s="142"/>
-      <c r="C22" s="142"/>
+      <c r="A22" s="109"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -28356,11 +28356,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="143" t="s">
+      <c r="A23" s="110" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="143"/>
-      <c r="C23" s="143"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -28418,6 +28418,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -28432,12 +28438,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="20" priority="5" operator="greaterThanOrEqual">
@@ -28519,62 +28519,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="114"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="135" t="s">
+      <c r="AS1" s="115" t="s">
         <v>277</v>
       </c>
-      <c r="AT1" s="135"/>
-      <c r="AU1" s="135"/>
-      <c r="AV1" s="135"/>
-      <c r="AW1" s="135"/>
-      <c r="AX1" s="135"/>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="135"/>
-      <c r="BB1" s="136" t="s">
+      <c r="AT1" s="115"/>
+      <c r="AU1" s="115"/>
+      <c r="AV1" s="115"/>
+      <c r="AW1" s="115"/>
+      <c r="AX1" s="115"/>
+      <c r="AY1" s="115"/>
+      <c r="AZ1" s="115"/>
+      <c r="BA1" s="115"/>
+      <c r="BB1" s="116" t="s">
         <v>278</v>
       </c>
-      <c r="BC1" s="136"/>
+      <c r="BC1" s="116"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="117" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -28583,20 +28583,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="138" t="s">
+      <c r="AT2" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="138"/>
-      <c r="AV2" s="138"/>
+      <c r="AU2" s="118"/>
+      <c r="AV2" s="118"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="139" t="s">
+      <c r="AX2" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="139"/>
-      <c r="AZ2" s="139"/>
-      <c r="BA2" s="139"/>
+      <c r="AY2" s="119"/>
+      <c r="AZ2" s="119"/>
+      <c r="BA2" s="119"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -28644,66 +28644,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144" t="s">
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="144"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="144"/>
-      <c r="L4" s="144" t="s">
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="144"/>
-      <c r="N4" s="144"/>
-      <c r="O4" s="144" t="s">
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144" t="s">
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="144"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144" t="s">
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="144"/>
-      <c r="W4" s="145" t="s">
+      <c r="V4" s="111"/>
+      <c r="W4" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="145"/>
-      <c r="Y4" s="144" t="s">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="111" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="144"/>
-      <c r="AA4" s="144"/>
-      <c r="AB4" s="144"/>
-      <c r="AC4" s="144"/>
-      <c r="AD4" s="145" t="s">
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="145"/>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="145"/>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="145"/>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="145"/>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="145"/>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="146" t="s">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112"/>
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="146"/>
+      <c r="AQ4" s="113"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Diciembre'!B6</f>
@@ -28915,10 +28915,10 @@
         <f>'Captura Diciembre'!AQ7</f>
         <v>0.25</v>
       </c>
-      <c r="BB5" s="140" t="s">
+      <c r="BB5" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="140"/>
+      <c r="BC5" s="107"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -31485,16 +31485,16 @@
         <v>0.25</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="141" t="s">
+      <c r="AS19" s="108" t="s">
         <v>280</v>
       </c>
-      <c r="AT19" s="141"/>
-      <c r="AU19" s="141"/>
-      <c r="AV19" s="141"/>
-      <c r="AW19" s="141"/>
-      <c r="AX19" s="141"/>
-      <c r="AY19" s="141"/>
-      <c r="AZ19" s="141"/>
+      <c r="AT19" s="108"/>
+      <c r="AU19" s="108"/>
+      <c r="AV19" s="108"/>
+      <c r="AW19" s="108"/>
+      <c r="AX19" s="108"/>
+      <c r="AY19" s="108"/>
+      <c r="AZ19" s="108"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.25</v>
@@ -31661,9 +31661,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="142"/>
-      <c r="B22" s="142"/>
-      <c r="C22" s="142"/>
+      <c r="A22" s="109"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -31690,11 +31690,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="143" t="s">
+      <c r="A23" s="110" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="143"/>
-      <c r="C23" s="143"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -31752,6 +31752,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -31766,12 +31772,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThanOrEqual">
@@ -31845,21 +31845,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>281</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="147" t="s">
+      <c r="A3" s="146" t="s">
         <v>282</v>
       </c>
-      <c r="B3" s="147"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="147"/>
+      <c r="B3" s="146"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="146"/>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -32067,22 +32067,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="147" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="99" t="s">
@@ -33080,16 +33080,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
@@ -33100,12 +33100,12 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="111" t="s">
+      <c r="A3" s="123" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="111"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
     </row>
     <row r="4" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
@@ -33241,10 +33241,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="111" t="s">
+      <c r="A13" s="123" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="111"/>
+      <c r="B13" s="123"/>
     </row>
     <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
@@ -33301,12 +33301,12 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="111" t="s">
+      <c r="A21" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="111"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="111"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="123"/>
     </row>
     <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
@@ -33641,10 +33641,10 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="111" t="s">
+      <c r="A39" s="123" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="111"/>
+      <c r="B39" s="123"/>
     </row>
     <row r="40" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="16" t="s">
@@ -33735,22 +33735,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="147" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
     </row>
     <row r="3" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="99" t="s">
@@ -34805,44 +34805,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="115" t="s">
+      <c r="B2" s="129" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
-      <c r="M2" s="115"/>
-      <c r="N2" s="115"/>
-      <c r="O2" s="115"/>
-      <c r="P2" s="115"/>
-      <c r="Q2" s="115"/>
-      <c r="R2" s="115"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
     </row>
     <row r="3" spans="2:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="115"/>
-      <c r="L3" s="115"/>
-      <c r="M3" s="115"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="Q3" s="115"/>
-      <c r="R3" s="115"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="129"/>
+      <c r="O3" s="129"/>
+      <c r="P3" s="129"/>
+      <c r="Q3" s="129"/>
+      <c r="R3" s="129"/>
     </row>
     <row r="4" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="19" t="s">
@@ -34852,153 +34852,153 @@
         <f>Calculos!$B$2</f>
         <v>Agosto</v>
       </c>
-      <c r="F4" s="116" t="s">
+      <c r="F4" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116"/>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="130"/>
+      <c r="O4" s="130"/>
+      <c r="P4" s="130"/>
+      <c r="Q4" s="130"/>
+      <c r="R4" s="130"/>
     </row>
     <row r="6" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="117" t="s">
+      <c r="B6" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="117" t="s">
+      <c r="C6" s="131"/>
+      <c r="D6" s="131"/>
+      <c r="E6" s="131"/>
+      <c r="F6" s="131" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="117"/>
-      <c r="J6" s="117" t="s">
+      <c r="G6" s="131"/>
+      <c r="H6" s="131"/>
+      <c r="I6" s="131"/>
+      <c r="J6" s="131" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="117"/>
-      <c r="L6" s="117"/>
-      <c r="M6" s="117" t="s">
+      <c r="K6" s="131"/>
+      <c r="L6" s="131"/>
+      <c r="M6" s="131" t="s">
         <v>64</v>
       </c>
-      <c r="N6" s="117"/>
-      <c r="O6" s="117"/>
-      <c r="P6" s="117" t="s">
+      <c r="N6" s="131"/>
+      <c r="O6" s="131"/>
+      <c r="P6" s="131" t="s">
         <v>65</v>
       </c>
-      <c r="Q6" s="117"/>
-      <c r="R6" s="117"/>
+      <c r="Q6" s="131"/>
+      <c r="R6" s="131"/>
     </row>
     <row r="7" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="117"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="117"/>
-      <c r="J7" s="117"/>
-      <c r="K7" s="117"/>
-      <c r="L7" s="117"/>
-      <c r="M7" s="117"/>
-      <c r="N7" s="117"/>
-      <c r="O7" s="117"/>
-      <c r="P7" s="117"/>
-      <c r="Q7" s="117"/>
-      <c r="R7" s="117"/>
+      <c r="B7" s="131"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="131"/>
+      <c r="J7" s="131"/>
+      <c r="K7" s="131"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="131"/>
+      <c r="N7" s="131"/>
+      <c r="O7" s="131"/>
+      <c r="P7" s="131"/>
+      <c r="Q7" s="131"/>
+      <c r="R7" s="131"/>
     </row>
     <row r="8" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="118">
+      <c r="B8" s="124">
         <f ca="1">Calculos!B44</f>
         <v>0.85630933333333326</v>
       </c>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="119" t="str">
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="125" t="str">
         <f ca="1">Calculos!B45</f>
         <v>Amarillo</v>
       </c>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120">
+      <c r="G8" s="125"/>
+      <c r="H8" s="125"/>
+      <c r="I8" s="125"/>
+      <c r="J8" s="126">
         <f ca="1">Calculos!B40</f>
         <v>0</v>
       </c>
-      <c r="K8" s="120"/>
-      <c r="L8" s="120"/>
-      <c r="M8" s="113">
+      <c r="K8" s="126"/>
+      <c r="L8" s="126"/>
+      <c r="M8" s="127">
         <f ca="1">Calculos!B41</f>
         <v>0</v>
       </c>
-      <c r="N8" s="113"/>
-      <c r="O8" s="113"/>
-      <c r="P8" s="114">
+      <c r="N8" s="127"/>
+      <c r="O8" s="127"/>
+      <c r="P8" s="128">
         <f ca="1">Calculos!B42</f>
         <v>15</v>
       </c>
-      <c r="Q8" s="114"/>
-      <c r="R8" s="114"/>
+      <c r="Q8" s="128"/>
+      <c r="R8" s="128"/>
     </row>
     <row r="9" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="118"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
-      <c r="L9" s="120"/>
-      <c r="M9" s="113"/>
-      <c r="N9" s="113"/>
-      <c r="O9" s="113"/>
-      <c r="P9" s="114"/>
-      <c r="Q9" s="114"/>
-      <c r="R9" s="114"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="126"/>
+      <c r="K9" s="126"/>
+      <c r="L9" s="126"/>
+      <c r="M9" s="127"/>
+      <c r="N9" s="127"/>
+      <c r="O9" s="127"/>
+      <c r="P9" s="128"/>
+      <c r="Q9" s="128"/>
+      <c r="R9" s="128"/>
     </row>
     <row r="10" spans="2:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="118"/>
-      <c r="C10" s="118"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="118"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
-      <c r="K10" s="120"/>
-      <c r="L10" s="120"/>
-      <c r="M10" s="113"/>
-      <c r="N10" s="113"/>
-      <c r="O10" s="113"/>
-      <c r="P10" s="114"/>
-      <c r="Q10" s="114"/>
-      <c r="R10" s="114"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="126"/>
+      <c r="K10" s="126"/>
+      <c r="L10" s="126"/>
+      <c r="M10" s="127"/>
+      <c r="N10" s="127"/>
+      <c r="O10" s="127"/>
+      <c r="P10" s="128"/>
+      <c r="Q10" s="128"/>
+      <c r="R10" s="128"/>
     </row>
     <row r="12" spans="2:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="111" t="s">
+      <c r="B12" s="123" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="G12" s="111" t="s">
+      <c r="C12" s="123"/>
+      <c r="D12" s="123"/>
+      <c r="E12" s="123"/>
+      <c r="G12" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="111"/>
+      <c r="H12" s="123"/>
     </row>
     <row r="13" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="7" t="s">
@@ -35249,11 +35249,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B8:E10"/>
-    <mergeCell ref="F8:I10"/>
-    <mergeCell ref="J8:L10"/>
     <mergeCell ref="M8:O10"/>
     <mergeCell ref="P8:R10"/>
     <mergeCell ref="B2:R3"/>
@@ -35263,6 +35258,11 @@
     <mergeCell ref="J6:L7"/>
     <mergeCell ref="M6:O7"/>
     <mergeCell ref="P6:R7"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B8:E10"/>
+    <mergeCell ref="F8:I10"/>
+    <mergeCell ref="J8:L10"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -35292,61 +35292,61 @@
   <sheetData>
     <row r="1" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="131" t="s">
+      <c r="B2" s="134" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="132" t="s">
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
       <c r="H2" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="133" t="s">
+      <c r="B4" s="136" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="133"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="133"/>
-      <c r="I4" s="133"/>
-      <c r="J4" s="133"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="133"/>
-      <c r="M4" s="133"/>
-      <c r="N4" s="133"/>
-      <c r="O4" s="133"/>
-      <c r="P4" s="133"/>
-      <c r="Q4" s="133"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="136"/>
+      <c r="M4" s="136"/>
+      <c r="N4" s="136"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
     </row>
     <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="134" t="str">
+      <c r="B5" s="137" t="str">
         <f>UPPER("Planta Cuyotenango  ·  "&amp;Calculos!$B$2&amp;" 2026  ·  Acumulado Año")</f>
         <v>PLANTA CUYOTENANGO  ·  AGOSTO 2026  ·  ACUMULADO AÑO</v>
       </c>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="137"/>
+      <c r="K5" s="137"/>
+      <c r="L5" s="137"/>
+      <c r="M5" s="137"/>
+      <c r="N5" s="137"/>
+      <c r="O5" s="137"/>
+      <c r="P5" s="137"/>
+      <c r="Q5" s="137"/>
     </row>
     <row r="6" spans="1:22" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="P6" s="28" t="s">
@@ -35357,7 +35357,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="121" t="str">
+      <c r="A7" s="138" t="str">
         <f>UPPER(Calculos!$B$2)</f>
         <v>AGOSTO</v>
       </c>
@@ -35374,13 +35374,13 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="121"/>
-      <c r="G8" s="122">
+      <c r="A8" s="138"/>
+      <c r="G8" s="139">
         <f ca="1">X31</f>
         <v>0</v>
       </c>
-      <c r="H8" s="122"/>
-      <c r="I8" s="122"/>
+      <c r="H8" s="139"/>
+      <c r="I8" s="139"/>
       <c r="P8" s="31" t="s">
         <v>76</v>
       </c>
@@ -35390,15 +35390,15 @@
       </c>
     </row>
     <row r="9" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="121"/>
-      <c r="F9" s="123">
+      <c r="A9" s="138"/>
+      <c r="F9" s="140">
         <f ca="1">X32</f>
         <v>0</v>
       </c>
-      <c r="G9" s="123"/>
-      <c r="H9" s="123"/>
-      <c r="I9" s="123"/>
-      <c r="J9" s="123"/>
+      <c r="G9" s="140"/>
+      <c r="H9" s="140"/>
+      <c r="I9" s="140"/>
+      <c r="J9" s="140"/>
       <c r="P9" s="31" t="s">
         <v>77</v>
       </c>
@@ -35408,17 +35408,17 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="121"/>
-      <c r="E10" s="124">
+      <c r="A10" s="138"/>
+      <c r="E10" s="141">
         <f ca="1">X33</f>
         <v>0</v>
       </c>
-      <c r="F10" s="124"/>
-      <c r="G10" s="124"/>
-      <c r="H10" s="124"/>
-      <c r="I10" s="124"/>
-      <c r="J10" s="124"/>
-      <c r="K10" s="124"/>
+      <c r="F10" s="141"/>
+      <c r="G10" s="141"/>
+      <c r="H10" s="141"/>
+      <c r="I10" s="141"/>
+      <c r="J10" s="141"/>
+      <c r="K10" s="141"/>
       <c r="P10" s="31" t="s">
         <v>78</v>
       </c>
@@ -35428,19 +35428,19 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="121"/>
-      <c r="D11" s="125">
+      <c r="A11" s="138"/>
+      <c r="D11" s="142">
         <f ca="1">X34</f>
         <v>5</v>
       </c>
-      <c r="E11" s="125"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="125"/>
-      <c r="H11" s="125"/>
-      <c r="I11" s="125"/>
-      <c r="J11" s="125"/>
-      <c r="K11" s="125"/>
-      <c r="L11" s="125"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="142"/>
+      <c r="I11" s="142"/>
+      <c r="J11" s="142"/>
+      <c r="K11" s="142"/>
+      <c r="L11" s="142"/>
       <c r="P11" s="31" t="s">
         <v>79</v>
       </c>
@@ -35450,21 +35450,21 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="121"/>
-      <c r="C12" s="126">
+      <c r="A12" s="138"/>
+      <c r="C12" s="143">
         <f ca="1">X35</f>
         <v>0</v>
       </c>
-      <c r="D12" s="126"/>
-      <c r="E12" s="126"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="126"/>
-      <c r="H12" s="126"/>
-      <c r="I12" s="126"/>
-      <c r="J12" s="126"/>
-      <c r="K12" s="126"/>
-      <c r="L12" s="126"/>
-      <c r="M12" s="126"/>
+      <c r="D12" s="143"/>
+      <c r="E12" s="143"/>
+      <c r="F12" s="143"/>
+      <c r="G12" s="143"/>
+      <c r="H12" s="143"/>
+      <c r="I12" s="143"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="143"/>
+      <c r="L12" s="143"/>
+      <c r="M12" s="143"/>
       <c r="P12" s="31" t="s">
         <v>80</v>
       </c>
@@ -35474,23 +35474,23 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="121"/>
-      <c r="B13" s="127">
+      <c r="A13" s="138"/>
+      <c r="B13" s="144">
         <f ca="1">X36</f>
         <v>52</v>
       </c>
-      <c r="C13" s="127"/>
-      <c r="D13" s="127"/>
-      <c r="E13" s="127"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="127"/>
-      <c r="K13" s="127"/>
-      <c r="L13" s="127"/>
-      <c r="M13" s="127"/>
-      <c r="N13" s="127"/>
+      <c r="C13" s="144"/>
+      <c r="D13" s="144"/>
+      <c r="E13" s="144"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="144"/>
+      <c r="H13" s="144"/>
+      <c r="I13" s="144"/>
+      <c r="J13" s="144"/>
+      <c r="K13" s="144"/>
+      <c r="L13" s="144"/>
+      <c r="M13" s="144"/>
+      <c r="N13" s="144"/>
       <c r="P13" s="31" t="s">
         <v>81</v>
       </c>
@@ -35500,23 +35500,23 @@
       </c>
     </row>
     <row r="14" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="121"/>
-      <c r="B14" s="128">
+      <c r="A14" s="138"/>
+      <c r="B14" s="145">
         <f ca="1">X37</f>
         <v>232</v>
       </c>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="128"/>
-      <c r="G14" s="128"/>
-      <c r="H14" s="128"/>
-      <c r="I14" s="128"/>
-      <c r="J14" s="128"/>
-      <c r="K14" s="128"/>
-      <c r="L14" s="128"/>
-      <c r="M14" s="128"/>
-      <c r="N14" s="128"/>
+      <c r="C14" s="145"/>
+      <c r="D14" s="145"/>
+      <c r="E14" s="145"/>
+      <c r="F14" s="145"/>
+      <c r="G14" s="145"/>
+      <c r="H14" s="145"/>
+      <c r="I14" s="145"/>
+      <c r="J14" s="145"/>
+      <c r="K14" s="145"/>
+      <c r="L14" s="145"/>
+      <c r="M14" s="145"/>
+      <c r="N14" s="145"/>
       <c r="P14" s="31" t="s">
         <v>82</v>
       </c>
@@ -35527,12 +35527,12 @@
     </row>
     <row r="15" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="S16" s="129" t="s">
+      <c r="S16" s="132" t="s">
         <v>83</v>
       </c>
-      <c r="T16" s="129"/>
-      <c r="U16" s="129"/>
-      <c r="V16" s="129"/>
+      <c r="T16" s="132"/>
+      <c r="U16" s="132"/>
+      <c r="V16" s="132"/>
     </row>
     <row r="17" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -35603,42 +35603,42 @@
     <row r="25" spans="2:25" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="26" spans="2:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="2:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="130" t="s">
+      <c r="B27" s="133" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="130"/>
-      <c r="D27" s="130"/>
-      <c r="E27" s="130"/>
-      <c r="F27" s="130"/>
-      <c r="G27" s="130"/>
-      <c r="H27" s="130"/>
-      <c r="I27" s="130"/>
-      <c r="J27" s="130"/>
-      <c r="K27" s="130"/>
-      <c r="L27" s="130"/>
-      <c r="M27" s="130"/>
-      <c r="N27" s="130"/>
-      <c r="O27" s="130"/>
-      <c r="P27" s="130"/>
-      <c r="Q27" s="130"/>
+      <c r="C27" s="133"/>
+      <c r="D27" s="133"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="133"/>
+      <c r="I27" s="133"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="133"/>
+      <c r="L27" s="133"/>
+      <c r="M27" s="133"/>
+      <c r="N27" s="133"/>
+      <c r="O27" s="133"/>
+      <c r="P27" s="133"/>
+      <c r="Q27" s="133"/>
     </row>
     <row r="28" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="130"/>
-      <c r="C28" s="130"/>
-      <c r="D28" s="130"/>
-      <c r="E28" s="130"/>
-      <c r="F28" s="130"/>
-      <c r="G28" s="130"/>
-      <c r="H28" s="130"/>
-      <c r="I28" s="130"/>
-      <c r="J28" s="130"/>
-      <c r="K28" s="130"/>
-      <c r="L28" s="130"/>
-      <c r="M28" s="130"/>
-      <c r="N28" s="130"/>
-      <c r="O28" s="130"/>
-      <c r="P28" s="130"/>
-      <c r="Q28" s="130"/>
+      <c r="B28" s="133"/>
+      <c r="C28" s="133"/>
+      <c r="D28" s="133"/>
+      <c r="E28" s="133"/>
+      <c r="F28" s="133"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="133"/>
+      <c r="I28" s="133"/>
+      <c r="J28" s="133"/>
+      <c r="K28" s="133"/>
+      <c r="L28" s="133"/>
+      <c r="M28" s="133"/>
+      <c r="N28" s="133"/>
+      <c r="O28" s="133"/>
+      <c r="P28" s="133"/>
+      <c r="Q28" s="133"/>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.35">
       <c r="W30" s="39" t="s">
@@ -35744,12 +35744,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="S16:V16"/>
-    <mergeCell ref="B27:Q28"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B4:Q4"/>
-    <mergeCell ref="B5:Q5"/>
     <mergeCell ref="A7:A14"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="F9:J9"/>
@@ -35758,6 +35752,12 @@
     <mergeCell ref="C12:M12"/>
     <mergeCell ref="B13:N13"/>
     <mergeCell ref="B14:N14"/>
+    <mergeCell ref="S16:V16"/>
+    <mergeCell ref="B27:Q28"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B4:Q4"/>
+    <mergeCell ref="B5:Q5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="E2" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -35792,26 +35792,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="114" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="111" t="s">
+      <c r="B4" s="123" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="H4" s="111" t="s">
+      <c r="C4" s="123"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123"/>
+      <c r="H4" s="123" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="111"/>
+      <c r="I4" s="123"/>
     </row>
     <row r="5" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="7" t="s">
@@ -36072,13 +36072,13 @@
       </c>
     </row>
     <row r="16" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="111" t="s">
+      <c r="B16" s="123" t="s">
         <v>132</v>
       </c>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="123"/>
+      <c r="F16" s="123"/>
       <c r="H16" s="8">
         <v>11</v>
       </c>
@@ -36161,13 +36161,13 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="111" t="s">
+      <c r="B21" s="123" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="111"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="111"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="123"/>
     </row>
     <row r="22" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="52"/>
@@ -36214,13 +36214,13 @@
       <c r="F25" s="52"/>
     </row>
     <row r="27" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="111" t="s">
+      <c r="B27" s="123" t="s">
         <v>149</v>
       </c>
-      <c r="C27" s="111"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="111"/>
+      <c r="C27" s="123"/>
+      <c r="D27" s="123"/>
+      <c r="E27" s="123"/>
+      <c r="F27" s="123"/>
     </row>
     <row r="28" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="52"/>
@@ -36289,13 +36289,13 @@
       <c r="F33" s="52"/>
     </row>
     <row r="35" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="111" t="s">
+      <c r="B35" s="123" t="s">
         <v>156</v>
       </c>
-      <c r="C35" s="111"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="111"/>
+      <c r="C35" s="123"/>
+      <c r="D35" s="123"/>
+      <c r="E35" s="123"/>
+      <c r="F35" s="123"/>
     </row>
     <row r="36" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="7" t="s">
@@ -36392,62 +36392,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="114"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="135" t="s">
+      <c r="AS1" s="115" t="s">
         <v>161</v>
       </c>
-      <c r="AT1" s="135"/>
-      <c r="AU1" s="135"/>
-      <c r="AV1" s="135"/>
-      <c r="AW1" s="135"/>
-      <c r="AX1" s="135"/>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="135"/>
-      <c r="BB1" s="136" t="s">
+      <c r="AT1" s="115"/>
+      <c r="AU1" s="115"/>
+      <c r="AV1" s="115"/>
+      <c r="AW1" s="115"/>
+      <c r="AX1" s="115"/>
+      <c r="AY1" s="115"/>
+      <c r="AZ1" s="115"/>
+      <c r="BA1" s="115"/>
+      <c r="BB1" s="116" t="s">
         <v>162</v>
       </c>
-      <c r="BC1" s="136"/>
+      <c r="BC1" s="116"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="117" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -36456,20 +36456,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="138" t="s">
+      <c r="AT2" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="138"/>
-      <c r="AV2" s="138"/>
+      <c r="AU2" s="118"/>
+      <c r="AV2" s="118"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="139" t="s">
+      <c r="AX2" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="139"/>
-      <c r="AZ2" s="139"/>
-      <c r="BA2" s="139"/>
+      <c r="AY2" s="119"/>
+      <c r="AZ2" s="119"/>
+      <c r="BA2" s="119"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -36517,66 +36517,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144" t="s">
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="144"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="144"/>
-      <c r="L4" s="144" t="s">
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="144"/>
-      <c r="N4" s="144"/>
-      <c r="O4" s="144" t="s">
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144" t="s">
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="144"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144" t="s">
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="144"/>
-      <c r="W4" s="145" t="s">
+      <c r="V4" s="111"/>
+      <c r="W4" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="145"/>
-      <c r="Y4" s="144" t="s">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="111" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="144"/>
-      <c r="AA4" s="144"/>
-      <c r="AB4" s="144"/>
-      <c r="AC4" s="144"/>
-      <c r="AD4" s="145" t="s">
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="145"/>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="145"/>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="145"/>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="145"/>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="145"/>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="146" t="s">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112"/>
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="146"/>
+      <c r="AQ4" s="113"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Enero'!B6</f>
@@ -36788,10 +36788,10 @@
         <f>'Captura Enero'!AQ7</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="BB5" s="140" t="s">
+      <c r="BB5" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="140"/>
+      <c r="BC5" s="107"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -39358,16 +39358,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="141" t="s">
+      <c r="AS19" s="108" t="s">
         <v>224</v>
       </c>
-      <c r="AT19" s="141"/>
-      <c r="AU19" s="141"/>
-      <c r="AV19" s="141"/>
-      <c r="AW19" s="141"/>
-      <c r="AX19" s="141"/>
-      <c r="AY19" s="141"/>
-      <c r="AZ19" s="141"/>
+      <c r="AT19" s="108"/>
+      <c r="AU19" s="108"/>
+      <c r="AV19" s="108"/>
+      <c r="AW19" s="108"/>
+      <c r="AX19" s="108"/>
+      <c r="AY19" s="108"/>
+      <c r="AZ19" s="108"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93297435897435899</v>
@@ -39539,9 +39539,9 @@
       </c>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="142"/>
-      <c r="B22" s="142"/>
-      <c r="C22" s="142"/>
+      <c r="A22" s="109"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -39568,11 +39568,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="143" t="s">
+      <c r="A23" s="110" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="143"/>
-      <c r="C23" s="143"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -39630,6 +39630,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -39644,12 +39650,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="110" priority="5" operator="greaterThanOrEqual">
@@ -39731,62 +39731,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="114"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="135" t="s">
+      <c r="AS1" s="115" t="s">
         <v>227</v>
       </c>
-      <c r="AT1" s="135"/>
-      <c r="AU1" s="135"/>
-      <c r="AV1" s="135"/>
-      <c r="AW1" s="135"/>
-      <c r="AX1" s="135"/>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="135"/>
-      <c r="BB1" s="136" t="s">
+      <c r="AT1" s="115"/>
+      <c r="AU1" s="115"/>
+      <c r="AV1" s="115"/>
+      <c r="AW1" s="115"/>
+      <c r="AX1" s="115"/>
+      <c r="AY1" s="115"/>
+      <c r="AZ1" s="115"/>
+      <c r="BA1" s="115"/>
+      <c r="BB1" s="116" t="s">
         <v>228</v>
       </c>
-      <c r="BC1" s="136"/>
+      <c r="BC1" s="116"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="117" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -39795,20 +39795,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="138" t="s">
+      <c r="AT2" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="138"/>
-      <c r="AV2" s="138"/>
+      <c r="AU2" s="118"/>
+      <c r="AV2" s="118"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="139" t="s">
+      <c r="AX2" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="139"/>
-      <c r="AZ2" s="139"/>
-      <c r="BA2" s="139"/>
+      <c r="AY2" s="119"/>
+      <c r="AZ2" s="119"/>
+      <c r="BA2" s="119"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -39856,66 +39856,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144" t="s">
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="144"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="144"/>
-      <c r="L4" s="144" t="s">
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="144"/>
-      <c r="N4" s="144"/>
-      <c r="O4" s="144" t="s">
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144" t="s">
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="144"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144" t="s">
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="144"/>
-      <c r="W4" s="145" t="s">
+      <c r="V4" s="111"/>
+      <c r="W4" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="145"/>
-      <c r="Y4" s="144" t="s">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="111" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="144"/>
-      <c r="AA4" s="144"/>
-      <c r="AB4" s="144"/>
-      <c r="AC4" s="144"/>
-      <c r="AD4" s="145" t="s">
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="145"/>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="145"/>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="145"/>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="145"/>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="145"/>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="146" t="s">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112"/>
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="146"/>
+      <c r="AQ4" s="113"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Febrero'!B6</f>
@@ -40127,10 +40127,10 @@
         <f>'Captura Febrero'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="140" t="s">
+      <c r="BB5" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="140"/>
+      <c r="BC5" s="107"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -42697,16 +42697,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="141" t="s">
+      <c r="AS19" s="108" t="s">
         <v>230</v>
       </c>
-      <c r="AT19" s="141"/>
-      <c r="AU19" s="141"/>
-      <c r="AV19" s="141"/>
-      <c r="AW19" s="141"/>
-      <c r="AX19" s="141"/>
-      <c r="AY19" s="141"/>
-      <c r="AZ19" s="141"/>
+      <c r="AT19" s="108"/>
+      <c r="AU19" s="108"/>
+      <c r="AV19" s="108"/>
+      <c r="AW19" s="108"/>
+      <c r="AX19" s="108"/>
+      <c r="AY19" s="108"/>
+      <c r="AZ19" s="108"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.9572597670647206</v>
@@ -42873,9 +42873,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="142"/>
-      <c r="B22" s="142"/>
-      <c r="C22" s="142"/>
+      <c r="A22" s="109"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -42902,11 +42902,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="143" t="s">
+      <c r="A23" s="110" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="143"/>
-      <c r="C23" s="143"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -42964,6 +42964,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -42978,12 +42984,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="101" priority="5" operator="greaterThanOrEqual">
@@ -43065,62 +43065,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="114"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="135" t="s">
+      <c r="AS1" s="115" t="s">
         <v>232</v>
       </c>
-      <c r="AT1" s="135"/>
-      <c r="AU1" s="135"/>
-      <c r="AV1" s="135"/>
-      <c r="AW1" s="135"/>
-      <c r="AX1" s="135"/>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="135"/>
-      <c r="BB1" s="136" t="s">
+      <c r="AT1" s="115"/>
+      <c r="AU1" s="115"/>
+      <c r="AV1" s="115"/>
+      <c r="AW1" s="115"/>
+      <c r="AX1" s="115"/>
+      <c r="AY1" s="115"/>
+      <c r="AZ1" s="115"/>
+      <c r="BA1" s="115"/>
+      <c r="BB1" s="116" t="s">
         <v>233</v>
       </c>
-      <c r="BC1" s="136"/>
+      <c r="BC1" s="116"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="117" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -43129,20 +43129,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="138" t="s">
+      <c r="AT2" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="138"/>
-      <c r="AV2" s="138"/>
+      <c r="AU2" s="118"/>
+      <c r="AV2" s="118"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="139" t="s">
+      <c r="AX2" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="139"/>
-      <c r="AZ2" s="139"/>
-      <c r="BA2" s="139"/>
+      <c r="AY2" s="119"/>
+      <c r="AZ2" s="119"/>
+      <c r="BA2" s="119"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -43190,66 +43190,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144" t="s">
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="144"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="144"/>
-      <c r="L4" s="144" t="s">
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="144"/>
-      <c r="N4" s="144"/>
-      <c r="O4" s="144" t="s">
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144" t="s">
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="144"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144" t="s">
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="144"/>
-      <c r="W4" s="145" t="s">
+      <c r="V4" s="111"/>
+      <c r="W4" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="145"/>
-      <c r="Y4" s="144" t="s">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="111" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="144"/>
-      <c r="AA4" s="144"/>
-      <c r="AB4" s="144"/>
-      <c r="AC4" s="144"/>
-      <c r="AD4" s="145" t="s">
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="145"/>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="145"/>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="145"/>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="145"/>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="145"/>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="146" t="s">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112"/>
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="146"/>
+      <c r="AQ4" s="113"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Marzo'!B6</f>
@@ -43461,10 +43461,10 @@
         <f>'Captura Marzo'!AQ7</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="140" t="s">
+      <c r="BB5" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="140"/>
+      <c r="BC5" s="107"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -46031,16 +46031,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="141" t="s">
+      <c r="AS19" s="108" t="s">
         <v>235</v>
       </c>
-      <c r="AT19" s="141"/>
-      <c r="AU19" s="141"/>
-      <c r="AV19" s="141"/>
-      <c r="AW19" s="141"/>
-      <c r="AX19" s="141"/>
-      <c r="AY19" s="141"/>
-      <c r="AZ19" s="141"/>
+      <c r="AT19" s="108"/>
+      <c r="AU19" s="108"/>
+      <c r="AV19" s="108"/>
+      <c r="AW19" s="108"/>
+      <c r="AX19" s="108"/>
+      <c r="AY19" s="108"/>
+      <c r="AZ19" s="108"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.99283333333333335</v>
@@ -46207,9 +46207,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="142"/>
-      <c r="B22" s="142"/>
-      <c r="C22" s="142"/>
+      <c r="A22" s="109"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -46236,11 +46236,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="143" t="s">
+      <c r="A23" s="110" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="143"/>
-      <c r="C23" s="143"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -46298,6 +46298,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -46312,12 +46318,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="92" priority="5" operator="greaterThanOrEqual">
@@ -46399,62 +46399,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="114"/>
+      <c r="AB1" s="114"/>
       <c r="AR1" s="58"/>
-      <c r="AS1" s="135" t="s">
+      <c r="AS1" s="115" t="s">
         <v>237</v>
       </c>
-      <c r="AT1" s="135"/>
-      <c r="AU1" s="135"/>
-      <c r="AV1" s="135"/>
-      <c r="AW1" s="135"/>
-      <c r="AX1" s="135"/>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="135"/>
-      <c r="BB1" s="136" t="s">
+      <c r="AT1" s="115"/>
+      <c r="AU1" s="115"/>
+      <c r="AV1" s="115"/>
+      <c r="AW1" s="115"/>
+      <c r="AX1" s="115"/>
+      <c r="AY1" s="115"/>
+      <c r="AZ1" s="115"/>
+      <c r="BA1" s="115"/>
+      <c r="BB1" s="116" t="s">
         <v>238</v>
       </c>
-      <c r="BC1" s="136"/>
+      <c r="BC1" s="116"/>
     </row>
     <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="117" t="s">
         <v>239</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
@@ -46463,20 +46463,20 @@
       </c>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
-      <c r="AT2" s="138" t="s">
+      <c r="AT2" s="118" t="s">
         <v>167</v>
       </c>
-      <c r="AU2" s="138"/>
-      <c r="AV2" s="138"/>
+      <c r="AU2" s="118"/>
+      <c r="AV2" s="118"/>
       <c r="AW2" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="AX2" s="139" t="s">
+      <c r="AX2" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="AY2" s="139"/>
-      <c r="AZ2" s="139"/>
-      <c r="BA2" s="139"/>
+      <c r="AY2" s="119"/>
+      <c r="AZ2" s="119"/>
+      <c r="BA2" s="119"/>
       <c r="BB2" s="62" t="s">
         <v>169</v>
       </c>
@@ -46524,66 +46524,66 @@
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
       <c r="C4" s="70"/>
-      <c r="D4" s="144" t="s">
+      <c r="D4" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144" t="s">
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="144"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="144"/>
-      <c r="L4" s="144" t="s">
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="M4" s="144"/>
-      <c r="N4" s="144"/>
-      <c r="O4" s="144" t="s">
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111" t="s">
         <v>184</v>
       </c>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144" t="s">
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111" t="s">
         <v>185</v>
       </c>
-      <c r="S4" s="144"/>
-      <c r="T4" s="144"/>
-      <c r="U4" s="144" t="s">
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111" t="s">
         <v>186</v>
       </c>
-      <c r="V4" s="144"/>
-      <c r="W4" s="145" t="s">
+      <c r="V4" s="111"/>
+      <c r="W4" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="X4" s="145"/>
-      <c r="Y4" s="144" t="s">
+      <c r="X4" s="112"/>
+      <c r="Y4" s="111" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="144"/>
-      <c r="AA4" s="144"/>
-      <c r="AB4" s="144"/>
-      <c r="AC4" s="144"/>
-      <c r="AD4" s="145" t="s">
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="111"/>
+      <c r="AD4" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="145"/>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="145"/>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="145"/>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="145"/>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="145"/>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="146" t="s">
+      <c r="AE4" s="112"/>
+      <c r="AF4" s="112"/>
+      <c r="AG4" s="112"/>
+      <c r="AH4" s="112"/>
+      <c r="AI4" s="112"/>
+      <c r="AJ4" s="112"/>
+      <c r="AK4" s="112"/>
+      <c r="AL4" s="112"/>
+      <c r="AM4" s="112"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="112"/>
+      <c r="AP4" s="113" t="s">
         <v>190</v>
       </c>
-      <c r="AQ4" s="146"/>
+      <c r="AQ4" s="113"/>
       <c r="AR4" s="58"/>
       <c r="AS4" s="71" t="str">
         <f>'Captura Abril'!B6</f>
@@ -46795,10 +46795,10 @@
         <f>'Captura Abril'!AQ7</f>
         <v>0.71000000000000008</v>
       </c>
-      <c r="BB5" s="140" t="s">
+      <c r="BB5" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="BC5" s="140"/>
+      <c r="BC5" s="107"/>
     </row>
     <row r="6" spans="1:55" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
@@ -49365,16 +49365,16 @@
         <v>1</v>
       </c>
       <c r="AR19" s="58"/>
-      <c r="AS19" s="141" t="s">
+      <c r="AS19" s="108" t="s">
         <v>240</v>
       </c>
-      <c r="AT19" s="141"/>
-      <c r="AU19" s="141"/>
-      <c r="AV19" s="141"/>
-      <c r="AW19" s="141"/>
-      <c r="AX19" s="141"/>
-      <c r="AY19" s="141"/>
-      <c r="AZ19" s="141"/>
+      <c r="AT19" s="108"/>
+      <c r="AU19" s="108"/>
+      <c r="AV19" s="108"/>
+      <c r="AW19" s="108"/>
+      <c r="AX19" s="108"/>
+      <c r="AY19" s="108"/>
+      <c r="AZ19" s="108"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
         <v>0.93466666666666676</v>
@@ -49541,9 +49541,9 @@
       <c r="BB20" s="58"/>
     </row>
     <row r="22" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="142"/>
-      <c r="B22" s="142"/>
-      <c r="C22" s="142"/>
+      <c r="A22" s="109"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="70"/>
       <c r="E22" s="70"/>
       <c r="F22" s="70"/>
@@ -49570,11 +49570,11 @@
       <c r="AV22" s="92"/>
     </row>
     <row r="23" spans="1:55" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="143" t="s">
+      <c r="A23" s="110" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="143"/>
-      <c r="C23" s="143"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="93"/>
       <c r="E23" s="93"/>
       <c r="F23" s="93"/>
@@ -49632,6 +49632,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:AB1"/>
+    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -49646,12 +49652,6 @@
     <mergeCell ref="L4:N4"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="AS1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AX2:BA2"/>
   </mergeCells>
   <conditionalFormatting sqref="AQ6:AQ20">
     <cfRule type="cellIs" dxfId="83" priority="5" operator="greaterThanOrEqual">
@@ -49712,26 +49712,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003E33BA48D1B17740BD20DC3C1E7D6897" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c5918174441eb6b55e4531b53824222f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbb49d05-d3df-47ef-b263-f54790ad9dd3" xmlns:ns3="4bae7dba-0f75-4d38-a352-dd7a188b5c30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9432285c6019c8f9bf7f2f5b0ebbd793" ns2:_="" ns3:_="">
     <xsd:import namespace="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
@@ -49978,32 +49958,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66EFD81E-D775-40C0-B455-ADBB6CF11754}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
-    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F89154A-65FC-4B0C-9F99-7590878B1EB9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76AB9A25-5769-416B-8E9A-2215F01CC611}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50020,4 +49995,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F89154A-65FC-4B0C-9F99-7590878B1EB9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66EFD81E-D775-40C0-B455-ADBB6CF11754}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
+    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
+++ b/NUEVO_NIVEL_DE_SEGURIDAD_2026_CBC-CUYOTENANGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mariposacbc.sharepoint.com/sites/CharlascortasSSOsemanalesCuyotenango/Shared Documents/General/04. Registros 2026/09. Nivel De Seguridad/NUEVO NIVEL DE SEGURIDAD - 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="11_425E79763165A80B9DB442E442D9E0A19AA5C458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83EE0A04-74F0-43B1-AA23-14AF25B1D2FB}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="11_425E79763165A80B9DB442E442D9E0A19AA5C458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B8FC795-B1B5-4A4F-AFB9-6AC7355799E1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="950" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="950" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="1" r:id="rId1"/>
@@ -25,8 +25,8 @@
     <sheet name="Captura Mayo" sheetId="10" state="hidden" r:id="rId10"/>
     <sheet name="Captura Junio" sheetId="11" state="hidden" r:id="rId11"/>
     <sheet name="Captura Julio" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet name="Captura Agosto" sheetId="13" r:id="rId13"/>
-    <sheet name="Captura Septiembre" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet name="Captura Agosto" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet name="Captura Septiembre" sheetId="14" r:id="rId14"/>
     <sheet name="Captura Octubre" sheetId="15" state="hidden" r:id="rId15"/>
     <sheet name="Captura Noviembre" sheetId="16" state="hidden" r:id="rId16"/>
     <sheet name="Captura Diciembre" sheetId="17" state="hidden" r:id="rId17"/>
@@ -35,7 +35,7 @@
     <sheet name="ACUMULADO - 2026" sheetId="20" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'ACUMULADO - 2026'!$A$3:$N$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'ACUMULADO - 2026'!$A$3:$N$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Dashboard Ejecutivo'!$A$1:$Y$75</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -1883,7 +1883,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="56" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2252,6 +2252,9 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3270,43 +3273,43 @@
               <c:strCache>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>Alrededores</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Calidad</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Centro de Distribucion</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>ETEI</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>Linea 4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Mantenimiento</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Calidad</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>Centro de Distribucion</c:v>
+                  <c:v>Equipos Auxiliares</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>Jarabes</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Materias Primas</c:v>
+                  <c:v>Linea 1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Equipos Auxiliares</c:v>
+                  <c:v>Linea 2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Linea 1</c:v>
+                  <c:v>Linea 3</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>Linea 4</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Linea 5</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>Linea 3</c:v>
-                </c:pt>
                 <c:pt idx="11">
-                  <c:v>Linea 2</c:v>
+                  <c:v>Mantenimiento</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Alrededores</c:v>
+                  <c:v>Materias Primas</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Almacen de Repuestos</c:v>
@@ -3687,25 +3690,25 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0.96048000000000033</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.95933333333333359</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.95933333333333359</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0000000000000004</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.95753333333333346</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.56000000000000005</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4371,7 +4374,7 @@
                   <c:v>0.88027777777777783</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.85630933333333326</c:v>
+                  <c:v>0.86230933333333326</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -4702,7 +4705,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBFEE834-8879-FEDC-0CA2-3975585942D5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9766DC6A-63FE-797F-7772-A786A5A63F1C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4784,6 +4787,133 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1036734-80E0-87A5-6FEF-22DCFCDD03C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1682750" y="4267200"/>
+          <a:ext cx="7632700" cy="3435350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>509163</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>517630</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{891B2074-E31B-AECC-1F07-85E99A2C7403}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9311240" y="4244731"/>
+          <a:ext cx="750928" cy="3458307"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -5038,7 +5168,7 @@
       </c>
       <c r="C12" s="3" t="str">
         <f>Calculos!$B$2</f>
-        <v>Agosto</v>
+        <v>Septiembre</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5047,7 +5177,7 @@
       </c>
       <c r="C13" s="4">
         <f ca="1">TODAY()</f>
-        <v>46266</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -17798,11 +17928,11 @@
       </c>
       <c r="AX17" s="80">
         <f>'Captura Agosto'!X19</f>
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="AY17" s="80">
         <f>'Captura Agosto'!AC19</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AZ17" s="81">
         <f>-'Captura Agosto'!AN19</f>
@@ -17810,7 +17940,7 @@
       </c>
       <c r="BA17" s="82">
         <f>'Captura Agosto'!AQ19</f>
-        <v>0.88124999999999998</v>
+        <v>0.97124999999999995</v>
       </c>
       <c r="BB17" s="58"/>
       <c r="BC17" s="58"/>
@@ -18077,17 +18207,17 @@
         <v>0.23125000000000001</v>
       </c>
       <c r="W19" s="87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X19" s="86">
         <f>MAX(0,Parametros!$E$12-Parametros!$E$18*W19)</f>
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="Y19" s="87">
         <v>3</v>
       </c>
       <c r="Z19" s="87">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA19" s="89">
         <f>IF(Y19&gt;=Parametros!$E$22,Parametros!$E$24,0)</f>
@@ -18095,11 +18225,11 @@
       </c>
       <c r="AB19" s="89">
         <f>IF(Z19&gt;=Parametros!$E$23,Parametros!$E$25,0)</f>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AC19" s="89">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>AA19+AB19</f>
+        <v>0.04</v>
       </c>
       <c r="AD19" s="87">
         <v>0</v>
@@ -18141,11 +18271,11 @@
       </c>
       <c r="AP19" s="11">
         <f t="shared" si="3"/>
-        <v>0.88124999999999998</v>
+        <v>0.93124999999999991</v>
       </c>
       <c r="AQ19" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP19-IF(S19="NO",Parametros!$E$17,0))+AC19-AN19-IF(AO19="SI",Parametros!$E$33,0)))</f>
-        <v>0.88124999999999998</v>
+        <v>0.97124999999999995</v>
       </c>
       <c r="AR19" s="58"/>
       <c r="AS19" s="108" t="s">
@@ -18160,7 +18290,7 @@
       <c r="AZ19" s="108"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
-        <v>0.85630933333333326</v>
+        <v>0.86230933333333326</v>
       </c>
       <c r="BB19" s="58"/>
       <c r="BC19" s="58"/>
@@ -18399,7 +18529,7 @@
       <c r="AP23" s="93"/>
       <c r="AQ23" s="96">
         <f>AVERAGE(AQ6:AQ20)</f>
-        <v>0.85630933333333326</v>
+        <v>0.86230933333333326</v>
       </c>
       <c r="AR23" s="58"/>
       <c r="AS23" s="58"/>
@@ -18564,7 +18694,7 @@
       </c>
       <c r="BC1" s="116"/>
     </row>
-    <row r="2" spans="1:55" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:55" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>163</v>
       </c>
@@ -18576,9 +18706,15 @@
       <c r="F2" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G2" s="59" t="s">
+      <c r="G2" s="149" t="s">
         <v>166</v>
       </c>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
       <c r="AR2" s="58"/>
       <c r="AS2" s="60"/>
       <c r="AT2" s="118" t="s">
@@ -18709,7 +18845,7 @@
       </c>
       <c r="AT4" s="72">
         <f>'Captura Septiembre'!K6+'Captura Septiembre'!N6+'Captura Septiembre'!Q6</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU4" s="72">
         <f>'Captura Septiembre'!T6</f>
@@ -18737,7 +18873,7 @@
       </c>
       <c r="BA4" s="74">
         <f>'Captura Septiembre'!AQ6</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB4" s="68" t="s">
         <v>191</v>
@@ -18746,7 +18882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:55" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:55" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="76" t="s">
         <v>93</v>
       </c>
@@ -18883,7 +19019,7 @@
       </c>
       <c r="AT5" s="80">
         <f>'Captura Septiembre'!K7+'Captura Septiembre'!N7+'Captura Septiembre'!Q7</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU5" s="80">
         <f>'Captura Septiembre'!T7</f>
@@ -18911,7 +19047,7 @@
       </c>
       <c r="BA5" s="82">
         <f>'Captura Septiembre'!AQ7</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB5" s="107" t="s">
         <v>221</v>
@@ -18944,17 +19080,17 @@
         <v>0</v>
       </c>
       <c r="H6" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I6" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J6" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K6" s="86">
         <f>IF(J6="NO",0,IFERROR(H6/I6,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L6" s="85">
         <v>0</v>
@@ -19058,11 +19194,11 @@
       </c>
       <c r="AP6" s="11">
         <f t="shared" ref="AP6:AP20" si="3">G6+K6+N6+Q6+T6+V6+X6</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ6" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP6-IF(S6="NO",Parametros!$E$17,0))+AC6-AN6-IF(AO6="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR6" s="58"/>
       <c r="AS6" s="71" t="str">
@@ -19071,7 +19207,7 @@
       </c>
       <c r="AT6" s="72">
         <f>'Captura Septiembre'!K8+'Captura Septiembre'!N8+'Captura Septiembre'!Q8</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU6" s="72">
         <f>'Captura Septiembre'!T8</f>
@@ -19099,7 +19235,7 @@
       </c>
       <c r="BA6" s="74">
         <f>'Captura Septiembre'!AQ8</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB6" s="58"/>
       <c r="BC6" s="58"/>
@@ -19130,17 +19266,17 @@
         <v>0</v>
       </c>
       <c r="H7" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I7" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J7" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K7" s="86">
         <f>IF(J7="NO",0,IFERROR(H7/I7,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L7" s="85">
         <v>0</v>
@@ -19244,11 +19380,11 @@
       </c>
       <c r="AP7" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ7" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP7-IF(S7="NO",Parametros!$E$17,0))+AC7-AN7-IF(AO7="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR7" s="58"/>
       <c r="AS7" s="79" t="str">
@@ -19257,7 +19393,7 @@
       </c>
       <c r="AT7" s="80">
         <f>'Captura Septiembre'!K9+'Captura Septiembre'!N9+'Captura Septiembre'!Q9</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU7" s="80">
         <f>'Captura Septiembre'!T9</f>
@@ -19285,7 +19421,7 @@
       </c>
       <c r="BA7" s="82">
         <f>'Captura Septiembre'!AQ9</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB7" s="58"/>
       <c r="BC7" s="58"/>
@@ -19316,17 +19452,17 @@
         <v>0</v>
       </c>
       <c r="H8" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I8" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J8" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K8" s="86">
         <f>IF(J8="NO",0,IFERROR(H8/I8,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L8" s="85">
         <v>0</v>
@@ -19430,11 +19566,11 @@
       </c>
       <c r="AP8" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ8" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP8-IF(S8="NO",Parametros!$E$17,0))+AC8-AN8-IF(AO8="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR8" s="58"/>
       <c r="AS8" s="71" t="str">
@@ -19443,7 +19579,7 @@
       </c>
       <c r="AT8" s="72">
         <f>'Captura Septiembre'!K10+'Captura Septiembre'!N10+'Captura Septiembre'!Q10</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU8" s="72">
         <f>'Captura Septiembre'!T10</f>
@@ -19471,7 +19607,7 @@
       </c>
       <c r="BA8" s="74">
         <f>'Captura Septiembre'!AQ10</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB8" s="58"/>
       <c r="BC8" s="58"/>
@@ -19502,17 +19638,17 @@
         <v>0</v>
       </c>
       <c r="H9" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I9" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J9" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K9" s="86">
         <f>IF(J9="NO",0,IFERROR(H9/I9,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L9" s="85">
         <v>0</v>
@@ -19616,11 +19752,11 @@
       </c>
       <c r="AP9" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ9" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP9-IF(S9="NO",Parametros!$E$17,0))+AC9-AN9-IF(AO9="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR9" s="58"/>
       <c r="AS9" s="79" t="str">
@@ -19629,7 +19765,7 @@
       </c>
       <c r="AT9" s="80">
         <f>'Captura Septiembre'!K11+'Captura Septiembre'!N11+'Captura Septiembre'!Q11</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU9" s="80">
         <f>'Captura Septiembre'!T11</f>
@@ -19657,7 +19793,7 @@
       </c>
       <c r="BA9" s="82">
         <f>'Captura Septiembre'!AQ11</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB9" s="58"/>
       <c r="BC9" s="58"/>
@@ -19688,17 +19824,17 @@
         <v>0</v>
       </c>
       <c r="H10" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I10" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J10" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K10" s="86">
         <f>IF(J10="NO",0,IFERROR(H10/I10,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L10" s="85">
         <v>0</v>
@@ -19802,11 +19938,11 @@
       </c>
       <c r="AP10" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ10" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP10-IF(S10="NO",Parametros!$E$17,0))+AC10-AN10-IF(AO10="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR10" s="58"/>
       <c r="AS10" s="71" t="str">
@@ -19815,7 +19951,7 @@
       </c>
       <c r="AT10" s="72">
         <f>'Captura Septiembre'!K12+'Captura Septiembre'!N12+'Captura Septiembre'!Q12</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU10" s="72">
         <f>'Captura Septiembre'!T12</f>
@@ -19843,7 +19979,7 @@
       </c>
       <c r="BA10" s="74">
         <f>'Captura Septiembre'!AQ12</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB10" s="58"/>
       <c r="BC10" s="58"/>
@@ -19874,17 +20010,17 @@
         <v>0</v>
       </c>
       <c r="H11" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I11" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J11" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K11" s="86">
         <f>IF(J11="NO",0,IFERROR(H11/I11,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L11" s="85">
         <v>0</v>
@@ -19988,11 +20124,11 @@
       </c>
       <c r="AP11" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ11" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP11-IF(S11="NO",Parametros!$E$17,0))+AC11-AN11-IF(AO11="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR11" s="58"/>
       <c r="AS11" s="79" t="str">
@@ -20001,7 +20137,7 @@
       </c>
       <c r="AT11" s="80">
         <f>'Captura Septiembre'!K13+'Captura Septiembre'!N13+'Captura Septiembre'!Q13</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU11" s="80">
         <f>'Captura Septiembre'!T13</f>
@@ -20029,7 +20165,7 @@
       </c>
       <c r="BA11" s="82">
         <f>'Captura Septiembre'!AQ13</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB11" s="58"/>
       <c r="BC11" s="58"/>
@@ -20060,17 +20196,17 @@
         <v>0</v>
       </c>
       <c r="H12" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I12" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J12" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K12" s="86">
         <f>IF(J12="NO",0,IFERROR(H12/I12,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L12" s="85">
         <v>0</v>
@@ -20174,11 +20310,11 @@
       </c>
       <c r="AP12" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ12" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP12-IF(S12="NO",Parametros!$E$17,0))+AC12-AN12-IF(AO12="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR12" s="58"/>
       <c r="AS12" s="71" t="str">
@@ -20187,7 +20323,7 @@
       </c>
       <c r="AT12" s="72">
         <f>'Captura Septiembre'!K14+'Captura Septiembre'!N14+'Captura Septiembre'!Q14</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU12" s="72">
         <f>'Captura Septiembre'!T14</f>
@@ -20215,7 +20351,7 @@
       </c>
       <c r="BA12" s="74">
         <f>'Captura Septiembre'!AQ14</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB12" s="58"/>
       <c r="BC12" s="58"/>
@@ -20246,17 +20382,17 @@
         <v>0</v>
       </c>
       <c r="H13" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I13" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J13" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K13" s="86">
         <f>IF(J13="NO",0,IFERROR(H13/I13,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L13" s="85">
         <v>0</v>
@@ -20360,11 +20496,11 @@
       </c>
       <c r="AP13" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ13" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP13-IF(S13="NO",Parametros!$E$17,0))+AC13-AN13-IF(AO13="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR13" s="58"/>
       <c r="AS13" s="79" t="str">
@@ -20373,7 +20509,7 @@
       </c>
       <c r="AT13" s="80">
         <f>'Captura Septiembre'!K15+'Captura Septiembre'!N15+'Captura Septiembre'!Q15</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU13" s="80">
         <f>'Captura Septiembre'!T15</f>
@@ -20401,7 +20537,7 @@
       </c>
       <c r="BA13" s="82">
         <f>'Captura Septiembre'!AQ15</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB13" s="58"/>
       <c r="BC13" s="58"/>
@@ -20432,17 +20568,17 @@
         <v>0</v>
       </c>
       <c r="H14" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I14" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J14" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K14" s="86">
         <f>IF(J14="NO",0,IFERROR(H14/I14,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L14" s="85">
         <v>0</v>
@@ -20546,11 +20682,11 @@
       </c>
       <c r="AP14" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ14" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP14-IF(S14="NO",Parametros!$E$17,0))+AC14-AN14-IF(AO14="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR14" s="58"/>
       <c r="AS14" s="71" t="str">
@@ -20559,7 +20695,7 @@
       </c>
       <c r="AT14" s="72">
         <f>'Captura Septiembre'!K16+'Captura Septiembre'!N16+'Captura Septiembre'!Q16</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU14" s="72">
         <f>'Captura Septiembre'!T16</f>
@@ -20587,7 +20723,7 @@
       </c>
       <c r="BA14" s="74">
         <f>'Captura Septiembre'!AQ16</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB14" s="58"/>
       <c r="BC14" s="58"/>
@@ -20618,17 +20754,17 @@
         <v>0</v>
       </c>
       <c r="H15" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I15" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J15" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K15" s="86">
         <f>IF(J15="NO",0,IFERROR(H15/I15,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L15" s="85">
         <v>0</v>
@@ -20732,11 +20868,11 @@
       </c>
       <c r="AP15" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ15" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP15-IF(S15="NO",Parametros!$E$17,0))+AC15-AN15-IF(AO15="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR15" s="58"/>
       <c r="AS15" s="79" t="str">
@@ -20745,7 +20881,7 @@
       </c>
       <c r="AT15" s="80">
         <f>'Captura Septiembre'!K17+'Captura Septiembre'!N17+'Captura Septiembre'!Q17</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU15" s="80">
         <f>'Captura Septiembre'!T17</f>
@@ -20773,7 +20909,7 @@
       </c>
       <c r="BA15" s="82">
         <f>'Captura Septiembre'!AQ17</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB15" s="58"/>
       <c r="BC15" s="58"/>
@@ -20804,17 +20940,17 @@
         <v>0</v>
       </c>
       <c r="H16" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I16" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J16" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K16" s="86">
         <f>IF(J16="NO",0,IFERROR(H16/I16,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L16" s="85">
         <v>0</v>
@@ -20918,11 +21054,11 @@
       </c>
       <c r="AP16" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ16" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP16-IF(S16="NO",Parametros!$E$17,0))+AC16-AN16-IF(AO16="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR16" s="58"/>
       <c r="AS16" s="71" t="str">
@@ -20931,7 +21067,7 @@
       </c>
       <c r="AT16" s="72">
         <f>'Captura Septiembre'!K18+'Captura Septiembre'!N18+'Captura Septiembre'!Q18</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU16" s="72">
         <f>'Captura Septiembre'!T18</f>
@@ -20959,7 +21095,7 @@
       </c>
       <c r="BA16" s="74">
         <f>'Captura Septiembre'!AQ18</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB16" s="58"/>
       <c r="BC16" s="58"/>
@@ -20990,17 +21126,17 @@
         <v>0</v>
       </c>
       <c r="H17" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I17" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J17" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K17" s="86">
         <f>IF(J17="NO",0,IFERROR(H17/I17,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L17" s="85">
         <v>0</v>
@@ -21104,11 +21240,11 @@
       </c>
       <c r="AP17" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ17" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP17-IF(S17="NO",Parametros!$E$17,0))+AC17-AN17-IF(AO17="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR17" s="58"/>
       <c r="AS17" s="79" t="str">
@@ -21117,7 +21253,7 @@
       </c>
       <c r="AT17" s="80">
         <f>'Captura Septiembre'!K19+'Captura Septiembre'!N19+'Captura Septiembre'!Q19</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU17" s="80">
         <f>'Captura Septiembre'!T19</f>
@@ -21145,7 +21281,7 @@
       </c>
       <c r="BA17" s="82">
         <f>'Captura Septiembre'!AQ19</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB17" s="58"/>
       <c r="BC17" s="58"/>
@@ -21176,17 +21312,17 @@
         <v>0</v>
       </c>
       <c r="H18" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I18" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J18" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K18" s="86">
         <f>IF(J18="NO",0,IFERROR(H18/I18,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L18" s="85">
         <v>0</v>
@@ -21290,11 +21426,11 @@
       </c>
       <c r="AP18" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ18" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP18-IF(S18="NO",Parametros!$E$17,0))+AC18-AN18-IF(AO18="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR18" s="58"/>
       <c r="AS18" s="71" t="str">
@@ -21303,7 +21439,7 @@
       </c>
       <c r="AT18" s="72">
         <f>'Captura Septiembre'!K20+'Captura Septiembre'!N20+'Captura Septiembre'!Q20</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AU18" s="72">
         <f>'Captura Septiembre'!T20</f>
@@ -21331,7 +21467,7 @@
       </c>
       <c r="BA18" s="74">
         <f>'Captura Septiembre'!AQ20</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB18" s="58"/>
       <c r="BC18" s="58"/>
@@ -21362,17 +21498,17 @@
         <v>0</v>
       </c>
       <c r="H19" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I19" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J19" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K19" s="86">
         <f>IF(J19="NO",0,IFERROR(H19/I19,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L19" s="85">
         <v>0</v>
@@ -21476,11 +21612,11 @@
       </c>
       <c r="AP19" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ19" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP19-IF(S19="NO",Parametros!$E$17,0))+AC19-AN19-IF(AO19="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR19" s="58"/>
       <c r="AS19" s="108" t="s">
@@ -21495,7 +21631,7 @@
       <c r="AZ19" s="108"/>
       <c r="BA19" s="91">
         <f>AVERAGE(BA4:BA18)</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BB19" s="58"/>
       <c r="BC19" s="58"/>
@@ -21526,17 +21662,17 @@
         <v>0</v>
       </c>
       <c r="H20" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I20" s="87">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J20" s="88" t="s">
         <v>222</v>
       </c>
       <c r="K20" s="86">
         <f>IF(J20="NO",0,IFERROR(H20/I20,0)*Parametros!$E$7)</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L20" s="85">
         <v>0</v>
@@ -21640,11 +21776,11 @@
       </c>
       <c r="AP20" s="11">
         <f t="shared" si="3"/>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ20" s="90">
         <f>MAX(0,MIN(1,MAX(0,AP20-IF(S20="NO",Parametros!$E$17,0))+AC20-AN20-IF(AO20="SI",Parametros!$E$33,0)))</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR20" s="58"/>
       <c r="AS20" s="58"/>
@@ -21734,7 +21870,7 @@
       <c r="AP23" s="93"/>
       <c r="AQ23" s="94">
         <f>AVERAGE(AQ6:AQ20)</f>
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR23" s="58"/>
       <c r="AS23" s="58"/>
@@ -21749,13 +21885,14 @@
       <c r="BB23" s="58"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="AS1:BA1"/>
     <mergeCell ref="BB1:BC1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="AT2:AV2"/>
     <mergeCell ref="AX2:BA2"/>
+    <mergeCell ref="G2:M2"/>
     <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AS19:AZ19"/>
     <mergeCell ref="A22:C22"/>
@@ -31969,7 +32106,7 @@
       </c>
       <c r="B13" s="97">
         <f>IF(AVERAGE('Captura Agosto'!D6:D20)=0,"",'Captura Agosto'!AQ23)</f>
-        <v>0.85630933333333326</v>
+        <v>0.86230933333333326</v>
       </c>
       <c r="C13" s="12" t="str">
         <f>IF(B13="","",IF(B13&gt;=Parametros!$C$37,"Verde",IF(B13&gt;=Parametros!$C$38,"Amarillo","Rojo")))</f>
@@ -32960,7 +33097,7 @@
       </c>
       <c r="I18" s="10">
         <f>IFERROR(IF('Captura Agosto'!D19=0,"",'Captura Agosto'!AQ19),"")</f>
-        <v>0.88124999999999998</v>
+        <v>0.97124999999999995</v>
       </c>
       <c r="J18" s="10" t="str">
         <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
@@ -32980,7 +33117,7 @@
       </c>
       <c r="N18" s="102">
         <f t="shared" si="0"/>
-        <v>0.8967187499999999</v>
+        <v>0.90796874999999999</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -33017,7 +33154,7 @@
       </c>
       <c r="I19" s="104">
         <f t="shared" si="1"/>
-        <v>0.85630933333333337</v>
+        <v>0.86230933333333337</v>
       </c>
       <c r="J19" s="104" t="str">
         <f t="shared" si="1"/>
@@ -33096,7 +33233,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>26</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33131,11 +33268,11 @@
       </c>
       <c r="C5" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"G6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"G20"))</f>
-        <v>0.19209600000000007</v>
+        <v>0</v>
       </c>
       <c r="D5" s="11">
         <f t="shared" ref="D5:D11" ca="1" si="0">IFERROR(C5/B5,0)</f>
-        <v>0.96048000000000033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33165,11 +33302,11 @@
       </c>
       <c r="C7" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N20"))</f>
-        <v>7.6746666666666685E-2</v>
+        <v>0</v>
       </c>
       <c r="D7" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0.95933333333333359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33182,11 +33319,11 @@
       </c>
       <c r="C8" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"N20"))</f>
-        <v>7.6746666666666685E-2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0.95933333333333359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33199,11 +33336,11 @@
       </c>
       <c r="C9" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"T6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"T20"))</f>
-        <v>6.0000000000000026E-2</v>
+        <v>0</v>
       </c>
       <c r="D9" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>1.0000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33216,11 +33353,11 @@
       </c>
       <c r="C10" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"V6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"V20"))</f>
-        <v>0.23938333333333336</v>
+        <v>0</v>
       </c>
       <c r="D10" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0.95753333333333346</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33233,11 +33370,11 @@
       </c>
       <c r="C11" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X20"))</f>
-        <v>0.14000000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="D11" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>0.56000000000000005</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33252,7 +33389,7 @@
       </c>
       <c r="B14" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X20"))</f>
-        <v>0.14000000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33261,7 +33398,7 @@
       </c>
       <c r="B15" s="12">
         <f ca="1">COUNTIF(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"X20"),"&gt;=0.04")</f>
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33270,7 +33407,7 @@
       </c>
       <c r="B16" s="10">
         <f ca="1">AVERAGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AN6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AN20"))</f>
-        <v>3.3333333333333333E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33331,7 +33468,7 @@
       </c>
       <c r="B23" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,1),$E$23:$E$37,0))</f>
-        <v>ETEI</v>
+        <v>Alrededores</v>
       </c>
       <c r="C23" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),1)</f>
@@ -33352,7 +33489,7 @@
       </c>
       <c r="B24" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,2),$E$23:$E$37,0))</f>
-        <v>Linea 4</v>
+        <v>Calidad</v>
       </c>
       <c r="C24" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),2)</f>
@@ -33364,7 +33501,7 @@
       </c>
       <c r="E24" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ7")*100000-7</f>
-        <v>64442.999999999993</v>
+        <v>32993</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -33373,7 +33510,7 @@
       </c>
       <c r="B25" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,3),$E$23:$E$37,0))</f>
-        <v>Mantenimiento</v>
+        <v>Centro de Distribucion</v>
       </c>
       <c r="C25" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),3)</f>
@@ -33385,7 +33522,7 @@
       </c>
       <c r="E25" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ8")*100000-8</f>
-        <v>97517</v>
+        <v>32992</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33394,7 +33531,7 @@
       </c>
       <c r="B26" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,4),$E$23:$E$37,0))</f>
-        <v>Calidad</v>
+        <v>ETEI</v>
       </c>
       <c r="C26" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),4)</f>
@@ -33406,7 +33543,7 @@
       </c>
       <c r="E26" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ9")*100000-9</f>
-        <v>97186.000000000015</v>
+        <v>32991</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33415,7 +33552,7 @@
       </c>
       <c r="B27" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,5),$E$23:$E$37,0))</f>
-        <v>Centro de Distribucion</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C27" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),5)</f>
@@ -33427,7 +33564,7 @@
       </c>
       <c r="E27" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ10")*100000-10</f>
-        <v>99990</v>
+        <v>32990</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33448,7 +33585,7 @@
       </c>
       <c r="E28" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ11")*100000-11</f>
-        <v>78989</v>
+        <v>32989</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33457,7 +33594,7 @@
       </c>
       <c r="B29" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,7),$E$23:$E$37,0))</f>
-        <v>Materias Primas</v>
+        <v>Linea 1</v>
       </c>
       <c r="C29" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),7)</f>
@@ -33469,7 +33606,7 @@
       </c>
       <c r="E29" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ12")*100000-12</f>
-        <v>92688</v>
+        <v>32988</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -33478,7 +33615,7 @@
       </c>
       <c r="B30" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,8),$E$23:$E$37,0))</f>
-        <v>Equipos Auxiliares</v>
+        <v>Linea 2</v>
       </c>
       <c r="C30" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),8)</f>
@@ -33490,7 +33627,7 @@
       </c>
       <c r="E30" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ13")*100000-13</f>
-        <v>74755</v>
+        <v>32987</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33499,7 +33636,7 @@
       </c>
       <c r="B31" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,9),$E$23:$E$37,0))</f>
-        <v>Linea 1</v>
+        <v>Linea 3</v>
       </c>
       <c r="C31" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),9)</f>
@@ -33511,7 +33648,7 @@
       </c>
       <c r="E31" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ14")*100000-14</f>
-        <v>64812.000000000007</v>
+        <v>32986</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33520,7 +33657,7 @@
       </c>
       <c r="B32" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,10),$E$23:$E$37,0))</f>
-        <v>Linea 5</v>
+        <v>Linea 4</v>
       </c>
       <c r="C32" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),10)</f>
@@ -33532,7 +33669,7 @@
       </c>
       <c r="E32" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ15")*100000-15</f>
-        <v>69360.000000000015</v>
+        <v>32985</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33541,7 +33678,7 @@
       </c>
       <c r="B33" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,11),$E$23:$E$37,0))</f>
-        <v>Linea 3</v>
+        <v>Linea 5</v>
       </c>
       <c r="C33" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),11)</f>
@@ -33553,7 +33690,7 @@
       </c>
       <c r="E33" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ16")*100000-16</f>
-        <v>99984</v>
+        <v>32984</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33562,7 +33699,7 @@
       </c>
       <c r="B34" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,12),$E$23:$E$37,0))</f>
-        <v>Linea 2</v>
+        <v>Mantenimiento</v>
       </c>
       <c r="C34" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),12)</f>
@@ -33574,7 +33711,7 @@
       </c>
       <c r="E34" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ17")*100000-17</f>
-        <v>70278.000000000015</v>
+        <v>32983</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33583,7 +33720,7 @@
       </c>
       <c r="B35" s="8" t="str">
         <f ca="1">INDEX(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"B20"),MATCH(LARGE($E$23:$E$37,13),$E$23:$E$37,0))</f>
-        <v>Alrededores</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C35" s="11">
         <f ca="1">LARGE(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL6"):INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AL20"),13)</f>
@@ -33595,7 +33732,7 @@
       </c>
       <c r="E35" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ18")*100000-18</f>
-        <v>99492.000000000015</v>
+        <v>32982</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33616,7 +33753,7 @@
       </c>
       <c r="E36" s="15">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ19")*100000-19</f>
-        <v>88106</v>
+        <v>32981</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33679,7 +33816,7 @@
       </c>
       <c r="B44" s="17">
         <f ca="1">INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!"&amp;"AQ23")</f>
-        <v>0.85630933333333326</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -33688,7 +33825,7 @@
       </c>
       <c r="B45" s="18" t="str">
         <f ca="1">IF(B44&gt;=Parametros!$C$37,"Verde",IF(B44&gt;=Parametros!$C$38,"Amarillo","Rojo"))</f>
-        <v>Amarillo</v>
+        <v>Rojo</v>
       </c>
     </row>
   </sheetData>
@@ -33852,10 +33989,7 @@
         <f t="shared" ref="N4:N18" si="0">IFERROR(AVERAGE(B4:M4),"")</f>
         <v>0.99690624999999999</v>
       </c>
-      <c r="O4" s="106">
-        <f>N4*1.005</f>
-        <v>1.00189078125</v>
-      </c>
+      <c r="O4" s="106"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="101" t="s">
@@ -33913,10 +34047,7 @@
         <f t="shared" si="0"/>
         <v>0.98618125000000001</v>
       </c>
-      <c r="O5" s="106">
-        <f t="shared" ref="O5:O18" si="1">N5*1.005</f>
-        <v>0.99111215624999993</v>
-      </c>
+      <c r="O5" s="106"/>
     </row>
     <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="101" t="s">
@@ -33974,10 +34105,7 @@
         <f t="shared" si="0"/>
         <v>0.97178571428571425</v>
       </c>
-      <c r="O6" s="106">
-        <f t="shared" si="1"/>
-        <v>0.9766446428571427</v>
-      </c>
+      <c r="O6" s="106"/>
     </row>
     <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="101" t="s">
@@ -34035,10 +34163,7 @@
         <f t="shared" si="0"/>
         <v>0.96124374999999995</v>
       </c>
-      <c r="O7" s="106">
-        <f t="shared" si="1"/>
-        <v>0.96604996874999982</v>
-      </c>
+      <c r="O7" s="106"/>
     </row>
     <row r="8" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="101" t="s">
@@ -34096,10 +34221,7 @@
         <f t="shared" si="0"/>
         <v>0.95687500000000003</v>
       </c>
-      <c r="O8" s="106">
-        <f t="shared" si="1"/>
-        <v>0.96165937499999998</v>
-      </c>
+      <c r="O8" s="106"/>
     </row>
     <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="101" t="s">
@@ -34157,254 +34279,239 @@
         <f t="shared" si="0"/>
         <v>0.94337500000000007</v>
       </c>
-      <c r="O9" s="106">
-        <f t="shared" si="1"/>
-        <v>0.94809187500000003</v>
-      </c>
+      <c r="O9" s="106"/>
     </row>
     <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="101" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B10" s="10">
-        <f>IFERROR(IF('Captura Enero'!D11=0,"",'Captura Enero'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Enero'!D18=0,"",'Captura Enero'!AQ18),"")</f>
         <v>0.84000000000000008</v>
       </c>
       <c r="C10" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D11=0,"",'Captura Febrero'!AQ11),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Febrero'!D18=0,"",'Captura Febrero'!AQ18),"")</f>
+        <v>0.81058823529411772</v>
       </c>
       <c r="D10" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D11=0,"",'Captura Marzo'!AQ11),"")</f>
-        <v>0.97500000000000009</v>
+        <f>IFERROR(IF('Captura Marzo'!D18=0,"",'Captura Marzo'!AQ18),"")</f>
+        <v>1</v>
       </c>
       <c r="E10" s="10">
-        <f>IFERROR(IF('Captura Abril'!D11=0,"",'Captura Abril'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Abril'!D18=0,"",'Captura Abril'!AQ18),"")</f>
         <v>1</v>
       </c>
       <c r="F10" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D11=0,"",'Captura Mayo'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Mayo'!D18=0,"",'Captura Mayo'!AQ18),"")</f>
         <v>1</v>
       </c>
       <c r="G10" s="10">
-        <f>IFERROR(IF('Captura Junio'!D11=0,"",'Captura Junio'!AQ11),"")</f>
-        <v>0.85</v>
+        <f>IFERROR(IF('Captura Junio'!D18=0,"",'Captura Junio'!AQ18),"")</f>
+        <v>0.91000000000000014</v>
       </c>
       <c r="H10" s="10">
-        <f>IFERROR(IF('Captura Julio'!D11=0,"",'Captura Julio'!AQ11),"")</f>
-        <v>0.94000000000000006</v>
+        <f>IFERROR(IF('Captura Julio'!D18=0,"",'Captura Julio'!AQ18),"")</f>
+        <v>0.97666666666666679</v>
       </c>
       <c r="I10" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
-        <v>0.79</v>
+        <f>IFERROR(IF('Captura Agosto'!D18=0,"",'Captura Agosto'!AQ18),"")</f>
+        <v>0.9951000000000001</v>
       </c>
       <c r="J10" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
         <v/>
       </c>
       <c r="K10" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D11=0,"",'Captura Octubre'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D18=0,"",'Captura Octubre'!AQ18),"")</f>
         <v/>
       </c>
       <c r="L10" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D11=0,"",'Captura Noviembre'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D18=0,"",'Captura Noviembre'!AQ18),"")</f>
         <v/>
       </c>
       <c r="M10" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D11=0,"",'Captura Diciembre'!AQ11),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D18=0,"",'Captura Diciembre'!AQ18),"")</f>
         <v/>
       </c>
       <c r="N10" s="102">
         <f t="shared" si="0"/>
-        <v>0.92437500000000006</v>
-      </c>
-      <c r="O10" s="106">
-        <f t="shared" si="1"/>
-        <v>0.92899687499999994</v>
-      </c>
+        <v>0.94154436274509801</v>
+      </c>
+      <c r="O10" s="106"/>
     </row>
     <row r="11" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="101" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B11" s="10">
-        <f>IFERROR(IF('Captura Enero'!D14=0,"",'Captura Enero'!AQ14),"")</f>
-        <v>0.99</v>
+        <f>IFERROR(IF('Captura Enero'!D11=0,"",'Captura Enero'!AQ11),"")</f>
+        <v>0.84000000000000008</v>
       </c>
       <c r="C11" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D14=0,"",'Captura Febrero'!AQ14),"")</f>
-        <v>0.95</v>
+        <f>IFERROR(IF('Captura Febrero'!D11=0,"",'Captura Febrero'!AQ11),"")</f>
+        <v>1</v>
       </c>
       <c r="D11" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D14=0,"",'Captura Marzo'!AQ14),"")</f>
-        <v>0.99</v>
+        <f>IFERROR(IF('Captura Marzo'!D11=0,"",'Captura Marzo'!AQ11),"")</f>
+        <v>0.97500000000000009</v>
       </c>
       <c r="E11" s="10">
-        <f>IFERROR(IF('Captura Abril'!D14=0,"",'Captura Abril'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Abril'!D11=0,"",'Captura Abril'!AQ11),"")</f>
         <v>1</v>
       </c>
       <c r="F11" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D14=0,"",'Captura Mayo'!AQ14),"")</f>
-        <v>0.9</v>
+        <f>IFERROR(IF('Captura Mayo'!D11=0,"",'Captura Mayo'!AQ11),"")</f>
+        <v>1</v>
       </c>
       <c r="G11" s="10">
-        <f>IFERROR(IF('Captura Junio'!D14=0,"",'Captura Junio'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Junio'!D11=0,"",'Captura Junio'!AQ11),"")</f>
+        <v>0.85</v>
+      </c>
+      <c r="H11" s="10">
+        <f>IFERROR(IF('Captura Julio'!D11=0,"",'Captura Julio'!AQ11),"")</f>
         <v>0.94000000000000006</v>
       </c>
-      <c r="H11" s="10">
-        <f>IFERROR(IF('Captura Julio'!D14=0,"",'Captura Julio'!AQ14),"")</f>
+      <c r="I11" s="10">
+        <f>IFERROR(IF('Captura Agosto'!D11=0,"",'Captura Agosto'!AQ11),"")</f>
         <v>0.79</v>
       </c>
-      <c r="I11" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
-        <v>0.64826000000000006</v>
-      </c>
       <c r="J11" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D11=0,"",'Captura Septiembre'!AQ11),"")</f>
         <v/>
       </c>
       <c r="K11" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D14=0,"",'Captura Octubre'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D11=0,"",'Captura Octubre'!AQ11),"")</f>
         <v/>
       </c>
       <c r="L11" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D14=0,"",'Captura Noviembre'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D11=0,"",'Captura Noviembre'!AQ11),"")</f>
         <v/>
       </c>
       <c r="M11" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D14=0,"",'Captura Diciembre'!AQ14),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D11=0,"",'Captura Diciembre'!AQ11),"")</f>
         <v/>
       </c>
       <c r="N11" s="102">
         <f t="shared" si="0"/>
-        <v>0.90103250000000012</v>
-      </c>
-      <c r="O11" s="106">
-        <f t="shared" si="1"/>
-        <v>0.90553766250000001</v>
-      </c>
+        <v>0.92437500000000006</v>
+      </c>
+      <c r="O11" s="106"/>
     </row>
     <row r="12" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="101" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B12" s="10">
-        <f>IFERROR(IF('Captura Enero'!D18=0,"",'Captura Enero'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Enero'!D19=0,"",'Captura Enero'!AQ19),"")</f>
+        <v>1</v>
+      </c>
+      <c r="C12" s="10">
+        <f>IFERROR(IF('Captura Febrero'!D19=0,"",'Captura Febrero'!AQ19),"")</f>
+        <v>1</v>
+      </c>
+      <c r="D12" s="10">
+        <f>IFERROR(IF('Captura Marzo'!D19=0,"",'Captura Marzo'!AQ19),"")</f>
+        <v>1</v>
+      </c>
+      <c r="E12" s="10">
+        <f>IFERROR(IF('Captura Abril'!D19=0,"",'Captura Abril'!AQ19),"")</f>
+        <v>1</v>
+      </c>
+      <c r="F12" s="10">
+        <f>IFERROR(IF('Captura Mayo'!D19=0,"",'Captura Mayo'!AQ19),"")</f>
         <v>0.84000000000000008</v>
       </c>
-      <c r="C12" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D18=0,"",'Captura Febrero'!AQ18),"")</f>
-        <v>0.81058823529411772</v>
-      </c>
-      <c r="D12" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D18=0,"",'Captura Marzo'!AQ18),"")</f>
-        <v>1</v>
-      </c>
-      <c r="E12" s="10">
-        <f>IFERROR(IF('Captura Abril'!D18=0,"",'Captura Abril'!AQ18),"")</f>
-        <v>1</v>
-      </c>
-      <c r="F12" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D18=0,"",'Captura Mayo'!AQ18),"")</f>
-        <v>1</v>
-      </c>
       <c r="G12" s="10">
-        <f>IFERROR(IF('Captura Junio'!D18=0,"",'Captura Junio'!AQ18),"")</f>
-        <v>0.91000000000000014</v>
+        <f>IFERROR(IF('Captura Junio'!D19=0,"",'Captura Junio'!AQ19),"")</f>
+        <v>0.71500000000000008</v>
       </c>
       <c r="H12" s="10">
-        <f>IFERROR(IF('Captura Julio'!D18=0,"",'Captura Julio'!AQ18),"")</f>
-        <v>0.97666666666666679</v>
+        <f>IFERROR(IF('Captura Julio'!D19=0,"",'Captura Julio'!AQ19),"")</f>
+        <v>0.73750000000000004</v>
       </c>
       <c r="I12" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D18=0,"",'Captura Agosto'!AQ18),"")</f>
-        <v>0.9951000000000001</v>
+        <f>IFERROR(IF('Captura Agosto'!D19=0,"",'Captura Agosto'!AQ19),"")</f>
+        <v>0.97124999999999995</v>
       </c>
       <c r="J12" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D18=0,"",'Captura Septiembre'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
         <v/>
       </c>
       <c r="K12" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D18=0,"",'Captura Octubre'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D19=0,"",'Captura Octubre'!AQ19),"")</f>
         <v/>
       </c>
       <c r="L12" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D18=0,"",'Captura Noviembre'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D19=0,"",'Captura Noviembre'!AQ19),"")</f>
         <v/>
       </c>
       <c r="M12" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D18=0,"",'Captura Diciembre'!AQ18),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D19=0,"",'Captura Diciembre'!AQ19),"")</f>
         <v/>
       </c>
       <c r="N12" s="102">
         <f t="shared" si="0"/>
-        <v>0.94154436274509801</v>
-      </c>
-      <c r="O12" s="106">
-        <f t="shared" si="1"/>
-        <v>0.94625208455882337</v>
-      </c>
+        <v>0.90796874999999999</v>
+      </c>
+      <c r="O12" s="106"/>
     </row>
     <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="101" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="B13" s="10">
-        <f>IFERROR(IF('Captura Enero'!D19=0,"",'Captura Enero'!AQ19),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Enero'!D14=0,"",'Captura Enero'!AQ14),"")</f>
+        <v>0.99</v>
       </c>
       <c r="C13" s="10">
-        <f>IFERROR(IF('Captura Febrero'!D19=0,"",'Captura Febrero'!AQ19),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Febrero'!D14=0,"",'Captura Febrero'!AQ14),"")</f>
+        <v>0.95</v>
       </c>
       <c r="D13" s="10">
-        <f>IFERROR(IF('Captura Marzo'!D19=0,"",'Captura Marzo'!AQ19),"")</f>
-        <v>1</v>
+        <f>IFERROR(IF('Captura Marzo'!D14=0,"",'Captura Marzo'!AQ14),"")</f>
+        <v>0.99</v>
       </c>
       <c r="E13" s="10">
-        <f>IFERROR(IF('Captura Abril'!D19=0,"",'Captura Abril'!AQ19),"")</f>
+        <f>IFERROR(IF('Captura Abril'!D14=0,"",'Captura Abril'!AQ14),"")</f>
         <v>1</v>
       </c>
       <c r="F13" s="10">
-        <f>IFERROR(IF('Captura Mayo'!D19=0,"",'Captura Mayo'!AQ19),"")</f>
-        <v>0.84000000000000008</v>
+        <f>IFERROR(IF('Captura Mayo'!D14=0,"",'Captura Mayo'!AQ14),"")</f>
+        <v>0.9</v>
       </c>
       <c r="G13" s="10">
-        <f>IFERROR(IF('Captura Junio'!D19=0,"",'Captura Junio'!AQ19),"")</f>
-        <v>0.71500000000000008</v>
+        <f>IFERROR(IF('Captura Junio'!D14=0,"",'Captura Junio'!AQ14),"")</f>
+        <v>0.94000000000000006</v>
       </c>
       <c r="H13" s="10">
-        <f>IFERROR(IF('Captura Julio'!D19=0,"",'Captura Julio'!AQ19),"")</f>
-        <v>0.73750000000000004</v>
+        <f>IFERROR(IF('Captura Julio'!D14=0,"",'Captura Julio'!AQ14),"")</f>
+        <v>0.79</v>
       </c>
       <c r="I13" s="10">
-        <f>IFERROR(IF('Captura Agosto'!D19=0,"",'Captura Agosto'!AQ19),"")</f>
-        <v>0.88124999999999998</v>
+        <f>IFERROR(IF('Captura Agosto'!D14=0,"",'Captura Agosto'!AQ14),"")</f>
+        <v>0.64826000000000006</v>
       </c>
       <c r="J13" s="10" t="str">
-        <f>IFERROR(IF('Captura Septiembre'!D19=0,"",'Captura Septiembre'!AQ19),"")</f>
+        <f>IFERROR(IF('Captura Septiembre'!D14=0,"",'Captura Septiembre'!AQ14),"")</f>
         <v/>
       </c>
       <c r="K13" s="10" t="str">
-        <f>IFERROR(IF('Captura Octubre'!D19=0,"",'Captura Octubre'!AQ19),"")</f>
+        <f>IFERROR(IF('Captura Octubre'!D14=0,"",'Captura Octubre'!AQ14),"")</f>
         <v/>
       </c>
       <c r="L13" s="10" t="str">
-        <f>IFERROR(IF('Captura Noviembre'!D19=0,"",'Captura Noviembre'!AQ19),"")</f>
+        <f>IFERROR(IF('Captura Noviembre'!D14=0,"",'Captura Noviembre'!AQ14),"")</f>
         <v/>
       </c>
       <c r="M13" s="10" t="str">
-        <f>IFERROR(IF('Captura Diciembre'!D19=0,"",'Captura Diciembre'!AQ19),"")</f>
+        <f>IFERROR(IF('Captura Diciembre'!D14=0,"",'Captura Diciembre'!AQ14),"")</f>
         <v/>
       </c>
       <c r="N13" s="102">
         <f t="shared" si="0"/>
-        <v>0.8967187499999999</v>
-      </c>
-      <c r="O13" s="106">
-        <f t="shared" si="1"/>
-        <v>0.90120234374999986</v>
-      </c>
+        <v>0.90103250000000012</v>
+      </c>
+      <c r="O13" s="106"/>
     </row>
     <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="101" t="s">
@@ -34462,10 +34569,7 @@
         <f t="shared" si="0"/>
         <v>0.85853804347826101</v>
       </c>
-      <c r="O14" s="106">
-        <f t="shared" si="1"/>
-        <v>0.86283073369565222</v>
-      </c>
+      <c r="O14" s="106"/>
     </row>
     <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="101" t="s">
@@ -34523,10 +34627,7 @@
         <f t="shared" si="0"/>
         <v>0.84808853021978026</v>
       </c>
-      <c r="O15" s="106">
-        <f t="shared" si="1"/>
-        <v>0.85232897287087905</v>
-      </c>
+      <c r="O15" s="106"/>
     </row>
     <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="101" t="s">
@@ -34584,10 +34685,7 @@
         <f t="shared" si="0"/>
         <v>0.83411641081871357</v>
       </c>
-      <c r="O16" s="106">
-        <f t="shared" si="1"/>
-        <v>0.83828699287280706</v>
-      </c>
+      <c r="O16" s="106"/>
     </row>
     <row r="17" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="101" t="s">
@@ -34645,10 +34743,7 @@
         <f t="shared" si="0"/>
         <v>0.82220999999999989</v>
       </c>
-      <c r="O17" s="106">
-        <f t="shared" si="1"/>
-        <v>0.82632104999999978</v>
-      </c>
+      <c r="O17" s="106"/>
     </row>
     <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="101" t="s">
@@ -34706,61 +34801,58 @@
         <f t="shared" si="0"/>
         <v>0.78306249999999999</v>
       </c>
-      <c r="O18" s="106">
-        <f t="shared" si="1"/>
-        <v>0.78697781249999987</v>
-      </c>
+      <c r="O18" s="106"/>
     </row>
     <row r="19" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="103" t="s">
         <v>298</v>
       </c>
       <c r="B19" s="104">
-        <f t="shared" ref="B19:M19" si="2">IFERROR(AVERAGE(B4:B18),"")</f>
+        <f t="shared" ref="B19:M19" si="1">IFERROR(AVERAGE(B4:B18),"")</f>
         <v>0.9329743589743591</v>
       </c>
       <c r="C19" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.9572597670647206</v>
       </c>
       <c r="D19" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.99283333333333335</v>
       </c>
       <c r="E19" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.93466666666666665</v>
       </c>
       <c r="F19" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.8793333333333333</v>
       </c>
       <c r="G19" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.83357372900851157</v>
       </c>
       <c r="H19" s="104">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.88027777777777794</v>
       </c>
       <c r="I19" s="104">
-        <f t="shared" si="2"/>
-        <v>0.85630933333333348</v>
+        <f t="shared" si="1"/>
+        <v>0.86230933333333348</v>
       </c>
       <c r="J19" s="104" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K19" s="104" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L19" s="104" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="M19" s="104" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="N19" s="105">
@@ -34772,16 +34864,12 @@
       <c r="M24" s="98"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N19" xr:uid="{00000000-0009-0000-0000-000013000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:N19">
-      <sortCondition descending="1" ref="C4:C19"/>
-    </sortState>
-  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -34850,7 +34938,7 @@
       </c>
       <c r="C4" s="20" t="str">
         <f>Calculos!$B$2</f>
-        <v>Agosto</v>
+        <v>Septiembre</v>
       </c>
       <c r="F4" s="130" t="s">
         <v>60</v>
@@ -34919,14 +35007,14 @@
     <row r="8" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="124">
         <f ca="1">Calculos!B44</f>
-        <v>0.85630933333333326</v>
+        <v>0.33</v>
       </c>
       <c r="C8" s="124"/>
       <c r="D8" s="124"/>
       <c r="E8" s="124"/>
       <c r="F8" s="125" t="str">
         <f ca="1">Calculos!B45</f>
-        <v>Amarillo</v>
+        <v>Rojo</v>
       </c>
       <c r="G8" s="125"/>
       <c r="H8" s="125"/>
@@ -35017,7 +35105,7 @@
     <row r="14" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="str">
         <f ca="1">Calculos!B23</f>
-        <v>ETEI</v>
+        <v>Alrededores</v>
       </c>
       <c r="C14" s="21">
         <f ca="1">Calculos!C23</f>
@@ -35029,13 +35117,13 @@
       </c>
       <c r="H14" s="22">
         <f ca="1">Calculos!D5</f>
-        <v>0.96048000000000033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="str">
         <f ca="1">Calculos!B24</f>
-        <v>Linea 4</v>
+        <v>Calidad</v>
       </c>
       <c r="C15" s="21">
         <f ca="1">Calculos!C24</f>
@@ -35053,7 +35141,7 @@
     <row r="16" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="str">
         <f ca="1">Calculos!B25</f>
-        <v>Mantenimiento</v>
+        <v>Centro de Distribucion</v>
       </c>
       <c r="C16" s="21">
         <f ca="1">Calculos!C25</f>
@@ -35065,13 +35153,13 @@
       </c>
       <c r="H16" s="22">
         <f ca="1">Calculos!D7</f>
-        <v>0.95933333333333359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="str">
         <f ca="1">Calculos!B26</f>
-        <v>Calidad</v>
+        <v>ETEI</v>
       </c>
       <c r="C17" s="21">
         <f ca="1">Calculos!C26</f>
@@ -35083,13 +35171,13 @@
       </c>
       <c r="H17" s="22">
         <f ca="1">Calculos!D8</f>
-        <v>0.95933333333333359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="3" t="str">
         <f ca="1">Calculos!B27</f>
-        <v>Centro de Distribucion</v>
+        <v>Equipos Auxiliares</v>
       </c>
       <c r="C18" s="21">
         <f ca="1">Calculos!C27</f>
@@ -35101,7 +35189,7 @@
       </c>
       <c r="H18" s="22">
         <f ca="1">Calculos!D9</f>
-        <v>1.0000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -35119,13 +35207,13 @@
       </c>
       <c r="H19" s="22">
         <f ca="1">Calculos!D10</f>
-        <v>0.95753333333333346</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="str">
         <f ca="1">Calculos!B29</f>
-        <v>Materias Primas</v>
+        <v>Linea 1</v>
       </c>
       <c r="C20" s="21">
         <f ca="1">Calculos!C29</f>
@@ -35137,13 +35225,13 @@
       </c>
       <c r="H20" s="22">
         <f ca="1">Calculos!D11</f>
-        <v>0.56000000000000005</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="3" t="str">
         <f ca="1">Calculos!B30</f>
-        <v>Equipos Auxiliares</v>
+        <v>Linea 2</v>
       </c>
       <c r="C21" s="21">
         <f ca="1">Calculos!C30</f>
@@ -35153,7 +35241,7 @@
     <row r="22" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="3" t="str">
         <f ca="1">Calculos!B31</f>
-        <v>Linea 1</v>
+        <v>Linea 3</v>
       </c>
       <c r="C22" s="21">
         <f ca="1">Calculos!C31</f>
@@ -35163,7 +35251,7 @@
     <row r="23" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="str">
         <f ca="1">Calculos!B32</f>
-        <v>Linea 5</v>
+        <v>Linea 4</v>
       </c>
       <c r="C23" s="21">
         <f ca="1">Calculos!C32</f>
@@ -35173,7 +35261,7 @@
     <row r="24" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="str">
         <f ca="1">Calculos!B33</f>
-        <v>Linea 3</v>
+        <v>Linea 5</v>
       </c>
       <c r="C24" s="21">
         <f ca="1">Calculos!C33</f>
@@ -35183,7 +35271,7 @@
     <row r="25" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="str">
         <f ca="1">Calculos!B34</f>
-        <v>Linea 2</v>
+        <v>Mantenimiento</v>
       </c>
       <c r="C25" s="21">
         <f ca="1">Calculos!C34</f>
@@ -35193,7 +35281,7 @@
     <row r="26" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="str">
         <f ca="1">Calculos!B35</f>
-        <v>Alrededores</v>
+        <v>Materias Primas</v>
       </c>
       <c r="C26" s="21">
         <f ca="1">Calculos!C35</f>
@@ -35298,7 +35386,7 @@
       <c r="C2" s="134"/>
       <c r="D2" s="134"/>
       <c r="E2" s="135" t="s">
-        <v>26</v>
+        <v>293</v>
       </c>
       <c r="F2" s="135"/>
       <c r="G2" s="135"/>
@@ -35330,7 +35418,7 @@
     <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="137" t="str">
         <f>UPPER("Planta Cuyotenango  ·  "&amp;Calculos!$B$2&amp;" 2026  ·  Acumulado Año")</f>
-        <v>PLANTA CUYOTENANGO  ·  AGOSTO 2026  ·  ACUMULADO AÑO</v>
+        <v>PLANTA CUYOTENANGO  ·  SEPTIEMBRE 2026  ·  ACUMULADO AÑO</v>
       </c>
       <c r="C5" s="137"/>
       <c r="D5" s="137"/>
@@ -35359,7 +35447,7 @@
     <row r="7" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="138" t="str">
         <f>UPPER(Calculos!$B$2)</f>
-        <v>AGOSTO</v>
+        <v>SEPTIEMBRE</v>
       </c>
       <c r="H7" s="30">
         <f>X30</f>
@@ -35431,7 +35519,7 @@
       <c r="A11" s="138"/>
       <c r="D11" s="142">
         <f ca="1">X34</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E11" s="142"/>
       <c r="F11" s="142"/>
@@ -35477,7 +35565,7 @@
       <c r="A13" s="138"/>
       <c r="B13" s="144">
         <f ca="1">X36</f>
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="C13" s="144"/>
       <c r="D13" s="144"/>
@@ -35495,7 +35583,7 @@
         <v>81</v>
       </c>
       <c r="Q13" s="34">
-        <f t="shared" si="0"/>
+        <f>Y36</f>
         <v>463</v>
       </c>
     </row>
@@ -35503,7 +35591,7 @@
       <c r="A14" s="138"/>
       <c r="B14" s="145">
         <f ca="1">X37</f>
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="C14" s="145"/>
       <c r="D14" s="145"/>
@@ -35538,11 +35626,11 @@
     <row r="18" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S18" s="35">
         <f ca="1">IF(T20="","—",INT(TODAY()-T20))</f>
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="U18" s="35">
         <f ca="1">IF(V20="","—",INT(TODAY()-V20))</f>
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -35571,11 +35659,11 @@
     <row r="22" spans="2:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="S22" s="35">
         <f ca="1">IF(T24="","—",INT(TODAY()-T24))</f>
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="U22" s="35">
         <f ca="1">IF(V24="","—",INT(TODAY()-V24))</f>
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="2:25" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -35696,7 +35784,7 @@
       </c>
       <c r="X34" s="41">
         <f ca="1">IFERROR(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF6")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF7")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF8")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF9")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF10")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF11")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF12")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF13")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF14")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF15")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF16")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF17")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF18")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF19")+INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!AF20"),0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y34" s="41">
         <f>SUM('Captura Enero'!AF6:AF20)+SUM('Captura Febrero'!AF6:AF20)+SUM('Captura Marzo'!AF6:AF20)+SUM('Captura Abril'!AF6:AF20)+SUM('Captura Mayo'!AF6:AF20)+SUM('Captura Junio'!AF6:AF20)+SUM('Captura Julio'!AF6:AF20)+SUM('Captura Agosto'!AF6:AF20)+SUM('Captura Septiembre'!AF6:AF20)+SUM('Captura Octubre'!AF6:AF20)+SUM('Captura Noviembre'!AF6:AF20)+SUM('Captura Diciembre'!AF6:AF20)</f>
@@ -35722,7 +35810,7 @@
       </c>
       <c r="X36" s="42">
         <f ca="1">IFERROR(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!BC3"),0)</f>
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="Y36" s="41">
         <f>'Captura Enero'!BC3+'Captura Febrero'!BC3+'Captura Marzo'!BC3+'Captura Abril'!BC3+'Captura Mayo'!BC3+'Captura Junio'!BC3+'Captura Julio'!BC3+'Captura Agosto'!BC3+'Captura Septiembre'!BC3+'Captura Octubre'!BC3+'Captura Noviembre'!BC3+'Captura Diciembre'!BC3</f>
@@ -35735,7 +35823,7 @@
       </c>
       <c r="X37" s="42">
         <f ca="1">IFERROR(INDIRECT("'Captura "&amp;Calculos!$B$2&amp;"'!BC4"),0)</f>
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="Y37" s="41">
         <f>'Captura Enero'!BC4+'Captura Febrero'!BC4+'Captura Marzo'!BC4+'Captura Abril'!BC4+'Captura Mayo'!BC4+'Captura Junio'!BC4+'Captura Julio'!BC4+'Captura Agosto'!BC4+'Captura Septiembre'!BC4+'Captura Octubre'!BC4+'Captura Noviembre'!BC4+'Captura Diciembre'!BC4</f>
@@ -49712,6 +49800,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003E33BA48D1B17740BD20DC3C1E7D6897" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c5918174441eb6b55e4531b53824222f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fbb49d05-d3df-47ef-b263-f54790ad9dd3" xmlns:ns3="4bae7dba-0f75-4d38-a352-dd7a188b5c30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9432285c6019c8f9bf7f2f5b0ebbd793" ns2:_="" ns3:_="">
     <xsd:import namespace="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
@@ -49958,27 +50066,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F89154A-65FC-4B0C-9F99-7590878B1EB9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fbb49d05-d3df-47ef-b263-f54790ad9dd3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4bae7dba-0f75-4d38-a352-dd7a188b5c30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66EFD81E-D775-40C0-B455-ADBB6CF11754}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
+    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76AB9A25-5769-416B-8E9A-2215F01CC611}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -49995,29 +50108,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F89154A-65FC-4B0C-9F99-7590878B1EB9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66EFD81E-D775-40C0-B455-ADBB6CF11754}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="4bae7dba-0f75-4d38-a352-dd7a188b5c30"/>
-    <ds:schemaRef ds:uri="fbb49d05-d3df-47ef-b263-f54790ad9dd3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>